--- a/research/traditional_assets/database/data/switzerland/switzerland_air_transport.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_air_transport.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="swx_fhzn" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,34 +590,37 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.104</v>
+        <v>-0.0304</v>
+      </c>
+      <c r="E2">
+        <v>-0.206</v>
       </c>
       <c r="G2">
-        <v>0.3385232585338969</v>
+        <v>0.349235807860262</v>
       </c>
       <c r="H2">
-        <v>0.3385232585338969</v>
+        <v>0.349235807860262</v>
       </c>
       <c r="I2">
-        <v>-0.141260706423694</v>
+        <v>0.1800218340611354</v>
       </c>
       <c r="J2">
-        <v>-0.141260706423694</v>
+        <v>0.1454613283753372</v>
       </c>
       <c r="K2">
-        <v>-93.974</v>
+        <v>94.7</v>
       </c>
       <c r="L2">
-        <v>-0.1505612360972703</v>
+        <v>0.1033842794759825</v>
       </c>
       <c r="M2">
-        <v>0.235</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="N2">
-        <v>4.253932624947957e-05</v>
+        <v>0.0001984761744401414</v>
       </c>
       <c r="O2">
-        <v>-0.002500691680677634</v>
+        <v>0.009957761351636746</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,82 +629,82 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>0.235</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>363.084</v>
+        <v>411</v>
       </c>
       <c r="V2">
-        <v>0.06572488822113209</v>
+        <v>0.08650446203064489</v>
       </c>
       <c r="W2">
-        <v>1.279754213856146</v>
+        <v>0.03762266099876842</v>
       </c>
       <c r="X2">
-        <v>0.05885709629109852</v>
+        <v>0.101296826590852</v>
       </c>
       <c r="Y2">
-        <v>1.220897117565047</v>
+        <v>-0.06367416559208358</v>
       </c>
       <c r="Z2">
-        <v>0.1593890611194246</v>
+        <v>0.2203141159775837</v>
       </c>
       <c r="AA2">
-        <v>1.454427635274891</v>
+        <v>0.03204718396993744</v>
       </c>
       <c r="AB2">
-        <v>0.05295482435318331</v>
+        <v>0.08262302454523175</v>
       </c>
       <c r="AC2">
-        <v>1.401472810921708</v>
+        <v>-0.05057584057529432</v>
       </c>
       <c r="AD2">
-        <v>2003.754</v>
+        <v>2178.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2003.754</v>
+        <v>2178.8</v>
       </c>
       <c r="AG2">
-        <v>1640.67</v>
+        <v>1767.8</v>
       </c>
       <c r="AH2">
-        <v>0.2661715763462908</v>
+        <v>0.3144011544011544</v>
       </c>
       <c r="AI2">
-        <v>0.4432483920318754</v>
+        <v>0.4499235947631438</v>
       </c>
       <c r="AJ2">
-        <v>0.2289849085202031</v>
+        <v>0.271176560822212</v>
       </c>
       <c r="AK2">
-        <v>0.3946263260283515</v>
+        <v>0.3989078436682011</v>
       </c>
       <c r="AL2">
-        <v>21.208</v>
+        <v>27.9</v>
       </c>
       <c r="AM2">
-        <v>20.431</v>
+        <v>25.28</v>
       </c>
       <c r="AN2">
-        <v>10.57763958761145</v>
+        <v>4.7624043715847</v>
       </c>
       <c r="AO2">
-        <v>-4.157346284420973</v>
+        <v>5.910394265232975</v>
       </c>
       <c r="AP2">
-        <v>8.660951365390401</v>
+        <v>3.864043715846995</v>
       </c>
       <c r="AQ2">
-        <v>-4.315452009201704</v>
+        <v>6.522943037974684</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +715,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Perfect Holding SA (SWX:PRFN)</t>
+          <t>Flughafen Zürich AG (SWX:FHZN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,32 +723,38 @@
           <t>Air Transport</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.0304</v>
+      </c>
+      <c r="E3">
+        <v>-0.206</v>
+      </c>
       <c r="G3">
-        <v>4.281690140845071</v>
+        <v>0.349235807860262</v>
       </c>
       <c r="H3">
-        <v>4.281690140845071</v>
+        <v>0.349235807860262</v>
       </c>
       <c r="I3">
-        <v>3.302816901408451</v>
+        <v>0.1800218340611354</v>
       </c>
       <c r="J3">
-        <v>3.302816901408451</v>
+        <v>0.1454613283753372</v>
       </c>
       <c r="K3">
-        <v>-0.174</v>
+        <v>94.7</v>
       </c>
       <c r="L3">
-        <v>1.225352112676056</v>
+        <v>0.1033842794759825</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0001984761744401414</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.009957761351636746</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,210 +763,8794 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.184</v>
+        <v>411</v>
       </c>
       <c r="V3">
-        <v>0.01333333333333333</v>
+        <v>0.08650446203064489</v>
       </c>
       <c r="W3">
-        <v>2.597014925373134</v>
+        <v>0.03762266099876842</v>
       </c>
       <c r="X3">
-        <v>0.05333063499103678</v>
+        <v>0.101296826590852</v>
       </c>
       <c r="Y3">
-        <v>2.543684290382097</v>
+        <v>-0.06367416559208358</v>
       </c>
       <c r="Z3">
-        <v>0.8875000000000001</v>
+        <v>0.2203141159775837</v>
       </c>
       <c r="AA3">
-        <v>2.93125</v>
+        <v>0.03204718396993744</v>
       </c>
       <c r="AB3">
-        <v>0.0529299036621316</v>
+        <v>0.08262302454523175</v>
       </c>
       <c r="AC3">
-        <v>2.878320096337869</v>
+        <v>-0.05057584057529432</v>
       </c>
       <c r="AD3">
-        <v>0.254</v>
+        <v>2178.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.254</v>
+        <v>2178.8</v>
       </c>
       <c r="AG3">
+        <v>1767.8</v>
+      </c>
+      <c r="AH3">
+        <v>0.3144011544011544</v>
+      </c>
+      <c r="AI3">
+        <v>0.4499235947631438</v>
+      </c>
+      <c r="AJ3">
+        <v>0.271176560822212</v>
+      </c>
+      <c r="AK3">
+        <v>0.3989078436682011</v>
+      </c>
+      <c r="AL3">
+        <v>27.9</v>
+      </c>
+      <c r="AM3">
+        <v>25.28</v>
+      </c>
+      <c r="AN3">
+        <v>4.7624043715847</v>
+      </c>
+      <c r="AO3">
+        <v>5.910394265232975</v>
+      </c>
+      <c r="AP3">
+        <v>3.864043715846995</v>
+      </c>
+      <c r="AQ3">
+        <v>6.522943037974684</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Flughafen Zürich AG (SWX:FHZN)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SWX:FHZN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.314401154401154</v>
+      </c>
+      <c r="F2">
+        <v>0.04</v>
+      </c>
+      <c r="G2">
+        <v>4751.2</v>
+      </c>
+      <c r="H2">
+        <v>6476.08686008553</v>
+      </c>
+      <c r="I2">
+        <v>6519</v>
+      </c>
+      <c r="J2">
+        <v>6342.28686008553</v>
+      </c>
+      <c r="K2">
+        <v>2178.8</v>
+      </c>
+      <c r="L2">
+        <v>277.2</v>
+      </c>
+      <c r="M2">
+        <v>0.08262302454523179</v>
+      </c>
+      <c r="N2">
+        <v>0.0838904904450519</v>
+      </c>
+      <c r="O2">
+        <v>0.041902</v>
+      </c>
+      <c r="P2">
+        <v>0.038786</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.101296826590852</v>
+      </c>
+      <c r="T2">
+        <v>0.08576984421359569</v>
+      </c>
+      <c r="U2">
+        <v>1.05671774066067</v>
+      </c>
+      <c r="V2">
+        <v>0.794182206746474</v>
+      </c>
+      <c r="W2">
+        <v>11.93603202059862</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>4751.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.0511</v>
+      </c>
+      <c r="AD2">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>457.5</v>
+      </c>
+      <c r="AH2">
+        <v>301</v>
+      </c>
+      <c r="AI2">
+        <v>143.4</v>
+      </c>
+      <c r="AJ2">
+        <v>2178.8</v>
+      </c>
+      <c r="AK2">
+        <v>2178.8</v>
+      </c>
+      <c r="AL2">
+        <v>27.9</v>
+      </c>
+      <c r="AM2">
+        <v>2178.8</v>
+      </c>
+      <c r="AN2">
+        <v>411</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08421806048051154</v>
+      </c>
+      <c r="C2">
+        <v>6709.163389039216</v>
+      </c>
+      <c r="D2">
+        <v>6298.163389039216</v>
+      </c>
+      <c r="E2">
+        <v>-2178.8</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>411</v>
+      </c>
+      <c r="H2">
+        <v>4751.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>457.5</v>
+      </c>
+      <c r="K2">
+        <v>301</v>
+      </c>
+      <c r="L2">
+        <v>156.5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>156.5</v>
+      </c>
+      <c r="O2">
+        <v>28.16999999999999</v>
+      </c>
+      <c r="P2">
+        <v>128.33</v>
+      </c>
+      <c r="Q2">
+        <v>429.33</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08421806048051154</v>
+      </c>
+      <c r="T2">
+        <v>0.7679441161126261</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W2">
+        <v>0.03747400000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08412304797164662</v>
+      </c>
+      <c r="C3">
+        <v>6652.598172936843</v>
+      </c>
+      <c r="D3">
+        <v>6310.898172936843</v>
+      </c>
+      <c r="E3">
+        <v>-2109.5</v>
+      </c>
+      <c r="F3">
+        <v>69.3</v>
+      </c>
+      <c r="G3">
+        <v>411</v>
+      </c>
+      <c r="H3">
+        <v>4751.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>457.5</v>
+      </c>
+      <c r="K3">
+        <v>301</v>
+      </c>
+      <c r="L3">
+        <v>156.5</v>
+      </c>
+      <c r="M3">
+        <v>3.16701</v>
+      </c>
+      <c r="N3">
+        <v>153.33299</v>
+      </c>
+      <c r="O3">
+        <v>27.59993819999999</v>
+      </c>
+      <c r="P3">
+        <v>125.7330518</v>
+      </c>
+      <c r="Q3">
+        <v>426.7330518</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08459425047641073</v>
+      </c>
+      <c r="T3">
+        <v>0.7743048653571953</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W3">
+        <v>0.03747400000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>49.41569492991812</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.0840280354627817</v>
+      </c>
+      <c r="C4">
+        <v>6596.084560227367</v>
+      </c>
+      <c r="D4">
+        <v>6323.684560227367</v>
+      </c>
+      <c r="E4">
+        <v>-2040.2</v>
+      </c>
+      <c r="F4">
+        <v>138.6</v>
+      </c>
+      <c r="G4">
+        <v>411</v>
+      </c>
+      <c r="H4">
+        <v>4751.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>457.5</v>
+      </c>
+      <c r="K4">
+        <v>301</v>
+      </c>
+      <c r="L4">
+        <v>156.5</v>
+      </c>
+      <c r="M4">
+        <v>6.334020000000001</v>
+      </c>
+      <c r="N4">
+        <v>150.16598</v>
+      </c>
+      <c r="O4">
+        <v>27.02987639999999</v>
+      </c>
+      <c r="P4">
+        <v>123.1361036</v>
+      </c>
+      <c r="Q4">
+        <v>424.1361036</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08497811781916501</v>
+      </c>
+      <c r="T4">
+        <v>0.7807954258108374</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W4">
+        <v>0.03747400000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>24.70784746495906</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08393302295391677</v>
+      </c>
+      <c r="C5">
+        <v>6539.62286520545</v>
+      </c>
+      <c r="D5">
+        <v>6336.522865205449</v>
+      </c>
+      <c r="E5">
+        <v>-1970.9</v>
+      </c>
+      <c r="F5">
+        <v>207.9</v>
+      </c>
+      <c r="G5">
+        <v>411</v>
+      </c>
+      <c r="H5">
+        <v>4751.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>457.5</v>
+      </c>
+      <c r="K5">
+        <v>301</v>
+      </c>
+      <c r="L5">
+        <v>156.5</v>
+      </c>
+      <c r="M5">
+        <v>9.501030000000002</v>
+      </c>
+      <c r="N5">
+        <v>146.99897</v>
+      </c>
+      <c r="O5">
+        <v>26.45981459999999</v>
+      </c>
+      <c r="P5">
+        <v>120.5391554</v>
+      </c>
+      <c r="Q5">
+        <v>421.5391554</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08536989995249153</v>
+      </c>
+      <c r="T5">
+        <v>0.7874198122532144</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W5">
+        <v>0.03747400000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>16.4718983099727</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08389049044505185</v>
+      </c>
+      <c r="C6">
+        <v>6476.086860085535</v>
+      </c>
+      <c r="D6">
+        <v>6342.286860085534</v>
+      </c>
+      <c r="E6">
+        <v>-1901.6</v>
+      </c>
+      <c r="F6">
+        <v>277.2</v>
+      </c>
+      <c r="G6">
+        <v>411</v>
+      </c>
+      <c r="H6">
+        <v>4751.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>457.5</v>
+      </c>
+      <c r="K6">
+        <v>301</v>
+      </c>
+      <c r="L6">
+        <v>156.5</v>
+      </c>
+      <c r="M6">
+        <v>13.11156</v>
+      </c>
+      <c r="N6">
+        <v>143.38844</v>
+      </c>
+      <c r="O6">
+        <v>25.80991919999999</v>
+      </c>
+      <c r="P6">
+        <v>117.5785208</v>
+      </c>
+      <c r="Q6">
+        <v>418.5785208</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08576984421359568</v>
+      </c>
+      <c r="T6">
+        <v>0.7941822067464742</v>
+      </c>
+      <c r="U6">
+        <v>0.0473</v>
+      </c>
+      <c r="V6">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W6">
+        <v>0.038786</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>11.93603202059862</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08396439793618693</v>
+      </c>
+      <c r="C7">
+        <v>6396.777645789844</v>
+      </c>
+      <c r="D7">
+        <v>6332.277645789844</v>
+      </c>
+      <c r="E7">
+        <v>-1832.3</v>
+      </c>
+      <c r="F7">
+        <v>346.5</v>
+      </c>
+      <c r="G7">
+        <v>411</v>
+      </c>
+      <c r="H7">
+        <v>4751.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>457.5</v>
+      </c>
+      <c r="K7">
+        <v>301</v>
+      </c>
+      <c r="L7">
+        <v>156.5</v>
+      </c>
+      <c r="M7">
+        <v>17.70615</v>
+      </c>
+      <c r="N7">
+        <v>138.79385</v>
+      </c>
+      <c r="O7">
+        <v>24.98289299999999</v>
+      </c>
+      <c r="P7">
+        <v>113.810957</v>
+      </c>
+      <c r="Q7">
+        <v>414.810957</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08617820835388099</v>
+      </c>
+      <c r="T7">
+        <v>0.8010869674395921</v>
+      </c>
+      <c r="U7">
+        <v>0.0511</v>
+      </c>
+      <c r="V7">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W7">
+        <v>0.041902</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>8.838736823081245</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.084007145427322</v>
+      </c>
+      <c r="C8">
+        <v>6321.702805440398</v>
+      </c>
+      <c r="D8">
+        <v>6326.502805440398</v>
+      </c>
+      <c r="E8">
+        <v>-1763</v>
+      </c>
+      <c r="F8">
+        <v>415.8</v>
+      </c>
+      <c r="G8">
+        <v>411</v>
+      </c>
+      <c r="H8">
+        <v>4751.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>457.5</v>
+      </c>
+      <c r="K8">
+        <v>301</v>
+      </c>
+      <c r="L8">
+        <v>156.5</v>
+      </c>
+      <c r="M8">
+        <v>22.0374</v>
+      </c>
+      <c r="N8">
+        <v>134.4626</v>
+      </c>
+      <c r="O8">
+        <v>24.20326799999999</v>
+      </c>
+      <c r="P8">
+        <v>110.259332</v>
+      </c>
+      <c r="Q8">
+        <v>411.259332</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08659526109289575</v>
+      </c>
+      <c r="T8">
+        <v>0.8081386379346912</v>
+      </c>
+      <c r="U8">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V8">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W8">
+        <v>0.04346000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>7.10156370533729</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH3">
-        <v>0.0180731464351786</v>
-      </c>
-      <c r="AI3">
-        <v>21.16666666666665</v>
-      </c>
-      <c r="AJ3">
-        <v>0.005046863734679163</v>
-      </c>
-      <c r="AK3">
-        <v>-0.4069767441860466</v>
-      </c>
-      <c r="AL3">
-        <v>0.008</v>
-      </c>
-      <c r="AM3">
-        <v>0.008</v>
-      </c>
-      <c r="AN3">
-        <v>-0.5438972162740899</v>
-      </c>
-      <c r="AO3">
-        <v>-58.62499999999999</v>
-      </c>
-      <c r="AP3">
-        <v>-0.1498929336188437</v>
-      </c>
-      <c r="AQ3">
-        <v>-58.62499999999999</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Flughafen Zürich AG (SWX:FHZN)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Air Transport</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>-0.104</v>
-      </c>
-      <c r="G4">
-        <v>0.3394201505686369</v>
-      </c>
-      <c r="H4">
-        <v>0.3394201505686369</v>
-      </c>
-      <c r="I4">
-        <v>-0.1404773346147686</v>
-      </c>
-      <c r="J4">
-        <v>-0.1404773346147686</v>
-      </c>
-      <c r="K4">
-        <v>-93.8</v>
-      </c>
-      <c r="L4">
-        <v>-0.15024827807144</v>
-      </c>
-      <c r="M4">
-        <v>0.235</v>
-      </c>
-      <c r="N4">
-        <v>4.264585790763088e-05</v>
-      </c>
-      <c r="O4">
-        <v>-0.002505330490405117</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0.235</v>
-      </c>
-      <c r="T4">
+      <c r="B9">
+        <v>0.0840867929184571</v>
+      </c>
+      <c r="C9">
+        <v>6241.671121197717</v>
+      </c>
+      <c r="D9">
+        <v>6315.771121197718</v>
+      </c>
+      <c r="E9">
+        <v>-1693.7</v>
+      </c>
+      <c r="F9">
+        <v>485.1</v>
+      </c>
+      <c r="G9">
+        <v>411</v>
+      </c>
+      <c r="H9">
+        <v>4751.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>457.5</v>
+      </c>
+      <c r="K9">
+        <v>301</v>
+      </c>
+      <c r="L9">
+        <v>156.5</v>
+      </c>
+      <c r="M9">
+        <v>26.6805</v>
+      </c>
+      <c r="N9">
+        <v>129.8195</v>
+      </c>
+      <c r="O9">
+        <v>23.36750999999999</v>
+      </c>
+      <c r="P9">
+        <v>106.45199</v>
+      </c>
+      <c r="Q9">
+        <v>407.45199</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08702128270801839</v>
+      </c>
+      <c r="T9">
+        <v>0.815341957257642</v>
+      </c>
+      <c r="U9">
+        <v>0.055</v>
+      </c>
+      <c r="V9">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W9">
+        <v>0.0451</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>5.865707164408463</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08406804040959219</v>
+      </c>
+      <c r="C10">
+        <v>6174.894551585067</v>
+      </c>
+      <c r="D10">
+        <v>6318.294551585067</v>
+      </c>
+      <c r="E10">
+        <v>-1624.4</v>
+      </c>
+      <c r="F10">
+        <v>554.4</v>
+      </c>
+      <c r="G10">
+        <v>411</v>
+      </c>
+      <c r="H10">
+        <v>4751.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>457.5</v>
+      </c>
+      <c r="K10">
+        <v>301</v>
+      </c>
+      <c r="L10">
+        <v>156.5</v>
+      </c>
+      <c r="M10">
+        <v>30.492</v>
+      </c>
+      <c r="N10">
+        <v>126.008</v>
+      </c>
+      <c r="O10">
+        <v>22.68143999999999</v>
+      </c>
+      <c r="P10">
+        <v>103.32656</v>
+      </c>
+      <c r="Q10">
+        <v>404.32656</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.0874565656626002</v>
+      </c>
+      <c r="T10">
+        <v>0.8227018704789179</v>
+      </c>
+      <c r="U10">
+        <v>0.055</v>
+      </c>
+      <c r="V10">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W10">
+        <v>0.0451</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>5.132493768857405</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08404928790072727</v>
+      </c>
+      <c r="C11">
+        <v>6108.119999222883</v>
+      </c>
+      <c r="D11">
+        <v>6320.819999222883</v>
+      </c>
+      <c r="E11">
+        <v>-1555.1</v>
+      </c>
+      <c r="F11">
+        <v>623.6999999999999</v>
+      </c>
+      <c r="G11">
+        <v>411</v>
+      </c>
+      <c r="H11">
+        <v>4751.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>457.5</v>
+      </c>
+      <c r="K11">
+        <v>301</v>
+      </c>
+      <c r="L11">
+        <v>156.5</v>
+      </c>
+      <c r="M11">
+        <v>34.3035</v>
+      </c>
+      <c r="N11">
+        <v>122.1965</v>
+      </c>
+      <c r="O11">
+        <v>21.99536999999999</v>
+      </c>
+      <c r="P11">
+        <v>100.20113</v>
+      </c>
+      <c r="Q11">
+        <v>401.20113</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08790141527552446</v>
+      </c>
+      <c r="T11">
+        <v>0.8302235400347271</v>
+      </c>
+      <c r="U11">
+        <v>0.055</v>
+      </c>
+      <c r="V11">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W11">
+        <v>0.0451</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>4.562216683428804</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08468653539186234</v>
+      </c>
+      <c r="C12">
+        <v>5954.116476386199</v>
+      </c>
+      <c r="D12">
+        <v>6236.116476386199</v>
+      </c>
+      <c r="E12">
+        <v>-1485.8</v>
+      </c>
+      <c r="F12">
+        <v>693</v>
+      </c>
+      <c r="G12">
+        <v>411</v>
+      </c>
+      <c r="H12">
+        <v>4751.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>457.5</v>
+      </c>
+      <c r="K12">
+        <v>301</v>
+      </c>
+      <c r="L12">
+        <v>156.5</v>
+      </c>
+      <c r="M12">
+        <v>43.659</v>
+      </c>
+      <c r="N12">
+        <v>112.841</v>
+      </c>
+      <c r="O12">
+        <v>20.31138</v>
+      </c>
+      <c r="P12">
+        <v>92.52962000000001</v>
+      </c>
+      <c r="Q12">
+        <v>393.52962</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.0883561504354026</v>
+      </c>
+      <c r="T12">
+        <v>0.8379123578028876</v>
+      </c>
+      <c r="U12">
+        <v>0.063</v>
+      </c>
+      <c r="V12">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W12">
+        <v>0.05166</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>3.584598822694061</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08729506288299742</v>
+      </c>
+      <c r="C13">
+        <v>5560.524030357101</v>
+      </c>
+      <c r="D13">
+        <v>5911.824030357101</v>
+      </c>
+      <c r="E13">
+        <v>-1416.5</v>
+      </c>
+      <c r="F13">
+        <v>762.3</v>
+      </c>
+      <c r="G13">
+        <v>411</v>
+      </c>
+      <c r="H13">
+        <v>4751.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>457.5</v>
+      </c>
+      <c r="K13">
+        <v>301</v>
+      </c>
+      <c r="L13">
+        <v>156.5</v>
+      </c>
+      <c r="M13">
+        <v>69.67422000000001</v>
+      </c>
+      <c r="N13">
+        <v>86.82577999999999</v>
+      </c>
+      <c r="O13">
+        <v>15.62864039999999</v>
+      </c>
+      <c r="P13">
+        <v>71.1971396</v>
+      </c>
+      <c r="Q13">
+        <v>372.1971396</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08882110436291844</v>
+      </c>
+      <c r="T13">
+        <v>0.8457739579928046</v>
+      </c>
+      <c r="U13">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V13">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W13">
+        <v>0.07494800000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>2.246167951359915</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.0875747903741325</v>
+      </c>
+      <c r="C14">
+        <v>5458.439518185944</v>
+      </c>
+      <c r="D14">
+        <v>5879.039518185944</v>
+      </c>
+      <c r="E14">
+        <v>-1347.2</v>
+      </c>
+      <c r="F14">
+        <v>831.6</v>
+      </c>
+      <c r="G14">
+        <v>411</v>
+      </c>
+      <c r="H14">
+        <v>4751.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>457.5</v>
+      </c>
+      <c r="K14">
+        <v>301</v>
+      </c>
+      <c r="L14">
+        <v>156.5</v>
+      </c>
+      <c r="M14">
+        <v>76.00824000000001</v>
+      </c>
+      <c r="N14">
+        <v>80.49175999999999</v>
+      </c>
+      <c r="O14">
+        <v>14.48851679999999</v>
+      </c>
+      <c r="P14">
+        <v>66.00324319999999</v>
+      </c>
+      <c r="Q14">
+        <v>367.0032432</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08929662542515057</v>
+      </c>
+      <c r="T14">
+        <v>0.8538142309143107</v>
+      </c>
+      <c r="U14">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V14">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W14">
+        <v>0.07494800000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>2.058987288746588</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09010377786526758</v>
+      </c>
+      <c r="C15">
+        <v>5108.454548339492</v>
+      </c>
+      <c r="D15">
+        <v>5598.354548339492</v>
+      </c>
+      <c r="E15">
+        <v>-1277.9</v>
+      </c>
+      <c r="F15">
+        <v>900.9</v>
+      </c>
+      <c r="G15">
+        <v>411</v>
+      </c>
+      <c r="H15">
+        <v>4751.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>457.5</v>
+      </c>
+      <c r="K15">
+        <v>301</v>
+      </c>
+      <c r="L15">
+        <v>156.5</v>
+      </c>
+      <c r="M15">
+        <v>101.35125</v>
+      </c>
+      <c r="N15">
+        <v>55.14875000000001</v>
+      </c>
+      <c r="O15">
+        <v>9.926774999999997</v>
+      </c>
+      <c r="P15">
+        <v>45.22197500000001</v>
+      </c>
+      <c r="Q15">
+        <v>346.221975</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08978307800605469</v>
+      </c>
+      <c r="T15">
+        <v>0.8620393376960813</v>
+      </c>
+      <c r="U15">
+        <v>0.1125</v>
+      </c>
+      <c r="V15">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W15">
+        <v>0.09225000000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>1.544134877468211</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1013060538660924</v>
+      </c>
+      <c r="C16">
+        <v>4061.881366750167</v>
+      </c>
+      <c r="D16">
+        <v>4621.081366750167</v>
+      </c>
+      <c r="E16">
+        <v>-1208.6</v>
+      </c>
+      <c r="F16">
+        <v>970.2</v>
+      </c>
+      <c r="G16">
+        <v>411</v>
+      </c>
+      <c r="H16">
+        <v>4751.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>457.5</v>
+      </c>
+      <c r="K16">
+        <v>301</v>
+      </c>
+      <c r="L16">
+        <v>156.5</v>
+      </c>
+      <c r="M16">
+        <v>190.74132</v>
+      </c>
+      <c r="N16">
+        <v>-34.24132</v>
+      </c>
+      <c r="O16">
+        <v>-6.163437599999998</v>
+      </c>
+      <c r="P16">
+        <v>-28.0778824</v>
+      </c>
+      <c r="Q16">
+        <v>272.9221176</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09051975457096215</v>
+      </c>
+      <c r="T16">
+        <v>0.8744953172670605</v>
+      </c>
+      <c r="U16">
+        <v>0.1966</v>
+      </c>
+      <c r="V16">
+        <v>0.1476869301313422</v>
+      </c>
+      <c r="W16">
+        <v>0.1675647495361781</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.8204829451741238</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1055396012498675</v>
+      </c>
+      <c r="C17">
+        <v>3706.590659080991</v>
+      </c>
+      <c r="D17">
+        <v>4335.090659080991</v>
+      </c>
+      <c r="E17">
+        <v>-1139.3</v>
+      </c>
+      <c r="F17">
+        <v>1039.5</v>
+      </c>
+      <c r="G17">
+        <v>411</v>
+      </c>
+      <c r="H17">
+        <v>4751.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>457.5</v>
+      </c>
+      <c r="K17">
+        <v>301</v>
+      </c>
+      <c r="L17">
+        <v>156.5</v>
+      </c>
+      <c r="M17">
+        <v>222.2451</v>
+      </c>
+      <c r="N17">
+        <v>-65.74509999999998</v>
+      </c>
+      <c r="O17">
+        <v>-11.83411799999999</v>
+      </c>
+      <c r="P17">
+        <v>-53.91098199999999</v>
+      </c>
+      <c r="Q17">
+        <v>247.089018</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09121710154682658</v>
+      </c>
+      <c r="T17">
+        <v>0.8862862986814654</v>
+      </c>
+      <c r="U17">
+        <v>0.2138</v>
+      </c>
+      <c r="V17">
+        <v>0.1267519508866562</v>
+      </c>
+      <c r="W17">
+        <v>0.1867004329004329</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.7041775049258679</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1072896012498675</v>
+      </c>
+      <c r="C18">
+        <v>3529.154848657587</v>
+      </c>
+      <c r="D18">
+        <v>4226.954848657587</v>
+      </c>
+      <c r="E18">
+        <v>-1070</v>
+      </c>
+      <c r="F18">
+        <v>1108.8</v>
+      </c>
+      <c r="G18">
+        <v>411</v>
+      </c>
+      <c r="H18">
+        <v>4751.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>457.5</v>
+      </c>
+      <c r="K18">
+        <v>301</v>
+      </c>
+      <c r="L18">
+        <v>156.5</v>
+      </c>
+      <c r="M18">
+        <v>237.06144</v>
+      </c>
+      <c r="N18">
+        <v>-80.56143999999998</v>
+      </c>
+      <c r="O18">
+        <v>-14.50105919999999</v>
+      </c>
+      <c r="P18">
+        <v>-66.06038079999999</v>
+      </c>
+      <c r="Q18">
+        <v>234.9396192</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09184111466047928</v>
+      </c>
+      <c r="T18">
+        <v>0.8968373260467208</v>
+      </c>
+      <c r="U18">
+        <v>0.2138</v>
+      </c>
+      <c r="V18">
+        <v>0.1188299539562402</v>
+      </c>
+      <c r="W18">
+        <v>0.1883941558441558</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.6601664108680012</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1090396012498675</v>
+      </c>
+      <c r="C19">
+        <v>3356.982489726553</v>
+      </c>
+      <c r="D19">
+        <v>4124.082489726554</v>
+      </c>
+      <c r="E19">
+        <v>-1000.7</v>
+      </c>
+      <c r="F19">
+        <v>1178.1</v>
+      </c>
+      <c r="G19">
+        <v>411</v>
+      </c>
+      <c r="H19">
+        <v>4751.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>457.5</v>
+      </c>
+      <c r="K19">
+        <v>301</v>
+      </c>
+      <c r="L19">
+        <v>156.5</v>
+      </c>
+      <c r="M19">
+        <v>251.87778</v>
+      </c>
+      <c r="N19">
+        <v>-95.37778000000003</v>
+      </c>
+      <c r="O19">
+        <v>-17.1680004</v>
+      </c>
+      <c r="P19">
+        <v>-78.20977960000003</v>
+      </c>
+      <c r="Q19">
+        <v>222.7902204</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09248016423470193</v>
+      </c>
+      <c r="T19">
+        <v>0.9076425950352356</v>
+      </c>
+      <c r="U19">
+        <v>0.2138</v>
+      </c>
+      <c r="V19">
+        <v>0.1118399566646966</v>
+      </c>
+      <c r="W19">
+        <v>0.1898886172650879</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.621333092581648</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1107896012498675</v>
+      </c>
+      <c r="C20">
+        <v>3189.698419276636</v>
+      </c>
+      <c r="D20">
+        <v>4026.098419276635</v>
+      </c>
+      <c r="E20">
+        <v>-931.4000000000003</v>
+      </c>
+      <c r="F20">
+        <v>1247.4</v>
+      </c>
+      <c r="G20">
+        <v>411</v>
+      </c>
+      <c r="H20">
+        <v>4751.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>457.5</v>
+      </c>
+      <c r="K20">
+        <v>301</v>
+      </c>
+      <c r="L20">
+        <v>156.5</v>
+      </c>
+      <c r="M20">
+        <v>266.6941199999999</v>
+      </c>
+      <c r="N20">
+        <v>-110.1941199999999</v>
+      </c>
+      <c r="O20">
+        <v>-19.83494159999998</v>
+      </c>
+      <c r="P20">
+        <v>-90.35917839999996</v>
+      </c>
+      <c r="Q20">
+        <v>210.6408216</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09313480038390559</v>
+      </c>
+      <c r="T20">
+        <v>0.9187114071698115</v>
+      </c>
+      <c r="U20">
+        <v>0.2138</v>
+      </c>
+      <c r="V20">
+        <v>0.1056266257388802</v>
+      </c>
+      <c r="W20">
+        <v>0.1912170274170274</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.5868145874382233</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1125396012498675</v>
+      </c>
+      <c r="C21">
+        <v>3026.962300842674</v>
+      </c>
+      <c r="D21">
+        <v>3932.662300842674</v>
+      </c>
+      <c r="E21">
+        <v>-862.1000000000001</v>
+      </c>
+      <c r="F21">
+        <v>1316.7</v>
+      </c>
+      <c r="G21">
+        <v>411</v>
+      </c>
+      <c r="H21">
+        <v>4751.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>457.5</v>
+      </c>
+      <c r="K21">
+        <v>301</v>
+      </c>
+      <c r="L21">
+        <v>156.5</v>
+      </c>
+      <c r="M21">
+        <v>281.51046</v>
+      </c>
+      <c r="N21">
+        <v>-125.01046</v>
+      </c>
+      <c r="O21">
+        <v>-22.5018828</v>
+      </c>
+      <c r="P21">
+        <v>-102.5085772</v>
+      </c>
+      <c r="Q21">
+        <v>198.4914228</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09380560038864519</v>
+      </c>
+      <c r="T21">
+        <v>0.9300535233077105</v>
+      </c>
+      <c r="U21">
+        <v>0.2138</v>
+      </c>
+      <c r="V21">
+        <v>0.1000673296473601</v>
+      </c>
+      <c r="W21">
+        <v>0.1924056049213944</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.555929609152001</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1142896012498675</v>
+      </c>
+      <c r="C22">
+        <v>2868.464674960767</v>
+      </c>
+      <c r="D22">
+        <v>3843.464674960768</v>
+      </c>
+      <c r="E22">
+        <v>-792.8000000000002</v>
+      </c>
+      <c r="F22">
+        <v>1386</v>
+      </c>
+      <c r="G22">
+        <v>411</v>
+      </c>
+      <c r="H22">
+        <v>4751.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>457.5</v>
+      </c>
+      <c r="K22">
+        <v>301</v>
+      </c>
+      <c r="L22">
+        <v>156.5</v>
+      </c>
+      <c r="M22">
+        <v>296.3268</v>
+      </c>
+      <c r="N22">
+        <v>-139.8268</v>
+      </c>
+      <c r="O22">
+        <v>-25.16882399999999</v>
+      </c>
+      <c r="P22">
+        <v>-114.657976</v>
+      </c>
+      <c r="Q22">
+        <v>186.342024</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09449317039350325</v>
+      </c>
+      <c r="T22">
+        <v>0.9416791923490569</v>
+      </c>
+      <c r="U22">
+        <v>0.2138</v>
+      </c>
+      <c r="V22">
+        <v>0.09506396316499212</v>
+      </c>
+      <c r="W22">
+        <v>0.1934753246753247</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.5281331286944009</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1160396012498675</v>
+      </c>
+      <c r="C23">
+        <v>2713.923535186247</v>
+      </c>
+      <c r="D23">
+        <v>3758.223535186248</v>
+      </c>
+      <c r="E23">
+        <v>-723.5000000000002</v>
+      </c>
+      <c r="F23">
+        <v>1455.3</v>
+      </c>
+      <c r="G23">
+        <v>411</v>
+      </c>
+      <c r="H23">
+        <v>4751.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>457.5</v>
+      </c>
+      <c r="K23">
+        <v>301</v>
+      </c>
+      <c r="L23">
+        <v>156.5</v>
+      </c>
+      <c r="M23">
+        <v>311.14314</v>
+      </c>
+      <c r="N23">
+        <v>-154.64314</v>
+      </c>
+      <c r="O23">
+        <v>-27.83576519999998</v>
+      </c>
+      <c r="P23">
+        <v>-126.8073748</v>
+      </c>
+      <c r="Q23">
+        <v>174.1926252</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09519814723392733</v>
+      </c>
+      <c r="T23">
+        <v>0.9535991821256271</v>
+      </c>
+      <c r="U23">
+        <v>0.2138</v>
+      </c>
+      <c r="V23">
+        <v>0.09053710777618298</v>
+      </c>
+      <c r="W23">
+        <v>0.1944431663574521</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.5029839320899057</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1233800036960263</v>
+      </c>
+      <c r="C24">
+        <v>2324.76351073101</v>
+      </c>
+      <c r="D24">
+        <v>3438.36351073101</v>
+      </c>
+      <c r="E24">
+        <v>-654.2000000000003</v>
+      </c>
+      <c r="F24">
+        <v>1524.6</v>
+      </c>
+      <c r="G24">
+        <v>411</v>
+      </c>
+      <c r="H24">
+        <v>4751.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>457.5</v>
+      </c>
+      <c r="K24">
+        <v>301</v>
+      </c>
+      <c r="L24">
+        <v>156.5</v>
+      </c>
+      <c r="M24">
+        <v>364.07448</v>
+      </c>
+      <c r="N24">
+        <v>-207.57448</v>
+      </c>
+      <c r="O24">
+        <v>-37.36340639999999</v>
+      </c>
+      <c r="P24">
+        <v>-170.2110736</v>
+      </c>
+      <c r="Q24">
+        <v>130.7889264</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09603710097559154</v>
+      </c>
+      <c r="T24">
+        <v>0.9677844992172311</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.07737427792247342</v>
+      </c>
+      <c r="W24">
+        <v>0.2203230224321134</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.429857099569297</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1253800036960263</v>
+      </c>
+      <c r="C25">
+        <v>2177.537348992225</v>
+      </c>
+      <c r="D25">
+        <v>3360.437348992225</v>
+      </c>
+      <c r="E25">
+        <v>-584.9000000000001</v>
+      </c>
+      <c r="F25">
+        <v>1593.9</v>
+      </c>
+      <c r="G25">
+        <v>411</v>
+      </c>
+      <c r="H25">
+        <v>4751.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>457.5</v>
+      </c>
+      <c r="K25">
+        <v>301</v>
+      </c>
+      <c r="L25">
+        <v>156.5</v>
+      </c>
+      <c r="M25">
+        <v>380.62332</v>
+      </c>
+      <c r="N25">
+        <v>-224.12332</v>
+      </c>
+      <c r="O25">
+        <v>-40.34219759999999</v>
+      </c>
+      <c r="P25">
+        <v>-183.7811224</v>
+      </c>
+      <c r="Q25">
+        <v>117.2188776</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09678043994930052</v>
+      </c>
+      <c r="T25">
+        <v>0.9803531290771952</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.07401017888236587</v>
+      </c>
+      <c r="W25">
+        <v>0.2211263692828911</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.4111676604575883</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1273800036960263</v>
+      </c>
+      <c r="C26">
+        <v>2033.765104449673</v>
+      </c>
+      <c r="D26">
+        <v>3285.965104449673</v>
+      </c>
+      <c r="E26">
+        <v>-515.6000000000001</v>
+      </c>
+      <c r="F26">
+        <v>1663.2</v>
+      </c>
+      <c r="G26">
+        <v>411</v>
+      </c>
+      <c r="H26">
+        <v>4751.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>457.5</v>
+      </c>
+      <c r="K26">
+        <v>301</v>
+      </c>
+      <c r="L26">
+        <v>156.5</v>
+      </c>
+      <c r="M26">
+        <v>397.17216</v>
+      </c>
+      <c r="N26">
+        <v>-240.67216</v>
+      </c>
+      <c r="O26">
+        <v>-43.32098879999999</v>
+      </c>
+      <c r="P26">
+        <v>-197.3511712</v>
+      </c>
+      <c r="Q26">
+        <v>103.6488288</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09754334047494922</v>
+      </c>
+      <c r="T26">
+        <v>0.9932525123545267</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.07092642142893396</v>
+      </c>
+      <c r="W26">
+        <v>0.2218627705627706</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.3940356746051888</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1293800036960263</v>
+      </c>
+      <c r="C27">
+        <v>1893.222124058727</v>
+      </c>
+      <c r="D27">
+        <v>3214.722124058727</v>
+      </c>
+      <c r="E27">
+        <v>-446.3000000000002</v>
+      </c>
+      <c r="F27">
+        <v>1732.5</v>
+      </c>
+      <c r="G27">
+        <v>411</v>
+      </c>
+      <c r="H27">
+        <v>4751.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>457.5</v>
+      </c>
+      <c r="K27">
+        <v>301</v>
+      </c>
+      <c r="L27">
+        <v>156.5</v>
+      </c>
+      <c r="M27">
+        <v>413.721</v>
+      </c>
+      <c r="N27">
+        <v>-257.221</v>
+      </c>
+      <c r="O27">
+        <v>-46.29977999999998</v>
+      </c>
+      <c r="P27">
+        <v>-210.92122</v>
+      </c>
+      <c r="Q27">
+        <v>90.07877999999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09832658501461521</v>
+      </c>
+      <c r="T27">
+        <v>1.00649587918592</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.06808936457177661</v>
+      </c>
+      <c r="W27">
+        <v>0.2225402597402598</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.3782742476209813</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1313800036960263</v>
+      </c>
+      <c r="C28">
+        <v>1755.702824134836</v>
+      </c>
+      <c r="D28">
+        <v>3146.502824134836</v>
+      </c>
+      <c r="E28">
+        <v>-377.0000000000002</v>
+      </c>
+      <c r="F28">
+        <v>1801.8</v>
+      </c>
+      <c r="G28">
+        <v>411</v>
+      </c>
+      <c r="H28">
+        <v>4751.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>457.5</v>
+      </c>
+      <c r="K28">
+        <v>301</v>
+      </c>
+      <c r="L28">
+        <v>156.5</v>
+      </c>
+      <c r="M28">
+        <v>430.26984</v>
+      </c>
+      <c r="N28">
+        <v>-273.76984</v>
+      </c>
+      <c r="O28">
+        <v>-49.27857119999998</v>
+      </c>
+      <c r="P28">
+        <v>-224.4912688</v>
+      </c>
+      <c r="Q28">
+        <v>76.5087312</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09913099832562353</v>
+      </c>
+      <c r="T28">
+        <v>1.020097174850595</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.06547054285747751</v>
+      </c>
+      <c r="W28">
+        <v>0.2231656343656344</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.3637252380970974</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1333800036960263</v>
+      </c>
+      <c r="C29">
+        <v>1621.018709053481</v>
+      </c>
+      <c r="D29">
+        <v>3081.118709053481</v>
+      </c>
+      <c r="E29">
+        <v>-307.7</v>
+      </c>
+      <c r="F29">
+        <v>1871.1</v>
+      </c>
+      <c r="G29">
+        <v>411</v>
+      </c>
+      <c r="H29">
+        <v>4751.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>457.5</v>
+      </c>
+      <c r="K29">
+        <v>301</v>
+      </c>
+      <c r="L29">
+        <v>156.5</v>
+      </c>
+      <c r="M29">
+        <v>446.81868</v>
+      </c>
+      <c r="N29">
+        <v>-290.31868</v>
+      </c>
+      <c r="O29">
+        <v>-52.25736239999998</v>
+      </c>
+      <c r="P29">
+        <v>-238.0613176000001</v>
+      </c>
+      <c r="Q29">
+        <v>62.93868239999995</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09995745035748138</v>
+      </c>
+      <c r="T29">
+        <v>1.034071108752658</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.06304570793683019</v>
+      </c>
+      <c r="W29">
+        <v>0.223744684944685</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.35025393298239</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1353800036960263</v>
+      </c>
+      <c r="C30">
+        <v>1488.996631949102</v>
+      </c>
+      <c r="D30">
+        <v>3018.396631949102</v>
+      </c>
+      <c r="E30">
+        <v>-238.4000000000001</v>
+      </c>
+      <c r="F30">
+        <v>1940.4</v>
+      </c>
+      <c r="G30">
+        <v>411</v>
+      </c>
+      <c r="H30">
+        <v>4751.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>457.5</v>
+      </c>
+      <c r="K30">
+        <v>301</v>
+      </c>
+      <c r="L30">
+        <v>156.5</v>
+      </c>
+      <c r="M30">
+        <v>463.3675200000001</v>
+      </c>
+      <c r="N30">
+        <v>-306.8675200000001</v>
+      </c>
+      <c r="O30">
+        <v>-55.23615359999999</v>
+      </c>
+      <c r="P30">
+        <v>-251.6313664000001</v>
+      </c>
+      <c r="Q30">
+        <v>49.36863359999992</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1008068593902242</v>
+      </c>
+      <c r="T30">
+        <v>1.048433207485334</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.06079407551051482</v>
+      </c>
+      <c r="W30">
+        <v>0.2242823747680891</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.3377448639473046</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1373800036960263</v>
+      </c>
+      <c r="C31">
+        <v>1359.477263616497</v>
+      </c>
+      <c r="D31">
+        <v>2958.177263616496</v>
+      </c>
+      <c r="E31">
+        <v>-169.1000000000004</v>
+      </c>
+      <c r="F31">
+        <v>2009.7</v>
+      </c>
+      <c r="G31">
+        <v>411</v>
+      </c>
+      <c r="H31">
+        <v>4751.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>457.5</v>
+      </c>
+      <c r="K31">
+        <v>301</v>
+      </c>
+      <c r="L31">
+        <v>156.5</v>
+      </c>
+      <c r="M31">
+        <v>479.91636</v>
+      </c>
+      <c r="N31">
+        <v>-323.41636</v>
+      </c>
+      <c r="O31">
+        <v>-58.21494479999998</v>
+      </c>
+      <c r="P31">
+        <v>-265.2014152</v>
+      </c>
+      <c r="Q31">
+        <v>35.79858479999996</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1016801954379738</v>
+      </c>
+      <c r="T31">
+        <v>1.063199872379493</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.05869772807911777</v>
+      </c>
+      <c r="W31">
+        <v>0.2247829825347067</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.3260984893284321</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1393800036960263</v>
+      </c>
+      <c r="C32">
+        <v>1232.313741106849</v>
+      </c>
+      <c r="D32">
+        <v>2900.313741106849</v>
+      </c>
+      <c r="E32">
+        <v>-99.80000000000018</v>
+      </c>
+      <c r="F32">
+        <v>2079</v>
+      </c>
+      <c r="G32">
+        <v>411</v>
+      </c>
+      <c r="H32">
+        <v>4751.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>457.5</v>
+      </c>
+      <c r="K32">
+        <v>301</v>
+      </c>
+      <c r="L32">
+        <v>156.5</v>
+      </c>
+      <c r="M32">
+        <v>496.4652</v>
+      </c>
+      <c r="N32">
+        <v>-339.9652</v>
+      </c>
+      <c r="O32">
+        <v>-61.19373599999999</v>
+      </c>
+      <c r="P32">
+        <v>-278.771464</v>
+      </c>
+      <c r="Q32">
+        <v>22.22853599999996</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1025784839442306</v>
+      </c>
+      <c r="T32">
+        <v>1.078388441984915</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.05674113714314716</v>
+      </c>
+      <c r="W32">
+        <v>0.2252502164502165</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.3152285396841511</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1413800036960263</v>
+      </c>
+      <c r="C33">
+        <v>1107.370471885966</v>
+      </c>
+      <c r="D33">
+        <v>2844.670471885966</v>
+      </c>
+      <c r="E33">
+        <v>-30.5</v>
+      </c>
+      <c r="F33">
+        <v>2148.3</v>
+      </c>
+      <c r="G33">
+        <v>411</v>
+      </c>
+      <c r="H33">
+        <v>4751.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>457.5</v>
+      </c>
+      <c r="K33">
+        <v>301</v>
+      </c>
+      <c r="L33">
+        <v>156.5</v>
+      </c>
+      <c r="M33">
+        <v>513.01404</v>
+      </c>
+      <c r="N33">
+        <v>-356.51404</v>
+      </c>
+      <c r="O33">
+        <v>-64.17252719999998</v>
+      </c>
+      <c r="P33">
+        <v>-292.3415128</v>
+      </c>
+      <c r="Q33">
+        <v>8.658487199999968</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1035028097984948</v>
+      </c>
+      <c r="T33">
+        <v>1.094017259984696</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.05491077788046501</v>
+      </c>
+      <c r="W33">
+        <v>0.2256873062421449</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.3050598771136945</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1433800036960263</v>
+      </c>
+      <c r="C34">
+        <v>984.5220730564806</v>
+      </c>
+      <c r="D34">
+        <v>2791.122073056481</v>
+      </c>
+      <c r="E34">
+        <v>38.79999999999973</v>
+      </c>
+      <c r="F34">
+        <v>2217.6</v>
+      </c>
+      <c r="G34">
+        <v>411</v>
+      </c>
+      <c r="H34">
+        <v>4751.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>457.5</v>
+      </c>
+      <c r="K34">
+        <v>301</v>
+      </c>
+      <c r="L34">
+        <v>156.5</v>
+      </c>
+      <c r="M34">
+        <v>529.56288</v>
+      </c>
+      <c r="N34">
+        <v>-373.06288</v>
+      </c>
+      <c r="O34">
+        <v>-67.15131839999997</v>
+      </c>
+      <c r="P34">
+        <v>-305.9115616</v>
+      </c>
+      <c r="Q34">
+        <v>-4.91156159999997</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1044543217072962</v>
+      </c>
+      <c r="T34">
+        <v>1.110105749102118</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.05319481607170048</v>
+      </c>
+      <c r="W34">
+        <v>0.2260970779220779</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2955267559538917</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1453800036960263</v>
+      </c>
+      <c r="C35">
+        <v>863.6524281756178</v>
+      </c>
+      <c r="D35">
+        <v>2739.552428175618</v>
+      </c>
+      <c r="E35">
+        <v>108.0999999999999</v>
+      </c>
+      <c r="F35">
+        <v>2286.9</v>
+      </c>
+      <c r="G35">
+        <v>411</v>
+      </c>
+      <c r="H35">
+        <v>4751.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>457.5</v>
+      </c>
+      <c r="K35">
+        <v>301</v>
+      </c>
+      <c r="L35">
+        <v>156.5</v>
+      </c>
+      <c r="M35">
+        <v>546.1117200000001</v>
+      </c>
+      <c r="N35">
+        <v>-389.6117200000001</v>
+      </c>
+      <c r="O35">
+        <v>-70.1301096</v>
+      </c>
+      <c r="P35">
+        <v>-319.4816104000001</v>
+      </c>
+      <c r="Q35">
+        <v>-18.48161040000014</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1054342369566588</v>
+      </c>
+      <c r="T35">
+        <v>1.126674491626031</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.0515828519483156</v>
+      </c>
+      <c r="W35">
+        <v>0.2264820149547422</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2865713997128646</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1473800036960263</v>
+      </c>
+      <c r="C36">
+        <v>744.6538467353366</v>
+      </c>
+      <c r="D36">
+        <v>2689.853846735337</v>
+      </c>
+      <c r="E36">
+        <v>177.4000000000001</v>
+      </c>
+      <c r="F36">
+        <v>2356.2</v>
+      </c>
+      <c r="G36">
+        <v>411</v>
+      </c>
+      <c r="H36">
+        <v>4751.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>457.5</v>
+      </c>
+      <c r="K36">
+        <v>301</v>
+      </c>
+      <c r="L36">
+        <v>156.5</v>
+      </c>
+      <c r="M36">
+        <v>562.6605600000001</v>
+      </c>
+      <c r="N36">
+        <v>-406.1605600000001</v>
+      </c>
+      <c r="O36">
+        <v>-73.1089008</v>
+      </c>
+      <c r="P36">
+        <v>-333.0516592000001</v>
+      </c>
+      <c r="Q36">
+        <v>-32.05165920000013</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1064438466075173</v>
+      </c>
+      <c r="T36">
+        <v>1.143745317256728</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.05006570924395338</v>
+      </c>
+      <c r="W36">
+        <v>0.226844308632544</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2781428291330744</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1493800036960263</v>
+      </c>
+      <c r="C37">
+        <v>627.426313500227</v>
+      </c>
+      <c r="D37">
+        <v>2641.926313500227</v>
+      </c>
+      <c r="E37">
+        <v>246.7000000000003</v>
+      </c>
+      <c r="F37">
+        <v>2425.5</v>
+      </c>
+      <c r="G37">
+        <v>411</v>
+      </c>
+      <c r="H37">
+        <v>4751.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>457.5</v>
+      </c>
+      <c r="K37">
+        <v>301</v>
+      </c>
+      <c r="L37">
+        <v>156.5</v>
+      </c>
+      <c r="M37">
+        <v>579.2094000000002</v>
+      </c>
+      <c r="N37">
+        <v>-422.7094000000002</v>
+      </c>
+      <c r="O37">
+        <v>-76.087692</v>
+      </c>
+      <c r="P37">
+        <v>-346.6217080000002</v>
+      </c>
+      <c r="Q37">
+        <v>-45.62170800000018</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1074845211707098</v>
+      </c>
+      <c r="T37">
+        <v>1.161341399060677</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.04863526040841185</v>
+      </c>
+      <c r="W37">
+        <v>0.2271858998144713</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.2701958911578437</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1513800036960263</v>
+      </c>
+      <c r="C38">
+        <v>511.8768166918449</v>
+      </c>
+      <c r="D38">
+        <v>2595.676816691845</v>
+      </c>
+      <c r="E38">
+        <v>315.9999999999995</v>
+      </c>
+      <c r="F38">
+        <v>2494.8</v>
+      </c>
+      <c r="G38">
+        <v>411</v>
+      </c>
+      <c r="H38">
+        <v>4751.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>457.5</v>
+      </c>
+      <c r="K38">
+        <v>301</v>
+      </c>
+      <c r="L38">
+        <v>156.5</v>
+      </c>
+      <c r="M38">
+        <v>595.75824</v>
+      </c>
+      <c r="N38">
+        <v>-439.25824</v>
+      </c>
+      <c r="O38">
+        <v>-79.06648319999998</v>
+      </c>
+      <c r="P38">
+        <v>-360.1917568</v>
+      </c>
+      <c r="Q38">
+        <v>-59.19175680000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1085577168140022</v>
+      </c>
+      <c r="T38">
+        <v>1.179487358421001</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.04728428095262265</v>
+      </c>
+      <c r="W38">
+        <v>0.2275085137085137</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2626904497367926</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1533800036960263</v>
+      </c>
+      <c r="C39">
+        <v>397.9187455237243</v>
+      </c>
+      <c r="D39">
+        <v>2551.018745523724</v>
+      </c>
+      <c r="E39">
+        <v>385.2999999999997</v>
+      </c>
+      <c r="F39">
+        <v>2564.1</v>
+      </c>
+      <c r="G39">
+        <v>411</v>
+      </c>
+      <c r="H39">
+        <v>4751.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>457.5</v>
+      </c>
+      <c r="K39">
+        <v>301</v>
+      </c>
+      <c r="L39">
+        <v>156.5</v>
+      </c>
+      <c r="M39">
+        <v>612.30708</v>
+      </c>
+      <c r="N39">
+        <v>-455.80708</v>
+      </c>
+      <c r="O39">
+        <v>-82.04527439999998</v>
+      </c>
+      <c r="P39">
+        <v>-373.7618056000001</v>
+      </c>
+      <c r="Q39">
+        <v>-72.76180560000006</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1096649821602562</v>
+      </c>
+      <c r="T39">
+        <v>1.198209379983239</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.04600632741336257</v>
+      </c>
+      <c r="W39">
+        <v>0.227813689013689</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2555907078520143</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1553800036960263</v>
+      </c>
+      <c r="C40">
+        <v>285.4713488761931</v>
+      </c>
+      <c r="D40">
+        <v>2507.871348876193</v>
+      </c>
+      <c r="E40">
+        <v>454.5999999999999</v>
+      </c>
+      <c r="F40">
+        <v>2633.4</v>
+      </c>
+      <c r="G40">
+        <v>411</v>
+      </c>
+      <c r="H40">
+        <v>4751.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>457.5</v>
+      </c>
+      <c r="K40">
+        <v>301</v>
+      </c>
+      <c r="L40">
+        <v>156.5</v>
+      </c>
+      <c r="M40">
+        <v>628.8559200000001</v>
+      </c>
+      <c r="N40">
+        <v>-472.3559200000001</v>
+      </c>
+      <c r="O40">
+        <v>-85.02406559999999</v>
+      </c>
+      <c r="P40">
+        <v>-387.3318544000001</v>
+      </c>
+      <c r="Q40">
+        <v>-86.33185440000011</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1108079657434861</v>
+      </c>
+      <c r="T40">
+        <v>1.217535337724904</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.04479563458669513</v>
+      </c>
+      <c r="W40">
+        <v>0.2281028024606972</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.2488646365927508</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1573800036960263</v>
+      </c>
+      <c r="C41">
+        <v>174.4592479926414</v>
+      </c>
+      <c r="D41">
+        <v>2466.159247992642</v>
+      </c>
+      <c r="E41">
+        <v>523.9000000000001</v>
+      </c>
+      <c r="F41">
+        <v>2702.7</v>
+      </c>
+      <c r="G41">
+        <v>411</v>
+      </c>
+      <c r="H41">
+        <v>4751.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>457.5</v>
+      </c>
+      <c r="K41">
+        <v>301</v>
+      </c>
+      <c r="L41">
+        <v>156.5</v>
+      </c>
+      <c r="M41">
+        <v>645.4047600000001</v>
+      </c>
+      <c r="N41">
+        <v>-488.9047600000001</v>
+      </c>
+      <c r="O41">
+        <v>-88.00285679999999</v>
+      </c>
+      <c r="P41">
+        <v>-400.9019032000001</v>
+      </c>
+      <c r="Q41">
+        <v>-99.90190320000011</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1119884241982974</v>
+      </c>
+      <c r="T41">
+        <v>1.237494933425312</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.04364702857165166</v>
+      </c>
+      <c r="W41">
+        <v>0.2283770895770896</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2424834920647315</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1593800036960263</v>
+      </c>
+      <c r="C42">
+        <v>64.81199701057858</v>
+      </c>
+      <c r="D42">
+        <v>2425.811997010579</v>
+      </c>
+      <c r="E42">
+        <v>593.1999999999998</v>
+      </c>
+      <c r="F42">
+        <v>2772</v>
+      </c>
+      <c r="G42">
+        <v>411</v>
+      </c>
+      <c r="H42">
+        <v>4751.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>457.5</v>
+      </c>
+      <c r="K42">
+        <v>301</v>
+      </c>
+      <c r="L42">
+        <v>156.5</v>
+      </c>
+      <c r="M42">
+        <v>661.9536000000001</v>
+      </c>
+      <c r="N42">
+        <v>-505.4536000000001</v>
+      </c>
+      <c r="O42">
+        <v>-90.98164799999998</v>
+      </c>
+      <c r="P42">
+        <v>-414.4719520000001</v>
+      </c>
+      <c r="Q42">
+        <v>-113.4719520000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.113208231268269</v>
+      </c>
+      <c r="T42">
+        <v>1.258119848982401</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.04255585285736038</v>
+      </c>
+      <c r="W42">
+        <v>0.2286376623376623</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.2364214047631132</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1613800036960263</v>
+      </c>
+      <c r="C43">
+        <v>-43.53631406251225</v>
+      </c>
+      <c r="D43">
+        <v>2386.763685937488</v>
+      </c>
+      <c r="E43">
+        <v>662.5</v>
+      </c>
+      <c r="F43">
+        <v>2841.3</v>
+      </c>
+      <c r="G43">
+        <v>411</v>
+      </c>
+      <c r="H43">
+        <v>4751.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>457.5</v>
+      </c>
+      <c r="K43">
+        <v>301</v>
+      </c>
+      <c r="L43">
+        <v>156.5</v>
+      </c>
+      <c r="M43">
+        <v>678.5024400000001</v>
+      </c>
+      <c r="N43">
+        <v>-522.0024400000001</v>
+      </c>
+      <c r="O43">
+        <v>-93.96043919999998</v>
+      </c>
+      <c r="P43">
+        <v>-428.0420008000001</v>
+      </c>
+      <c r="Q43">
+        <v>-127.0420008000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1144693877304431</v>
+      </c>
+      <c r="T43">
+        <v>1.279443914219391</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.04151790522669305</v>
+      </c>
+      <c r="W43">
+        <v>0.2288855242318657</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.2306550290371837</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1633800036960263</v>
+      </c>
+      <c r="C44">
+        <v>-150.6474186353712</v>
+      </c>
+      <c r="D44">
+        <v>2348.952581364629</v>
+      </c>
+      <c r="E44">
+        <v>731.7999999999997</v>
+      </c>
+      <c r="F44">
+        <v>2910.6</v>
+      </c>
+      <c r="G44">
+        <v>411</v>
+      </c>
+      <c r="H44">
+        <v>4751.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>457.5</v>
+      </c>
+      <c r="K44">
+        <v>301</v>
+      </c>
+      <c r="L44">
+        <v>156.5</v>
+      </c>
+      <c r="M44">
+        <v>695.05128</v>
+      </c>
+      <c r="N44">
+        <v>-538.55128</v>
+      </c>
+      <c r="O44">
+        <v>-96.93923039999997</v>
+      </c>
+      <c r="P44">
+        <v>-441.6120496</v>
+      </c>
+      <c r="Q44">
+        <v>-140.6120496</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1157740323464852</v>
+      </c>
+      <c r="T44">
+        <v>1.301503292050759</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.04052938367367655</v>
+      </c>
+      <c r="W44">
+        <v>0.2291215831787261</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.2251632426315364</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1653800036960263</v>
+      </c>
+      <c r="C45">
+        <v>-256.5791992008913</v>
+      </c>
+      <c r="D45">
+        <v>2312.320800799109</v>
+      </c>
+      <c r="E45">
+        <v>801.0999999999999</v>
+      </c>
+      <c r="F45">
+        <v>2979.9</v>
+      </c>
+      <c r="G45">
+        <v>411</v>
+      </c>
+      <c r="H45">
+        <v>4751.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>457.5</v>
+      </c>
+      <c r="K45">
+        <v>301</v>
+      </c>
+      <c r="L45">
+        <v>156.5</v>
+      </c>
+      <c r="M45">
+        <v>711.6001200000001</v>
+      </c>
+      <c r="N45">
+        <v>-555.1001200000001</v>
+      </c>
+      <c r="O45">
+        <v>-99.91802159999997</v>
+      </c>
+      <c r="P45">
+        <v>-455.1820984000001</v>
+      </c>
+      <c r="Q45">
+        <v>-154.1820984000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1171244539665989</v>
+      </c>
+      <c r="T45">
+        <v>1.324336683139369</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.03958683986731198</v>
+      </c>
+      <c r="W45">
+        <v>0.2293466626396859</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.2199268881517333</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1673800036960263</v>
+      </c>
+      <c r="C46">
+        <v>-361.3859829993171</v>
+      </c>
+      <c r="D46">
+        <v>2276.814017000683</v>
+      </c>
+      <c r="E46">
+        <v>870.3999999999996</v>
+      </c>
+      <c r="F46">
+        <v>3049.2</v>
+      </c>
+      <c r="G46">
+        <v>411</v>
+      </c>
+      <c r="H46">
+        <v>4751.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>457.5</v>
+      </c>
+      <c r="K46">
+        <v>301</v>
+      </c>
+      <c r="L46">
+        <v>156.5</v>
+      </c>
+      <c r="M46">
+        <v>728.14896</v>
+      </c>
+      <c r="N46">
+        <v>-571.64896</v>
+      </c>
+      <c r="O46">
+        <v>-102.8968128</v>
+      </c>
+      <c r="P46">
+        <v>-468.7521472</v>
+      </c>
+      <c r="Q46">
+        <v>-167.7521472</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1185231049302882</v>
+      </c>
+      <c r="T46">
+        <v>1.347985552481143</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.03868713896123671</v>
+      </c>
+      <c r="W46">
+        <v>0.2295615112160567</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.2149285497846485</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1693800036960263</v>
+      </c>
+      <c r="C47">
+        <v>-465.1188108531251</v>
+      </c>
+      <c r="D47">
+        <v>2242.381189146875</v>
+      </c>
+      <c r="E47">
+        <v>939.6999999999998</v>
+      </c>
+      <c r="F47">
+        <v>3118.5</v>
+      </c>
+      <c r="G47">
+        <v>411</v>
+      </c>
+      <c r="H47">
+        <v>4751.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>457.5</v>
+      </c>
+      <c r="K47">
+        <v>301</v>
+      </c>
+      <c r="L47">
+        <v>156.5</v>
+      </c>
+      <c r="M47">
+        <v>744.6978</v>
+      </c>
+      <c r="N47">
+        <v>-588.1978</v>
+      </c>
+      <c r="O47">
+        <v>-105.875604</v>
+      </c>
+      <c r="P47">
+        <v>-482.3221960000001</v>
+      </c>
+      <c r="Q47">
+        <v>-181.3221960000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1199726159290207</v>
+      </c>
+      <c r="T47">
+        <v>1.372494380708073</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.03782742476209811</v>
+      </c>
+      <c r="W47">
+        <v>0.229766810966811</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.210152359789434</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1713800036960264</v>
+      </c>
+      <c r="C48">
+        <v>-567.8256819713738</v>
+      </c>
+      <c r="D48">
+        <v>2208.974318028626</v>
+      </c>
+      <c r="E48">
+        <v>1009</v>
+      </c>
+      <c r="F48">
+        <v>3187.8</v>
+      </c>
+      <c r="G48">
+        <v>411</v>
+      </c>
+      <c r="H48">
+        <v>4751.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>457.5</v>
+      </c>
+      <c r="K48">
+        <v>301</v>
+      </c>
+      <c r="L48">
+        <v>156.5</v>
+      </c>
+      <c r="M48">
+        <v>761.2466400000001</v>
+      </c>
+      <c r="N48">
+        <v>-604.7466400000001</v>
+      </c>
+      <c r="O48">
+        <v>-108.8543952</v>
+      </c>
+      <c r="P48">
+        <v>-495.8922448000001</v>
+      </c>
+      <c r="Q48">
+        <v>-194.8922448000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1214758125202989</v>
+      </c>
+      <c r="T48">
+        <v>1.397910943313778</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.03700508944118294</v>
+      </c>
+      <c r="W48">
+        <v>0.2299631846414455</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2055838302287941</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1733800036960264</v>
+      </c>
+      <c r="C49">
+        <v>-669.5517771927834</v>
+      </c>
+      <c r="D49">
+        <v>2176.548222807217</v>
+      </c>
+      <c r="E49">
+        <v>1078.3</v>
+      </c>
+      <c r="F49">
+        <v>3257.1</v>
+      </c>
+      <c r="G49">
+        <v>411</v>
+      </c>
+      <c r="H49">
+        <v>4751.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>457.5</v>
+      </c>
+      <c r="K49">
+        <v>301</v>
+      </c>
+      <c r="L49">
+        <v>156.5</v>
+      </c>
+      <c r="M49">
+        <v>777.7954800000001</v>
+      </c>
+      <c r="N49">
+        <v>-621.2954800000001</v>
+      </c>
+      <c r="O49">
+        <v>-111.8331864</v>
+      </c>
+      <c r="P49">
+        <v>-509.4622936000001</v>
+      </c>
+      <c r="Q49">
+        <v>-208.4622936000001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1230357335112479</v>
+      </c>
+      <c r="T49">
+        <v>1.42428662148951</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.03621774711264712</v>
+      </c>
+      <c r="W49">
+        <v>0.2301512019894999</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.201209706181373</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1753800036960264</v>
+      </c>
+      <c r="C50">
+        <v>-770.3396628510172</v>
+      </c>
+      <c r="D50">
+        <v>2145.060337148983</v>
+      </c>
+      <c r="E50">
+        <v>1147.6</v>
+      </c>
+      <c r="F50">
+        <v>3326.4</v>
+      </c>
+      <c r="G50">
+        <v>411</v>
+      </c>
+      <c r="H50">
+        <v>4751.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>457.5</v>
+      </c>
+      <c r="K50">
+        <v>301</v>
+      </c>
+      <c r="L50">
+        <v>156.5</v>
+      </c>
+      <c r="M50">
+        <v>794.34432</v>
+      </c>
+      <c r="N50">
+        <v>-637.84432</v>
+      </c>
+      <c r="O50">
+        <v>-114.8119776</v>
+      </c>
+      <c r="P50">
+        <v>-523.0323424000001</v>
+      </c>
+      <c r="Q50">
+        <v>-222.0323424000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1246556514633873</v>
+      </c>
+      <c r="T50">
+        <v>1.451676748825847</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.03546321071446698</v>
+      </c>
+      <c r="W50">
+        <v>0.2303313852813853</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1970178373025944</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1773800036960263</v>
+      </c>
+      <c r="C51">
+        <v>-870.2294771965348</v>
+      </c>
+      <c r="D51">
+        <v>2114.470522803465</v>
+      </c>
+      <c r="E51">
+        <v>1216.9</v>
+      </c>
+      <c r="F51">
+        <v>3395.7</v>
+      </c>
+      <c r="G51">
+        <v>411</v>
+      </c>
+      <c r="H51">
+        <v>4751.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>457.5</v>
+      </c>
+      <c r="K51">
+        <v>301</v>
+      </c>
+      <c r="L51">
+        <v>156.5</v>
+      </c>
+      <c r="M51">
+        <v>810.89316</v>
+      </c>
+      <c r="N51">
+        <v>-654.39316</v>
+      </c>
+      <c r="O51">
+        <v>-117.7907688</v>
+      </c>
+      <c r="P51">
+        <v>-536.6023912000001</v>
+      </c>
+      <c r="Q51">
+        <v>-235.6023912000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1263390956097282</v>
+      </c>
+      <c r="T51">
+        <v>1.480140998802824</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.03473947172029419</v>
+      </c>
+      <c r="W51">
+        <v>0.2305042141531937</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1929970651127456</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1793800036960264</v>
+      </c>
+      <c r="C52">
+        <v>-969.2591010918113</v>
+      </c>
+      <c r="D52">
+        <v>2084.740898908189</v>
+      </c>
+      <c r="E52">
+        <v>1286.2</v>
+      </c>
+      <c r="F52">
+        <v>3465</v>
+      </c>
+      <c r="G52">
+        <v>411</v>
+      </c>
+      <c r="H52">
+        <v>4751.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>457.5</v>
+      </c>
+      <c r="K52">
+        <v>301</v>
+      </c>
+      <c r="L52">
+        <v>156.5</v>
+      </c>
+      <c r="M52">
+        <v>827.442</v>
+      </c>
+      <c r="N52">
+        <v>-670.942</v>
+      </c>
+      <c r="O52">
+        <v>-120.76956</v>
+      </c>
+      <c r="P52">
+        <v>-550.1724400000001</v>
+      </c>
+      <c r="Q52">
+        <v>-249.1724400000001</v>
+      </c>
+      <c r="R52">
         <v>1</v>
       </c>
-      <c r="U4">
-        <v>362.9</v>
-      </c>
-      <c r="V4">
-        <v>0.06585609291352872</v>
-      </c>
-      <c r="W4">
-        <v>-0.0375064976608421</v>
-      </c>
-      <c r="X4">
-        <v>0.06438355759116025</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1018900552520023</v>
-      </c>
-      <c r="Z4">
-        <v>0.1594188095298894</v>
-      </c>
-      <c r="AA4">
-        <v>-0.02239472945021833</v>
-      </c>
-      <c r="AB4">
-        <v>0.05297974504423503</v>
-      </c>
-      <c r="AC4">
-        <v>-0.07537447449445335</v>
-      </c>
-      <c r="AD4">
-        <v>2003.5</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>2003.5</v>
-      </c>
-      <c r="AG4">
-        <v>1640.6</v>
-      </c>
-      <c r="AH4">
-        <v>0.2666356135214267</v>
-      </c>
-      <c r="AI4">
-        <v>0.4431933814095474</v>
-      </c>
-      <c r="AJ4">
-        <v>0.2294192501852862</v>
-      </c>
-      <c r="AK4">
-        <v>0.3945931644899824</v>
-      </c>
-      <c r="AL4">
-        <v>21.2</v>
-      </c>
-      <c r="AM4">
-        <v>20.423</v>
-      </c>
-      <c r="AN4">
-        <v>10.55028962611901</v>
-      </c>
-      <c r="AO4">
-        <v>-4.136792452830189</v>
-      </c>
-      <c r="AP4">
-        <v>8.639283833596629</v>
-      </c>
-      <c r="AQ4">
-        <v>-4.294178132497675</v>
+      <c r="S52">
+        <v>0.1280898775219228</v>
+      </c>
+      <c r="T52">
+        <v>1.509743818778881</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.03404468228588831</v>
+      </c>
+      <c r="W52">
+        <v>0.2306701298701299</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1891371238104906</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1813800036960264</v>
+      </c>
+      <c r="C53">
+        <v>-1067.464314506268</v>
+      </c>
+      <c r="D53">
+        <v>2055.835685493732</v>
+      </c>
+      <c r="E53">
+        <v>1355.5</v>
+      </c>
+      <c r="F53">
+        <v>3534.3</v>
+      </c>
+      <c r="G53">
+        <v>411</v>
+      </c>
+      <c r="H53">
+        <v>4751.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>457.5</v>
+      </c>
+      <c r="K53">
+        <v>301</v>
+      </c>
+      <c r="L53">
+        <v>156.5</v>
+      </c>
+      <c r="M53">
+        <v>843.99084</v>
+      </c>
+      <c r="N53">
+        <v>-687.49084</v>
+      </c>
+      <c r="O53">
+        <v>-123.7483512</v>
+      </c>
+      <c r="P53">
+        <v>-563.7424888</v>
+      </c>
+      <c r="Q53">
+        <v>-262.7424888</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1299121199203294</v>
+      </c>
+      <c r="T53">
+        <v>1.540554917121307</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.03337713949596893</v>
+      </c>
+      <c r="W53">
+        <v>0.2308295390883627</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1854285527553829</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1833800036960264</v>
+      </c>
+      <c r="C54">
+        <v>-1164.878940170332</v>
+      </c>
+      <c r="D54">
+        <v>2027.721059829668</v>
+      </c>
+      <c r="E54">
+        <v>1424.8</v>
+      </c>
+      <c r="F54">
+        <v>3603.6</v>
+      </c>
+      <c r="G54">
+        <v>411</v>
+      </c>
+      <c r="H54">
+        <v>4751.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>457.5</v>
+      </c>
+      <c r="K54">
+        <v>301</v>
+      </c>
+      <c r="L54">
+        <v>156.5</v>
+      </c>
+      <c r="M54">
+        <v>860.53968</v>
+      </c>
+      <c r="N54">
+        <v>-704.03968</v>
+      </c>
+      <c r="O54">
+        <v>-126.7271423999999</v>
+      </c>
+      <c r="P54">
+        <v>-577.3125376</v>
+      </c>
+      <c r="Q54">
+        <v>-276.3125376</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1318102890853363</v>
+      </c>
+      <c r="T54">
+        <v>1.572649811228001</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.03273527142873876</v>
+      </c>
+      <c r="W54">
+        <v>0.2309828171828172</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1818626190485487</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1853800036960264</v>
+      </c>
+      <c r="C55">
+        <v>-1261.534975601223</v>
+      </c>
+      <c r="D55">
+        <v>2000.365024398777</v>
+      </c>
+      <c r="E55">
+        <v>1494.1</v>
+      </c>
+      <c r="F55">
+        <v>3672.9</v>
+      </c>
+      <c r="G55">
+        <v>411</v>
+      </c>
+      <c r="H55">
+        <v>4751.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>457.5</v>
+      </c>
+      <c r="K55">
+        <v>301</v>
+      </c>
+      <c r="L55">
+        <v>156.5</v>
+      </c>
+      <c r="M55">
+        <v>877.08852</v>
+      </c>
+      <c r="N55">
+        <v>-720.58852</v>
+      </c>
+      <c r="O55">
+        <v>-129.7059336</v>
+      </c>
+      <c r="P55">
+        <v>-590.8825864</v>
+      </c>
+      <c r="Q55">
+        <v>-289.8825864</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1337892314063009</v>
+      </c>
+      <c r="T55">
+        <v>1.606110445509447</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.03211762479800783</v>
+      </c>
+      <c r="W55">
+        <v>0.2311303111982357</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1784312488778214</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1873800036960263</v>
+      </c>
+      <c r="C56">
+        <v>-1357.462714584042</v>
+      </c>
+      <c r="D56">
+        <v>1973.737285415958</v>
+      </c>
+      <c r="E56">
+        <v>1563.4</v>
+      </c>
+      <c r="F56">
+        <v>3742.2</v>
+      </c>
+      <c r="G56">
+        <v>411</v>
+      </c>
+      <c r="H56">
+        <v>4751.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>457.5</v>
+      </c>
+      <c r="K56">
+        <v>301</v>
+      </c>
+      <c r="L56">
+        <v>156.5</v>
+      </c>
+      <c r="M56">
+        <v>893.6373600000001</v>
+      </c>
+      <c r="N56">
+        <v>-737.1373600000001</v>
+      </c>
+      <c r="O56">
+        <v>-132.6847248</v>
+      </c>
+      <c r="P56">
+        <v>-604.4526352</v>
+      </c>
+      <c r="Q56">
+        <v>-303.4526352</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1358542146977422</v>
+      </c>
+      <c r="T56">
+        <v>1.641025889977044</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.03152285396841509</v>
+      </c>
+      <c r="W56">
+        <v>0.2312723424723425</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1751269664911951</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1893800036960263</v>
+      </c>
+      <c r="C57">
+        <v>-1452.690859077777</v>
+      </c>
+      <c r="D57">
+        <v>1947.809140922223</v>
+      </c>
+      <c r="E57">
+        <v>1632.7</v>
+      </c>
+      <c r="F57">
+        <v>3811.5</v>
+      </c>
+      <c r="G57">
+        <v>411</v>
+      </c>
+      <c r="H57">
+        <v>4751.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>457.5</v>
+      </c>
+      <c r="K57">
+        <v>301</v>
+      </c>
+      <c r="L57">
+        <v>156.5</v>
+      </c>
+      <c r="M57">
+        <v>910.1862000000001</v>
+      </c>
+      <c r="N57">
+        <v>-753.6862000000001</v>
+      </c>
+      <c r="O57">
+        <v>-135.663516</v>
+      </c>
+      <c r="P57">
+        <v>-618.0226840000001</v>
+      </c>
+      <c r="Q57">
+        <v>-317.0226840000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1380109750243587</v>
+      </c>
+      <c r="T57">
+        <v>1.677493131976534</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.03094971116898936</v>
+      </c>
+      <c r="W57">
+        <v>0.2314092089728453</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1719428398277187</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1913800036960264</v>
+      </c>
+      <c r="C58">
+        <v>-1547.246622415313</v>
+      </c>
+      <c r="D58">
+        <v>1922.553377584687</v>
+      </c>
+      <c r="E58">
+        <v>1702</v>
+      </c>
+      <c r="F58">
+        <v>3880.8</v>
+      </c>
+      <c r="G58">
+        <v>411</v>
+      </c>
+      <c r="H58">
+        <v>4751.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>457.5</v>
+      </c>
+      <c r="K58">
+        <v>301</v>
+      </c>
+      <c r="L58">
+        <v>156.5</v>
+      </c>
+      <c r="M58">
+        <v>926.7350400000001</v>
+      </c>
+      <c r="N58">
+        <v>-770.2350400000001</v>
+      </c>
+      <c r="O58">
+        <v>-138.6423072</v>
+      </c>
+      <c r="P58">
+        <v>-631.5927328000001</v>
+      </c>
+      <c r="Q58">
+        <v>-330.5927328000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1402657699112759</v>
+      </c>
+      <c r="T58">
+        <v>1.715617975885092</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.03039703775525741</v>
+      </c>
+      <c r="W58">
+        <v>0.2315411873840446</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1688724319736523</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1933800036960264</v>
+      </c>
+      <c r="C59">
+        <v>-1641.155824577507</v>
+      </c>
+      <c r="D59">
+        <v>1897.944175422493</v>
+      </c>
+      <c r="E59">
+        <v>1771.3</v>
+      </c>
+      <c r="F59">
+        <v>3950.1</v>
+      </c>
+      <c r="G59">
+        <v>411</v>
+      </c>
+      <c r="H59">
+        <v>4751.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>457.5</v>
+      </c>
+      <c r="K59">
+        <v>301</v>
+      </c>
+      <c r="L59">
+        <v>156.5</v>
+      </c>
+      <c r="M59">
+        <v>943.2838800000002</v>
+      </c>
+      <c r="N59">
+        <v>-786.7838800000002</v>
+      </c>
+      <c r="O59">
+        <v>-141.6210984</v>
+      </c>
+      <c r="P59">
+        <v>-645.1627816000002</v>
+      </c>
+      <c r="Q59">
+        <v>-344.1627816000002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.14262543897898</v>
+      </c>
+      <c r="T59">
+        <v>1.755516068347536</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.02986375639113008</v>
+      </c>
+      <c r="W59">
+        <v>0.2316685349737982</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1659097577285006</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1953800036960263</v>
+      </c>
+      <c r="C60">
+        <v>-1734.442980242547</v>
+      </c>
+      <c r="D60">
+        <v>1873.957019757453</v>
+      </c>
+      <c r="E60">
+        <v>1840.599999999999</v>
+      </c>
+      <c r="F60">
+        <v>4019.4</v>
+      </c>
+      <c r="G60">
+        <v>411</v>
+      </c>
+      <c r="H60">
+        <v>4751.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>457.5</v>
+      </c>
+      <c r="K60">
+        <v>301</v>
+      </c>
+      <c r="L60">
+        <v>156.5</v>
+      </c>
+      <c r="M60">
+        <v>959.83272</v>
+      </c>
+      <c r="N60">
+        <v>-803.33272</v>
+      </c>
+      <c r="O60">
+        <v>-144.5998896</v>
+      </c>
+      <c r="P60">
+        <v>-658.7328304</v>
+      </c>
+      <c r="Q60">
+        <v>-357.7328304</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1450974732403843</v>
+      </c>
+      <c r="T60">
+        <v>1.797314069974858</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.02934886403955888</v>
+      </c>
+      <c r="W60">
+        <v>0.2317914912673534</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1630492446642161</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1973800036960263</v>
+      </c>
+      <c r="C61">
+        <v>-1827.131380241771</v>
+      </c>
+      <c r="D61">
+        <v>1850.568619758229</v>
+      </c>
+      <c r="E61">
+        <v>1909.9</v>
+      </c>
+      <c r="F61">
+        <v>4088.7</v>
+      </c>
+      <c r="G61">
+        <v>411</v>
+      </c>
+      <c r="H61">
+        <v>4751.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>457.5</v>
+      </c>
+      <c r="K61">
+        <v>301</v>
+      </c>
+      <c r="L61">
+        <v>156.5</v>
+      </c>
+      <c r="M61">
+        <v>976.38156</v>
+      </c>
+      <c r="N61">
+        <v>-819.88156</v>
+      </c>
+      <c r="O61">
+        <v>-147.5786807999999</v>
+      </c>
+      <c r="P61">
+        <v>-672.3028792000001</v>
+      </c>
+      <c r="Q61">
+        <v>-371.3028792000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1476900945389302</v>
+      </c>
+      <c r="T61">
+        <v>1.84115099851083</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.02885142566600704</v>
+      </c>
+      <c r="W61">
+        <v>0.2319102795509575</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1602856981444836</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1993800036960263</v>
+      </c>
+      <c r="C62">
+        <v>-1919.243166990896</v>
+      </c>
+      <c r="D62">
+        <v>1827.756833009103</v>
+      </c>
+      <c r="E62">
+        <v>1979.2</v>
+      </c>
+      <c r="F62">
+        <v>4158</v>
+      </c>
+      <c r="G62">
+        <v>411</v>
+      </c>
+      <c r="H62">
+        <v>4751.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>457.5</v>
+      </c>
+      <c r="K62">
+        <v>301</v>
+      </c>
+      <c r="L62">
+        <v>156.5</v>
+      </c>
+      <c r="M62">
+        <v>992.9304000000001</v>
+      </c>
+      <c r="N62">
+        <v>-836.4304000000001</v>
+      </c>
+      <c r="O62">
+        <v>-150.557472</v>
+      </c>
+      <c r="P62">
+        <v>-685.8729280000001</v>
+      </c>
+      <c r="Q62">
+        <v>-384.8729280000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1504123469024035</v>
+      </c>
+      <c r="T62">
+        <v>1.8871797734736</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.02837056857157358</v>
+      </c>
+      <c r="W62">
+        <v>0.2320251082251082</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1576142698420755</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2013800036960263</v>
+      </c>
+      <c r="C63">
+        <v>-2010.799404410179</v>
+      </c>
+      <c r="D63">
+        <v>1805.500595589821</v>
+      </c>
+      <c r="E63">
+        <v>2048.5</v>
+      </c>
+      <c r="F63">
+        <v>4227.3</v>
+      </c>
+      <c r="G63">
+        <v>411</v>
+      </c>
+      <c r="H63">
+        <v>4751.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>457.5</v>
+      </c>
+      <c r="K63">
+        <v>301</v>
+      </c>
+      <c r="L63">
+        <v>156.5</v>
+      </c>
+      <c r="M63">
+        <v>1009.47924</v>
+      </c>
+      <c r="N63">
+        <v>-852.9792400000001</v>
+      </c>
+      <c r="O63">
+        <v>-153.5362632</v>
+      </c>
+      <c r="P63">
+        <v>-699.4429768000001</v>
+      </c>
+      <c r="Q63">
+        <v>-398.4429768000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1532742019511831</v>
+      </c>
+      <c r="T63">
+        <v>1.935568998434462</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.027905477283515</v>
+      </c>
+      <c r="W63">
+        <v>0.2321361720246966</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1550304293528612</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2033800036960264</v>
+      </c>
+      <c r="C64">
+        <v>-2101.820142797611</v>
+      </c>
+      <c r="D64">
+        <v>1783.77985720239</v>
+      </c>
+      <c r="E64">
+        <v>2117.8</v>
+      </c>
+      <c r="F64">
+        <v>4296.6</v>
+      </c>
+      <c r="G64">
+        <v>411</v>
+      </c>
+      <c r="H64">
+        <v>4751.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>457.5</v>
+      </c>
+      <c r="K64">
+        <v>301</v>
+      </c>
+      <c r="L64">
+        <v>156.5</v>
+      </c>
+      <c r="M64">
+        <v>1026.02808</v>
+      </c>
+      <c r="N64">
+        <v>-869.52808</v>
+      </c>
+      <c r="O64">
+        <v>-156.5150543999999</v>
+      </c>
+      <c r="P64">
+        <v>-713.0130256000001</v>
+      </c>
+      <c r="Q64">
+        <v>-412.0130256000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1562866809498984</v>
+      </c>
+      <c r="T64">
+        <v>1.986505024709053</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.0274553889402325</v>
+      </c>
+      <c r="W64">
+        <v>0.2322436531210725</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1525299385568473</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2053800036960264</v>
+      </c>
+      <c r="C65">
+        <v>-2192.324479075103</v>
+      </c>
+      <c r="D65">
+        <v>1762.575520924897</v>
+      </c>
+      <c r="E65">
+        <v>2187.099999999999</v>
+      </c>
+      <c r="F65">
+        <v>4365.9</v>
+      </c>
+      <c r="G65">
+        <v>411</v>
+      </c>
+      <c r="H65">
+        <v>4751.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>457.5</v>
+      </c>
+      <c r="K65">
+        <v>301</v>
+      </c>
+      <c r="L65">
+        <v>156.5</v>
+      </c>
+      <c r="M65">
+        <v>1042.57692</v>
+      </c>
+      <c r="N65">
+        <v>-886.07692</v>
+      </c>
+      <c r="O65">
+        <v>-159.4938455999999</v>
+      </c>
+      <c r="P65">
+        <v>-726.5830744</v>
+      </c>
+      <c r="Q65">
+        <v>-425.5830744</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1594619966512471</v>
+      </c>
+      <c r="T65">
+        <v>2.04019434970119</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.02701958911578437</v>
+      </c>
+      <c r="W65">
+        <v>0.2323477221191507</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1501088284210244</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2073800036960264</v>
+      </c>
+      <c r="C66">
+        <v>-2282.330612788171</v>
+      </c>
+      <c r="D66">
+        <v>1741.869387211829</v>
+      </c>
+      <c r="E66">
+        <v>2256.4</v>
+      </c>
+      <c r="F66">
+        <v>4435.2</v>
+      </c>
+      <c r="G66">
+        <v>411</v>
+      </c>
+      <c r="H66">
+        <v>4751.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>457.5</v>
+      </c>
+      <c r="K66">
+        <v>301</v>
+      </c>
+      <c r="L66">
+        <v>156.5</v>
+      </c>
+      <c r="M66">
+        <v>1059.12576</v>
+      </c>
+      <c r="N66">
+        <v>-902.6257599999999</v>
+      </c>
+      <c r="O66">
+        <v>-162.4726367999999</v>
+      </c>
+      <c r="P66">
+        <v>-740.1531232</v>
+      </c>
+      <c r="Q66">
+        <v>-439.1531232</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1628137187804483</v>
+      </c>
+      <c r="T66">
+        <v>2.096866414970668</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.02659740803585024</v>
+      </c>
+      <c r="W66">
+        <v>0.232448538961039</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1477633779769458</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2093800036960264</v>
+      </c>
+      <c r="C67">
+        <v>-2371.855898204248</v>
+      </c>
+      <c r="D67">
+        <v>1721.644101795752</v>
+      </c>
+      <c r="E67">
+        <v>2325.7</v>
+      </c>
+      <c r="F67">
+        <v>4504.5</v>
+      </c>
+      <c r="G67">
+        <v>411</v>
+      </c>
+      <c r="H67">
+        <v>4751.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>457.5</v>
+      </c>
+      <c r="K67">
+        <v>301</v>
+      </c>
+      <c r="L67">
+        <v>156.5</v>
+      </c>
+      <c r="M67">
+        <v>1075.6746</v>
+      </c>
+      <c r="N67">
+        <v>-919.1746000000001</v>
+      </c>
+      <c r="O67">
+        <v>-165.451428</v>
+      </c>
+      <c r="P67">
+        <v>-753.7231720000001</v>
+      </c>
+      <c r="Q67">
+        <v>-452.7231720000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1663569678884612</v>
+      </c>
+      <c r="T67">
+        <v>2.15677688396983</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.026188217142991</v>
+      </c>
+      <c r="W67">
+        <v>0.2325462537462538</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1454900952388389</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2113800036960264</v>
+      </c>
+      <c r="C68">
+        <v>-2460.91689282311</v>
+      </c>
+      <c r="D68">
+        <v>1701.88310717689</v>
+      </c>
+      <c r="E68">
+        <v>2395</v>
+      </c>
+      <c r="F68">
+        <v>4573.8</v>
+      </c>
+      <c r="G68">
+        <v>411</v>
+      </c>
+      <c r="H68">
+        <v>4751.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>457.5</v>
+      </c>
+      <c r="K68">
+        <v>301</v>
+      </c>
+      <c r="L68">
+        <v>156.5</v>
+      </c>
+      <c r="M68">
+        <v>1092.22344</v>
+      </c>
+      <c r="N68">
+        <v>-935.7234400000002</v>
+      </c>
+      <c r="O68">
+        <v>-168.4302192</v>
+      </c>
+      <c r="P68">
+        <v>-767.2932208000002</v>
+      </c>
+      <c r="Q68">
+        <v>-466.2932208000002</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1701086434145924</v>
+      </c>
+      <c r="T68">
+        <v>2.220211498204236</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0257914259741578</v>
+      </c>
+      <c r="W68">
+        <v>0.2326410074773711</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1432856998564322</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2133800036960263</v>
+      </c>
+      <c r="C69">
+        <v>-2549.529402584394</v>
+      </c>
+      <c r="D69">
+        <v>1682.570597415606</v>
+      </c>
+      <c r="E69">
+        <v>2464.3</v>
+      </c>
+      <c r="F69">
+        <v>4643.1</v>
+      </c>
+      <c r="G69">
+        <v>411</v>
+      </c>
+      <c r="H69">
+        <v>4751.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>457.5</v>
+      </c>
+      <c r="K69">
+        <v>301</v>
+      </c>
+      <c r="L69">
+        <v>156.5</v>
+      </c>
+      <c r="M69">
+        <v>1108.77228</v>
+      </c>
+      <c r="N69">
+        <v>-952.2722800000001</v>
+      </c>
+      <c r="O69">
+        <v>-171.4090104</v>
+      </c>
+      <c r="P69">
+        <v>-780.8632696000002</v>
+      </c>
+      <c r="Q69">
+        <v>-479.8632696000002</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1740876932150346</v>
+      </c>
+      <c r="T69">
+        <v>2.287490634513456</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.02540647931782709</v>
+      </c>
+      <c r="W69">
+        <v>0.2327329327389029</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1411471073212617</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2153800036960263</v>
+      </c>
+      <c r="C70">
+        <v>-2637.708524031636</v>
+      </c>
+      <c r="D70">
+        <v>1663.691475968365</v>
+      </c>
+      <c r="E70">
+        <v>2533.6</v>
+      </c>
+      <c r="F70">
+        <v>4712.400000000001</v>
+      </c>
+      <c r="G70">
+        <v>411</v>
+      </c>
+      <c r="H70">
+        <v>4751.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>457.5</v>
+      </c>
+      <c r="K70">
+        <v>301</v>
+      </c>
+      <c r="L70">
+        <v>156.5</v>
+      </c>
+      <c r="M70">
+        <v>1125.32112</v>
+      </c>
+      <c r="N70">
+        <v>-968.8211200000003</v>
+      </c>
+      <c r="O70">
+        <v>-174.3878016</v>
+      </c>
+      <c r="P70">
+        <v>-794.4333184000003</v>
+      </c>
+      <c r="Q70">
+        <v>-493.4333184000003</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1783154336280044</v>
+      </c>
+      <c r="T70">
+        <v>2.358974716842001</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.02503285462197669</v>
+      </c>
+      <c r="W70">
+        <v>0.232822154316272</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1390714145665372</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2173800036960264</v>
+      </c>
+      <c r="C71">
+        <v>-2725.468683669229</v>
+      </c>
+      <c r="D71">
+        <v>1645.231316330772</v>
+      </c>
+      <c r="E71">
+        <v>2602.900000000001</v>
+      </c>
+      <c r="F71">
+        <v>4781.700000000001</v>
+      </c>
+      <c r="G71">
+        <v>411</v>
+      </c>
+      <c r="H71">
+        <v>4751.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>457.5</v>
+      </c>
+      <c r="K71">
+        <v>301</v>
+      </c>
+      <c r="L71">
+        <v>156.5</v>
+      </c>
+      <c r="M71">
+        <v>1141.86996</v>
+      </c>
+      <c r="N71">
+        <v>-985.3699600000002</v>
+      </c>
+      <c r="O71">
+        <v>-177.3665928</v>
+      </c>
+      <c r="P71">
+        <v>-808.0033672000002</v>
+      </c>
+      <c r="Q71">
+        <v>-507.0033672000002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1828159314869723</v>
+      </c>
+      <c r="T71">
+        <v>2.435070675449808</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.02467005962745529</v>
+      </c>
+      <c r="W71">
+        <v>0.2329087897609637</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1370558868191961</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2193800036960264</v>
+      </c>
+      <c r="C72">
+        <v>-2812.823674727924</v>
+      </c>
+      <c r="D72">
+        <v>1627.176325272077</v>
+      </c>
+      <c r="E72">
+        <v>2672.200000000001</v>
+      </c>
+      <c r="F72">
+        <v>4851.000000000001</v>
+      </c>
+      <c r="G72">
+        <v>411</v>
+      </c>
+      <c r="H72">
+        <v>4751.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>457.5</v>
+      </c>
+      <c r="K72">
+        <v>301</v>
+      </c>
+      <c r="L72">
+        <v>156.5</v>
+      </c>
+      <c r="M72">
+        <v>1158.4188</v>
+      </c>
+      <c r="N72">
+        <v>-1001.9188</v>
+      </c>
+      <c r="O72">
+        <v>-180.345384</v>
+      </c>
+      <c r="P72">
+        <v>-821.5734160000004</v>
+      </c>
+      <c r="Q72">
+        <v>-520.5734160000004</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.187616462536538</v>
+      </c>
+      <c r="T72">
+        <v>2.516239697964802</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.02431763020420593</v>
+      </c>
+      <c r="W72">
+        <v>0.2329929499072356</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1350979455789219</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2213800036960264</v>
+      </c>
+      <c r="C73">
+        <v>-2899.786691535787</v>
+      </c>
+      <c r="D73">
+        <v>1609.513308464213</v>
+      </c>
+      <c r="E73">
+        <v>2741.5</v>
+      </c>
+      <c r="F73">
+        <v>4920.3</v>
+      </c>
+      <c r="G73">
+        <v>411</v>
+      </c>
+      <c r="H73">
+        <v>4751.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>457.5</v>
+      </c>
+      <c r="K73">
+        <v>301</v>
+      </c>
+      <c r="L73">
+        <v>156.5</v>
+      </c>
+      <c r="M73">
+        <v>1174.96764</v>
+      </c>
+      <c r="N73">
+        <v>-1018.46764</v>
+      </c>
+      <c r="O73">
+        <v>-183.3241752</v>
+      </c>
+      <c r="P73">
+        <v>-835.1434648000002</v>
+      </c>
+      <c r="Q73">
+        <v>-534.1434648000002</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1927480646929703</v>
+      </c>
+      <c r="T73">
+        <v>2.603006584101518</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.02397512837034387</v>
+      </c>
+      <c r="W73">
+        <v>0.2330747393451619</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1331951576130216</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2233800036960263</v>
+      </c>
+      <c r="C74">
+        <v>-2986.370361674618</v>
+      </c>
+      <c r="D74">
+        <v>1592.229638325382</v>
+      </c>
+      <c r="E74">
+        <v>2810.799999999999</v>
+      </c>
+      <c r="F74">
+        <v>4989.599999999999</v>
+      </c>
+      <c r="G74">
+        <v>411</v>
+      </c>
+      <c r="H74">
+        <v>4751.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>457.5</v>
+      </c>
+      <c r="K74">
+        <v>301</v>
+      </c>
+      <c r="L74">
+        <v>156.5</v>
+      </c>
+      <c r="M74">
+        <v>1191.51648</v>
+      </c>
+      <c r="N74">
+        <v>-1035.01648</v>
+      </c>
+      <c r="O74">
+        <v>-186.3029663999999</v>
+      </c>
+      <c r="P74">
+        <v>-848.7135136000001</v>
+      </c>
+      <c r="Q74">
+        <v>-547.7135136000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1982462098605764</v>
+      </c>
+      <c r="T74">
+        <v>2.695971104962287</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.02364214047631132</v>
+      </c>
+      <c r="W74">
+        <v>0.2331542568542569</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1313452248683963</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2253800036960263</v>
+      </c>
+      <c r="C75">
+        <v>-3072.586776086525</v>
+      </c>
+      <c r="D75">
+        <v>1575.313223913475</v>
+      </c>
+      <c r="E75">
+        <v>2880.099999999999</v>
+      </c>
+      <c r="F75">
+        <v>5058.9</v>
+      </c>
+      <c r="G75">
+        <v>411</v>
+      </c>
+      <c r="H75">
+        <v>4751.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>457.5</v>
+      </c>
+      <c r="K75">
+        <v>301</v>
+      </c>
+      <c r="L75">
+        <v>156.5</v>
+      </c>
+      <c r="M75">
+        <v>1208.06532</v>
+      </c>
+      <c r="N75">
+        <v>-1051.56532</v>
+      </c>
+      <c r="O75">
+        <v>-189.2817575999999</v>
+      </c>
+      <c r="P75">
+        <v>-862.2835623999999</v>
+      </c>
+      <c r="Q75">
+        <v>-561.2835623999999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2041516250405978</v>
+      </c>
+      <c r="T75">
+        <v>2.795821886627556</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.02331827553827966</v>
+      </c>
+      <c r="W75">
+        <v>0.2332315958014588</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1295459752126649</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2273800036960263</v>
+      </c>
+      <c r="C76">
+        <v>-3158.447517281486</v>
+      </c>
+      <c r="D76">
+        <v>1558.752482718513</v>
+      </c>
+      <c r="E76">
+        <v>2949.4</v>
+      </c>
+      <c r="F76">
+        <v>5128.2</v>
+      </c>
+      <c r="G76">
+        <v>411</v>
+      </c>
+      <c r="H76">
+        <v>4751.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>457.5</v>
+      </c>
+      <c r="K76">
+        <v>301</v>
+      </c>
+      <c r="L76">
+        <v>156.5</v>
+      </c>
+      <c r="M76">
+        <v>1224.61416</v>
+      </c>
+      <c r="N76">
+        <v>-1068.11416</v>
+      </c>
+      <c r="O76">
+        <v>-192.2605488</v>
+      </c>
+      <c r="P76">
+        <v>-875.8536112000002</v>
+      </c>
+      <c r="Q76">
+        <v>-574.8536112000002</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2105113029267746</v>
+      </c>
+      <c r="T76">
+        <v>2.903353497651693</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.02300316370668129</v>
+      </c>
+      <c r="W76">
+        <v>0.2333068445068445</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1277953539260072</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2293800036960263</v>
+      </c>
+      <c r="C77">
+        <v>-3243.963685784216</v>
+      </c>
+      <c r="D77">
+        <v>1542.536314215784</v>
+      </c>
+      <c r="E77">
+        <v>3018.7</v>
+      </c>
+      <c r="F77">
+        <v>5197.5</v>
+      </c>
+      <c r="G77">
+        <v>411</v>
+      </c>
+      <c r="H77">
+        <v>4751.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>457.5</v>
+      </c>
+      <c r="K77">
+        <v>301</v>
+      </c>
+      <c r="L77">
+        <v>156.5</v>
+      </c>
+      <c r="M77">
+        <v>1241.163</v>
+      </c>
+      <c r="N77">
+        <v>-1084.663</v>
+      </c>
+      <c r="O77">
+        <v>-195.2393399999999</v>
+      </c>
+      <c r="P77">
+        <v>-889.42366</v>
+      </c>
+      <c r="Q77">
+        <v>-588.42366</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2173797550438456</v>
+      </c>
+      <c r="T77">
+        <v>3.019487637557761</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.02269645485725887</v>
+      </c>
+      <c r="W77">
+        <v>0.2333800865800866</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1260914158736605</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2313800036960263</v>
+      </c>
+      <c r="C78">
+        <v>-3329.145924947202</v>
+      </c>
+      <c r="D78">
+        <v>1526.654075052798</v>
+      </c>
+      <c r="E78">
+        <v>3088</v>
+      </c>
+      <c r="F78">
+        <v>5266.8</v>
+      </c>
+      <c r="G78">
+        <v>411</v>
+      </c>
+      <c r="H78">
+        <v>4751.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>457.5</v>
+      </c>
+      <c r="K78">
+        <v>301</v>
+      </c>
+      <c r="L78">
+        <v>156.5</v>
+      </c>
+      <c r="M78">
+        <v>1257.71184</v>
+      </c>
+      <c r="N78">
+        <v>-1101.21184</v>
+      </c>
+      <c r="O78">
+        <v>-198.2181312</v>
+      </c>
+      <c r="P78">
+        <v>-902.9937088000001</v>
+      </c>
+      <c r="Q78">
+        <v>-601.9937088000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2248205781706726</v>
+      </c>
+      <c r="T78">
+        <v>3.145299622456002</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.02239781729334757</v>
+      </c>
+      <c r="W78">
+        <v>0.2334514012303486</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1244323182963754</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2333800036960264</v>
+      </c>
+      <c r="C79">
+        <v>-3414.004444246505</v>
+      </c>
+      <c r="D79">
+        <v>1511.095555753495</v>
+      </c>
+      <c r="E79">
+        <v>3157.3</v>
+      </c>
+      <c r="F79">
+        <v>5336.1</v>
+      </c>
+      <c r="G79">
+        <v>411</v>
+      </c>
+      <c r="H79">
+        <v>4751.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>457.5</v>
+      </c>
+      <c r="K79">
+        <v>301</v>
+      </c>
+      <c r="L79">
+        <v>156.5</v>
+      </c>
+      <c r="M79">
+        <v>1274.26068</v>
+      </c>
+      <c r="N79">
+        <v>-1117.76068</v>
+      </c>
+      <c r="O79">
+        <v>-201.1969223999999</v>
+      </c>
+      <c r="P79">
+        <v>-916.5637576000001</v>
+      </c>
+      <c r="Q79">
+        <v>-615.5637576000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2329084293954844</v>
+      </c>
+      <c r="T79">
+        <v>3.282051779954088</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.02210693654927812</v>
+      </c>
+      <c r="W79">
+        <v>0.2335208635520324</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1228163141626563</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2353800036960264</v>
+      </c>
+      <c r="C80">
+        <v>-3498.549041167438</v>
+      </c>
+      <c r="D80">
+        <v>1495.850958832563</v>
+      </c>
+      <c r="E80">
+        <v>3226.6</v>
+      </c>
+      <c r="F80">
+        <v>5405.400000000001</v>
+      </c>
+      <c r="G80">
+        <v>411</v>
+      </c>
+      <c r="H80">
+        <v>4751.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>457.5</v>
+      </c>
+      <c r="K80">
+        <v>301</v>
+      </c>
+      <c r="L80">
+        <v>156.5</v>
+      </c>
+      <c r="M80">
+        <v>1290.80952</v>
+      </c>
+      <c r="N80">
+        <v>-1134.30952</v>
+      </c>
+      <c r="O80">
+        <v>-204.1757136</v>
+      </c>
+      <c r="P80">
+        <v>-930.1338064000003</v>
+      </c>
+      <c r="Q80">
+        <v>-629.1338064000003</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2417315398225519</v>
+      </c>
+      <c r="T80">
+        <v>3.431235951770184</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.02182351428582583</v>
+      </c>
+      <c r="W80">
+        <v>0.2335885447885448</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1212417460323658</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2373800036960264</v>
+      </c>
+      <c r="C81">
+        <v>-3582.789121778719</v>
+      </c>
+      <c r="D81">
+        <v>1480.910878221281</v>
+      </c>
+      <c r="E81">
+        <v>3295.9</v>
+      </c>
+      <c r="F81">
+        <v>5474.7</v>
+      </c>
+      <c r="G81">
+        <v>411</v>
+      </c>
+      <c r="H81">
+        <v>4751.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>457.5</v>
+      </c>
+      <c r="K81">
+        <v>301</v>
+      </c>
+      <c r="L81">
+        <v>156.5</v>
+      </c>
+      <c r="M81">
+        <v>1307.35836</v>
+      </c>
+      <c r="N81">
+        <v>-1150.85836</v>
+      </c>
+      <c r="O81">
+        <v>-207.1545047999999</v>
+      </c>
+      <c r="P81">
+        <v>-943.7038552</v>
+      </c>
+      <c r="Q81">
+        <v>-642.7038552</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2513949464807687</v>
+      </c>
+      <c r="T81">
+        <v>3.594628139949716</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.02154726726954956</v>
+      </c>
+      <c r="W81">
+        <v>0.2336545125760316</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1197070403863865</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2393800036960264</v>
+      </c>
+      <c r="C82">
+        <v>-3666.733720085904</v>
+      </c>
+      <c r="D82">
+        <v>1466.266279914096</v>
+      </c>
+      <c r="E82">
+        <v>3365.2</v>
+      </c>
+      <c r="F82">
+        <v>5544</v>
+      </c>
+      <c r="G82">
+        <v>411</v>
+      </c>
+      <c r="H82">
+        <v>4751.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>457.5</v>
+      </c>
+      <c r="K82">
+        <v>301</v>
+      </c>
+      <c r="L82">
+        <v>156.5</v>
+      </c>
+      <c r="M82">
+        <v>1323.9072</v>
+      </c>
+      <c r="N82">
+        <v>-1167.4072</v>
+      </c>
+      <c r="O82">
+        <v>-210.1332959999999</v>
+      </c>
+      <c r="P82">
+        <v>-957.2739040000001</v>
+      </c>
+      <c r="Q82">
+        <v>-656.2739040000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2620246938048071</v>
+      </c>
+      <c r="T82">
+        <v>3.774359546947202</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.02127792642868019</v>
+      </c>
+      <c r="W82">
+        <v>0.2337188311688312</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1182107023815566</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2413800036960264</v>
+      </c>
+      <c r="C83">
+        <v>-3750.39151624774</v>
+      </c>
+      <c r="D83">
+        <v>1451.908483752261</v>
+      </c>
+      <c r="E83">
+        <v>3434.5</v>
+      </c>
+      <c r="F83">
+        <v>5613.3</v>
+      </c>
+      <c r="G83">
+        <v>411</v>
+      </c>
+      <c r="H83">
+        <v>4751.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>457.5</v>
+      </c>
+      <c r="K83">
+        <v>301</v>
+      </c>
+      <c r="L83">
+        <v>156.5</v>
+      </c>
+      <c r="M83">
+        <v>1340.45604</v>
+      </c>
+      <c r="N83">
+        <v>-1183.95604</v>
+      </c>
+      <c r="O83">
+        <v>-213.1120871999999</v>
+      </c>
+      <c r="P83">
+        <v>-970.8439528000001</v>
+      </c>
+      <c r="Q83">
+        <v>-669.8439528000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2737733618997969</v>
+      </c>
+      <c r="T83">
+        <v>3.973010049418107</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.0210152359789434</v>
+      </c>
+      <c r="W83">
+        <v>0.2337815616482283</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1167513109941301</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2433800036960264</v>
+      </c>
+      <c r="C84">
+        <v>-3833.770853732649</v>
+      </c>
+      <c r="D84">
+        <v>1437.829146267351</v>
+      </c>
+      <c r="E84">
+        <v>3503.8</v>
+      </c>
+      <c r="F84">
+        <v>5682.6</v>
+      </c>
+      <c r="G84">
+        <v>411</v>
+      </c>
+      <c r="H84">
+        <v>4751.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>457.5</v>
+      </c>
+      <c r="K84">
+        <v>301</v>
+      </c>
+      <c r="L84">
+        <v>156.5</v>
+      </c>
+      <c r="M84">
+        <v>1357.00488</v>
+      </c>
+      <c r="N84">
+        <v>-1200.50488</v>
+      </c>
+      <c r="O84">
+        <v>-216.0908784</v>
+      </c>
+      <c r="P84">
+        <v>-984.4140016000002</v>
+      </c>
+      <c r="Q84">
+        <v>-683.4140016000002</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2868274375608968</v>
+      </c>
+      <c r="T84">
+        <v>4.193732829941337</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.02075895261334652</v>
+      </c>
+      <c r="W84">
+        <v>0.2338427621159329</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1153275145185918</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2453800036960263</v>
+      </c>
+      <c r="C85">
+        <v>-3916.879755486589</v>
+      </c>
+      <c r="D85">
+        <v>1424.020244513412</v>
+      </c>
+      <c r="E85">
+        <v>3573.1</v>
+      </c>
+      <c r="F85">
+        <v>5751.900000000001</v>
+      </c>
+      <c r="G85">
+        <v>411</v>
+      </c>
+      <c r="H85">
+        <v>4751.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>457.5</v>
+      </c>
+      <c r="K85">
+        <v>301</v>
+      </c>
+      <c r="L85">
+        <v>156.5</v>
+      </c>
+      <c r="M85">
+        <v>1373.55372</v>
+      </c>
+      <c r="N85">
+        <v>-1217.05372</v>
+      </c>
+      <c r="O85">
+        <v>-219.0696695999999</v>
+      </c>
+      <c r="P85">
+        <v>-997.9840504000001</v>
+      </c>
+      <c r="Q85">
+        <v>-696.9840504000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3014172868291848</v>
+      </c>
+      <c r="T85">
+        <v>4.440422996408474</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.02050884475053512</v>
+      </c>
+      <c r="W85">
+        <v>0.2339024878735722</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1139380263918618</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2473800036960264</v>
+      </c>
+      <c r="C86">
+        <v>-3999.725939178116</v>
+      </c>
+      <c r="D86">
+        <v>1410.474060821884</v>
+      </c>
+      <c r="E86">
+        <v>3642.4</v>
+      </c>
+      <c r="F86">
+        <v>5821.2</v>
+      </c>
+      <c r="G86">
+        <v>411</v>
+      </c>
+      <c r="H86">
+        <v>4751.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>457.5</v>
+      </c>
+      <c r="K86">
+        <v>301</v>
+      </c>
+      <c r="L86">
+        <v>156.5</v>
+      </c>
+      <c r="M86">
+        <v>1390.10256</v>
+      </c>
+      <c r="N86">
+        <v>-1233.60256</v>
+      </c>
+      <c r="O86">
+        <v>-222.0484607999999</v>
+      </c>
+      <c r="P86">
+        <v>-1011.5540992</v>
+      </c>
+      <c r="Q86">
+        <v>-710.5540992000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3178308672560088</v>
+      </c>
+      <c r="T86">
+        <v>4.717949433684002</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.02026469183683828</v>
+      </c>
+      <c r="W86">
+        <v>0.233960791589363</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1125816213157682</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2493800036960264</v>
+      </c>
+      <c r="C87">
+        <v>-4082.316831581528</v>
+      </c>
+      <c r="D87">
+        <v>1397.183168418472</v>
+      </c>
+      <c r="E87">
+        <v>3711.7</v>
+      </c>
+      <c r="F87">
+        <v>5890.5</v>
+      </c>
+      <c r="G87">
+        <v>411</v>
+      </c>
+      <c r="H87">
+        <v>4751.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>457.5</v>
+      </c>
+      <c r="K87">
+        <v>301</v>
+      </c>
+      <c r="L87">
+        <v>156.5</v>
+      </c>
+      <c r="M87">
+        <v>1406.6514</v>
+      </c>
+      <c r="N87">
+        <v>-1250.1514</v>
+      </c>
+      <c r="O87">
+        <v>-225.0272519999999</v>
+      </c>
+      <c r="P87">
+        <v>-1025.124148</v>
+      </c>
+      <c r="Q87">
+        <v>-724.1241480000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.336432925073076</v>
+      </c>
+      <c r="T87">
+        <v>5.032479395929601</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.02002628369758136</v>
+      </c>
+      <c r="W87">
+        <v>0.2340177234530176</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1112571316532298</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2513800036960264</v>
+      </c>
+      <c r="C88">
+        <v>-4164.659582154396</v>
+      </c>
+      <c r="D88">
+        <v>1384.140417845604</v>
+      </c>
+      <c r="E88">
+        <v>3781</v>
+      </c>
+      <c r="F88">
+        <v>5959.8</v>
+      </c>
+      <c r="G88">
+        <v>411</v>
+      </c>
+      <c r="H88">
+        <v>4751.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>457.5</v>
+      </c>
+      <c r="K88">
+        <v>301</v>
+      </c>
+      <c r="L88">
+        <v>156.5</v>
+      </c>
+      <c r="M88">
+        <v>1423.20024</v>
+      </c>
+      <c r="N88">
+        <v>-1266.70024</v>
+      </c>
+      <c r="O88">
+        <v>-228.0060431999999</v>
+      </c>
+      <c r="P88">
+        <v>-1038.6941968</v>
+      </c>
+      <c r="Q88">
+        <v>-737.6941968000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3576924197211528</v>
+      </c>
+      <c r="T88">
+        <v>5.391942209924573</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.01979341993365599</v>
+      </c>
+      <c r="W88">
+        <v>0.234073331319843</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1099634440758667</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2533800036960264</v>
+      </c>
+      <c r="C89">
+        <v>-4246.761075861657</v>
+      </c>
+      <c r="D89">
+        <v>1371.338924138343</v>
+      </c>
+      <c r="E89">
+        <v>3850.3</v>
+      </c>
+      <c r="F89">
+        <v>6029.1</v>
+      </c>
+      <c r="G89">
+        <v>411</v>
+      </c>
+      <c r="H89">
+        <v>4751.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>457.5</v>
+      </c>
+      <c r="K89">
+        <v>301</v>
+      </c>
+      <c r="L89">
+        <v>156.5</v>
+      </c>
+      <c r="M89">
+        <v>1439.74908</v>
+      </c>
+      <c r="N89">
+        <v>-1283.24908</v>
+      </c>
+      <c r="O89">
+        <v>-230.9848343999999</v>
+      </c>
+      <c r="P89">
+        <v>-1052.2642456</v>
+      </c>
+      <c r="Q89">
+        <v>-751.2642456000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3822226058535492</v>
+      </c>
+      <c r="T89">
+        <v>5.806706995303387</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.01956590935970592</v>
+      </c>
+      <c r="W89">
+        <v>0.2341276608449022</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1086994964428107</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2553800036960264</v>
+      </c>
+      <c r="C90">
+        <v>-4328.627945294592</v>
+      </c>
+      <c r="D90">
+        <v>1358.772054705408</v>
+      </c>
+      <c r="E90">
+        <v>3919.599999999999</v>
+      </c>
+      <c r="F90">
+        <v>6098.4</v>
+      </c>
+      <c r="G90">
+        <v>411</v>
+      </c>
+      <c r="H90">
+        <v>4751.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>457.5</v>
+      </c>
+      <c r="K90">
+        <v>301</v>
+      </c>
+      <c r="L90">
+        <v>156.5</v>
+      </c>
+      <c r="M90">
+        <v>1456.29792</v>
+      </c>
+      <c r="N90">
+        <v>-1299.79792</v>
+      </c>
+      <c r="O90">
+        <v>-233.9636255999999</v>
+      </c>
+      <c r="P90">
+        <v>-1065.8342944</v>
+      </c>
+      <c r="Q90">
+        <v>-764.8342944000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4108411563413451</v>
+      </c>
+      <c r="T90">
+        <v>6.290599244912004</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.01934356948061836</v>
+      </c>
+      <c r="W90">
+        <v>0.2341807556080284</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1074642748923242</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2573800036960264</v>
+      </c>
+      <c r="C91">
+        <v>-4410.266582129501</v>
+      </c>
+      <c r="D91">
+        <v>1346.433417870498</v>
+      </c>
+      <c r="E91">
+        <v>3988.9</v>
+      </c>
+      <c r="F91">
+        <v>6167.7</v>
+      </c>
+      <c r="G91">
+        <v>411</v>
+      </c>
+      <c r="H91">
+        <v>4751.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>457.5</v>
+      </c>
+      <c r="K91">
+        <v>301</v>
+      </c>
+      <c r="L91">
+        <v>156.5</v>
+      </c>
+      <c r="M91">
+        <v>1472.84676</v>
+      </c>
+      <c r="N91">
+        <v>-1316.34676</v>
+      </c>
+      <c r="O91">
+        <v>-236.9424167999999</v>
+      </c>
+      <c r="P91">
+        <v>-1079.4043432</v>
+      </c>
+      <c r="Q91">
+        <v>-778.4043432000003</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4446630796451037</v>
+      </c>
+      <c r="T91">
+        <v>6.862471903540367</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.01912622600330803</v>
+      </c>
+      <c r="W91">
+        <v>0.2342326572304101</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1062568111294891</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2593800036960264</v>
+      </c>
+      <c r="C92">
+        <v>-4491.683147967689</v>
+      </c>
+      <c r="D92">
+        <v>1334.316852032311</v>
+      </c>
+      <c r="E92">
+        <v>4058.2</v>
+      </c>
+      <c r="F92">
+        <v>6237</v>
+      </c>
+      <c r="G92">
+        <v>411</v>
+      </c>
+      <c r="H92">
+        <v>4751.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>457.5</v>
+      </c>
+      <c r="K92">
+        <v>301</v>
+      </c>
+      <c r="L92">
+        <v>156.5</v>
+      </c>
+      <c r="M92">
+        <v>1489.3956</v>
+      </c>
+      <c r="N92">
+        <v>-1332.8956</v>
+      </c>
+      <c r="O92">
+        <v>-239.9212079999999</v>
+      </c>
+      <c r="P92">
+        <v>-1092.974392</v>
+      </c>
+      <c r="Q92">
+        <v>-791.9743920000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4852493876096141</v>
+      </c>
+      <c r="T92">
+        <v>7.548719093894404</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.01891371238104906</v>
+      </c>
+      <c r="W92">
+        <v>0.2342834054834055</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1050761798947171</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2613800036960264</v>
+      </c>
+      <c r="C93">
+        <v>-4572.883584595363</v>
+      </c>
+      <c r="D93">
+        <v>1322.416415404638</v>
+      </c>
+      <c r="E93">
+        <v>4127.5</v>
+      </c>
+      <c r="F93">
+        <v>6306.3</v>
+      </c>
+      <c r="G93">
+        <v>411</v>
+      </c>
+      <c r="H93">
+        <v>4751.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>457.5</v>
+      </c>
+      <c r="K93">
+        <v>301</v>
+      </c>
+      <c r="L93">
+        <v>156.5</v>
+      </c>
+      <c r="M93">
+        <v>1505.94444</v>
+      </c>
+      <c r="N93">
+        <v>-1349.44444</v>
+      </c>
+      <c r="O93">
+        <v>-242.8999992</v>
+      </c>
+      <c r="P93">
+        <v>-1106.5444408</v>
+      </c>
+      <c r="Q93">
+        <v>-805.5444408000003</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5348548751217936</v>
+      </c>
+      <c r="T93">
+        <v>8.387465659882674</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.01870586938785071</v>
+      </c>
+      <c r="W93">
+        <v>0.2343330383901813</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1039214965991707</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2633800036960264</v>
+      </c>
+      <c r="C94">
+        <v>-4653.873623699365</v>
+      </c>
+      <c r="D94">
+        <v>1310.726376300636</v>
+      </c>
+      <c r="E94">
+        <v>4196.8</v>
+      </c>
+      <c r="F94">
+        <v>6375.6</v>
+      </c>
+      <c r="G94">
+        <v>411</v>
+      </c>
+      <c r="H94">
+        <v>4751.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>457.5</v>
+      </c>
+      <c r="K94">
+        <v>301</v>
+      </c>
+      <c r="L94">
+        <v>156.5</v>
+      </c>
+      <c r="M94">
+        <v>1522.49328</v>
+      </c>
+      <c r="N94">
+        <v>-1365.99328</v>
+      </c>
+      <c r="O94">
+        <v>-245.8787903999999</v>
+      </c>
+      <c r="P94">
+        <v>-1120.1144896</v>
+      </c>
+      <c r="Q94">
+        <v>-819.1144896000003</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.596861734512018</v>
+      </c>
+      <c r="T94">
+        <v>9.43589886736801</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.01850254472059147</v>
+      </c>
+      <c r="W94">
+        <v>0.2343815923207228</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1027919151143971</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2653800036960264</v>
+      </c>
+      <c r="C95">
+        <v>-4734.658796072093</v>
+      </c>
+      <c r="D95">
+        <v>1299.241203927908</v>
+      </c>
+      <c r="E95">
+        <v>4266.1</v>
+      </c>
+      <c r="F95">
+        <v>6444.900000000001</v>
+      </c>
+      <c r="G95">
+        <v>411</v>
+      </c>
+      <c r="H95">
+        <v>4751.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>457.5</v>
+      </c>
+      <c r="K95">
+        <v>301</v>
+      </c>
+      <c r="L95">
+        <v>156.5</v>
+      </c>
+      <c r="M95">
+        <v>1539.04212</v>
+      </c>
+      <c r="N95">
+        <v>-1382.54212</v>
+      </c>
+      <c r="O95">
+        <v>-248.8575816</v>
+      </c>
+      <c r="P95">
+        <v>-1133.6845384</v>
+      </c>
+      <c r="Q95">
+        <v>-832.6845384000003</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6765848394423062</v>
+      </c>
+      <c r="T95">
+        <v>10.78388441984916</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.01830359262682166</v>
+      </c>
+      <c r="W95">
+        <v>0.234429102080715</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1016866257045649</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2673800036960264</v>
+      </c>
+      <c r="C96">
+        <v>-4815.244440336684</v>
+      </c>
+      <c r="D96">
+        <v>1287.955559663316</v>
+      </c>
+      <c r="E96">
+        <v>4335.400000000001</v>
+      </c>
+      <c r="F96">
+        <v>6514.200000000001</v>
+      </c>
+      <c r="G96">
+        <v>411</v>
+      </c>
+      <c r="H96">
+        <v>4751.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>457.5</v>
+      </c>
+      <c r="K96">
+        <v>301</v>
+      </c>
+      <c r="L96">
+        <v>156.5</v>
+      </c>
+      <c r="M96">
+        <v>1555.59096</v>
+      </c>
+      <c r="N96">
+        <v>-1399.09096</v>
+      </c>
+      <c r="O96">
+        <v>-251.8363728</v>
+      </c>
+      <c r="P96">
+        <v>-1147.2545872</v>
+      </c>
+      <c r="Q96">
+        <v>-846.2545872000003</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7828823126826909</v>
+      </c>
+      <c r="T96">
+        <v>12.58119848982402</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.01810887355632356</v>
+      </c>
+      <c r="W96">
+        <v>0.23447560099475</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1006048530906865</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2693800036960264</v>
+      </c>
+      <c r="C97">
+        <v>-4895.635711221376</v>
+      </c>
+      <c r="D97">
+        <v>1276.864288778625</v>
+      </c>
+      <c r="E97">
+        <v>4404.700000000001</v>
+      </c>
+      <c r="F97">
+        <v>6583.500000000001</v>
+      </c>
+      <c r="G97">
+        <v>411</v>
+      </c>
+      <c r="H97">
+        <v>4751.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>457.5</v>
+      </c>
+      <c r="K97">
+        <v>301</v>
+      </c>
+      <c r="L97">
+        <v>156.5</v>
+      </c>
+      <c r="M97">
+        <v>1572.1398</v>
+      </c>
+      <c r="N97">
+        <v>-1415.6398</v>
+      </c>
+      <c r="O97">
+        <v>-254.815164</v>
+      </c>
+      <c r="P97">
+        <v>-1160.824636</v>
+      </c>
+      <c r="Q97">
+        <v>-859.8246360000003</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.9316987752192294</v>
+      </c>
+      <c r="T97">
+        <v>15.09743818778883</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.01791825383467805</v>
+      </c>
+      <c r="W97">
+        <v>0.2345211209842789</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.09954585463710031</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2713800036960263</v>
+      </c>
+      <c r="C98">
+        <v>-4975.837587409978</v>
+      </c>
+      <c r="D98">
+        <v>1265.962412590022</v>
+      </c>
+      <c r="E98">
+        <v>4474</v>
+      </c>
+      <c r="F98">
+        <v>6652.8</v>
+      </c>
+      <c r="G98">
+        <v>411</v>
+      </c>
+      <c r="H98">
+        <v>4751.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>457.5</v>
+      </c>
+      <c r="K98">
+        <v>301</v>
+      </c>
+      <c r="L98">
+        <v>156.5</v>
+      </c>
+      <c r="M98">
+        <v>1588.68864</v>
+      </c>
+      <c r="N98">
+        <v>-1432.18864</v>
+      </c>
+      <c r="O98">
+        <v>-257.7939551999999</v>
+      </c>
+      <c r="P98">
+        <v>-1174.3946848</v>
+      </c>
+      <c r="Q98">
+        <v>-873.3946848000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.154923469024034</v>
+      </c>
+      <c r="T98">
+        <v>18.87179773473599</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01773160535723349</v>
+      </c>
+      <c r="W98">
+        <v>0.2345656926406927</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.09850891865129718</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2733800036960263</v>
+      </c>
+      <c r="C99">
+        <v>-5055.854878993604</v>
+      </c>
+      <c r="D99">
+        <v>1255.245121006395</v>
+      </c>
+      <c r="E99">
+        <v>4543.299999999999</v>
+      </c>
+      <c r="F99">
+        <v>6722.099999999999</v>
+      </c>
+      <c r="G99">
+        <v>411</v>
+      </c>
+      <c r="H99">
+        <v>4751.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>457.5</v>
+      </c>
+      <c r="K99">
+        <v>301</v>
+      </c>
+      <c r="L99">
+        <v>156.5</v>
+      </c>
+      <c r="M99">
+        <v>1605.23748</v>
+      </c>
+      <c r="N99">
+        <v>-1448.73748</v>
+      </c>
+      <c r="O99">
+        <v>-260.7727463999999</v>
+      </c>
+      <c r="P99">
+        <v>-1187.9647336</v>
+      </c>
+      <c r="Q99">
+        <v>-886.9647336</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.526964625365379</v>
+      </c>
+      <c r="T99">
+        <v>25.16239697964799</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01754880530200428</v>
+      </c>
+      <c r="W99">
+        <v>0.2346093452938814</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.09749336278891274</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2753800036960264</v>
+      </c>
+      <c r="C100">
+        <v>-5135.692234547053</v>
+      </c>
+      <c r="D100">
+        <v>1244.707765452946</v>
+      </c>
+      <c r="E100">
+        <v>4612.599999999999</v>
+      </c>
+      <c r="F100">
+        <v>6791.4</v>
+      </c>
+      <c r="G100">
+        <v>411</v>
+      </c>
+      <c r="H100">
+        <v>4751.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>457.5</v>
+      </c>
+      <c r="K100">
+        <v>301</v>
+      </c>
+      <c r="L100">
+        <v>156.5</v>
+      </c>
+      <c r="M100">
+        <v>1621.78632</v>
+      </c>
+      <c r="N100">
+        <v>-1465.28632</v>
+      </c>
+      <c r="O100">
+        <v>-263.7515375999999</v>
+      </c>
+      <c r="P100">
+        <v>-1201.5347824</v>
+      </c>
+      <c r="Q100">
+        <v>-900.5347824</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.271046938048069</v>
+      </c>
+      <c r="T100">
+        <v>37.74359546947198</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.01736973586014709</v>
+      </c>
+      <c r="W100">
+        <v>0.2346521070765969</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.09649853255637275</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2773800036960263</v>
+      </c>
+      <c r="C101">
+        <v>-5215.354147851749</v>
+      </c>
+      <c r="D101">
+        <v>1234.345852148251</v>
+      </c>
+      <c r="E101">
+        <v>4681.9</v>
+      </c>
+      <c r="F101">
+        <v>6860.7</v>
+      </c>
+      <c r="G101">
+        <v>411</v>
+      </c>
+      <c r="H101">
+        <v>4751.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>457.5</v>
+      </c>
+      <c r="K101">
+        <v>301</v>
+      </c>
+      <c r="L101">
+        <v>156.5</v>
+      </c>
+      <c r="M101">
+        <v>1638.33516</v>
+      </c>
+      <c r="N101">
+        <v>-1481.83516</v>
+      </c>
+      <c r="O101">
+        <v>-266.7303287999999</v>
+      </c>
+      <c r="P101">
+        <v>-1215.1048312</v>
+      </c>
+      <c r="Q101">
+        <v>-914.1048312000003</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.503293876096137</v>
+      </c>
+      <c r="T101">
+        <v>75.48719093894397</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.01719428398277187</v>
+      </c>
+      <c r="W101">
+        <v>0.2346940049849141</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.09552379990428816</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_air_transport.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_air_transport.xlsx
@@ -650,10 +650,10 @@
         <v>0.1169973544973545</v>
       </c>
       <c r="X2">
-        <v>0.08713225374410977</v>
+        <v>0.08710568077982495</v>
       </c>
       <c r="Y2">
-        <v>0.02986510075324474</v>
+        <v>0.02989167371752956</v>
       </c>
       <c r="Z2">
         <v>0.3212695998389513</v>
@@ -662,10 +662,10 @@
         <v>0.08152265592228485</v>
       </c>
       <c r="AB2">
-        <v>0.07971465913045306</v>
+        <v>0.07969284224728979</v>
       </c>
       <c r="AC2">
-        <v>0.001807996791831787</v>
+        <v>0.001829813674995059</v>
       </c>
       <c r="AD2">
         <v>1606.9</v>
@@ -787,10 +787,10 @@
         <v>0.1169973544973545</v>
       </c>
       <c r="X3">
-        <v>0.08713225374410977</v>
+        <v>0.08710568077982495</v>
       </c>
       <c r="Y3">
-        <v>0.02986510075324474</v>
+        <v>0.02989167371752956</v>
       </c>
       <c r="Z3">
         <v>0.3212695998389513</v>
@@ -799,10 +799,10 @@
         <v>0.08152265592228485</v>
       </c>
       <c r="AB3">
-        <v>0.07971465913045306</v>
+        <v>0.07969284224728979</v>
       </c>
       <c r="AC3">
-        <v>0.001807996791831787</v>
+        <v>0.001829813674995059</v>
       </c>
       <c r="AD3">
         <v>1606.9</v>
@@ -1139,49 +1139,49 @@
         <v>28.4493670886076</v>
       </c>
       <c r="F2">
-        <v>6.77311012296532</v>
+        <v>3.01789210542252</v>
       </c>
       <c r="G2">
         <v>2.08688311688312</v>
       </c>
       <c r="H2">
-        <v>1.63236363636364</v>
+        <v>3.49792207792208</v>
       </c>
       <c r="I2">
         <v>0.178981955892181</v>
       </c>
       <c r="J2">
-        <v>0.14</v>
+        <v>0.3</v>
       </c>
       <c r="K2">
         <v>7371.1</v>
       </c>
       <c r="L2">
-        <v>7690.60477664641</v>
+        <v>6327.91663363127</v>
       </c>
       <c r="M2">
         <v>8719.4</v>
       </c>
       <c r="N2">
-        <v>8688.92477664641</v>
+        <v>8762.716633631269</v>
       </c>
       <c r="O2">
         <v>1606.9</v>
       </c>
       <c r="P2">
-        <v>1256.92</v>
+        <v>2693.4</v>
       </c>
       <c r="Q2">
-        <v>0.0797146591304531</v>
+        <v>0.0796928422472898</v>
       </c>
       <c r="R2">
-        <v>0.0798336101903977</v>
+        <v>0.0795253001605454</v>
       </c>
       <c r="S2">
         <v>0.045689</v>
       </c>
       <c r="T2">
-        <v>0.0450912</v>
+        <v>0.0472262</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1190,20 +1190,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="W2">
-        <v>0.08713225374410979</v>
+        <v>0.0871056807798249</v>
       </c>
       <c r="X2">
-        <v>0.0854893513841834</v>
+        <v>0.093367771657922</v>
       </c>
       <c r="Y2">
         <v>0.953941819395495</v>
       </c>
       <c r="Z2">
-        <v>0.916023895151147</v>
+        <v>1.09856285584115</v>
       </c>
       <c r="AA2">
         <v>1606.9</v>
@@ -1236,7 +1236,7 @@
         <v>7371.1</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08064507553431921</v>
+        <v>0.08062267324884481</v>
       </c>
       <c r="C2">
-        <v>8745.178785883811</v>
+        <v>8745.175587668937</v>
       </c>
       <c r="D2">
-        <v>8486.57878588381</v>
+        <v>8486.575587668936</v>
       </c>
       <c r="E2">
         <v>-1606.9</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08064507553431921</v>
+        <v>0.08062267324884481</v>
       </c>
       <c r="T2">
         <v>0.8042187817285175</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.146</v>
       </c>
       <c r="W2">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.0805777197240391</v>
+        <v>0.08054339414590148</v>
       </c>
       <c r="C3">
-        <v>8671.835182380331</v>
+        <v>8674.760653063118</v>
       </c>
       <c r="D3">
-        <v>8503.015182380332</v>
+        <v>8505.940653063119</v>
       </c>
       <c r="E3">
         <v>-1517.12</v>
@@ -1539,37 +1539,37 @@
         <v>449.5</v>
       </c>
       <c r="M3">
-        <v>4.641626</v>
+        <v>4.515934</v>
       </c>
       <c r="N3">
-        <v>444.858374</v>
+        <v>444.984066</v>
       </c>
       <c r="O3">
-        <v>64.949322604</v>
+        <v>64.967673636</v>
       </c>
       <c r="P3">
-        <v>379.909051396</v>
+        <v>380.016392364</v>
       </c>
       <c r="Q3">
-        <v>700.409051396</v>
+        <v>700.516392364</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.0809456583071102</v>
+        <v>0.08092306277363787</v>
       </c>
       <c r="T3">
         <v>0.8111561841486805</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.146</v>
       </c>
       <c r="W3">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>96.84106388580209</v>
+        <v>99.53644140946258</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08051036391375897</v>
+        <v>0.08046411504295817</v>
       </c>
       <c r="C4">
-        <v>8598.555368862286</v>
+        <v>8604.434296804729</v>
       </c>
       <c r="D4">
-        <v>8519.515368862285</v>
+        <v>8525.394296804729</v>
       </c>
       <c r="E4">
         <v>-1427.34</v>
@@ -1621,37 +1621,37 @@
         <v>449.5</v>
       </c>
       <c r="M4">
-        <v>9.283252000000001</v>
+        <v>9.031867999999999</v>
       </c>
       <c r="N4">
-        <v>440.216748</v>
+        <v>440.468132</v>
       </c>
       <c r="O4">
-        <v>64.271645208</v>
+        <v>64.30834727200001</v>
       </c>
       <c r="P4">
-        <v>375.945102792</v>
+        <v>376.159784728</v>
       </c>
       <c r="Q4">
-        <v>696.4451027919999</v>
+        <v>696.659784728</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08125237542220304</v>
+        <v>0.08122958269689609</v>
       </c>
       <c r="T4">
         <v>0.8182351662100715</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.146</v>
       </c>
       <c r="W4">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>48.42053194290104</v>
+        <v>49.7682207047313</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08044300810347887</v>
+        <v>0.08038483594001486</v>
       </c>
       <c r="C5">
-        <v>8525.339717407001</v>
+        <v>8534.197128040387</v>
       </c>
       <c r="D5">
-        <v>8536.079717407001</v>
+        <v>8544.937128040387</v>
       </c>
       <c r="E5">
         <v>-1337.56</v>
@@ -1703,37 +1703,37 @@
         <v>449.5</v>
       </c>
       <c r="M5">
-        <v>13.924878</v>
+        <v>13.547802</v>
       </c>
       <c r="N5">
-        <v>435.575122</v>
+        <v>435.952198</v>
       </c>
       <c r="O5">
-        <v>63.593967812</v>
+        <v>63.649020908</v>
       </c>
       <c r="P5">
-        <v>371.981154188</v>
+        <v>372.303177092</v>
       </c>
       <c r="Q5">
-        <v>692.481154188</v>
+        <v>692.8031770919999</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08156541660152461</v>
+        <v>0.08154242261857203</v>
       </c>
       <c r="T5">
         <v>0.8254601066644809</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.146</v>
       </c>
       <c r="W5">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>32.2803546286007</v>
+        <v>33.1788138031542</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08037565229319878</v>
+        <v>0.08030555683707155</v>
       </c>
       <c r="C6">
-        <v>8452.188602991166</v>
+        <v>8464.049761514952</v>
       </c>
       <c r="D6">
-        <v>8552.708602991166</v>
+        <v>8564.569761514953</v>
       </c>
       <c r="E6">
         <v>-1247.78</v>
@@ -1785,37 +1785,37 @@
         <v>449.5</v>
       </c>
       <c r="M6">
-        <v>18.566504</v>
+        <v>18.063736</v>
       </c>
       <c r="N6">
-        <v>430.933496</v>
+        <v>431.436264</v>
       </c>
       <c r="O6">
-        <v>62.916290416</v>
+        <v>62.989694544</v>
       </c>
       <c r="P6">
-        <v>368.017205584</v>
+        <v>368.446569456</v>
       </c>
       <c r="Q6">
-        <v>688.5172055840001</v>
+        <v>688.946569456</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08188497947208206</v>
+        <v>0.0818617800386162</v>
       </c>
       <c r="T6">
         <v>0.8328355667116906</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.146</v>
       </c>
       <c r="W6">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>24.21026597145052</v>
+        <v>24.88411035236565</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08030829648291868</v>
+        <v>0.08022627773412824</v>
       </c>
       <c r="C7">
-        <v>8379.102403519082</v>
+        <v>8393.992817635981</v>
       </c>
       <c r="D7">
-        <v>8569.402403519081</v>
+        <v>8584.29281763598</v>
       </c>
       <c r="E7">
         <v>-1158</v>
@@ -1867,37 +1867,37 @@
         <v>449.5</v>
       </c>
       <c r="M7">
-        <v>23.20813</v>
+        <v>22.57967</v>
       </c>
       <c r="N7">
-        <v>426.29187</v>
+        <v>426.92033</v>
       </c>
       <c r="O7">
-        <v>62.23861302</v>
+        <v>62.33036817999999</v>
       </c>
       <c r="P7">
-        <v>364.05325698</v>
+        <v>364.58996182</v>
       </c>
       <c r="Q7">
-        <v>684.55325698</v>
+        <v>685.08996182</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08221126998201966</v>
+        <v>0.08218786077276657</v>
       </c>
       <c r="T7">
         <v>0.8403662996019993</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.146</v>
       </c>
       <c r="W7">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.36821277716042</v>
+        <v>19.90728828189252</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08024094067263855</v>
+        <v>0.08014699863118492</v>
       </c>
       <c r="C8">
-        <v>8306.081499851314</v>
+        <v>8324.026922539082</v>
       </c>
       <c r="D8">
-        <v>8586.161499851314</v>
+        <v>8604.106922539082</v>
       </c>
       <c r="E8">
         <v>-1068.22</v>
@@ -1949,37 +1949,37 @@
         <v>449.5</v>
       </c>
       <c r="M8">
-        <v>27.849756</v>
+        <v>27.09560399999999</v>
       </c>
       <c r="N8">
-        <v>421.650244</v>
+        <v>422.404396</v>
       </c>
       <c r="O8">
-        <v>61.560935624</v>
+        <v>61.671041816</v>
       </c>
       <c r="P8">
-        <v>360.089308376</v>
+        <v>360.733354184</v>
       </c>
       <c r="Q8">
-        <v>680.589308376</v>
+        <v>681.2333541840001</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08254450284323252</v>
+        <v>0.08252087939487758</v>
       </c>
       <c r="T8">
         <v>0.8480572608516763</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.146</v>
       </c>
       <c r="W8">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.14017731430035</v>
+        <v>16.5894069015771</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08017358486235845</v>
+        <v>0.08006771952824161</v>
       </c>
       <c r="C9">
-        <v>8233.126275833631</v>
+        <v>8254.152708154172</v>
       </c>
       <c r="D9">
-        <v>8602.986275833629</v>
+        <v>8624.01270815417</v>
       </c>
       <c r="E9">
         <v>-978.4400000000003</v>
@@ -2031,37 +2031,37 @@
         <v>449.5</v>
       </c>
       <c r="M9">
-        <v>32.491382</v>
+        <v>31.611538</v>
       </c>
       <c r="N9">
-        <v>417.008618</v>
+        <v>417.888462</v>
       </c>
       <c r="O9">
-        <v>60.883258228</v>
+        <v>61.011715452</v>
       </c>
       <c r="P9">
-        <v>356.125359772</v>
+        <v>356.876746548</v>
       </c>
       <c r="Q9">
-        <v>676.625359772</v>
+        <v>677.376746548</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08288490200253598</v>
+        <v>0.08286105970778668</v>
       </c>
       <c r="T9">
         <v>0.8559136191174753</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.146</v>
       </c>
       <c r="W9">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>13.83443769797173</v>
+        <v>14.21949162992323</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08010622905207836</v>
+        <v>0.07998844042529829</v>
       </c>
       <c r="C10">
-        <v>8160.237118326337</v>
+        <v>8184.370812272673</v>
       </c>
       <c r="D10">
-        <v>8619.877118326336</v>
+        <v>8644.010812272672</v>
       </c>
       <c r="E10">
         <v>-888.6600000000003</v>
@@ -2113,37 +2113,37 @@
         <v>449.5</v>
       </c>
       <c r="M10">
-        <v>37.133008</v>
+        <v>36.127472</v>
       </c>
       <c r="N10">
-        <v>412.366992</v>
+        <v>413.372528</v>
       </c>
       <c r="O10">
-        <v>60.205580832</v>
+        <v>60.352389088</v>
       </c>
       <c r="P10">
-        <v>352.161411168</v>
+        <v>353.020138912</v>
       </c>
       <c r="Q10">
-        <v>672.661411168</v>
+        <v>673.520138912</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08323270114356343</v>
+        <v>0.08320863524488945</v>
       </c>
       <c r="T10">
         <v>0.8639407677803569</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.146</v>
       </c>
       <c r="W10">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.10513298572526</v>
+        <v>12.44205517618282</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08003887324179824</v>
+        <v>0.07990916132235498</v>
       </c>
       <c r="C11">
-        <v>8087.414417233915</v>
+        <v>8114.681878615605</v>
       </c>
       <c r="D11">
-        <v>8636.834417233915</v>
+        <v>8664.101878615606</v>
       </c>
       <c r="E11">
         <v>-798.8800000000003</v>
@@ -2195,37 +2195,37 @@
         <v>449.5</v>
       </c>
       <c r="M11">
-        <v>41.774634</v>
+        <v>40.643406</v>
       </c>
       <c r="N11">
-        <v>407.725366</v>
+        <v>408.856594</v>
       </c>
       <c r="O11">
-        <v>59.527903436</v>
+        <v>59.69306272399999</v>
       </c>
       <c r="P11">
-        <v>348.197462564</v>
+        <v>349.163531276</v>
       </c>
       <c r="Q11">
-        <v>668.697462564</v>
+        <v>669.663531276</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08358814422175631</v>
+        <v>0.08356384980478569</v>
       </c>
       <c r="T11">
         <v>0.8721443372929721</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.146</v>
       </c>
       <c r="W11">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>10.76011820953357</v>
+        <v>11.0596046010514</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07997151743151813</v>
+        <v>0.07982988221941167</v>
       </c>
       <c r="C12">
-        <v>8014.658565535018</v>
+        <v>8045.086556902686</v>
       </c>
       <c r="D12">
-        <v>8653.858565535018</v>
+        <v>8684.286556902685</v>
       </c>
       <c r="E12">
         <v>-709.1000000000003</v>
@@ -2277,37 +2277,37 @@
         <v>449.5</v>
       </c>
       <c r="M12">
-        <v>46.41626000000001</v>
+        <v>45.15934</v>
       </c>
       <c r="N12">
-        <v>403.08374</v>
+        <v>404.34066</v>
       </c>
       <c r="O12">
-        <v>58.85022604</v>
+        <v>59.03373636</v>
       </c>
       <c r="P12">
-        <v>344.23351396</v>
+        <v>345.30692364</v>
       </c>
       <c r="Q12">
-        <v>664.73351396</v>
+        <v>665.80692364</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08395148603502015</v>
+        <v>0.08392695802156852</v>
       </c>
       <c r="T12">
         <v>0.8805302083503123</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.146</v>
       </c>
       <c r="W12">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.684106388580206</v>
+        <v>9.953644140946258</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07990416162123803</v>
+        <v>0.07975060311646837</v>
       </c>
       <c r="C13">
-        <v>7941.969959312839</v>
+        <v>7975.585502922349</v>
       </c>
       <c r="D13">
-        <v>8670.949959312838</v>
+        <v>8704.565502922349</v>
       </c>
       <c r="E13">
         <v>-619.3200000000003</v>
@@ -2359,37 +2359,37 @@
         <v>449.5</v>
       </c>
       <c r="M13">
-        <v>51.057886</v>
+        <v>49.675274</v>
       </c>
       <c r="N13">
-        <v>398.442114</v>
+        <v>399.824726</v>
       </c>
       <c r="O13">
-        <v>58.172548644</v>
+        <v>58.374409996</v>
       </c>
       <c r="P13">
-        <v>340.269565356</v>
+        <v>341.450316004</v>
       </c>
       <c r="Q13">
-        <v>660.7695653559999</v>
+        <v>661.950316004</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08432299283285172</v>
+        <v>0.08429822597355996</v>
       </c>
       <c r="T13">
         <v>0.8891045259482668</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.146</v>
       </c>
       <c r="W13">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.803733080527461</v>
+        <v>9.048767400860234</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07994953381095793</v>
+        <v>0.07982504401352504</v>
       </c>
       <c r="C14">
-        <v>7840.669451045186</v>
+        <v>7866.761422795119</v>
       </c>
       <c r="D14">
-        <v>8659.429451045185</v>
+        <v>8685.521422795118</v>
       </c>
       <c r="E14">
         <v>-529.5400000000004</v>
@@ -2441,37 +2441,37 @@
         <v>449.5</v>
       </c>
       <c r="M14">
-        <v>56.88460799999999</v>
+        <v>55.80724799999999</v>
       </c>
       <c r="N14">
-        <v>392.615392</v>
+        <v>393.692752</v>
       </c>
       <c r="O14">
-        <v>57.321847232</v>
+        <v>57.47914179199999</v>
       </c>
       <c r="P14">
-        <v>335.293544768</v>
+        <v>336.213610208</v>
       </c>
       <c r="Q14">
-        <v>655.7935447679999</v>
+        <v>656.713610208</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08470294296699765</v>
+        <v>0.08467793183355118</v>
       </c>
       <c r="T14">
         <v>0.8978737144007202</v>
       </c>
       <c r="U14">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.146</v>
       </c>
       <c r="W14">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.901961810126212</v>
+        <v>8.054509335418224</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07989157200067783</v>
+        <v>0.07975857491058173</v>
       </c>
       <c r="C15">
-        <v>7765.612040163852</v>
+        <v>7793.982101389206</v>
       </c>
       <c r="D15">
-        <v>8674.152040163852</v>
+        <v>8702.522101389206</v>
       </c>
       <c r="E15">
         <v>-439.7600000000002</v>
@@ -2523,37 +2523,37 @@
         <v>449.5</v>
       </c>
       <c r="M15">
-        <v>61.62499200000001</v>
+        <v>60.457852</v>
       </c>
       <c r="N15">
-        <v>387.875008</v>
+        <v>389.042148</v>
       </c>
       <c r="O15">
-        <v>56.62975116799999</v>
+        <v>56.800153608</v>
       </c>
       <c r="P15">
-        <v>331.245256832</v>
+        <v>332.241994392</v>
       </c>
       <c r="Q15">
-        <v>651.745256832</v>
+        <v>652.7419943919999</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.085091627586986</v>
+        <v>0.08506636656388705</v>
       </c>
       <c r="T15">
         <v>0.9068444933923105</v>
       </c>
       <c r="U15">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.146</v>
       </c>
       <c r="W15">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.294118593962656</v>
+        <v>7.434931694232207</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07983361019039772</v>
+        <v>0.07969210580763843</v>
       </c>
       <c r="C16">
-        <v>7690.604776646405</v>
+        <v>7721.269463349739</v>
       </c>
       <c r="D16">
-        <v>8688.924776646405</v>
+        <v>8719.589463349739</v>
       </c>
       <c r="E16">
         <v>-349.9800000000002</v>
@@ -2605,37 +2605,37 @@
         <v>449.5</v>
       </c>
       <c r="M16">
-        <v>66.365376</v>
+        <v>65.108456</v>
       </c>
       <c r="N16">
-        <v>383.134624</v>
+        <v>384.391544</v>
       </c>
       <c r="O16">
-        <v>55.937655104</v>
+        <v>56.121165424</v>
       </c>
       <c r="P16">
-        <v>327.196968896</v>
+        <v>328.270378576</v>
       </c>
       <c r="Q16">
-        <v>647.696968896</v>
+        <v>648.770378576</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.0854893513841834</v>
+        <v>0.08546383466004467</v>
       </c>
       <c r="T16">
         <v>0.9160238951511471</v>
       </c>
       <c r="U16">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.146</v>
       </c>
       <c r="W16">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.773110122965325</v>
+        <v>6.903865144644191</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08005746838011761</v>
+        <v>0.0798434067046951</v>
       </c>
       <c r="C17">
-        <v>7544.046297001331</v>
+        <v>7592.736534795479</v>
       </c>
       <c r="D17">
-        <v>8632.146297001331</v>
+        <v>8680.836534795479</v>
       </c>
       <c r="E17">
         <v>-260.2000000000003</v>
@@ -2687,37 +2687,37 @@
         <v>449.5</v>
       </c>
       <c r="M17">
-        <v>74.0685</v>
+        <v>72.04845</v>
       </c>
       <c r="N17">
-        <v>375.4315</v>
+        <v>377.45155</v>
       </c>
       <c r="O17">
-        <v>54.812999</v>
+        <v>55.1079263</v>
       </c>
       <c r="P17">
-        <v>320.618501</v>
+        <v>322.3436237</v>
       </c>
       <c r="Q17">
-        <v>641.118501</v>
+        <v>642.8436237000001</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08589643338837366</v>
+        <v>0.08587065494670013</v>
       </c>
       <c r="T17">
         <v>0.9254192828337211</v>
       </c>
       <c r="U17">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.146</v>
       </c>
       <c r="W17">
-        <v>0.04697</v>
+        <v>0.045689</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.068706670176931</v>
+        <v>6.238857324480957</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08001829456983751</v>
+        <v>0.07979145560175178</v>
       </c>
       <c r="C18">
-        <v>7464.14855634826</v>
+        <v>7516.223958166132</v>
       </c>
       <c r="D18">
-        <v>8642.028556348259</v>
+        <v>8694.103958166132</v>
       </c>
       <c r="E18">
         <v>-170.4200000000003</v>
@@ -2769,37 +2769,37 @@
         <v>449.5</v>
       </c>
       <c r="M18">
-        <v>79.0064</v>
+        <v>76.85168</v>
       </c>
       <c r="N18">
-        <v>370.4936</v>
+        <v>372.64832</v>
       </c>
       <c r="O18">
-        <v>54.0920656</v>
+        <v>54.40665472</v>
       </c>
       <c r="P18">
-        <v>316.4015344</v>
+        <v>318.24166528</v>
       </c>
       <c r="Q18">
-        <v>636.9015343999999</v>
+        <v>638.74166528</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08631320782123514</v>
+        <v>0.0862871614306569</v>
       </c>
       <c r="T18">
         <v>0.9350383702230231</v>
       </c>
       <c r="U18">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.146</v>
       </c>
       <c r="W18">
-        <v>0.04697</v>
+        <v>0.045689</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.689412503290873</v>
+        <v>5.848928741700897</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.0801968907595574</v>
+        <v>0.07985564849880847</v>
       </c>
       <c r="C19">
-        <v>7329.497251485178</v>
+        <v>7410.056082880006</v>
       </c>
       <c r="D19">
-        <v>8597.157251485178</v>
+        <v>8677.716082880006</v>
       </c>
       <c r="E19">
         <v>-80.6400000000001</v>
@@ -2851,37 +2851,37 @@
         <v>449.5</v>
       </c>
       <c r="M19">
-        <v>86.23369000000001</v>
+        <v>82.87591800000001</v>
       </c>
       <c r="N19">
-        <v>363.26631</v>
+        <v>366.624082</v>
       </c>
       <c r="O19">
-        <v>53.03688125999999</v>
+        <v>53.527115972</v>
       </c>
       <c r="P19">
-        <v>310.22942874</v>
+        <v>313.096966028</v>
       </c>
       <c r="Q19">
-        <v>630.72942874</v>
+        <v>633.596966028</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08674002501151494</v>
+        <v>0.0867137042154319</v>
       </c>
       <c r="T19">
         <v>0.9448892428506213</v>
       </c>
       <c r="U19">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.146</v>
       </c>
       <c r="W19">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.212579909313865</v>
+        <v>5.423770992195826</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08017052694927729</v>
+        <v>0.07981052939586515</v>
       </c>
       <c r="C20">
-        <v>7246.311675337361</v>
+        <v>7331.788128479154</v>
       </c>
       <c r="D20">
-        <v>8603.75167533736</v>
+        <v>8689.228128479153</v>
       </c>
       <c r="E20">
         <v>9.139999999999645</v>
@@ -2933,37 +2933,37 @@
         <v>449.5</v>
       </c>
       <c r="M20">
-        <v>91.30625999999999</v>
+        <v>87.750972</v>
       </c>
       <c r="N20">
-        <v>358.19374</v>
+        <v>361.749028</v>
       </c>
       <c r="O20">
-        <v>52.29628604</v>
+        <v>52.815358088</v>
       </c>
       <c r="P20">
-        <v>305.89745396</v>
+        <v>308.933669912</v>
       </c>
       <c r="Q20">
-        <v>626.39745396</v>
+        <v>629.433669912</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08717725237716742</v>
+        <v>0.08715065048276238</v>
       </c>
       <c r="T20">
         <v>0.9549803806642585</v>
       </c>
       <c r="U20">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.146</v>
       </c>
       <c r="W20">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.922992136574207</v>
+        <v>5.122450381518281</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08014416313899721</v>
+        <v>0.07976541029292185</v>
       </c>
       <c r="C21">
-        <v>7163.136223421632</v>
+        <v>7253.55075890951</v>
       </c>
       <c r="D21">
-        <v>8610.356223421632</v>
+        <v>8700.77075890951</v>
       </c>
       <c r="E21">
         <v>98.91999999999962</v>
@@ -3015,37 +3015,37 @@
         <v>449.5</v>
       </c>
       <c r="M21">
-        <v>96.37882999999999</v>
+        <v>92.626026</v>
       </c>
       <c r="N21">
-        <v>353.12117</v>
+        <v>356.873974</v>
       </c>
       <c r="O21">
-        <v>51.55569082</v>
+        <v>52.103600204</v>
       </c>
       <c r="P21">
-        <v>301.56547918</v>
+        <v>304.770373796</v>
       </c>
       <c r="Q21">
-        <v>622.06547918</v>
+        <v>625.2703737960001</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08762527548024344</v>
+        <v>0.08759838554681709</v>
       </c>
       <c r="T21">
         <v>0.9653206823745289</v>
       </c>
       <c r="U21">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.146</v>
       </c>
       <c r="W21">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.663887287280827</v>
+        <v>4.852847729859424</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08011779932871708</v>
+        <v>0.07972029118997853</v>
       </c>
       <c r="C22">
-        <v>7079.970919071087</v>
+        <v>7175.344096218403</v>
       </c>
       <c r="D22">
-        <v>8616.970919071087</v>
+        <v>8712.344096218403</v>
       </c>
       <c r="E22">
         <v>188.6999999999998</v>
@@ -3097,37 +3097,37 @@
         <v>449.5</v>
       </c>
       <c r="M22">
-        <v>101.4514</v>
+        <v>97.50108000000002</v>
       </c>
       <c r="N22">
-        <v>348.0486</v>
+        <v>351.99892</v>
       </c>
       <c r="O22">
-        <v>50.81509559999999</v>
+        <v>51.39184231999999</v>
       </c>
       <c r="P22">
-        <v>297.2335044</v>
+        <v>300.60707768</v>
       </c>
       <c r="Q22">
-        <v>617.7335043999999</v>
+        <v>621.10707768</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08808449916089636</v>
+        <v>0.08805731398747317</v>
       </c>
       <c r="T22">
         <v>0.975919491627556</v>
       </c>
       <c r="U22">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.146</v>
       </c>
       <c r="W22">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.430692922916785</v>
+        <v>4.610205343366452</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08034251151843697</v>
+        <v>0.07967517208703521</v>
       </c>
       <c r="C23">
-        <v>6934.13424227318</v>
+        <v>7097.168263103368</v>
       </c>
       <c r="D23">
-        <v>8560.91424227318</v>
+        <v>8723.948263103368</v>
       </c>
       <c r="E23">
         <v>278.4799999999996</v>
@@ -3179,45 +3179,45 @@
         <v>449.5</v>
       </c>
       <c r="M23">
-        <v>109.163502</v>
+        <v>102.376134</v>
       </c>
       <c r="N23">
-        <v>340.336498</v>
+        <v>347.123866</v>
       </c>
       <c r="O23">
-        <v>49.689128708</v>
+        <v>50.680084436</v>
       </c>
       <c r="P23">
-        <v>290.647369292</v>
+        <v>296.443781564</v>
       </c>
       <c r="Q23">
-        <v>611.147369292</v>
+        <v>616.943781564</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08855534875751515</v>
+        <v>0.08852786086966483</v>
       </c>
       <c r="T23">
         <v>0.9867866251654697</v>
       </c>
       <c r="U23">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.146</v>
       </c>
       <c r="W23">
-        <v>0.0494466</v>
+        <v>0.0463722</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.117676620524688</v>
+        <v>4.390671755587098</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08032810370815688</v>
+        <v>0.07981793298409191</v>
       </c>
       <c r="C24">
-        <v>6847.926521517627</v>
+        <v>6970.777023951969</v>
       </c>
       <c r="D24">
-        <v>8564.486521517627</v>
+        <v>8687.337023951968</v>
       </c>
       <c r="E24">
         <v>368.2599999999998</v>
@@ -3261,37 +3261,37 @@
         <v>449.5</v>
       </c>
       <c r="M24">
-        <v>114.361764</v>
+        <v>109.226348</v>
       </c>
       <c r="N24">
-        <v>335.138236</v>
+        <v>340.273652</v>
       </c>
       <c r="O24">
-        <v>48.930182456</v>
+        <v>49.67995319199999</v>
       </c>
       <c r="P24">
-        <v>286.208053544</v>
+        <v>290.593698808</v>
       </c>
       <c r="Q24">
-        <v>606.708053544</v>
+        <v>611.093698808</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08903827142071394</v>
+        <v>0.08901047305652809</v>
       </c>
       <c r="T24">
         <v>0.9979324031530737</v>
       </c>
       <c r="U24">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.146</v>
       </c>
       <c r="W24">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.930509501409929</v>
+        <v>4.11530741648526</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08031369589787676</v>
+        <v>0.0797813538811486</v>
       </c>
       <c r="C25">
-        <v>6761.721783272083</v>
+        <v>6890.348475822128</v>
       </c>
       <c r="D25">
-        <v>8568.061783272084</v>
+        <v>8696.688475822128</v>
       </c>
       <c r="E25">
         <v>458.0399999999997</v>
@@ -3343,37 +3343,37 @@
         <v>449.5</v>
       </c>
       <c r="M25">
-        <v>119.560026</v>
+        <v>114.191182</v>
       </c>
       <c r="N25">
-        <v>329.939974</v>
+        <v>335.308818</v>
       </c>
       <c r="O25">
-        <v>48.171236204</v>
+        <v>48.95508742799999</v>
       </c>
       <c r="P25">
-        <v>281.768737796</v>
+        <v>286.353730572</v>
       </c>
       <c r="Q25">
-        <v>602.268737796</v>
+        <v>606.8537305719999</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08953373752971008</v>
+        <v>0.0895056206248683</v>
       </c>
       <c r="T25">
         <v>1.009367681867628</v>
       </c>
       <c r="U25">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.146</v>
       </c>
       <c r="W25">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.759617783957323</v>
+        <v>3.936381007072857</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08029928808759666</v>
+        <v>0.07974477477820528</v>
       </c>
       <c r="C26">
-        <v>6675.520031273265</v>
+        <v>6809.940082059071</v>
       </c>
       <c r="D26">
-        <v>8571.640031273264</v>
+        <v>8706.06008205907</v>
       </c>
       <c r="E26">
         <v>547.8199999999995</v>
@@ -3425,37 +3425,37 @@
         <v>449.5</v>
       </c>
       <c r="M26">
-        <v>124.758288</v>
+        <v>119.156016</v>
       </c>
       <c r="N26">
-        <v>324.741712</v>
+        <v>330.343984</v>
       </c>
       <c r="O26">
-        <v>47.41228995199999</v>
+        <v>48.23022166399999</v>
       </c>
       <c r="P26">
-        <v>277.329422048</v>
+        <v>282.113762336</v>
       </c>
       <c r="Q26">
-        <v>597.829422048</v>
+        <v>602.613762336</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09004224222052191</v>
+        <v>0.09001379839237537</v>
       </c>
       <c r="T26">
         <v>1.021103888969408</v>
       </c>
       <c r="U26">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.146</v>
       </c>
       <c r="W26">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.602967042959102</v>
+        <v>3.772365131778155</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08028488027731656</v>
+        <v>0.07970819567526197</v>
       </c>
       <c r="C27">
-        <v>6589.321269264139</v>
+        <v>6729.551907888501</v>
       </c>
       <c r="D27">
-        <v>8575.221269264139</v>
+        <v>8715.451907888501</v>
       </c>
       <c r="E27">
         <v>637.5999999999997</v>
@@ -3507,37 +3507,37 @@
         <v>449.5</v>
       </c>
       <c r="M27">
-        <v>129.95655</v>
+        <v>124.12085</v>
       </c>
       <c r="N27">
-        <v>319.54345</v>
+        <v>325.37915</v>
       </c>
       <c r="O27">
-        <v>46.6533437</v>
+        <v>47.5053559</v>
       </c>
       <c r="P27">
-        <v>272.8901063</v>
+        <v>277.8737941</v>
       </c>
       <c r="Q27">
-        <v>593.3901063000001</v>
+        <v>598.3737940999999</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09056430703642207</v>
+        <v>0.09053552756701595</v>
       </c>
       <c r="T27">
         <v>1.033153061593902</v>
       </c>
       <c r="U27">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.146</v>
       </c>
       <c r="W27">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.458848361240738</v>
+        <v>3.621470526507029</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08027047246703645</v>
+        <v>0.07967161657231867</v>
       </c>
       <c r="C28">
-        <v>6503.125500993938</v>
+        <v>6649.184018817879</v>
       </c>
       <c r="D28">
-        <v>8578.805500993938</v>
+        <v>8724.86401881788</v>
       </c>
       <c r="E28">
         <v>727.3799999999999</v>
@@ -3589,37 +3589,37 @@
         <v>449.5</v>
       </c>
       <c r="M28">
-        <v>135.154812</v>
+        <v>129.085684</v>
       </c>
       <c r="N28">
-        <v>314.345188</v>
+        <v>320.414316</v>
       </c>
       <c r="O28">
-        <v>45.894397448</v>
+        <v>46.780490136</v>
       </c>
       <c r="P28">
-        <v>268.450790552</v>
+        <v>273.633825864</v>
       </c>
       <c r="Q28">
-        <v>588.9507905519999</v>
+        <v>594.133825864</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09110048171221141</v>
+        <v>0.09107135753016035</v>
       </c>
       <c r="T28">
         <v>1.045527887532572</v>
       </c>
       <c r="U28">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.146</v>
       </c>
       <c r="W28">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.325815731962248</v>
+        <v>3.482183198564451</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08025606465675633</v>
+        <v>0.07963503746937535</v>
       </c>
       <c r="C29">
-        <v>6416.932730218161</v>
+        <v>6568.83648063796</v>
       </c>
       <c r="D29">
-        <v>8582.39273021816</v>
+        <v>8734.296480637959</v>
       </c>
       <c r="E29">
         <v>817.1599999999996</v>
@@ -3671,37 +3671,37 @@
         <v>449.5</v>
       </c>
       <c r="M29">
-        <v>140.353074</v>
+        <v>134.050518</v>
       </c>
       <c r="N29">
-        <v>309.146926</v>
+        <v>315.449482</v>
       </c>
       <c r="O29">
-        <v>45.135451196</v>
+        <v>46.055624372</v>
       </c>
       <c r="P29">
-        <v>264.011474804</v>
+        <v>269.393857628</v>
       </c>
       <c r="Q29">
-        <v>584.511474804</v>
+        <v>589.893857628</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09165134610514566</v>
+        <v>0.0916218677662676</v>
       </c>
       <c r="T29">
         <v>1.058241749798328</v>
       </c>
       <c r="U29">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.146</v>
       </c>
       <c r="W29">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.202637371519202</v>
+        <v>3.353213450469471</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08024165684647623</v>
+        <v>0.07959845836643203</v>
       </c>
       <c r="C30">
-        <v>6330.742960698577</v>
+        <v>6488.509359424288</v>
       </c>
       <c r="D30">
-        <v>8585.982960698577</v>
+        <v>8743.749359424288</v>
       </c>
       <c r="E30">
         <v>906.9399999999998</v>
@@ -3753,37 +3753,37 @@
         <v>449.5</v>
       </c>
       <c r="M30">
-        <v>145.551336</v>
+        <v>139.015352</v>
       </c>
       <c r="N30">
-        <v>303.948664</v>
+        <v>310.484648</v>
       </c>
       <c r="O30">
-        <v>44.376504944</v>
+        <v>45.330758608</v>
       </c>
       <c r="P30">
-        <v>259.572159056</v>
+        <v>265.153889392</v>
       </c>
       <c r="Q30">
-        <v>580.072159056</v>
+        <v>585.653889392</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09221751228677255</v>
+        <v>0.09218766995337782</v>
       </c>
       <c r="T30">
         <v>1.0713087749048</v>
       </c>
       <c r="U30">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.146</v>
       </c>
       <c r="W30">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.088257465393516</v>
+        <v>3.233455827238419</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08087116503619612</v>
+        <v>0.07956187926348872</v>
       </c>
       <c r="C31">
-        <v>6086.849272573962</v>
+        <v>6408.202721538783</v>
       </c>
       <c r="D31">
-        <v>8431.869272573962</v>
+        <v>8753.222721538783</v>
       </c>
       <c r="E31">
         <v>996.7199999999996</v>
@@ -3835,45 +3835,45 @@
         <v>449.5</v>
       </c>
       <c r="M31">
-        <v>157.51901</v>
+        <v>143.980186</v>
       </c>
       <c r="N31">
-        <v>291.98099</v>
+        <v>305.519814</v>
       </c>
       <c r="O31">
-        <v>42.62922454</v>
+        <v>44.605892844</v>
       </c>
       <c r="P31">
-        <v>249.35176546</v>
+        <v>260.913921156</v>
       </c>
       <c r="Q31">
-        <v>569.85176546</v>
+        <v>581.413921156</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09279962681154386</v>
+        <v>0.0927694102302658</v>
       </c>
       <c r="T31">
         <v>1.084743885225538</v>
       </c>
       <c r="U31">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.146</v>
       </c>
       <c r="W31">
-        <v>0.051667</v>
+        <v>0.0472262</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.853623826102005</v>
+        <v>3.121957350437094</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08087896122591602</v>
+        <v>0.0795253001605454</v>
       </c>
       <c r="C32">
-        <v>5995.195315927442</v>
+        <v>6327.91663363127</v>
       </c>
       <c r="D32">
-        <v>8429.995315927441</v>
+        <v>8762.716633631269</v>
       </c>
       <c r="E32">
         <v>1086.5</v>
@@ -3917,45 +3917,45 @@
         <v>449.5</v>
       </c>
       <c r="M32">
-        <v>162.9507</v>
+        <v>148.94502</v>
       </c>
       <c r="N32">
-        <v>286.5493</v>
+        <v>300.55498</v>
       </c>
       <c r="O32">
-        <v>41.8361978</v>
+        <v>43.88102708</v>
       </c>
       <c r="P32">
-        <v>244.7131022</v>
+        <v>256.67395292</v>
       </c>
       <c r="Q32">
-        <v>565.2131022</v>
+        <v>577.17395292</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09339837317988003</v>
+        <v>0.09336777165792201</v>
       </c>
       <c r="T32">
         <v>1.098562855841155</v>
       </c>
       <c r="U32">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.146</v>
       </c>
       <c r="W32">
-        <v>0.051667</v>
+        <v>0.0472262</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.758503031898605</v>
+        <v>3.017892105422524</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08088675741563592</v>
+        <v>0.08015057105760208</v>
       </c>
       <c r="C33">
-        <v>5903.542192057877</v>
+        <v>6078.63210367815</v>
       </c>
       <c r="D33">
-        <v>8428.122192057877</v>
+        <v>8603.21210367815</v>
       </c>
       <c r="E33">
         <v>1176.28</v>
@@ -3999,37 +3999,37 @@
         <v>449.5</v>
       </c>
       <c r="M33">
-        <v>168.38239</v>
+        <v>160.867804</v>
       </c>
       <c r="N33">
-        <v>281.11761</v>
+        <v>288.632196</v>
       </c>
       <c r="O33">
-        <v>41.04317106</v>
+        <v>42.140300616</v>
       </c>
       <c r="P33">
-        <v>240.07443894</v>
+        <v>246.491895384</v>
       </c>
       <c r="Q33">
-        <v>560.5744389400001</v>
+        <v>566.991895384</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09401447451541438</v>
+        <v>0.0939834768950755</v>
       </c>
       <c r="T33">
         <v>1.112782376329688</v>
       </c>
       <c r="U33">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.146</v>
       </c>
       <c r="W33">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.669519063127682</v>
+        <v>2.794219780609425</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08089455360535582</v>
+        <v>0.08013534195465877</v>
       </c>
       <c r="C34">
-        <v>5811.889900410272</v>
+        <v>5992.667973720833</v>
       </c>
       <c r="D34">
-        <v>8426.249900410272</v>
+        <v>8607.027973720833</v>
       </c>
       <c r="E34">
         <v>1266.06</v>
@@ -4081,37 +4081,37 @@
         <v>449.5</v>
       </c>
       <c r="M34">
-        <v>173.81408</v>
+        <v>166.057088</v>
       </c>
       <c r="N34">
-        <v>275.68592</v>
+        <v>283.442912</v>
       </c>
       <c r="O34">
-        <v>40.25014432</v>
+        <v>41.38266515199999</v>
       </c>
       <c r="P34">
-        <v>235.43577568</v>
+        <v>242.060246848</v>
       </c>
       <c r="Q34">
-        <v>555.93577568</v>
+        <v>562.560246848</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09464869647846444</v>
+        <v>0.09461729110979232</v>
       </c>
       <c r="T34">
         <v>1.127420118009061</v>
       </c>
       <c r="U34">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V34">
         <v>0.146</v>
       </c>
       <c r="W34">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.586096592404942</v>
+        <v>2.70690041246538</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08090234979507568</v>
+        <v>0.08012011285171547</v>
       </c>
       <c r="C35">
-        <v>5720.238440430125</v>
+        <v>5906.707230248747</v>
       </c>
       <c r="D35">
-        <v>8424.378440430124</v>
+        <v>8610.847230248746</v>
       </c>
       <c r="E35">
         <v>1355.84</v>
@@ -4163,37 +4163,37 @@
         <v>449.5</v>
       </c>
       <c r="M35">
-        <v>179.24577</v>
+        <v>171.246372</v>
       </c>
       <c r="N35">
-        <v>270.25423</v>
+        <v>278.2536279999999</v>
       </c>
       <c r="O35">
-        <v>39.45711758</v>
+        <v>40.62502968799999</v>
       </c>
       <c r="P35">
-        <v>230.79711242</v>
+        <v>237.628598312</v>
       </c>
       <c r="Q35">
-        <v>551.2971124200001</v>
+        <v>558.1285983119999</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09530185044041149</v>
+        <v>0.09527002515181413</v>
       </c>
       <c r="T35">
         <v>1.14249480720125</v>
       </c>
       <c r="U35">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.146</v>
       </c>
       <c r="W35">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.507730028998732</v>
+        <v>2.624873127239156</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08169411798479559</v>
+        <v>0.08010488374877214</v>
       </c>
       <c r="C36">
-        <v>5444.629807724337</v>
+        <v>5820.749877772027</v>
       </c>
       <c r="D36">
-        <v>8238.549807724337</v>
+        <v>8614.669877772027</v>
       </c>
       <c r="E36">
         <v>1445.62</v>
@@ -4245,45 +4245,45 @@
         <v>449.5</v>
       </c>
       <c r="M36">
-        <v>192.9192640000001</v>
+        <v>176.4356560000001</v>
       </c>
       <c r="N36">
-        <v>256.5807359999999</v>
+        <v>273.0643439999999</v>
       </c>
       <c r="O36">
-        <v>37.46078745599999</v>
+        <v>39.86739422399999</v>
       </c>
       <c r="P36">
-        <v>219.119948544</v>
+        <v>233.196949776</v>
       </c>
       <c r="Q36">
-        <v>539.619948544</v>
+        <v>553.696949776</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09597479694666</v>
+        <v>0.09594253901329114</v>
       </c>
       <c r="T36">
         <v>1.158026305156839</v>
       </c>
       <c r="U36">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.146</v>
       </c>
       <c r="W36">
-        <v>0.0539728</v>
+        <v>0.0493612</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.329990228451213</v>
+        <v>2.547670976438004</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08172497217451548</v>
+        <v>0.08113580464582884</v>
       </c>
       <c r="C37">
-        <v>5347.774122945809</v>
+        <v>5479.637177490972</v>
       </c>
       <c r="D37">
-        <v>8231.474122945809</v>
+        <v>8363.337177490972</v>
       </c>
       <c r="E37">
         <v>1535.4</v>
@@ -4327,37 +4327,37 @@
         <v>449.5</v>
       </c>
       <c r="M37">
-        <v>198.59336</v>
+        <v>192.62299</v>
       </c>
       <c r="N37">
-        <v>250.90664</v>
+        <v>256.87701</v>
       </c>
       <c r="O37">
-        <v>36.63236944</v>
+        <v>37.50404346</v>
       </c>
       <c r="P37">
-        <v>214.27427056</v>
+        <v>219.37296654</v>
       </c>
       <c r="Q37">
-        <v>534.77427056</v>
+        <v>539.87296654</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.0966684494992546</v>
+        <v>0.09663574560896744</v>
       </c>
       <c r="T37">
         <v>1.174035695357216</v>
       </c>
       <c r="U37">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V37">
         <v>0.146</v>
       </c>
       <c r="W37">
-        <v>0.0539728</v>
+        <v>0.0523502</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.263419079066893</v>
+        <v>2.333573993426226</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08320079436423539</v>
+        <v>0.08115046554288552</v>
       </c>
       <c r="C38">
-        <v>4933.183049511354</v>
+        <v>5386.388651022467</v>
       </c>
       <c r="D38">
-        <v>7906.663049511353</v>
+        <v>8359.868651022467</v>
       </c>
       <c r="E38">
         <v>1625.18</v>
@@ -4409,45 +4409,45 @@
         <v>449.5</v>
       </c>
       <c r="M38">
-        <v>219.458232</v>
+        <v>198.126504</v>
       </c>
       <c r="N38">
-        <v>230.041768</v>
+        <v>251.373496</v>
       </c>
       <c r="O38">
-        <v>33.586098128</v>
+        <v>36.700530416</v>
       </c>
       <c r="P38">
-        <v>196.455669872</v>
+        <v>214.672965584</v>
       </c>
       <c r="Q38">
-        <v>516.955669872</v>
+        <v>535.1729655840001</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.0973837786941178</v>
+        <v>0.09735061491075864</v>
       </c>
       <c r="T38">
         <v>1.190545379001354</v>
       </c>
       <c r="U38">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V38">
         <v>0.146</v>
       </c>
       <c r="W38">
-        <v>0.0579866</v>
+        <v>0.0523502</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.048225741652744</v>
+        <v>2.268752493608831</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08621040055395528</v>
+        <v>0.08204987043994222</v>
       </c>
       <c r="C39">
-        <v>4254.546177823902</v>
+        <v>5089.189790976125</v>
       </c>
       <c r="D39">
-        <v>7317.806177823903</v>
+        <v>8152.449790976125</v>
       </c>
       <c r="E39">
         <v>1714.96</v>
@@ -4491,45 +4491,45 @@
         <v>449.5</v>
       </c>
       <c r="M39">
-        <v>256.447592</v>
+        <v>212.931226</v>
       </c>
       <c r="N39">
-        <v>193.052408</v>
+        <v>236.568774</v>
       </c>
       <c r="O39">
-        <v>28.185651568</v>
+        <v>34.539041004</v>
       </c>
       <c r="P39">
-        <v>164.866756432</v>
+        <v>202.029732996</v>
       </c>
       <c r="Q39">
-        <v>485.366756432</v>
+        <v>522.529732996</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09812181675230996</v>
+        <v>0.09808817847609874</v>
       </c>
       <c r="T39">
         <v>1.207579179586576</v>
       </c>
       <c r="U39">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V39">
         <v>0.146</v>
       </c>
       <c r="W39">
-        <v>0.0659288</v>
+        <v>0.0547414</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>1.75279477765578</v>
+        <v>2.111010247036289</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08788605874367517</v>
+        <v>0.0820884433369989</v>
       </c>
       <c r="C40">
-        <v>3873.40741868383</v>
+        <v>4990.744122856202</v>
       </c>
       <c r="D40">
-        <v>7026.44741868383</v>
+        <v>8143.784122856202</v>
       </c>
       <c r="E40">
         <v>1804.74</v>
@@ -4573,45 +4573,45 @@
         <v>449.5</v>
       </c>
       <c r="M40">
-        <v>279.413316</v>
+        <v>218.686124</v>
       </c>
       <c r="N40">
-        <v>170.086684</v>
+        <v>230.813876</v>
       </c>
       <c r="O40">
-        <v>24.832655864</v>
+        <v>33.698825896</v>
       </c>
       <c r="P40">
-        <v>145.254028136</v>
+        <v>197.115050104</v>
       </c>
       <c r="Q40">
-        <v>465.754028136</v>
+        <v>517.615050104</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.09888366248979866</v>
+        <v>0.09884953441451434</v>
       </c>
       <c r="T40">
         <v>1.225162457610031</v>
       </c>
       <c r="U40">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V40">
         <v>0.146</v>
       </c>
       <c r="W40">
-        <v>0.06994259999999999</v>
+        <v>0.0547414</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>1.608727910447904</v>
+        <v>2.055457345798493</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08807661093339506</v>
+        <v>0.08212701623405558</v>
       </c>
       <c r="C41">
-        <v>3751.9573081423</v>
+        <v>4892.316857564751</v>
       </c>
       <c r="D41">
-        <v>6994.777308142299</v>
+        <v>8135.13685756475</v>
       </c>
       <c r="E41">
         <v>1894.52</v>
@@ -4655,45 +4655,45 @@
         <v>449.5</v>
       </c>
       <c r="M41">
-        <v>286.766298</v>
+        <v>224.441022</v>
       </c>
       <c r="N41">
-        <v>162.733702</v>
+        <v>225.058978</v>
       </c>
       <c r="O41">
-        <v>23.759120492</v>
+        <v>32.85861078799999</v>
       </c>
       <c r="P41">
-        <v>138.974581508</v>
+        <v>192.200367212</v>
       </c>
       <c r="Q41">
-        <v>459.474581508</v>
+        <v>512.7003672119999</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09967048677605748</v>
+        <v>0.09963585284271406</v>
       </c>
       <c r="T41">
         <v>1.243322236552288</v>
       </c>
       <c r="U41">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.146</v>
       </c>
       <c r="W41">
-        <v>0.06994259999999999</v>
+        <v>0.0547414</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>1.567478476846676</v>
+        <v>2.002753311290839</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08826716312311496</v>
+        <v>0.08616230913111227</v>
       </c>
       <c r="C42">
-        <v>3630.791408198724</v>
+        <v>3989.212231580684</v>
       </c>
       <c r="D42">
-        <v>6963.391408198724</v>
+        <v>7321.812231580684</v>
       </c>
       <c r="E42">
         <v>1984.3</v>
@@ -4737,37 +4737,37 @@
         <v>449.5</v>
       </c>
       <c r="M42">
-        <v>294.11928</v>
+        <v>272.2129600000001</v>
       </c>
       <c r="N42">
-        <v>155.38072</v>
+        <v>177.2870399999999</v>
       </c>
       <c r="O42">
-        <v>22.68558512</v>
+        <v>25.88390783999999</v>
       </c>
       <c r="P42">
-        <v>132.69513488</v>
+        <v>151.40313216</v>
       </c>
       <c r="Q42">
-        <v>453.19513488</v>
+        <v>471.9031321599999</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1004835385385249</v>
+        <v>0.1004483818851871</v>
       </c>
       <c r="T42">
         <v>1.262087341459287</v>
       </c>
       <c r="U42">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V42">
         <v>0.146</v>
       </c>
       <c r="W42">
-        <v>0.06994259999999999</v>
+        <v>0.0647332</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.528291514925509</v>
+        <v>1.651280673778353</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1062804891581739</v>
+        <v>0.08630080002816896</v>
       </c>
       <c r="C43">
-        <v>1467.055964194856</v>
+        <v>3874.39558185211</v>
       </c>
       <c r="D43">
-        <v>4889.435964194856</v>
+        <v>7296.77558185211</v>
       </c>
       <c r="E43">
         <v>2074.08</v>
@@ -4819,45 +4819,45 @@
         <v>449.5</v>
       </c>
       <c r="M43">
-        <v>481.840282</v>
+        <v>279.0182840000001</v>
       </c>
       <c r="N43">
-        <v>-32.340282</v>
+        <v>170.4817159999999</v>
       </c>
       <c r="O43">
-        <v>-4.721681172</v>
+        <v>24.89033053599999</v>
       </c>
       <c r="P43">
-        <v>-27.618600828</v>
+        <v>145.591385464</v>
       </c>
       <c r="Q43">
-        <v>292.881399172</v>
+        <v>466.0913854639999</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1015614344786475</v>
+        <v>0.1012884542850321</v>
       </c>
       <c r="T43">
-        <v>1.286965007714929</v>
+        <v>1.28148855161737</v>
       </c>
       <c r="U43">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
-        <v>0.1362007338356987</v>
+        <v>0.146</v>
       </c>
       <c r="W43">
-        <v>0.113071323940907</v>
+        <v>0.0647332</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.932881738600676</v>
+        <v>1.611005535393515</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1071314891581739</v>
+        <v>0.08643929092522565</v>
       </c>
       <c r="C44">
-        <v>1309.433000284443</v>
+        <v>3759.749572309489</v>
       </c>
       <c r="D44">
-        <v>4821.593000284442</v>
+        <v>7271.909572309489</v>
       </c>
       <c r="E44">
         <v>2163.86</v>
@@ -4901,45 +4901,45 @@
         <v>449.5</v>
       </c>
       <c r="M44">
-        <v>493.5924839999999</v>
+        <v>285.823608</v>
       </c>
       <c r="N44">
-        <v>-44.0924839999999</v>
+        <v>163.676392</v>
       </c>
       <c r="O44">
-        <v>-6.437502663999985</v>
+        <v>23.896753232</v>
       </c>
       <c r="P44">
-        <v>-37.65498133599991</v>
+        <v>139.779638768</v>
       </c>
       <c r="Q44">
-        <v>282.8450186640001</v>
+        <v>460.279638768</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1025228385213828</v>
+        <v>0.1021574946986649</v>
       </c>
       <c r="T44">
-        <v>1.309154059572083</v>
+        <v>1.301558769022284</v>
       </c>
       <c r="U44">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
-        <v>0.132957859220563</v>
+        <v>0.146</v>
       </c>
       <c r="W44">
-        <v>0.1134958162280283</v>
+        <v>0.0647332</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.9106702686339934</v>
+        <v>1.572648260741289</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1079824891581739</v>
+        <v>0.08657778182228233</v>
       </c>
       <c r="C45">
-        <v>1153.666969509689</v>
+        <v>3645.272464350715</v>
       </c>
       <c r="D45">
-        <v>4755.606969509688</v>
+        <v>7247.212464350715</v>
       </c>
       <c r="E45">
         <v>2253.639999999999</v>
@@ -4983,45 +4983,45 @@
         <v>449.5</v>
       </c>
       <c r="M45">
-        <v>505.344686</v>
+        <v>292.628932</v>
       </c>
       <c r="N45">
-        <v>-55.84468599999997</v>
+        <v>156.871068</v>
       </c>
       <c r="O45">
-        <v>-8.153324155999995</v>
+        <v>22.903175928</v>
       </c>
       <c r="P45">
-        <v>-47.69136184399997</v>
+        <v>133.967892072</v>
       </c>
       <c r="Q45">
-        <v>272.808638156</v>
+        <v>454.467892072</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1035179760393018</v>
+        <v>0.10305702775839</v>
       </c>
       <c r="T45">
-        <v>1.332121674652295</v>
+        <v>1.322333204581756</v>
       </c>
       <c r="U45">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V45">
-        <v>0.1298658159828755</v>
+        <v>0.146</v>
       </c>
       <c r="W45">
-        <v>0.1139005646878416</v>
+        <v>0.0647332</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.8894918902936678</v>
+        <v>1.536075045375212</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1088334891581739</v>
+        <v>0.08671627271933902</v>
       </c>
       <c r="C46">
-        <v>999.682661845593</v>
+        <v>3530.962542912541</v>
       </c>
       <c r="D46">
-        <v>4691.402661845593</v>
+        <v>7222.682542912541</v>
       </c>
       <c r="E46">
         <v>2343.42</v>
@@ -5065,45 +5065,45 @@
         <v>449.5</v>
       </c>
       <c r="M46">
-        <v>517.0968879999999</v>
+        <v>299.4342560000001</v>
       </c>
       <c r="N46">
-        <v>-67.59688799999992</v>
+        <v>150.0657439999999</v>
       </c>
       <c r="O46">
-        <v>-9.869145647999988</v>
+        <v>21.90959862399999</v>
       </c>
       <c r="P46">
-        <v>-57.72774235199994</v>
+        <v>128.156145376</v>
       </c>
       <c r="Q46">
-        <v>262.772257648</v>
+        <v>448.6561453759999</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1045486541828607</v>
+        <v>0.1039886869988197</v>
       </c>
       <c r="T46">
-        <v>1.355909561699658</v>
+        <v>1.343849584268352</v>
       </c>
       <c r="U46">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V46">
-        <v>0.1269143201650829</v>
+        <v>0.146</v>
       </c>
       <c r="W46">
-        <v>0.1142869154903906</v>
+        <v>0.0647332</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.8692761655142665</v>
+        <v>1.501164248889412</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1096844891581739</v>
+        <v>0.1039266657614567</v>
       </c>
       <c r="C47">
-        <v>847.4088747332685</v>
+        <v>1302.659650646583</v>
       </c>
       <c r="D47">
-        <v>4628.908874733268</v>
+        <v>5084.159650646583</v>
       </c>
       <c r="E47">
         <v>2433.2</v>
@@ -5147,37 +5147,37 @@
         <v>449.5</v>
       </c>
       <c r="M47">
-        <v>528.8490899999999</v>
+        <v>479.15586</v>
       </c>
       <c r="N47">
-        <v>-79.34908999999993</v>
+        <v>-29.65586000000002</v>
       </c>
       <c r="O47">
-        <v>-11.58496713999999</v>
+        <v>-4.329755560000002</v>
       </c>
       <c r="P47">
-        <v>-67.76412285999994</v>
+        <v>-25.32610444000002</v>
       </c>
       <c r="Q47">
-        <v>252.7358771400001</v>
+        <v>295.17389556</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.10561681153164</v>
+        <v>0.1052116780830633</v>
       </c>
       <c r="T47">
-        <v>1.38056246282147</v>
+        <v>1.37209418205689</v>
       </c>
       <c r="U47">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V47">
-        <v>0.1240940019391922</v>
+        <v>0.136963784602363</v>
       </c>
       <c r="W47">
-        <v>0.1146560951461597</v>
+        <v>0.1023560951461598</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8499589173917271</v>
+        <v>0.9381081137148151</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1105354891581739</v>
+        <v>0.1046546657614567</v>
       </c>
       <c r="C48">
-        <v>696.7781496731222</v>
+        <v>1149.991378701036</v>
       </c>
       <c r="D48">
-        <v>4568.058149673122</v>
+        <v>5021.271378701035</v>
       </c>
       <c r="E48">
         <v>2522.98</v>
@@ -5229,37 +5229,37 @@
         <v>449.5</v>
       </c>
       <c r="M48">
-        <v>540.6012919999999</v>
+        <v>489.803768</v>
       </c>
       <c r="N48">
-        <v>-91.10129199999994</v>
+        <v>-40.30376800000005</v>
       </c>
       <c r="O48">
-        <v>-13.30078863199999</v>
+        <v>-5.884350128000007</v>
       </c>
       <c r="P48">
-        <v>-77.80050336799995</v>
+        <v>-34.41941787200004</v>
       </c>
       <c r="Q48">
-        <v>242.699496632</v>
+        <v>286.0805821279999</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1067245302637074</v>
+        <v>0.1063118943438608</v>
       </c>
       <c r="T48">
-        <v>1.406128434355201</v>
+        <v>1.397503333576463</v>
       </c>
       <c r="U48">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V48">
-        <v>0.1213963062448619</v>
+        <v>0.1339863110240507</v>
       </c>
       <c r="W48">
-        <v>0.1150092235125476</v>
+        <v>0.1027092235125476</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8314815496223418</v>
+        <v>0.9177144590688407</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1113864891581739</v>
+        <v>0.1053826657614567</v>
       </c>
       <c r="C49">
-        <v>547.7265293246601</v>
+        <v>998.8598846552795</v>
       </c>
       <c r="D49">
-        <v>4508.78652932466</v>
+        <v>4959.919884655279</v>
       </c>
       <c r="E49">
         <v>2612.759999999999</v>
@@ -5311,37 +5311,37 @@
         <v>449.5</v>
       </c>
       <c r="M49">
-        <v>552.353494</v>
+        <v>500.451676</v>
       </c>
       <c r="N49">
-        <v>-102.853494</v>
+        <v>-50.95167600000002</v>
       </c>
       <c r="O49">
-        <v>-15.01661012399999</v>
+        <v>-7.438944696000003</v>
       </c>
       <c r="P49">
-        <v>-87.83688387599996</v>
+        <v>-43.51273130400002</v>
       </c>
       <c r="Q49">
-        <v>232.6631161240001</v>
+        <v>276.987268696</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1078740497026453</v>
+        <v>0.1074536281994054</v>
       </c>
       <c r="T49">
-        <v>1.432659159531714</v>
+        <v>1.423871321002433</v>
       </c>
       <c r="U49">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V49">
-        <v>0.1188134061119925</v>
+        <v>0.1311355384490709</v>
       </c>
       <c r="W49">
-        <v>0.1153473251399402</v>
+        <v>0.1030473251399402</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8137904528218664</v>
+        <v>0.8981886195141846</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1537550169542525</v>
+        <v>0.1061106657614568</v>
       </c>
       <c r="C50">
-        <v>-1311.592791624441</v>
+        <v>849.2095179392036</v>
       </c>
       <c r="D50">
-        <v>2739.247208375558</v>
+        <v>4900.049517939203</v>
       </c>
       <c r="E50">
         <v>2702.539999999999</v>
@@ -5393,45 +5393,45 @@
         <v>449.5</v>
       </c>
       <c r="M50">
-        <v>929.977152</v>
+        <v>511.099584</v>
       </c>
       <c r="N50">
-        <v>-480.477152</v>
+        <v>-61.59958399999999</v>
       </c>
       <c r="O50">
-        <v>-70.149664192</v>
+        <v>-8.993539263999999</v>
       </c>
       <c r="P50">
-        <v>-410.3274878080001</v>
+        <v>-52.60604473599999</v>
       </c>
       <c r="Q50">
-        <v>-89.82748780800006</v>
+        <v>267.893955264</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1105399502663089</v>
+        <v>0.1086392748955478</v>
       </c>
       <c r="T50">
-        <v>1.494187719038131</v>
+        <v>1.451253461790942</v>
       </c>
       <c r="U50">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V50">
-        <v>0.07056840037291583</v>
+        <v>0.1284035480647153</v>
       </c>
       <c r="W50">
-        <v>0.2005713391995248</v>
+        <v>0.1033713391995248</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.48334520803367</v>
+        <v>0.8794763566076391</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1554550169542525</v>
+        <v>0.1068386657614567</v>
       </c>
       <c r="C51">
-        <v>-1443.839797545213</v>
+        <v>700.9872829303213</v>
       </c>
       <c r="D51">
-        <v>2696.780202454787</v>
+        <v>4841.607282930321</v>
       </c>
       <c r="E51">
         <v>2792.32</v>
@@ -5475,45 +5475,45 @@
         <v>449.5</v>
       </c>
       <c r="M51">
-        <v>949.3516760000001</v>
+        <v>521.7474920000001</v>
       </c>
       <c r="N51">
-        <v>-499.8516760000001</v>
+        <v>-72.24749200000008</v>
       </c>
       <c r="O51">
-        <v>-72.97834469600001</v>
+        <v>-10.54813383200001</v>
       </c>
       <c r="P51">
-        <v>-426.8733313040001</v>
+        <v>-61.69935816800007</v>
       </c>
       <c r="Q51">
-        <v>-106.3733313040001</v>
+        <v>258.8006418319999</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1118093610558444</v>
+        <v>0.1098714175405585</v>
       </c>
       <c r="T51">
-        <v>1.523485517450643</v>
+        <v>1.479709412022137</v>
       </c>
       <c r="U51">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V51">
-        <v>0.06912822893673386</v>
+        <v>0.125783067491966</v>
       </c>
       <c r="W51">
-        <v>0.2008821281954528</v>
+        <v>0.1036821281954528</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.4734810201146155</v>
+        <v>0.8615278595340137</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1571550169542525</v>
+        <v>0.1075666657614567</v>
       </c>
       <c r="C52">
-        <v>-1574.790159416349</v>
+        <v>554.1426824938062</v>
       </c>
       <c r="D52">
-        <v>2655.609840583651</v>
+        <v>4784.542682493806</v>
       </c>
       <c r="E52">
         <v>2882.099999999999</v>
@@ -5557,45 +5557,45 @@
         <v>449.5</v>
       </c>
       <c r="M52">
-        <v>968.7262000000001</v>
+        <v>532.3954</v>
       </c>
       <c r="N52">
-        <v>-519.2262000000001</v>
+        <v>-82.8954</v>
       </c>
       <c r="O52">
-        <v>-75.8070252</v>
+        <v>-12.1027284</v>
       </c>
       <c r="P52">
-        <v>-443.4191748000001</v>
+        <v>-70.79267159999999</v>
       </c>
       <c r="Q52">
-        <v>-122.9191748000001</v>
+        <v>249.7073284</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1131295482769613</v>
+        <v>0.1111528458913697</v>
       </c>
       <c r="T52">
-        <v>1.553955227799656</v>
+        <v>1.509303600262579</v>
       </c>
       <c r="U52">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V52">
-        <v>0.06774566435799918</v>
+        <v>0.1232674061421267</v>
       </c>
       <c r="W52">
-        <v>0.2011804856315438</v>
+        <v>0.1039804856315438</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.4640113997123232</v>
+        <v>0.8442973023433336</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1588550169542525</v>
+        <v>0.1082946657614567</v>
       </c>
       <c r="C53">
-        <v>-1704.502369862339</v>
+        <v>408.6275724581637</v>
       </c>
       <c r="D53">
-        <v>2615.677630137661</v>
+        <v>4728.807572458163</v>
       </c>
       <c r="E53">
         <v>2971.879999999999</v>
@@ -5639,45 +5639,45 @@
         <v>449.5</v>
       </c>
       <c r="M53">
-        <v>988.100724</v>
+        <v>543.043308</v>
       </c>
       <c r="N53">
-        <v>-538.600724</v>
+        <v>-93.54330800000002</v>
       </c>
       <c r="O53">
-        <v>-78.635705704</v>
+        <v>-13.657322968</v>
       </c>
       <c r="P53">
-        <v>-459.965018296</v>
+        <v>-79.88598503200002</v>
       </c>
       <c r="Q53">
-        <v>-139.465018296</v>
+        <v>240.614014968</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1145036206907768</v>
+        <v>0.1124865774401732</v>
       </c>
       <c r="T53">
-        <v>1.585668599795567</v>
+        <v>1.540105714553653</v>
       </c>
       <c r="U53">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V53">
-        <v>0.06641731799803842</v>
+        <v>0.1208503981785556</v>
       </c>
       <c r="W53">
-        <v>0.2014671427760233</v>
+        <v>0.1042671427760233</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.454913136972866</v>
+        <v>0.827742453277778</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1605550169542525</v>
+        <v>0.1090226657614567</v>
       </c>
       <c r="C54">
-        <v>-1833.031455429611</v>
+        <v>264.396026145032</v>
       </c>
       <c r="D54">
-        <v>2576.928544570389</v>
+        <v>4674.356026145032</v>
       </c>
       <c r="E54">
         <v>3061.66</v>
@@ -5721,45 +5721,45 @@
         <v>449.5</v>
       </c>
       <c r="M54">
-        <v>1007.475248</v>
+        <v>553.6912160000001</v>
       </c>
       <c r="N54">
-        <v>-557.9752480000002</v>
+        <v>-104.1912160000001</v>
       </c>
       <c r="O54">
-        <v>-81.46438620800002</v>
+        <v>-15.21191753600001</v>
       </c>
       <c r="P54">
-        <v>-476.5108617920002</v>
+        <v>-88.97929846400005</v>
       </c>
       <c r="Q54">
-        <v>-156.0108617920002</v>
+        <v>231.5207015359999</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1159349461218347</v>
+        <v>0.1138758811368434</v>
       </c>
       <c r="T54">
-        <v>1.618703362291308</v>
+        <v>1.57219125027352</v>
       </c>
       <c r="U54">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V54">
-        <v>0.06514006188269152</v>
+        <v>0.1185263520597372</v>
       </c>
       <c r="W54">
-        <v>0.2017427746457152</v>
+        <v>0.1045427746457152</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.4461648074156953</v>
+        <v>0.8118243291762821</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1622550169542525</v>
+        <v>0.154195260258069</v>
       </c>
       <c r="C55">
-        <v>-1960.429229574031</v>
+        <v>-1773.37310916522</v>
       </c>
       <c r="D55">
-        <v>2539.310770425969</v>
+        <v>2726.36689083478</v>
       </c>
       <c r="E55">
         <v>3151.44</v>
@@ -5803,37 +5803,37 @@
         <v>449.5</v>
       </c>
       <c r="M55">
-        <v>1026.849772</v>
+        <v>955.4746720000001</v>
       </c>
       <c r="N55">
-        <v>-577.349772</v>
+        <v>-505.9746720000001</v>
       </c>
       <c r="O55">
-        <v>-84.293066712</v>
+        <v>-73.872302112</v>
       </c>
       <c r="P55">
-        <v>-493.056705288</v>
+        <v>-432.1023698880001</v>
       </c>
       <c r="Q55">
-        <v>-172.556705288</v>
+        <v>-111.6023698880001</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1174271790180439</v>
+        <v>0.1171936541325471</v>
       </c>
       <c r="T55">
-        <v>1.653143859361336</v>
+        <v>1.648814183199702</v>
       </c>
       <c r="U55">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.06391100411131999</v>
+        <v>0.0686852325060899</v>
       </c>
       <c r="W55">
-        <v>0.2020080053127772</v>
+        <v>0.1870080053127771</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4377466035021917</v>
+        <v>0.4704467979869172</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1639550169542525</v>
+        <v>0.155745260258069</v>
       </c>
       <c r="C56">
-        <v>-2086.744523808685</v>
+        <v>-1901.589224290827</v>
       </c>
       <c r="D56">
-        <v>2502.775476191315</v>
+        <v>2687.930775709173</v>
       </c>
       <c r="E56">
         <v>3241.219999999999</v>
@@ -5885,37 +5885,37 @@
         <v>449.5</v>
       </c>
       <c r="M56">
-        <v>1046.224296</v>
+        <v>973.5024960000001</v>
       </c>
       <c r="N56">
-        <v>-596.7242960000001</v>
+        <v>-524.0024960000001</v>
       </c>
       <c r="O56">
-        <v>-87.121747216</v>
+        <v>-76.504364416</v>
       </c>
       <c r="P56">
-        <v>-509.6025487840001</v>
+        <v>-447.4981315840001</v>
       </c>
       <c r="Q56">
-        <v>-189.1025487840001</v>
+        <v>-126.9981315840001</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1189842916053927</v>
+        <v>0.1187456900919503</v>
       </c>
       <c r="T56">
-        <v>1.689081769347452</v>
+        <v>1.684657969791</v>
       </c>
       <c r="U56">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.06272746699814739</v>
+        <v>0.06741328375597713</v>
       </c>
       <c r="W56">
-        <v>0.2022634126217998</v>
+        <v>0.1872634126217998</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4296401849188178</v>
+        <v>0.4617348202464188</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1656550169542526</v>
+        <v>0.157295260258069</v>
       </c>
       <c r="C57">
-        <v>-2212.023399180329</v>
+        <v>-2028.736666572282</v>
       </c>
       <c r="D57">
-        <v>2467.276600819671</v>
+        <v>2650.563333427719</v>
       </c>
       <c r="E57">
         <v>3331</v>
@@ -5967,37 +5967,37 @@
         <v>449.5</v>
       </c>
       <c r="M57">
-        <v>1065.59882</v>
+        <v>991.5303200000002</v>
       </c>
       <c r="N57">
-        <v>-616.0988200000002</v>
+        <v>-542.0303200000002</v>
       </c>
       <c r="O57">
-        <v>-89.95042772000002</v>
+        <v>-79.13642672000002</v>
       </c>
       <c r="P57">
-        <v>-526.1483922800002</v>
+        <v>-462.8938932800002</v>
       </c>
       <c r="Q57">
-        <v>-205.6483922800002</v>
+        <v>-142.3938932800002</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1206106091966237</v>
+        <v>0.120366705427327</v>
       </c>
       <c r="T57">
-        <v>1.726616919777396</v>
+        <v>1.722094813564134</v>
       </c>
       <c r="U57">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.06158696759818107</v>
+        <v>0.06618758768768662</v>
       </c>
       <c r="W57">
-        <v>0.2025095323923125</v>
+        <v>0.1875095323923125</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.421828545193021</v>
+        <v>0.4533396416964838</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1673550169542525</v>
+        <v>0.158845260258069</v>
       </c>
       <c r="C58">
-        <v>-2336.309340000295</v>
+        <v>-2154.859394763044</v>
       </c>
       <c r="D58">
-        <v>2432.770659999705</v>
+        <v>2614.220605236957</v>
       </c>
       <c r="E58">
         <v>3420.78</v>
@@ -6049,37 +6049,37 @@
         <v>449.5</v>
       </c>
       <c r="M58">
-        <v>1084.973344</v>
+        <v>1009.558144</v>
       </c>
       <c r="N58">
-        <v>-635.4733440000002</v>
+        <v>-560.0581440000001</v>
       </c>
       <c r="O58">
-        <v>-92.77910822400003</v>
+        <v>-81.768489024</v>
       </c>
       <c r="P58">
-        <v>-542.6942357760001</v>
+        <v>-478.2896549760001</v>
       </c>
       <c r="Q58">
-        <v>-222.1942357760001</v>
+        <v>-157.7896549760001</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1223108503147287</v>
+        <v>0.122061403277948</v>
       </c>
       <c r="T58">
-        <v>1.7658582134087</v>
+        <v>1.761233332054227</v>
       </c>
       <c r="U58">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.06048720031964212</v>
+        <v>0.06500566647897794</v>
       </c>
       <c r="W58">
-        <v>0.2027468621710213</v>
+        <v>0.1877468621710212</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4142958926002885</v>
+        <v>0.4452442909519038</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1690550169542525</v>
+        <v>0.1603952602580691</v>
       </c>
       <c r="C59">
-        <v>-2459.643431543154</v>
+        <v>-2279.998989295943</v>
       </c>
       <c r="D59">
-        <v>2399.216568456847</v>
+        <v>2578.861010704058</v>
       </c>
       <c r="E59">
         <v>3510.56</v>
@@ -6131,37 +6131,37 @@
         <v>449.5</v>
       </c>
       <c r="M59">
-        <v>1104.347868</v>
+        <v>1027.585968</v>
       </c>
       <c r="N59">
-        <v>-654.8478680000003</v>
+        <v>-578.0859680000003</v>
       </c>
       <c r="O59">
-        <v>-95.60778872800003</v>
+        <v>-84.40055132800005</v>
       </c>
       <c r="P59">
-        <v>-559.2400792720002</v>
+        <v>-493.6854166720003</v>
       </c>
       <c r="Q59">
-        <v>-238.7400792720002</v>
+        <v>-173.1854166720003</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1240901724150713</v>
+        <v>0.123834924284412</v>
       </c>
       <c r="T59">
-        <v>1.806924683487972</v>
+        <v>1.802192246753163</v>
       </c>
       <c r="U59">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.05942602136666594</v>
+        <v>0.06386521618987305</v>
       </c>
       <c r="W59">
-        <v>0.2029758645890735</v>
+        <v>0.1879758645890735</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.407027543607301</v>
+        <v>0.4374329876018702</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1707550169542525</v>
+        <v>0.161945260258069</v>
       </c>
       <c r="C60">
-        <v>-2582.064523239933</v>
+        <v>-2404.19481098087</v>
       </c>
       <c r="D60">
-        <v>2366.575476760067</v>
+        <v>2544.44518901913</v>
       </c>
       <c r="E60">
         <v>3600.339999999999</v>
@@ -6213,37 +6213,37 @@
         <v>449.5</v>
       </c>
       <c r="M60">
-        <v>1123.722392</v>
+        <v>1045.613792</v>
       </c>
       <c r="N60">
-        <v>-674.2223920000001</v>
+        <v>-596.1137919999999</v>
       </c>
       <c r="O60">
-        <v>-98.43646923200001</v>
+        <v>-87.03261363199998</v>
       </c>
       <c r="P60">
-        <v>-575.7859227680001</v>
+        <v>-509.0811783679999</v>
       </c>
       <c r="Q60">
-        <v>-255.2859227680001</v>
+        <v>-188.5811783679999</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1259542241392396</v>
+        <v>0.125692898672136</v>
       </c>
       <c r="T60">
-        <v>1.849946699761495</v>
+        <v>1.845101585961572</v>
       </c>
       <c r="U60">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.05840143479137861</v>
+        <v>0.06276409177280631</v>
       </c>
       <c r="W60">
-        <v>0.2031969703720205</v>
+        <v>0.1881969703720205</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4000098273382097</v>
+        <v>0.4298910395397693</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1724550169542525</v>
+        <v>0.163495260258069</v>
       </c>
       <c r="C61">
-        <v>-2703.609378728803</v>
+        <v>-2527.484147162564</v>
       </c>
       <c r="D61">
-        <v>2334.810621271197</v>
+        <v>2510.935852837436</v>
       </c>
       <c r="E61">
         <v>3690.119999999999</v>
@@ -6295,37 +6295,37 @@
         <v>449.5</v>
       </c>
       <c r="M61">
-        <v>1143.096916</v>
+        <v>1063.641616</v>
       </c>
       <c r="N61">
-        <v>-693.596916</v>
+        <v>-614.1416159999999</v>
       </c>
       <c r="O61">
-        <v>-101.265149736</v>
+        <v>-89.66467593599998</v>
       </c>
       <c r="P61">
-        <v>-592.331766264</v>
+        <v>-524.4769400639999</v>
       </c>
       <c r="Q61">
-        <v>-271.831766264</v>
+        <v>-203.9769400639999</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1279092052158064</v>
+        <v>0.1276415059568223</v>
       </c>
       <c r="T61">
-        <v>1.89506735097519</v>
+        <v>1.890104063667951</v>
       </c>
       <c r="U61">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.05741157996440609</v>
+        <v>0.06170029360716552</v>
       </c>
       <c r="W61">
-        <v>0.2034105810436812</v>
+        <v>0.1884105810436812</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3932299997562062</v>
+        <v>0.4226047507340105</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1741550169542526</v>
+        <v>0.165045260258069</v>
       </c>
       <c r="C62">
-        <v>-2824.312813981637</v>
+        <v>-2649.902346479461</v>
       </c>
       <c r="D62">
-        <v>2303.887186018364</v>
+        <v>2478.297653520539</v>
       </c>
       <c r="E62">
         <v>3779.9</v>
@@ -6377,37 +6377,37 @@
         <v>449.5</v>
       </c>
       <c r="M62">
-        <v>1162.47144</v>
+        <v>1081.66944</v>
       </c>
       <c r="N62">
-        <v>-712.9714400000003</v>
+        <v>-632.1694400000001</v>
       </c>
       <c r="O62">
-        <v>-104.09383024</v>
+        <v>-92.29673824000001</v>
       </c>
       <c r="P62">
-        <v>-608.8776097600003</v>
+        <v>-539.8727017600002</v>
       </c>
       <c r="Q62">
-        <v>-288.3776097600003</v>
+        <v>-219.3727017600002</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1299619353462016</v>
+        <v>0.1296875436057428</v>
       </c>
       <c r="T62">
-        <v>1.94244403474957</v>
+        <v>1.93735666525965</v>
       </c>
       <c r="U62">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.05645472029833265</v>
+        <v>0.06067195538037942</v>
       </c>
       <c r="W62">
-        <v>0.2036170713596198</v>
+        <v>0.1886170713596198</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3866761664269359</v>
+        <v>0.4155613382217769</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1758550169542525</v>
+        <v>0.166595260258069</v>
       </c>
       <c r="C63">
-        <v>-2944.207824597557</v>
+        <v>-2771.482943247497</v>
       </c>
       <c r="D63">
-        <v>2273.772175402443</v>
+        <v>2446.497056752503</v>
       </c>
       <c r="E63">
         <v>3869.679999999999</v>
@@ -6459,37 +6459,37 @@
         <v>449.5</v>
       </c>
       <c r="M63">
-        <v>1181.845964</v>
+        <v>1099.697264</v>
       </c>
       <c r="N63">
-        <v>-732.3459640000001</v>
+        <v>-650.1972640000001</v>
       </c>
       <c r="O63">
-        <v>-106.922510744</v>
+        <v>-94.92880054400001</v>
       </c>
       <c r="P63">
-        <v>-625.4234532560001</v>
+        <v>-555.2684634560001</v>
       </c>
       <c r="Q63">
-        <v>-304.9234532560001</v>
+        <v>-234.7684634560001</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1321199336884119</v>
+        <v>0.1318385062623004</v>
       </c>
       <c r="T63">
-        <v>1.992250292050841</v>
+        <v>1.987032477189385</v>
       </c>
       <c r="U63">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.0555292330803272</v>
+        <v>0.05967733316102893</v>
       </c>
       <c r="W63">
-        <v>0.2038167915012654</v>
+        <v>0.1888167915012654</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3803372128789535</v>
+        <v>0.4087488572673215</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1775550169542525</v>
+        <v>0.168145260258069</v>
       </c>
       <c r="C64">
-        <v>-3063.325703241877</v>
+        <v>-2892.257772388957</v>
       </c>
       <c r="D64">
-        <v>2244.434296758123</v>
+        <v>2415.502227611043</v>
       </c>
       <c r="E64">
         <v>3959.459999999999</v>
@@ -6541,37 +6541,37 @@
         <v>449.5</v>
       </c>
       <c r="M64">
-        <v>1201.220488</v>
+        <v>1117.725088</v>
       </c>
       <c r="N64">
-        <v>-751.7204879999999</v>
+        <v>-668.2250879999999</v>
       </c>
       <c r="O64">
-        <v>-109.751191248</v>
+        <v>-97.56086284799999</v>
       </c>
       <c r="P64">
-        <v>-641.969296752</v>
+        <v>-570.664225152</v>
       </c>
       <c r="Q64">
-        <v>-321.469296752</v>
+        <v>-250.164225152</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1343915108907385</v>
+        <v>0.1341026774797293</v>
       </c>
       <c r="T64">
-        <v>2.044677931315336</v>
+        <v>2.039322805536474</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.05463360028870903</v>
+        <v>0.05871479552939944</v>
       </c>
       <c r="W64">
-        <v>0.2040100690576966</v>
+        <v>0.1890100690576966</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3742027417034866</v>
+        <v>0.40215613376301</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1792550169542525</v>
+        <v>0.169695260258069</v>
       </c>
       <c r="C65">
-        <v>-3181.696148109129</v>
+        <v>-3012.257075734368</v>
       </c>
       <c r="D65">
-        <v>2215.843851890871</v>
+        <v>2385.282924265633</v>
       </c>
       <c r="E65">
         <v>4049.24</v>
@@ -6623,37 +6623,37 @@
         <v>449.5</v>
       </c>
       <c r="M65">
-        <v>1220.595012</v>
+        <v>1135.752912</v>
       </c>
       <c r="N65">
-        <v>-771.0950120000002</v>
+        <v>-686.2529120000002</v>
       </c>
       <c r="O65">
-        <v>-112.579871752</v>
+        <v>-100.192925152</v>
       </c>
       <c r="P65">
-        <v>-658.5151402480002</v>
+        <v>-586.0599868480001</v>
       </c>
       <c r="Q65">
-        <v>-338.0151402480002</v>
+        <v>-265.5599868480001</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1367858760499477</v>
+        <v>0.1364892363305328</v>
       </c>
       <c r="T65">
-        <v>2.099939497026562</v>
+        <v>2.094439638118541</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.05376640028412633</v>
+        <v>0.05778281464798039</v>
       </c>
       <c r="W65">
-        <v>0.2041972108186856</v>
+        <v>0.1891972108186855</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3682630156447009</v>
+        <v>0.3957727030683589</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1809550169542525</v>
+        <v>0.171245260258069</v>
       </c>
       <c r="C66">
-        <v>-3299.347363200535</v>
+        <v>-3131.509600443597</v>
       </c>
       <c r="D66">
-        <v>2187.972636799465</v>
+        <v>2355.810399556403</v>
       </c>
       <c r="E66">
         <v>4139.02</v>
@@ -6705,37 +6705,37 @@
         <v>449.5</v>
       </c>
       <c r="M66">
-        <v>1239.969536</v>
+        <v>1153.780736</v>
       </c>
       <c r="N66">
-        <v>-790.4695360000001</v>
+        <v>-704.2807360000002</v>
       </c>
       <c r="O66">
-        <v>-115.408552256</v>
+        <v>-102.824987456</v>
       </c>
       <c r="P66">
-        <v>-675.0609837440001</v>
+        <v>-601.4557485440001</v>
       </c>
       <c r="Q66">
-        <v>-354.5609837440001</v>
+        <v>-280.9557485440001</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1393132614957796</v>
+        <v>0.1390083817841587</v>
       </c>
       <c r="T66">
-        <v>2.158271149721744</v>
+        <v>2.152618516955167</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.05292630027968687</v>
+        <v>0.0568799581691057</v>
       </c>
       <c r="W66">
-        <v>0.2043785043996436</v>
+        <v>0.1893785043996436</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3625089060252525</v>
+        <v>0.3895887545829158</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1826550169542525</v>
+        <v>0.172795260258069</v>
       </c>
       <c r="C67">
-        <v>-3416.306151127634</v>
+        <v>-3250.042690219484</v>
       </c>
       <c r="D67">
-        <v>2160.793848872366</v>
+        <v>2327.057309780515</v>
       </c>
       <c r="E67">
         <v>4228.799999999999</v>
@@ -6787,37 +6787,37 @@
         <v>449.5</v>
       </c>
       <c r="M67">
-        <v>1259.34406</v>
+        <v>1171.80856</v>
       </c>
       <c r="N67">
-        <v>-809.8440600000001</v>
+        <v>-722.3085599999999</v>
       </c>
       <c r="O67">
-        <v>-118.23723276</v>
+        <v>-105.45704976</v>
       </c>
       <c r="P67">
-        <v>-691.6068272400001</v>
+        <v>-616.8515102399999</v>
       </c>
       <c r="Q67">
-        <v>-371.1068272400001</v>
+        <v>-296.3515102399999</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1419850689670876</v>
+        <v>0.1416714784065632</v>
       </c>
       <c r="T67">
-        <v>2.219936039713794</v>
+        <v>2.214121903153886</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.05211204950615322</v>
+        <v>0.05600488188958101</v>
       </c>
       <c r="W67">
-        <v>0.2045542197165721</v>
+        <v>0.1895542197165722</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3569318459325563</v>
+        <v>0.3835950814354864</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1843550169542525</v>
+        <v>0.174345260258069</v>
       </c>
       <c r="C68">
-        <v>-3532.597999084001</v>
+        <v>-3367.882369922327</v>
       </c>
       <c r="D68">
-        <v>2134.282000915999</v>
+        <v>2298.997630077673</v>
       </c>
       <c r="E68">
         <v>4318.58</v>
@@ -6869,37 +6869,37 @@
         <v>449.5</v>
       </c>
       <c r="M68">
-        <v>1278.718584</v>
+        <v>1189.836384</v>
       </c>
       <c r="N68">
-        <v>-829.2185840000002</v>
+        <v>-740.3363840000002</v>
       </c>
       <c r="O68">
-        <v>-121.065913264</v>
+        <v>-108.089112064</v>
       </c>
       <c r="P68">
-        <v>-708.1526707360001</v>
+        <v>-632.2472719360002</v>
       </c>
       <c r="Q68">
-        <v>-387.6526707360001</v>
+        <v>-311.7472719360002</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1448140415837666</v>
+        <v>0.1444912277714622</v>
       </c>
       <c r="T68">
-        <v>2.285228276175964</v>
+        <v>2.279243135599589</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.05132247299848423</v>
+        <v>0.05515632307307219</v>
       </c>
       <c r="W68">
-        <v>0.2047246103269271</v>
+        <v>0.1897246103269271</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3515237876608509</v>
+        <v>0.3777830347470699</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1860550169542526</v>
+        <v>0.175895260258069</v>
       </c>
       <c r="C69">
-        <v>-3648.247158564697</v>
+        <v>-3485.053424135613</v>
       </c>
       <c r="D69">
-        <v>2108.412841435304</v>
+        <v>2271.606575864387</v>
       </c>
       <c r="E69">
         <v>4408.36</v>
@@ -6951,37 +6951,37 @@
         <v>449.5</v>
       </c>
       <c r="M69">
-        <v>1298.093108</v>
+        <v>1207.864208</v>
       </c>
       <c r="N69">
-        <v>-848.5931080000003</v>
+        <v>-758.3642080000002</v>
       </c>
       <c r="O69">
-        <v>-123.894593768</v>
+        <v>-110.721174368</v>
       </c>
       <c r="P69">
-        <v>-724.6985142320002</v>
+        <v>-647.6430336320002</v>
       </c>
       <c r="Q69">
-        <v>-404.1985142320002</v>
+        <v>-327.1430336320002</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.147814467086305</v>
+        <v>0.1474818710372641</v>
       </c>
       <c r="T69">
-        <v>2.354477617878266</v>
+        <v>2.348311109405637</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.05055646593880535</v>
+        <v>0.05433309437048903</v>
       </c>
       <c r="W69">
-        <v>0.2048899146504058</v>
+        <v>0.1898899146504058</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3462771639644203</v>
+        <v>0.3721444819896509</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1877550169542526</v>
+        <v>0.1774452602580691</v>
       </c>
       <c r="C70">
-        <v>-3763.276719357572</v>
+        <v>-3601.579470181537</v>
       </c>
       <c r="D70">
-        <v>2083.163280642429</v>
+        <v>2244.860529818464</v>
       </c>
       <c r="E70">
         <v>4498.14</v>
@@ -7033,37 +7033,37 @@
         <v>449.5</v>
       </c>
       <c r="M70">
-        <v>1317.467632</v>
+        <v>1225.892032</v>
       </c>
       <c r="N70">
-        <v>-867.9676320000003</v>
+        <v>-776.3920320000002</v>
       </c>
       <c r="O70">
-        <v>-126.723274272</v>
+        <v>-113.353236672</v>
       </c>
       <c r="P70">
-        <v>-741.2443577280003</v>
+        <v>-663.0387953280002</v>
       </c>
       <c r="Q70">
-        <v>-420.7443577280003</v>
+        <v>-342.5387953280002</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.151002419182752</v>
+        <v>0.1506594295071786</v>
       </c>
       <c r="T70">
-        <v>2.428055043436963</v>
+        <v>2.421695831574563</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.0498129884985288</v>
+        <v>0.05353407827680536</v>
       </c>
       <c r="W70">
-        <v>0.2050503570820175</v>
+        <v>0.1900503570820175</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3411848527296494</v>
+        <v>0.3666717690192148</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1894550169542526</v>
+        <v>0.1789952602580691</v>
       </c>
       <c r="C71">
-        <v>-3877.708678280941</v>
+        <v>-3717.483026038381</v>
       </c>
       <c r="D71">
-        <v>2058.51132171906</v>
+        <v>2218.73697396162</v>
       </c>
       <c r="E71">
         <v>4587.92</v>
@@ -7115,37 +7115,37 @@
         <v>449.5</v>
       </c>
       <c r="M71">
-        <v>1336.842156</v>
+        <v>1243.919856</v>
       </c>
       <c r="N71">
-        <v>-887.3421560000002</v>
+        <v>-794.4198560000002</v>
       </c>
       <c r="O71">
-        <v>-129.551954776</v>
+        <v>-115.985298976</v>
       </c>
       <c r="P71">
-        <v>-757.7902012240002</v>
+        <v>-678.4345570240002</v>
       </c>
       <c r="Q71">
-        <v>-437.2902012240002</v>
+        <v>-357.9345570240002</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1543960456080021</v>
+        <v>0.1540419917493456</v>
       </c>
       <c r="T71">
-        <v>2.506379399676865</v>
+        <v>2.499815051947936</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.04909106112898491</v>
+        <v>0.05275822206989514</v>
       </c>
       <c r="W71">
-        <v>0.2052061490083651</v>
+        <v>0.1902061490083651</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3362401447190748</v>
+        <v>0.3613576854102407</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1911550169542525</v>
+        <v>0.1805452602580691</v>
       </c>
       <c r="C72">
-        <v>-3991.564003097722</v>
+        <v>-3832.785573570323</v>
       </c>
       <c r="D72">
-        <v>2034.435996902278</v>
+        <v>2193.214426429678</v>
       </c>
       <c r="E72">
         <v>4677.7</v>
@@ -7197,37 +7197,37 @@
         <v>449.5</v>
       </c>
       <c r="M72">
-        <v>1356.21668</v>
+        <v>1261.94768</v>
       </c>
       <c r="N72">
-        <v>-906.7166800000002</v>
+        <v>-812.4476800000002</v>
       </c>
       <c r="O72">
-        <v>-132.38063528</v>
+        <v>-118.61736128</v>
       </c>
       <c r="P72">
-        <v>-774.3360447200002</v>
+        <v>-693.8303187200002</v>
       </c>
       <c r="Q72">
-        <v>-453.8360447200002</v>
+        <v>-373.3303187200002</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1580159137949355</v>
+        <v>0.1576500581409905</v>
       </c>
       <c r="T72">
-        <v>2.589925379666093</v>
+        <v>2.5831422203462</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.0483897602557137</v>
+        <v>0.05200453318318235</v>
       </c>
       <c r="W72">
-        <v>0.205357489736817</v>
+        <v>0.190357489736817</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3314367140802308</v>
+        <v>0.356195432761523</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1928550169542525</v>
+        <v>0.182095260258069</v>
       </c>
       <c r="C73">
-        <v>-4104.862691996379</v>
+        <v>-3947.507617442789</v>
       </c>
       <c r="D73">
-        <v>2010.917308003621</v>
+        <v>2168.272382557211</v>
       </c>
       <c r="E73">
         <v>4767.48</v>
@@ -7279,37 +7279,37 @@
         <v>449.5</v>
       </c>
       <c r="M73">
-        <v>1375.591204</v>
+        <v>1279.975504</v>
       </c>
       <c r="N73">
-        <v>-926.0912040000001</v>
+        <v>-830.475504</v>
       </c>
       <c r="O73">
-        <v>-135.209315784</v>
+        <v>-121.249423584</v>
       </c>
       <c r="P73">
-        <v>-790.8818882160001</v>
+        <v>-709.2260804160001</v>
       </c>
       <c r="Q73">
-        <v>-470.3818882160001</v>
+        <v>-388.7260804160001</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1618854280637264</v>
+        <v>0.1615069566975763</v>
       </c>
       <c r="T73">
-        <v>2.679233151378717</v>
+        <v>2.67221609001331</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.04770821433661915</v>
+        <v>0.05127207496933472</v>
       </c>
       <c r="W73">
-        <v>0.2055045673461576</v>
+        <v>0.1905045673461576</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3267685913467065</v>
+        <v>0.3511785956803748</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1945550169542525</v>
+        <v>0.183645260258069</v>
       </c>
       <c r="C74">
-        <v>-4217.623828993308</v>
+        <v>-4061.668740062977</v>
       </c>
       <c r="D74">
-        <v>1987.936171006692</v>
+        <v>2143.891259937023</v>
       </c>
       <c r="E74">
         <v>4857.259999999999</v>
@@ -7361,37 +7361,37 @@
         <v>449.5</v>
       </c>
       <c r="M74">
-        <v>1394.965728</v>
+        <v>1298.003328</v>
       </c>
       <c r="N74">
-        <v>-945.4657280000001</v>
+        <v>-848.503328</v>
       </c>
       <c r="O74">
-        <v>-138.037996288</v>
+        <v>-123.881485888</v>
       </c>
       <c r="P74">
-        <v>-807.4277317120001</v>
+        <v>-724.621842112</v>
       </c>
       <c r="Q74">
-        <v>-486.9277317120001</v>
+        <v>-404.121842112</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1660313362088594</v>
+        <v>0.1656393480082041</v>
       </c>
       <c r="T74">
-        <v>2.774920049642242</v>
+        <v>2.767652378942357</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.04704560024861054</v>
+        <v>0.05055996281698285</v>
       </c>
       <c r="W74">
-        <v>0.2056475594663499</v>
+        <v>0.1906475594663498</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3222301386891133</v>
+        <v>0.3463011151848141</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1962550169542525</v>
+        <v>0.185195260258069</v>
       </c>
       <c r="C75">
-        <v>-4329.865635579252</v>
+        <v>-4175.28765285492</v>
       </c>
       <c r="D75">
-        <v>1965.474364420747</v>
+        <v>2120.05234714508</v>
       </c>
       <c r="E75">
         <v>4947.039999999999</v>
@@ -7443,37 +7443,37 @@
         <v>449.5</v>
       </c>
       <c r="M75">
-        <v>1414.340252</v>
+        <v>1316.031152</v>
       </c>
       <c r="N75">
-        <v>-964.840252</v>
+        <v>-866.531152</v>
       </c>
       <c r="O75">
-        <v>-140.866676792</v>
+        <v>-126.513548192</v>
       </c>
       <c r="P75">
-        <v>-823.9735752079999</v>
+        <v>-740.017603808</v>
       </c>
       <c r="Q75">
-        <v>-503.4735752079999</v>
+        <v>-419.517603808</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1704843486610394</v>
+        <v>0.1700778423788783</v>
       </c>
       <c r="T75">
-        <v>2.877694866295658</v>
+        <v>2.870158022606889</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.04640113997123232</v>
+        <v>0.04986736058661322</v>
       </c>
       <c r="W75">
-        <v>0.2057866339942081</v>
+        <v>0.1907866339942081</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3178160272002214</v>
+        <v>0.3415572642918714</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1979550169542525</v>
+        <v>0.186745260258069</v>
       </c>
       <c r="C76">
-        <v>-4441.605518903507</v>
+        <v>-4288.382244151273</v>
       </c>
       <c r="D76">
-        <v>1943.514481096494</v>
+        <v>2096.737755848727</v>
       </c>
       <c r="E76">
         <v>5036.82</v>
@@ -7525,37 +7525,37 @@
         <v>449.5</v>
       </c>
       <c r="M76">
-        <v>1433.714776</v>
+        <v>1334.058976</v>
       </c>
       <c r="N76">
-        <v>-984.2147760000003</v>
+        <v>-884.558976</v>
       </c>
       <c r="O76">
-        <v>-143.695357296</v>
+        <v>-129.145610496</v>
       </c>
       <c r="P76">
-        <v>-840.5194187040003</v>
+        <v>-755.413365504</v>
       </c>
       <c r="Q76">
-        <v>-520.0194187040003</v>
+        <v>-434.913365504</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1752799005326179</v>
+        <v>0.1748577593934505</v>
       </c>
       <c r="T76">
-        <v>2.988375438076261</v>
+        <v>2.980548715784077</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.04577409753918863</v>
+        <v>0.04919347733544278</v>
       </c>
       <c r="W76">
-        <v>0.2059219497510431</v>
+        <v>0.1909219497510431</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.31352121602184</v>
+        <v>0.3369416255852244</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1996550169542526</v>
+        <v>0.188295260258069</v>
       </c>
       <c r="C77">
-        <v>-4552.860116763688</v>
+        <v>-4400.969623959413</v>
       </c>
       <c r="D77">
-        <v>1922.039883236311</v>
+        <v>2073.930376040587</v>
       </c>
       <c r="E77">
         <v>5126.599999999999</v>
@@ -7607,37 +7607,37 @@
         <v>449.5</v>
       </c>
       <c r="M77">
-        <v>1453.0893</v>
+        <v>1352.0868</v>
       </c>
       <c r="N77">
-        <v>-1003.5893</v>
+        <v>-902.5868</v>
       </c>
       <c r="O77">
-        <v>-146.5240378</v>
+        <v>-131.7776728</v>
       </c>
       <c r="P77">
-        <v>-857.0652622000001</v>
+        <v>-770.8091272</v>
       </c>
       <c r="Q77">
-        <v>-536.5652622000001</v>
+        <v>-450.3091272</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1804590965539226</v>
+        <v>0.1800200697691886</v>
       </c>
       <c r="T77">
-        <v>3.107910455599312</v>
+        <v>3.09977066441544</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.04516377623866612</v>
+        <v>0.04853756430430354</v>
       </c>
       <c r="W77">
-        <v>0.2060536570876959</v>
+        <v>0.1910536570876958</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3093409331415489</v>
+        <v>0.3324490705774215</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2013550169542525</v>
+        <v>0.189845260258069</v>
       </c>
       <c r="C78">
-        <v>-4663.645339645458</v>
+        <v>-4513.066165837317</v>
       </c>
       <c r="D78">
-        <v>1901.034660354541</v>
+        <v>2051.613834162683</v>
       </c>
       <c r="E78">
         <v>5216.379999999999</v>
@@ -7689,37 +7689,37 @@
         <v>449.5</v>
       </c>
       <c r="M78">
-        <v>1472.463824</v>
+        <v>1370.114624</v>
       </c>
       <c r="N78">
-        <v>-1022.963824</v>
+        <v>-920.614624</v>
       </c>
       <c r="O78">
-        <v>-149.352718304</v>
+        <v>-134.409735104</v>
       </c>
       <c r="P78">
-        <v>-873.6111056960001</v>
+        <v>-786.2048888960001</v>
       </c>
       <c r="Q78">
-        <v>-553.1111056960001</v>
+        <v>-465.7048888960001</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1860698922436693</v>
+        <v>0.1856125726762381</v>
       </c>
       <c r="T78">
-        <v>3.237406724582616</v>
+        <v>3.22892777543275</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.04456951602499946</v>
+        <v>0.04789891214240481</v>
       </c>
       <c r="W78">
-        <v>0.2061818984418051</v>
+        <v>0.1911818984418051</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3052706577054758</v>
+        <v>0.3280747407014027</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2030550169542525</v>
+        <v>0.191395260258069</v>
       </c>
       <c r="C79">
-        <v>-4773.97641003543</v>
+        <v>-4624.687546094584</v>
       </c>
       <c r="D79">
-        <v>1880.483589964571</v>
+        <v>2029.772453905416</v>
       </c>
       <c r="E79">
         <v>5306.16</v>
@@ -7771,37 +7771,37 @@
         <v>449.5</v>
       </c>
       <c r="M79">
-        <v>1491.838348</v>
+        <v>1388.142448</v>
       </c>
       <c r="N79">
-        <v>-1042.338348</v>
+        <v>-938.6424480000001</v>
       </c>
       <c r="O79">
-        <v>-152.181398808</v>
+        <v>-137.041797408</v>
       </c>
       <c r="P79">
-        <v>-890.1569491920002</v>
+        <v>-801.6006505920001</v>
       </c>
       <c r="Q79">
-        <v>-569.6569491920002</v>
+        <v>-481.1006505920001</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1921685832107854</v>
+        <v>0.1916913801839006</v>
       </c>
       <c r="T79">
-        <v>3.378163538694904</v>
+        <v>3.369315939582</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.04399069114155791</v>
+        <v>0.0472768483483476</v>
       </c>
       <c r="W79">
-        <v>0.2063068088516518</v>
+        <v>0.1913068088516518</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3013061037093008</v>
+        <v>0.3238140297832027</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2047550169542525</v>
+        <v>0.192945260258069</v>
       </c>
       <c r="C80">
-        <v>-4883.867899211387</v>
+        <v>-4735.848780515833</v>
       </c>
       <c r="D80">
-        <v>1860.372100788612</v>
+        <v>2008.391219484167</v>
       </c>
       <c r="E80">
         <v>5395.94</v>
@@ -7853,37 +7853,37 @@
         <v>449.5</v>
       </c>
       <c r="M80">
-        <v>1511.212872</v>
+        <v>1406.170272</v>
       </c>
       <c r="N80">
-        <v>-1061.712872</v>
+        <v>-956.6702720000001</v>
       </c>
       <c r="O80">
-        <v>-155.010079312</v>
+        <v>-139.673859712</v>
       </c>
       <c r="P80">
-        <v>-906.702792688</v>
+        <v>-816.9964122880001</v>
       </c>
       <c r="Q80">
-        <v>-586.202792688</v>
+        <v>-496.4964122880001</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1988217006294575</v>
+        <v>0.1983228065558961</v>
       </c>
       <c r="T80">
-        <v>3.5317164268174</v>
+        <v>3.522466664108455</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.04342670792179435</v>
+        <v>0.04667073490798417</v>
       </c>
       <c r="W80">
-        <v>0.2064285164304768</v>
+        <v>0.1914285164304768</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2974432049437969</v>
+        <v>0.3196625678629053</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2064550169542525</v>
+        <v>0.1944952602580691</v>
       </c>
       <c r="C81">
-        <v>-4993.333761696722</v>
+        <v>-4846.564258787283</v>
       </c>
       <c r="D81">
-        <v>1840.686238303277</v>
+        <v>1987.455741212717</v>
       </c>
       <c r="E81">
         <v>5485.719999999999</v>
@@ -7935,37 +7935,37 @@
         <v>449.5</v>
       </c>
       <c r="M81">
-        <v>1530.587396</v>
+        <v>1424.198096</v>
       </c>
       <c r="N81">
-        <v>-1081.087396</v>
+        <v>-974.6980960000001</v>
       </c>
       <c r="O81">
-        <v>-157.838759816</v>
+        <v>-142.305922016</v>
       </c>
       <c r="P81">
-        <v>-923.2486361840001</v>
+        <v>-832.392173984</v>
       </c>
       <c r="Q81">
-        <v>-602.7486361840001</v>
+        <v>-511.892173984</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2061084482784793</v>
+        <v>0.2055857973442721</v>
       </c>
       <c r="T81">
-        <v>3.69989339952299</v>
+        <v>3.690203171923144</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.04287700275822733</v>
+        <v>0.04607996611168057</v>
       </c>
       <c r="W81">
-        <v>0.2065471428047745</v>
+        <v>0.1915471428047746</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2936781010837489</v>
+        <v>0.3156162062443875</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2081550169542526</v>
+        <v>0.196045260258069</v>
       </c>
       <c r="C82">
-        <v>-5102.387367550229</v>
+        <v>-4956.847776792367</v>
       </c>
       <c r="D82">
-        <v>1821.412632449771</v>
+        <v>1966.952223207634</v>
       </c>
       <c r="E82">
         <v>5575.5</v>
@@ -8017,37 +8017,37 @@
         <v>449.5</v>
       </c>
       <c r="M82">
-        <v>1549.96192</v>
+        <v>1442.22592</v>
       </c>
       <c r="N82">
-        <v>-1100.46192</v>
+        <v>-992.7259200000001</v>
       </c>
       <c r="O82">
-        <v>-160.66744032</v>
+        <v>-144.93798432</v>
       </c>
       <c r="P82">
-        <v>-939.7944796800002</v>
+        <v>-847.7879356800001</v>
       </c>
       <c r="Q82">
-        <v>-619.2944796800002</v>
+        <v>-527.2879356800001</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2141238706924033</v>
+        <v>0.2135750872114857</v>
       </c>
       <c r="T82">
-        <v>3.88488806949914</v>
+        <v>3.874713330519301</v>
       </c>
       <c r="U82">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.04234104022374949</v>
+        <v>0.04550396653528457</v>
       </c>
       <c r="W82">
-        <v>0.2066628035197149</v>
+        <v>0.1916628035197149</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.290007124820202</v>
+        <v>0.3116710036663326</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2098550169542525</v>
+        <v>0.1975952602580691</v>
       </c>
       <c r="C83">
-        <v>-5211.04153264832</v>
+        <v>-5066.712566928689</v>
       </c>
       <c r="D83">
-        <v>1802.538467351681</v>
+        <v>1946.867433071311</v>
       </c>
       <c r="E83">
         <v>5665.28</v>
@@ -8099,37 +8099,37 @@
         <v>449.5</v>
       </c>
       <c r="M83">
-        <v>1569.336444</v>
+        <v>1460.253744</v>
       </c>
       <c r="N83">
-        <v>-1119.836444</v>
+        <v>-1010.753744</v>
       </c>
       <c r="O83">
-        <v>-163.496120824</v>
+        <v>-147.570046624</v>
       </c>
       <c r="P83">
-        <v>-956.3403231760002</v>
+        <v>-863.1836973760001</v>
       </c>
       <c r="Q83">
-        <v>-635.8403231760002</v>
+        <v>-542.6836973760001</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2229830217814771</v>
+        <v>0.2224053549594587</v>
       </c>
       <c r="T83">
-        <v>4.089355862630674</v>
+        <v>4.078645611072949</v>
       </c>
       <c r="U83">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.04181831133209826</v>
+        <v>0.04494218917065142</v>
       </c>
       <c r="W83">
-        <v>0.2067756084145332</v>
+        <v>0.1917756084145332</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2864267899458786</v>
+        <v>0.3078232134976124</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2115550169542526</v>
+        <v>0.1991452602580691</v>
       </c>
       <c r="C84">
-        <v>-5319.308547103778</v>
+        <v>-5176.171326586355</v>
       </c>
       <c r="D84">
-        <v>1784.051452896223</v>
+        <v>1927.188673413647</v>
       </c>
       <c r="E84">
         <v>5755.06</v>
@@ -8181,37 +8181,37 @@
         <v>449.5</v>
       </c>
       <c r="M84">
-        <v>1588.710968</v>
+        <v>1478.281568</v>
       </c>
       <c r="N84">
-        <v>-1139.210968</v>
+        <v>-1028.781568</v>
       </c>
       <c r="O84">
-        <v>-166.324801328</v>
+        <v>-150.202108928</v>
       </c>
       <c r="P84">
-        <v>-972.8861666720003</v>
+        <v>-878.5794590720003</v>
       </c>
       <c r="Q84">
-        <v>-652.3861666720003</v>
+        <v>-558.0794590720003</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2328265229915592</v>
+        <v>0.2322167635683175</v>
       </c>
       <c r="T84">
-        <v>4.31654229944349</v>
+        <v>4.305237033910335</v>
       </c>
       <c r="U84">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.04130833192560926</v>
+        <v>0.04439411369296054</v>
       </c>
       <c r="W84">
-        <v>0.2068856619704535</v>
+        <v>0.1918856619704535</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2829337803123921</v>
+        <v>0.3040692718695928</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2132550169542526</v>
+        <v>0.2006952602580691</v>
       </c>
       <c r="C85">
-        <v>-5427.200201953463</v>
+        <v>-5285.236244916419</v>
       </c>
       <c r="D85">
-        <v>1765.939798046538</v>
+        <v>1907.903755083581</v>
       </c>
       <c r="E85">
         <v>5844.84</v>
@@ -8263,37 +8263,37 @@
         <v>449.5</v>
       </c>
       <c r="M85">
-        <v>1608.085492</v>
+        <v>1496.309392</v>
       </c>
       <c r="N85">
-        <v>-1158.585492</v>
+        <v>-1046.809392</v>
       </c>
       <c r="O85">
-        <v>-169.153481832</v>
+        <v>-152.834171232</v>
       </c>
       <c r="P85">
-        <v>-989.4320101680004</v>
+        <v>-893.9752207680001</v>
       </c>
       <c r="Q85">
-        <v>-668.9320101680004</v>
+        <v>-573.4752207680001</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2438280831675333</v>
+        <v>0.2431824555429244</v>
       </c>
       <c r="T85">
-        <v>4.57045655235193</v>
+        <v>4.558486271199178</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.04081064117951758</v>
+        <v>0.04385924485328632</v>
       </c>
       <c r="W85">
-        <v>0.2069930636334601</v>
+        <v>0.1919930636334601</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2795249395857369</v>
+        <v>0.3004057866663448</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2149550169542526</v>
+        <v>0.202245260258069</v>
       </c>
       <c r="C86">
-        <v>-5534.727814236761</v>
+        <v>-5393.919028008097</v>
       </c>
       <c r="D86">
-        <v>1748.192185763238</v>
+        <v>1889.000971991902</v>
       </c>
       <c r="E86">
         <v>5934.619999999999</v>
@@ -8345,37 +8345,37 @@
         <v>449.5</v>
       </c>
       <c r="M86">
-        <v>1627.460016</v>
+        <v>1514.337216</v>
       </c>
       <c r="N86">
-        <v>-1177.960016</v>
+        <v>-1064.837216</v>
       </c>
       <c r="O86">
-        <v>-171.982162336</v>
+        <v>-155.466233536</v>
       </c>
       <c r="P86">
-        <v>-1005.977853664</v>
+        <v>-909.3709824639999</v>
       </c>
       <c r="Q86">
-        <v>-685.477853664</v>
+        <v>-588.8709824639999</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.256204838365504</v>
+        <v>0.2555188590143571</v>
       </c>
       <c r="T86">
-        <v>4.856110086873924</v>
+        <v>4.843391663149125</v>
       </c>
       <c r="U86">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.04032480021309476</v>
+        <v>0.04333711098598531</v>
       </c>
       <c r="W86">
-        <v>0.2070979081140142</v>
+        <v>0.1920979081140142</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2761972617335258</v>
+        <v>0.2968295273012692</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2166550169542525</v>
+        <v>0.203795260258069</v>
       </c>
       <c r="C87">
-        <v>-5641.902250576863</v>
+        <v>-5502.230922583953</v>
       </c>
       <c r="D87">
-        <v>1730.797749423138</v>
+        <v>1870.469077416047</v>
       </c>
       <c r="E87">
         <v>6024.4</v>
@@ -8427,37 +8427,37 @@
         <v>449.5</v>
       </c>
       <c r="M87">
-        <v>1646.83454</v>
+        <v>1532.36504</v>
       </c>
       <c r="N87">
-        <v>-1197.33454</v>
+        <v>-1082.86504</v>
       </c>
       <c r="O87">
-        <v>-174.81084284</v>
+        <v>-158.09829584</v>
       </c>
       <c r="P87">
-        <v>-1022.52369716</v>
+        <v>-924.7667441600001</v>
       </c>
       <c r="Q87">
-        <v>-702.0236971600002</v>
+        <v>-604.2667441600001</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2702318275898709</v>
+        <v>0.2695001162819809</v>
       </c>
       <c r="T87">
-        <v>5.179850759332186</v>
+        <v>5.1662844406924</v>
       </c>
       <c r="U87">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.03985039079882305</v>
+        <v>0.04282726262144429</v>
       </c>
       <c r="W87">
-        <v>0.207200285665614</v>
+        <v>0.192200285665614</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2729478821837195</v>
+        <v>0.2933374152153719</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2183550169542526</v>
+        <v>0.205345260258069</v>
       </c>
       <c r="C88">
-        <v>-5748.733949368091</v>
+        <v>-5610.182738313893</v>
       </c>
       <c r="D88">
-        <v>1713.746050631909</v>
+        <v>1852.297261686107</v>
       </c>
       <c r="E88">
         <v>6114.179999999999</v>
@@ -8509,37 +8509,37 @@
         <v>449.5</v>
       </c>
       <c r="M88">
-        <v>1666.209064</v>
+        <v>1550.392864</v>
       </c>
       <c r="N88">
-        <v>-1216.709064</v>
+        <v>-1100.892864</v>
       </c>
       <c r="O88">
-        <v>-177.639523344</v>
+        <v>-160.730358144</v>
       </c>
       <c r="P88">
-        <v>-1039.069540656</v>
+        <v>-940.1625058560002</v>
       </c>
       <c r="Q88">
-        <v>-718.5695406560001</v>
+        <v>-619.6625058560002</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2862626724177189</v>
+        <v>0.2854786960164081</v>
       </c>
       <c r="T88">
-        <v>5.549840099284484</v>
+        <v>5.535304757884714</v>
       </c>
       <c r="U88">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.03938701416162743</v>
+        <v>0.04232927119561355</v>
       </c>
       <c r="W88">
-        <v>0.2073002823439208</v>
+        <v>0.1923002823439208</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2697740696001879</v>
+        <v>0.289926515038449</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2200550169542525</v>
+        <v>0.206895260258069</v>
       </c>
       <c r="C89">
-        <v>-5855.232941664532</v>
+        <v>-5717.784868840974</v>
       </c>
       <c r="D89">
-        <v>1697.027058335469</v>
+        <v>1834.475131159025</v>
       </c>
       <c r="E89">
         <v>6203.959999999999</v>
@@ -8591,37 +8591,37 @@
         <v>449.5</v>
       </c>
       <c r="M89">
-        <v>1685.583588</v>
+        <v>1568.420688</v>
       </c>
       <c r="N89">
-        <v>-1236.083588</v>
+        <v>-1118.920688</v>
       </c>
       <c r="O89">
-        <v>-180.468203848</v>
+        <v>-163.362420448</v>
       </c>
       <c r="P89">
-        <v>-1055.615384152</v>
+        <v>-955.558267552</v>
       </c>
       <c r="Q89">
-        <v>-735.1153841520002</v>
+        <v>-635.058267552</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3047598010652356</v>
+        <v>0.303915518786901</v>
       </c>
       <c r="T89">
-        <v>5.976750876152521</v>
+        <v>5.961097431568153</v>
       </c>
       <c r="U89">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.03893428986091908</v>
+        <v>0.04184272784853754</v>
       </c>
       <c r="W89">
-        <v>0.2073979802480137</v>
+        <v>0.1923979802480137</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2666732182254731</v>
+        <v>0.2865940263598461</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2217550169542525</v>
+        <v>0.208445260258069</v>
       </c>
       <c r="C90">
-        <v>-5961.408870857733</v>
+        <v>-5825.047311604969</v>
       </c>
       <c r="D90">
-        <v>1680.631129142268</v>
+        <v>1816.992688395032</v>
       </c>
       <c r="E90">
         <v>6293.74</v>
@@ -8673,37 +8673,37 @@
         <v>449.5</v>
       </c>
       <c r="M90">
-        <v>1704.958112</v>
+        <v>1586.448512</v>
       </c>
       <c r="N90">
-        <v>-1255.458112</v>
+        <v>-1136.948512</v>
       </c>
       <c r="O90">
-        <v>-183.296884352</v>
+        <v>-165.994482752</v>
       </c>
       <c r="P90">
-        <v>-1072.161227648</v>
+        <v>-970.9540292480001</v>
       </c>
       <c r="Q90">
-        <v>-751.6612276480002</v>
+        <v>-650.4540292480001</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3263397844873387</v>
+        <v>0.3254251453524761</v>
       </c>
       <c r="T90">
-        <v>6.474813449165232</v>
+        <v>6.4578555508655</v>
       </c>
       <c r="U90">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.03849185474886316</v>
+        <v>0.04136724230480415</v>
       </c>
       <c r="W90">
-        <v>0.2074934577451953</v>
+        <v>0.1924934577451953</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2636428407456382</v>
+        <v>0.2833372760603023</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2234550169542525</v>
+        <v>0.209995260258069</v>
       </c>
       <c r="C91">
-        <v>-6067.27101122463</v>
+        <v>-5931.979686543111</v>
       </c>
       <c r="D91">
-        <v>1664.54898877537</v>
+        <v>1799.84031345689</v>
       </c>
       <c r="E91">
         <v>6383.52</v>
@@ -8755,37 +8755,37 @@
         <v>449.5</v>
       </c>
       <c r="M91">
-        <v>1724.332636</v>
+        <v>1604.476336</v>
       </c>
       <c r="N91">
-        <v>-1274.832636</v>
+        <v>-1154.976336</v>
       </c>
       <c r="O91">
-        <v>-186.125564856</v>
+        <v>-168.626545056</v>
       </c>
       <c r="P91">
-        <v>-1088.707071144</v>
+        <v>-986.3497909440001</v>
       </c>
       <c r="Q91">
-        <v>-768.2070711440001</v>
+        <v>-665.8497909440001</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.351843401258915</v>
+        <v>0.3508456131117922</v>
       </c>
       <c r="T91">
-        <v>7.0634328536348</v>
+        <v>7.04493332821691</v>
       </c>
       <c r="U91">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.03805936199887595</v>
+        <v>0.04090244182946927</v>
       </c>
       <c r="W91">
-        <v>0.2075867896806426</v>
+        <v>0.1925867896806426</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2606805616361366</v>
+        <v>0.2801537111607484</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2251550169542526</v>
+        <v>0.211545260258069</v>
       </c>
       <c r="C92">
-        <v>-6172.828285420645</v>
+        <v>-6038.59125374156</v>
       </c>
       <c r="D92">
-        <v>1648.771714579356</v>
+        <v>1783.00874625844</v>
       </c>
       <c r="E92">
         <v>6473.299999999999</v>
@@ -8837,37 +8837,37 @@
         <v>449.5</v>
       </c>
       <c r="M92">
-        <v>1743.70716</v>
+        <v>1622.50416</v>
       </c>
       <c r="N92">
-        <v>-1294.20716</v>
+        <v>-1173.00416</v>
       </c>
       <c r="O92">
-        <v>-188.95424536</v>
+        <v>-171.25860736</v>
       </c>
       <c r="P92">
-        <v>-1105.25291464</v>
+        <v>-1001.74555264</v>
       </c>
       <c r="Q92">
-        <v>-784.7529146400002</v>
+        <v>-681.2455526399999</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3824477413848065</v>
+        <v>0.3813501744229715</v>
       </c>
       <c r="T92">
-        <v>7.769776138998281</v>
+        <v>7.749426661038602</v>
       </c>
       <c r="U92">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.03763648019888843</v>
+        <v>0.04044797025358628</v>
       </c>
       <c r="W92">
-        <v>0.2076780475730799</v>
+        <v>0.1926780475730799</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2577841109512907</v>
+        <v>0.2770408921478512</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2268550169542526</v>
+        <v>0.213095260258069</v>
       </c>
       <c r="C93">
-        <v>-6278.089280987275</v>
+        <v>-6144.890930105597</v>
       </c>
       <c r="D93">
-        <v>1633.290719012725</v>
+        <v>1766.489069894403</v>
       </c>
       <c r="E93">
         <v>6563.08</v>
@@ -8919,37 +8919,37 @@
         <v>449.5</v>
       </c>
       <c r="M93">
-        <v>1763.081684</v>
+        <v>1640.531984</v>
       </c>
       <c r="N93">
-        <v>-1313.581684</v>
+        <v>-1191.031984</v>
       </c>
       <c r="O93">
-        <v>-191.782925864</v>
+        <v>-173.890669664</v>
       </c>
       <c r="P93">
-        <v>-1121.798758136</v>
+        <v>-1017.141314336</v>
       </c>
       <c r="Q93">
-        <v>-801.2987581360003</v>
+        <v>-696.6413143360002</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4198530459831183</v>
+        <v>0.418633527136635</v>
       </c>
       <c r="T93">
-        <v>8.633084598886979</v>
+        <v>8.61047406782067</v>
       </c>
       <c r="U93">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.03722289250439515</v>
+        <v>0.04000348706398642</v>
       </c>
       <c r="W93">
-        <v>0.2077672997975515</v>
+        <v>0.1927672997975515</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2549513185232545</v>
+        <v>0.2739964867396331</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2285550169542526</v>
+        <v>0.214645260258069</v>
       </c>
       <c r="C94">
-        <v>-6383.062265938363</v>
+        <v>-6250.887305111632</v>
       </c>
       <c r="D94">
-        <v>1618.097734061638</v>
+        <v>1750.272694888369</v>
       </c>
       <c r="E94">
         <v>6652.86</v>
@@ -9001,37 +9001,37 @@
         <v>449.5</v>
       </c>
       <c r="M94">
-        <v>1782.456208</v>
+        <v>1658.559808</v>
       </c>
       <c r="N94">
-        <v>-1332.956208</v>
+        <v>-1209.059808</v>
       </c>
       <c r="O94">
-        <v>-194.611606368</v>
+        <v>-176.522731968</v>
       </c>
       <c r="P94">
-        <v>-1138.344601632</v>
+        <v>-1032.537076032</v>
       </c>
       <c r="Q94">
-        <v>-817.8446016320004</v>
+        <v>-712.0370760320002</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4666096767310082</v>
+        <v>0.4652377180287145</v>
       </c>
       <c r="T94">
-        <v>9.712220173747854</v>
+        <v>9.686783326298256</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.03681829584673868</v>
+        <v>0.03956866655242135</v>
       </c>
       <c r="W94">
-        <v>0.2078546117562738</v>
+        <v>0.1928546117562738</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2521801085393061</v>
+        <v>0.2710182640576806</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2302550169542525</v>
+        <v>0.2161952602580691</v>
       </c>
       <c r="C95">
-        <v>-6487.755203484469</v>
+        <v>-6356.588655699485</v>
       </c>
       <c r="D95">
-        <v>1603.184796515531</v>
+        <v>1734.351344300517</v>
       </c>
       <c r="E95">
         <v>6742.64</v>
@@ -9083,37 +9083,37 @@
         <v>449.5</v>
       </c>
       <c r="M95">
-        <v>1801.830732</v>
+        <v>1676.587632</v>
       </c>
       <c r="N95">
-        <v>-1352.330732</v>
+        <v>-1227.087632</v>
       </c>
       <c r="O95">
-        <v>-197.440286872</v>
+        <v>-179.154794272</v>
       </c>
       <c r="P95">
-        <v>-1154.890445128</v>
+        <v>-1047.932837728</v>
       </c>
       <c r="Q95">
-        <v>-834.3904451280002</v>
+        <v>-727.4328377280001</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5267253448354381</v>
+        <v>0.5251573920328166</v>
       </c>
       <c r="T95">
-        <v>11.09968019856898</v>
+        <v>11.07060951576944</v>
       </c>
       <c r="U95">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.03642240019247268</v>
+        <v>0.03914319701959963</v>
       </c>
       <c r="W95">
-        <v>0.2079400460384644</v>
+        <v>0.1929400460384644</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.249468494468991</v>
+        <v>0.2681040891753399</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2319550169542525</v>
+        <v>0.2177452602580691</v>
       </c>
       <c r="C96">
-        <v>-6592.175765950459</v>
+        <v>-6462.002960359182</v>
       </c>
       <c r="D96">
-        <v>1588.544234049541</v>
+        <v>1718.717039640818</v>
       </c>
       <c r="E96">
         <v>6832.419999999999</v>
@@ -9165,37 +9165,37 @@
         <v>449.5</v>
       </c>
       <c r="M96">
-        <v>1821.205256</v>
+        <v>1694.615456</v>
       </c>
       <c r="N96">
-        <v>-1371.705256</v>
+        <v>-1245.115456</v>
       </c>
       <c r="O96">
-        <v>-200.268967376</v>
+        <v>-181.786856576</v>
       </c>
       <c r="P96">
-        <v>-1171.436288624</v>
+        <v>-1063.328599424</v>
       </c>
       <c r="Q96">
-        <v>-850.9362886240001</v>
+        <v>-742.828599424</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6068795689746779</v>
+        <v>0.6050502907049528</v>
       </c>
       <c r="T96">
-        <v>12.94962689833048</v>
+        <v>12.91571110173101</v>
       </c>
       <c r="U96">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.03603492784999957</v>
+        <v>0.03872678003002942</v>
       </c>
       <c r="W96">
-        <v>0.2080236625699701</v>
+        <v>0.1930236625699701</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2468145743150655</v>
+        <v>0.2652519180139001</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2336550169542526</v>
+        <v>0.2192952602580691</v>
       </c>
       <c r="C97">
-        <v>-6696.331347937402</v>
+        <v>-6567.137912462661</v>
       </c>
       <c r="D97">
-        <v>1574.168652062599</v>
+        <v>1703.362087537339</v>
       </c>
       <c r="E97">
         <v>6922.2</v>
@@ -9247,37 +9247,37 @@
         <v>449.5</v>
       </c>
       <c r="M97">
-        <v>1840.57978</v>
+        <v>1712.64328</v>
       </c>
       <c r="N97">
-        <v>-1391.07978</v>
+        <v>-1263.14328</v>
       </c>
       <c r="O97">
-        <v>-203.09764788</v>
+        <v>-184.41891888</v>
       </c>
       <c r="P97">
-        <v>-1187.98213212</v>
+        <v>-1078.72436112</v>
       </c>
       <c r="Q97">
-        <v>-867.4821321200002</v>
+        <v>-758.2243611200001</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7190954827696138</v>
+        <v>0.7169003488459437</v>
       </c>
       <c r="T97">
-        <v>15.53955227799658</v>
+        <v>15.49885332207722</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.03565561281999957</v>
+        <v>0.03831912971392384</v>
       </c>
       <c r="W97">
-        <v>0.2081055187534441</v>
+        <v>0.1931055187534441</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2442165261643806</v>
+        <v>0.2624597925611222</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2353550169542525</v>
+        <v>0.220845260258069</v>
       </c>
       <c r="C98">
-        <v>-6800.229078776212</v>
+        <v>-6672.000932887151</v>
       </c>
       <c r="D98">
-        <v>1560.050921223788</v>
+        <v>1688.279067112848</v>
       </c>
       <c r="E98">
         <v>7011.979999999999</v>
@@ -9329,37 +9329,37 @@
         <v>449.5</v>
       </c>
       <c r="M98">
-        <v>1859.954304</v>
+        <v>1730.671104</v>
       </c>
       <c r="N98">
-        <v>-1410.454304</v>
+        <v>-1281.171104</v>
       </c>
       <c r="O98">
-        <v>-205.926328384</v>
+        <v>-187.050981184</v>
       </c>
       <c r="P98">
-        <v>-1204.527975616</v>
+        <v>-1094.120122816</v>
       </c>
       <c r="Q98">
-        <v>-884.027975616</v>
+        <v>-773.6201228159998</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8874193534620152</v>
+        <v>0.8846754360574277</v>
       </c>
       <c r="T98">
-        <v>19.42444034749568</v>
+        <v>19.37356665259648</v>
       </c>
       <c r="U98">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.03528420018645791</v>
+        <v>0.03791997211273714</v>
       </c>
       <c r="W98">
-        <v>0.2081856695997624</v>
+        <v>0.1931856695997624</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.241672604016835</v>
+        <v>0.2597258363886106</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2370550169542525</v>
+        <v>0.222395260258069</v>
       </c>
       <c r="C99">
-        <v>-6903.875834317139</v>
+        <v>-6776.599181973797</v>
       </c>
       <c r="D99">
-        <v>1546.184165682861</v>
+        <v>1673.460818026203</v>
       </c>
       <c r="E99">
         <v>7101.759999999999</v>
@@ -9411,37 +9411,37 @@
         <v>449.5</v>
       </c>
       <c r="M99">
-        <v>1879.328828</v>
+        <v>1748.698928</v>
       </c>
       <c r="N99">
-        <v>-1429.828828</v>
+        <v>-1299.198928</v>
       </c>
       <c r="O99">
-        <v>-208.755008888</v>
+        <v>-189.683043488</v>
       </c>
       <c r="P99">
-        <v>-1221.073819112</v>
+        <v>-1109.515884512</v>
       </c>
       <c r="Q99">
-        <v>-900.5738191120001</v>
+        <v>-789.015884512</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.167959137949354</v>
+        <v>1.164300581409904</v>
       </c>
       <c r="T99">
-        <v>25.89925379666091</v>
+        <v>25.83142220346198</v>
       </c>
       <c r="U99">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.0349204455453604</v>
+        <v>0.03752904456518314</v>
       </c>
       <c r="W99">
-        <v>0.2082641678513112</v>
+        <v>0.1932641678513112</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2391811338723315</v>
+        <v>0.25704825044646</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2387550169542526</v>
+        <v>0.223945260258069</v>
       </c>
       <c r="C100">
-        <v>-7007.278248096016</v>
+        <v>-6880.93957086196</v>
       </c>
       <c r="D100">
-        <v>1532.561751903984</v>
+        <v>1658.90042913804</v>
       </c>
       <c r="E100">
         <v>7191.54</v>
@@ -9493,37 +9493,37 @@
         <v>449.5</v>
       </c>
       <c r="M100">
-        <v>1898.703352</v>
+        <v>1766.726752</v>
       </c>
       <c r="N100">
-        <v>-1449.203352</v>
+        <v>-1317.226752</v>
       </c>
       <c r="O100">
-        <v>-211.583689392</v>
+        <v>-192.315105792</v>
       </c>
       <c r="P100">
-        <v>-1237.619662608</v>
+        <v>-1124.911646208</v>
       </c>
       <c r="Q100">
-        <v>-917.1196626080002</v>
+        <v>-804.4116462080003</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.72903870692403</v>
+        <v>1.723550872114856</v>
       </c>
       <c r="T100">
-        <v>38.84888069499136</v>
+        <v>38.74713330519297</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.03456411446836693</v>
+        <v>0.03714609513084454</v>
       </c>
       <c r="W100">
-        <v>0.2083410640977264</v>
+        <v>0.1933410640977264</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2367405100573078</v>
+        <v>0.2544253091153735</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2404550169542525</v>
+        <v>0.225495260258069</v>
       </c>
       <c r="C101">
-        <v>-7110.442721915402</v>
+        <v>-6985.028772236948</v>
       </c>
       <c r="D101">
-        <v>1519.177278084597</v>
+        <v>1644.59122776305</v>
       </c>
       <c r="E101">
         <v>7281.319999999999</v>
@@ -9575,37 +9575,37 @@
         <v>449.5</v>
       </c>
       <c r="M101">
-        <v>1918.077876</v>
+        <v>1784.754576</v>
       </c>
       <c r="N101">
-        <v>-1468.577876</v>
+        <v>-1335.254576</v>
       </c>
       <c r="O101">
-        <v>-214.412369896</v>
+        <v>-194.947168096</v>
       </c>
       <c r="P101">
-        <v>-1254.165506104</v>
+        <v>-1140.307407904</v>
       </c>
       <c r="Q101">
-        <v>-933.6655061040001</v>
+        <v>-819.8074079039998</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.412277413848061</v>
+        <v>3.401301744229711</v>
       </c>
       <c r="T101">
-        <v>77.69776138998272</v>
+        <v>77.49426661038594</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V101">
-        <v>0.03421498199898949</v>
+        <v>0.03677088204871481</v>
       </c>
       <c r="W101">
-        <v>0.2084164068846181</v>
+        <v>0.1934164068846181</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2343491917739007</v>
+        <v>0.2518553564980466</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/switzerland/switzerland_air_transport.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_air_transport.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08062267324884481</v>
+        <v>0.08054339414590148</v>
       </c>
       <c r="C2">
-        <v>8745.175587668937</v>
+        <v>8674.760653063118</v>
       </c>
       <c r="D2">
-        <v>8486.575587668936</v>
+        <v>8505.940653063119</v>
       </c>
       <c r="E2">
-        <v>-1606.9</v>
+        <v>-1517.12</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>89.78</v>
       </c>
       <c r="G2">
         <v>258.6</v>
@@ -1457,28 +1457,28 @@
         <v>449.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.515934</v>
       </c>
       <c r="N2">
-        <v>449.5</v>
+        <v>444.984066</v>
       </c>
       <c r="O2">
-        <v>65.627</v>
+        <v>64.967673636</v>
       </c>
       <c r="P2">
-        <v>383.873</v>
+        <v>380.016392364</v>
       </c>
       <c r="Q2">
-        <v>704.373</v>
+        <v>700.516392364</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08062267324884481</v>
+        <v>0.08092306277363787</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285175</v>
+        <v>0.8111561841486805</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>99.53644140946258</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08054339414590148</v>
+        <v>0.08046411504295817</v>
       </c>
       <c r="C3">
-        <v>8674.760653063118</v>
+        <v>8604.434296804729</v>
       </c>
       <c r="D3">
-        <v>8505.940653063119</v>
+        <v>8525.394296804729</v>
       </c>
       <c r="E3">
-        <v>-1517.12</v>
+        <v>-1427.34</v>
       </c>
       <c r="F3">
-        <v>89.78</v>
+        <v>179.56</v>
       </c>
       <c r="G3">
         <v>258.6</v>
@@ -1539,28 +1539,28 @@
         <v>449.5</v>
       </c>
       <c r="M3">
-        <v>4.515934</v>
+        <v>9.031867999999999</v>
       </c>
       <c r="N3">
-        <v>444.984066</v>
+        <v>440.468132</v>
       </c>
       <c r="O3">
-        <v>64.967673636</v>
+        <v>64.30834727200001</v>
       </c>
       <c r="P3">
-        <v>380.016392364</v>
+        <v>376.159784728</v>
       </c>
       <c r="Q3">
-        <v>700.516392364</v>
+        <v>696.659784728</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08092306277363787</v>
+        <v>0.08122958269689609</v>
       </c>
       <c r="T3">
-        <v>0.8111561841486805</v>
+        <v>0.8182351662100715</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>99.53644140946258</v>
+        <v>49.7682207047313</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08046411504295817</v>
+        <v>0.08038483594001486</v>
       </c>
       <c r="C4">
-        <v>8604.434296804729</v>
+        <v>8534.197128040387</v>
       </c>
       <c r="D4">
-        <v>8525.394296804729</v>
+        <v>8544.937128040387</v>
       </c>
       <c r="E4">
-        <v>-1427.34</v>
+        <v>-1337.56</v>
       </c>
       <c r="F4">
-        <v>179.56</v>
+        <v>269.34</v>
       </c>
       <c r="G4">
         <v>258.6</v>
@@ -1621,28 +1621,28 @@
         <v>449.5</v>
       </c>
       <c r="M4">
-        <v>9.031867999999999</v>
+        <v>13.547802</v>
       </c>
       <c r="N4">
-        <v>440.468132</v>
+        <v>435.952198</v>
       </c>
       <c r="O4">
-        <v>64.30834727200001</v>
+        <v>63.649020908</v>
       </c>
       <c r="P4">
-        <v>376.159784728</v>
+        <v>372.303177092</v>
       </c>
       <c r="Q4">
-        <v>696.659784728</v>
+        <v>692.8031770919999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08122958269689609</v>
+        <v>0.08154242261857203</v>
       </c>
       <c r="T4">
-        <v>0.8182351662100715</v>
+        <v>0.8254601066644809</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>49.7682207047313</v>
+        <v>33.1788138031542</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08038483594001486</v>
+        <v>0.08030555683707155</v>
       </c>
       <c r="C5">
-        <v>8534.197128040387</v>
+        <v>8464.049761514952</v>
       </c>
       <c r="D5">
-        <v>8544.937128040387</v>
+        <v>8564.569761514953</v>
       </c>
       <c r="E5">
-        <v>-1337.56</v>
+        <v>-1247.78</v>
       </c>
       <c r="F5">
-        <v>269.34</v>
+        <v>359.12</v>
       </c>
       <c r="G5">
         <v>258.6</v>
@@ -1703,28 +1703,28 @@
         <v>449.5</v>
       </c>
       <c r="M5">
-        <v>13.547802</v>
+        <v>18.063736</v>
       </c>
       <c r="N5">
-        <v>435.952198</v>
+        <v>431.436264</v>
       </c>
       <c r="O5">
-        <v>63.649020908</v>
+        <v>62.989694544</v>
       </c>
       <c r="P5">
-        <v>372.303177092</v>
+        <v>368.446569456</v>
       </c>
       <c r="Q5">
-        <v>692.8031770919999</v>
+        <v>688.946569456</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08154242261857203</v>
+        <v>0.0818617800386162</v>
       </c>
       <c r="T5">
-        <v>0.8254601066644809</v>
+        <v>0.8328355667116906</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>33.1788138031542</v>
+        <v>24.88411035236565</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08030555683707155</v>
+        <v>0.08022627773412824</v>
       </c>
       <c r="C6">
-        <v>8464.049761514952</v>
+        <v>8393.992817635981</v>
       </c>
       <c r="D6">
-        <v>8564.569761514953</v>
+        <v>8584.29281763598</v>
       </c>
       <c r="E6">
-        <v>-1247.78</v>
+        <v>-1158</v>
       </c>
       <c r="F6">
-        <v>359.12</v>
+        <v>448.9</v>
       </c>
       <c r="G6">
         <v>258.6</v>
@@ -1785,28 +1785,28 @@
         <v>449.5</v>
       </c>
       <c r="M6">
-        <v>18.063736</v>
+        <v>22.57967</v>
       </c>
       <c r="N6">
-        <v>431.436264</v>
+        <v>426.92033</v>
       </c>
       <c r="O6">
-        <v>62.989694544</v>
+        <v>62.33036817999999</v>
       </c>
       <c r="P6">
-        <v>368.446569456</v>
+        <v>364.58996182</v>
       </c>
       <c r="Q6">
-        <v>688.946569456</v>
+        <v>685.08996182</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0818617800386162</v>
+        <v>0.08218786077276657</v>
       </c>
       <c r="T6">
-        <v>0.8328355667116906</v>
+        <v>0.8403662996019993</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>24.88411035236565</v>
+        <v>19.90728828189252</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08022627773412824</v>
+        <v>0.08014699863118492</v>
       </c>
       <c r="C7">
-        <v>8393.992817635981</v>
+        <v>8324.026922539082</v>
       </c>
       <c r="D7">
-        <v>8584.29281763598</v>
+        <v>8604.106922539082</v>
       </c>
       <c r="E7">
-        <v>-1158</v>
+        <v>-1068.22</v>
       </c>
       <c r="F7">
-        <v>448.9</v>
+        <v>538.6800000000001</v>
       </c>
       <c r="G7">
         <v>258.6</v>
@@ -1867,28 +1867,28 @@
         <v>449.5</v>
       </c>
       <c r="M7">
-        <v>22.57967</v>
+        <v>27.095604</v>
       </c>
       <c r="N7">
-        <v>426.92033</v>
+        <v>422.404396</v>
       </c>
       <c r="O7">
-        <v>62.33036817999999</v>
+        <v>61.671041816</v>
       </c>
       <c r="P7">
-        <v>364.58996182</v>
+        <v>360.733354184</v>
       </c>
       <c r="Q7">
-        <v>685.08996182</v>
+        <v>681.2333541840001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08218786077276657</v>
+        <v>0.08252087939487758</v>
       </c>
       <c r="T7">
-        <v>0.8403662996019993</v>
+        <v>0.8480572608516763</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.90728828189252</v>
+        <v>16.5894069015771</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08014699863118492</v>
+        <v>0.08006771952824161</v>
       </c>
       <c r="C8">
-        <v>8324.026922539082</v>
+        <v>8254.152708154172</v>
       </c>
       <c r="D8">
-        <v>8604.106922539082</v>
+        <v>8624.01270815417</v>
       </c>
       <c r="E8">
-        <v>-1068.22</v>
+        <v>-978.4400000000004</v>
       </c>
       <c r="F8">
-        <v>538.6799999999999</v>
+        <v>628.4599999999999</v>
       </c>
       <c r="G8">
         <v>258.6</v>
@@ -1949,28 +1949,28 @@
         <v>449.5</v>
       </c>
       <c r="M8">
-        <v>27.09560399999999</v>
+        <v>31.611538</v>
       </c>
       <c r="N8">
-        <v>422.404396</v>
+        <v>417.888462</v>
       </c>
       <c r="O8">
-        <v>61.671041816</v>
+        <v>61.011715452</v>
       </c>
       <c r="P8">
-        <v>360.733354184</v>
+        <v>356.876746548</v>
       </c>
       <c r="Q8">
-        <v>681.2333541840001</v>
+        <v>677.376746548</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08252087939487758</v>
+        <v>0.08286105970778668</v>
       </c>
       <c r="T8">
-        <v>0.8480572608516763</v>
+        <v>0.8559136191174753</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.5894069015771</v>
+        <v>14.21949162992323</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08006771952824161</v>
+        <v>0.07998844042529829</v>
       </c>
       <c r="C9">
-        <v>8254.152708154172</v>
+        <v>8184.370812272673</v>
       </c>
       <c r="D9">
-        <v>8624.01270815417</v>
+        <v>8644.010812272672</v>
       </c>
       <c r="E9">
-        <v>-978.4400000000003</v>
+        <v>-888.6600000000003</v>
       </c>
       <c r="F9">
-        <v>628.46</v>
+        <v>718.24</v>
       </c>
       <c r="G9">
         <v>258.6</v>
@@ -2031,28 +2031,28 @@
         <v>449.5</v>
       </c>
       <c r="M9">
-        <v>31.611538</v>
+        <v>36.127472</v>
       </c>
       <c r="N9">
-        <v>417.888462</v>
+        <v>413.372528</v>
       </c>
       <c r="O9">
-        <v>61.011715452</v>
+        <v>60.352389088</v>
       </c>
       <c r="P9">
-        <v>356.876746548</v>
+        <v>353.020138912</v>
       </c>
       <c r="Q9">
-        <v>677.376746548</v>
+        <v>673.520138912</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08286105970778668</v>
+        <v>0.08320863524488945</v>
       </c>
       <c r="T9">
-        <v>0.8559136191174753</v>
+        <v>0.8639407677803569</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.21949162992323</v>
+        <v>12.44205517618282</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07998844042529829</v>
+        <v>0.07990916132235498</v>
       </c>
       <c r="C10">
-        <v>8184.370812272673</v>
+        <v>8114.681878615605</v>
       </c>
       <c r="D10">
-        <v>8644.010812272672</v>
+        <v>8664.101878615606</v>
       </c>
       <c r="E10">
-        <v>-888.6600000000003</v>
+        <v>-798.8800000000003</v>
       </c>
       <c r="F10">
-        <v>718.24</v>
+        <v>808.02</v>
       </c>
       <c r="G10">
         <v>258.6</v>
@@ -2113,28 +2113,28 @@
         <v>449.5</v>
       </c>
       <c r="M10">
-        <v>36.127472</v>
+        <v>40.643406</v>
       </c>
       <c r="N10">
-        <v>413.372528</v>
+        <v>408.856594</v>
       </c>
       <c r="O10">
-        <v>60.352389088</v>
+        <v>59.69306272399999</v>
       </c>
       <c r="P10">
-        <v>353.020138912</v>
+        <v>349.163531276</v>
       </c>
       <c r="Q10">
-        <v>673.520138912</v>
+        <v>669.663531276</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08320863524488945</v>
+        <v>0.08356384980478569</v>
       </c>
       <c r="T10">
-        <v>0.8639407677803569</v>
+        <v>0.8721443372929721</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.44205517618282</v>
+        <v>11.0596046010514</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07990916132235498</v>
+        <v>0.07982988221941167</v>
       </c>
       <c r="C11">
-        <v>8114.681878615605</v>
+        <v>8045.086556902686</v>
       </c>
       <c r="D11">
-        <v>8664.101878615606</v>
+        <v>8684.286556902685</v>
       </c>
       <c r="E11">
-        <v>-798.8800000000003</v>
+        <v>-709.1000000000004</v>
       </c>
       <c r="F11">
-        <v>808.02</v>
+        <v>897.8</v>
       </c>
       <c r="G11">
         <v>258.6</v>
@@ -2195,28 +2195,28 @@
         <v>449.5</v>
       </c>
       <c r="M11">
-        <v>40.643406</v>
+        <v>45.15933999999999</v>
       </c>
       <c r="N11">
-        <v>408.856594</v>
+        <v>404.34066</v>
       </c>
       <c r="O11">
-        <v>59.69306272399999</v>
+        <v>59.03373636</v>
       </c>
       <c r="P11">
-        <v>349.163531276</v>
+        <v>345.30692364</v>
       </c>
       <c r="Q11">
-        <v>669.663531276</v>
+        <v>665.80692364</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08356384980478569</v>
+        <v>0.08392695802156852</v>
       </c>
       <c r="T11">
-        <v>0.8721443372929721</v>
+        <v>0.8805302083503123</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.0596046010514</v>
+        <v>9.95364414094626</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07982988221941167</v>
+        <v>0.07975060311646837</v>
       </c>
       <c r="C12">
-        <v>8045.086556902686</v>
+        <v>7975.585502922349</v>
       </c>
       <c r="D12">
-        <v>8684.286556902685</v>
+        <v>8704.565502922349</v>
       </c>
       <c r="E12">
-        <v>-709.1000000000003</v>
+        <v>-619.3200000000003</v>
       </c>
       <c r="F12">
-        <v>897.8000000000001</v>
+        <v>987.58</v>
       </c>
       <c r="G12">
         <v>258.6</v>
@@ -2277,28 +2277,28 @@
         <v>449.5</v>
       </c>
       <c r="M12">
-        <v>45.15934</v>
+        <v>49.675274</v>
       </c>
       <c r="N12">
-        <v>404.34066</v>
+        <v>399.824726</v>
       </c>
       <c r="O12">
-        <v>59.03373636</v>
+        <v>58.374409996</v>
       </c>
       <c r="P12">
-        <v>345.30692364</v>
+        <v>341.450316004</v>
       </c>
       <c r="Q12">
-        <v>665.80692364</v>
+        <v>661.950316004</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08392695802156852</v>
+        <v>0.08429822597355996</v>
       </c>
       <c r="T12">
-        <v>0.8805302083503123</v>
+        <v>0.8891045259482668</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.953644140946258</v>
+        <v>9.048767400860234</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07975060311646837</v>
+        <v>0.07982504401352504</v>
       </c>
       <c r="C13">
-        <v>7975.585502922349</v>
+        <v>7866.761422795119</v>
       </c>
       <c r="D13">
-        <v>8704.565502922349</v>
+        <v>8685.521422795118</v>
       </c>
       <c r="E13">
-        <v>-619.3200000000003</v>
+        <v>-529.5400000000004</v>
       </c>
       <c r="F13">
-        <v>987.58</v>
+        <v>1077.36</v>
       </c>
       <c r="G13">
         <v>258.6</v>
@@ -2359,45 +2359,45 @@
         <v>449.5</v>
       </c>
       <c r="M13">
-        <v>49.675274</v>
+        <v>55.80724799999999</v>
       </c>
       <c r="N13">
-        <v>399.824726</v>
+        <v>393.692752</v>
       </c>
       <c r="O13">
-        <v>58.374409996</v>
+        <v>57.47914179199999</v>
       </c>
       <c r="P13">
-        <v>341.450316004</v>
+        <v>336.213610208</v>
       </c>
       <c r="Q13">
-        <v>661.950316004</v>
+        <v>656.713610208</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08429822597355996</v>
+        <v>0.08467793183355118</v>
       </c>
       <c r="T13">
-        <v>0.8891045259482668</v>
+        <v>0.8978737144007202</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.146</v>
       </c>
       <c r="W13">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>9.048767400860234</v>
+        <v>8.054509335418224</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07982504401352504</v>
+        <v>0.07975857491058173</v>
       </c>
       <c r="C14">
-        <v>7866.761422795119</v>
+        <v>7793.982101389206</v>
       </c>
       <c r="D14">
-        <v>8685.521422795118</v>
+        <v>8702.522101389206</v>
       </c>
       <c r="E14">
-        <v>-529.5400000000004</v>
+        <v>-439.7600000000002</v>
       </c>
       <c r="F14">
-        <v>1077.36</v>
+        <v>1167.14</v>
       </c>
       <c r="G14">
         <v>258.6</v>
@@ -2441,28 +2441,28 @@
         <v>449.5</v>
       </c>
       <c r="M14">
-        <v>55.80724799999999</v>
+        <v>60.457852</v>
       </c>
       <c r="N14">
-        <v>393.692752</v>
+        <v>389.042148</v>
       </c>
       <c r="O14">
-        <v>57.47914179199999</v>
+        <v>56.800153608</v>
       </c>
       <c r="P14">
-        <v>336.213610208</v>
+        <v>332.241994392</v>
       </c>
       <c r="Q14">
-        <v>656.713610208</v>
+        <v>652.7419943919999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08467793183355118</v>
+        <v>0.08506636656388705</v>
       </c>
       <c r="T14">
-        <v>0.8978737144007202</v>
+        <v>0.9068444933923105</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.054509335418224</v>
+        <v>7.434931694232207</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07975857491058173</v>
+        <v>0.07969210580763843</v>
       </c>
       <c r="C15">
-        <v>7793.982101389206</v>
+        <v>7721.269463349739</v>
       </c>
       <c r="D15">
-        <v>8702.522101389206</v>
+        <v>8719.589463349739</v>
       </c>
       <c r="E15">
-        <v>-439.7600000000002</v>
+        <v>-349.9800000000002</v>
       </c>
       <c r="F15">
-        <v>1167.14</v>
+        <v>1256.92</v>
       </c>
       <c r="G15">
         <v>258.6</v>
@@ -2523,28 +2523,28 @@
         <v>449.5</v>
       </c>
       <c r="M15">
-        <v>60.457852</v>
+        <v>65.108456</v>
       </c>
       <c r="N15">
-        <v>389.042148</v>
+        <v>384.391544</v>
       </c>
       <c r="O15">
-        <v>56.800153608</v>
+        <v>56.121165424</v>
       </c>
       <c r="P15">
-        <v>332.241994392</v>
+        <v>328.270378576</v>
       </c>
       <c r="Q15">
-        <v>652.7419943919999</v>
+        <v>648.770378576</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08506636656388705</v>
+        <v>0.08546383466004467</v>
       </c>
       <c r="T15">
-        <v>0.9068444933923105</v>
+        <v>0.9160238951511471</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.434931694232207</v>
+        <v>6.903865144644191</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07969210580763843</v>
+        <v>0.07984340670469511</v>
       </c>
       <c r="C16">
-        <v>7721.269463349739</v>
+        <v>7592.736534795473</v>
       </c>
       <c r="D16">
-        <v>8719.589463349739</v>
+        <v>8680.836534795473</v>
       </c>
       <c r="E16">
-        <v>-349.9800000000002</v>
+        <v>-260.2</v>
       </c>
       <c r="F16">
-        <v>1256.92</v>
+        <v>1346.7</v>
       </c>
       <c r="G16">
         <v>258.6</v>
@@ -2605,45 +2605,45 @@
         <v>449.5</v>
       </c>
       <c r="M16">
-        <v>65.108456</v>
+        <v>72.04845000000002</v>
       </c>
       <c r="N16">
-        <v>384.391544</v>
+        <v>377.45155</v>
       </c>
       <c r="O16">
-        <v>56.121165424</v>
+        <v>55.1079263</v>
       </c>
       <c r="P16">
-        <v>328.270378576</v>
+        <v>322.3436237</v>
       </c>
       <c r="Q16">
-        <v>648.770378576</v>
+        <v>642.8436237000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08546383466004467</v>
+        <v>0.08587065494670013</v>
       </c>
       <c r="T16">
-        <v>0.9160238951511471</v>
+        <v>0.9254192828337211</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.146</v>
       </c>
       <c r="W16">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.903865144644191</v>
+        <v>6.238857324480955</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0798434067046951</v>
+        <v>0.07979145560175178</v>
       </c>
       <c r="C17">
-        <v>7592.736534795479</v>
+        <v>7516.223958166132</v>
       </c>
       <c r="D17">
-        <v>8680.836534795479</v>
+        <v>8694.103958166132</v>
       </c>
       <c r="E17">
-        <v>-260.2000000000003</v>
+        <v>-170.4200000000003</v>
       </c>
       <c r="F17">
-        <v>1346.7</v>
+        <v>1436.48</v>
       </c>
       <c r="G17">
         <v>258.6</v>
@@ -2687,28 +2687,28 @@
         <v>449.5</v>
       </c>
       <c r="M17">
-        <v>72.04845</v>
+        <v>76.85168</v>
       </c>
       <c r="N17">
-        <v>377.45155</v>
+        <v>372.64832</v>
       </c>
       <c r="O17">
-        <v>55.1079263</v>
+        <v>54.40665472</v>
       </c>
       <c r="P17">
-        <v>322.3436237</v>
+        <v>318.24166528</v>
       </c>
       <c r="Q17">
-        <v>642.8436237000001</v>
+        <v>638.74166528</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08587065494670013</v>
+        <v>0.0862871614306569</v>
       </c>
       <c r="T17">
-        <v>0.9254192828337211</v>
+        <v>0.9350383702230231</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.238857324480957</v>
+        <v>5.848928741700897</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07979145560175178</v>
+        <v>0.07985564849880847</v>
       </c>
       <c r="C18">
-        <v>7516.223958166132</v>
+        <v>7410.056082880006</v>
       </c>
       <c r="D18">
-        <v>8694.103958166132</v>
+        <v>8677.716082880006</v>
       </c>
       <c r="E18">
-        <v>-170.4200000000003</v>
+        <v>-80.6400000000001</v>
       </c>
       <c r="F18">
-        <v>1436.48</v>
+        <v>1526.26</v>
       </c>
       <c r="G18">
         <v>258.6</v>
@@ -2769,45 +2769,45 @@
         <v>449.5</v>
       </c>
       <c r="M18">
-        <v>76.85168</v>
+        <v>82.87591800000001</v>
       </c>
       <c r="N18">
-        <v>372.64832</v>
+        <v>366.624082</v>
       </c>
       <c r="O18">
-        <v>54.40665472</v>
+        <v>53.527115972</v>
       </c>
       <c r="P18">
-        <v>318.24166528</v>
+        <v>313.096966028</v>
       </c>
       <c r="Q18">
-        <v>638.74166528</v>
+        <v>633.596966028</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0862871614306569</v>
+        <v>0.0867137042154319</v>
       </c>
       <c r="T18">
-        <v>0.9350383702230231</v>
+        <v>0.9448892428506213</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.146</v>
       </c>
       <c r="W18">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>5.848928741700897</v>
+        <v>5.423770992195826</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07985564849880847</v>
+        <v>0.07981052939586514</v>
       </c>
       <c r="C19">
-        <v>7410.056082880006</v>
+        <v>7331.788128479156</v>
       </c>
       <c r="D19">
-        <v>8677.716082880006</v>
+        <v>8689.228128479155</v>
       </c>
       <c r="E19">
-        <v>-80.6400000000001</v>
+        <v>9.139999999999873</v>
       </c>
       <c r="F19">
-        <v>1526.26</v>
+        <v>1616.04</v>
       </c>
       <c r="G19">
         <v>258.6</v>
@@ -2851,28 +2851,28 @@
         <v>449.5</v>
       </c>
       <c r="M19">
-        <v>82.87591800000001</v>
+        <v>87.75097200000002</v>
       </c>
       <c r="N19">
-        <v>366.624082</v>
+        <v>361.749028</v>
       </c>
       <c r="O19">
-        <v>53.527115972</v>
+        <v>52.81535808799999</v>
       </c>
       <c r="P19">
-        <v>313.096966028</v>
+        <v>308.933669912</v>
       </c>
       <c r="Q19">
-        <v>633.596966028</v>
+        <v>629.4336699119999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0867137042154319</v>
+        <v>0.08715065048276238</v>
       </c>
       <c r="T19">
-        <v>0.9448892428506213</v>
+        <v>0.9549803806642585</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.423770992195826</v>
+        <v>5.12245038151828</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07981052939586515</v>
+        <v>0.07976541029292185</v>
       </c>
       <c r="C20">
-        <v>7331.788128479154</v>
+        <v>7253.55075890951</v>
       </c>
       <c r="D20">
-        <v>8689.228128479153</v>
+        <v>8700.77075890951</v>
       </c>
       <c r="E20">
-        <v>9.139999999999645</v>
+        <v>98.91999999999962</v>
       </c>
       <c r="F20">
-        <v>1616.04</v>
+        <v>1705.82</v>
       </c>
       <c r="G20">
         <v>258.6</v>
@@ -2933,28 +2933,28 @@
         <v>449.5</v>
       </c>
       <c r="M20">
-        <v>87.750972</v>
+        <v>92.626026</v>
       </c>
       <c r="N20">
-        <v>361.749028</v>
+        <v>356.873974</v>
       </c>
       <c r="O20">
-        <v>52.815358088</v>
+        <v>52.103600204</v>
       </c>
       <c r="P20">
-        <v>308.933669912</v>
+        <v>304.770373796</v>
       </c>
       <c r="Q20">
-        <v>629.433669912</v>
+        <v>625.2703737960001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08715065048276238</v>
+        <v>0.08759838554681709</v>
       </c>
       <c r="T20">
-        <v>0.9549803806642585</v>
+        <v>0.9653206823745289</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.122450381518281</v>
+        <v>4.852847729859424</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07976541029292185</v>
+        <v>0.07972029118997853</v>
       </c>
       <c r="C21">
-        <v>7253.55075890951</v>
+        <v>7175.344096218403</v>
       </c>
       <c r="D21">
-        <v>8700.77075890951</v>
+        <v>8712.344096218403</v>
       </c>
       <c r="E21">
-        <v>98.91999999999962</v>
+        <v>188.6999999999998</v>
       </c>
       <c r="F21">
-        <v>1705.82</v>
+        <v>1795.6</v>
       </c>
       <c r="G21">
         <v>258.6</v>
@@ -3015,28 +3015,28 @@
         <v>449.5</v>
       </c>
       <c r="M21">
-        <v>92.626026</v>
+        <v>97.50108000000002</v>
       </c>
       <c r="N21">
-        <v>356.873974</v>
+        <v>351.99892</v>
       </c>
       <c r="O21">
-        <v>52.103600204</v>
+        <v>51.39184231999999</v>
       </c>
       <c r="P21">
-        <v>304.770373796</v>
+        <v>300.60707768</v>
       </c>
       <c r="Q21">
-        <v>625.2703737960001</v>
+        <v>621.10707768</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08759838554681709</v>
+        <v>0.08805731398747317</v>
       </c>
       <c r="T21">
-        <v>0.9653206823745289</v>
+        <v>0.975919491627556</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.852847729859424</v>
+        <v>4.610205343366452</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07972029118997853</v>
+        <v>0.07967517208703523</v>
       </c>
       <c r="C22">
-        <v>7175.344096218403</v>
+        <v>7097.168263103365</v>
       </c>
       <c r="D22">
-        <v>8712.344096218403</v>
+        <v>8723.948263103364</v>
       </c>
       <c r="E22">
-        <v>188.6999999999998</v>
+        <v>278.4799999999998</v>
       </c>
       <c r="F22">
-        <v>1795.6</v>
+        <v>1885.38</v>
       </c>
       <c r="G22">
         <v>258.6</v>
@@ -3097,28 +3097,28 @@
         <v>449.5</v>
       </c>
       <c r="M22">
-        <v>97.50108000000002</v>
+        <v>102.376134</v>
       </c>
       <c r="N22">
-        <v>351.99892</v>
+        <v>347.123866</v>
       </c>
       <c r="O22">
-        <v>51.39184231999999</v>
+        <v>50.680084436</v>
       </c>
       <c r="P22">
-        <v>300.60707768</v>
+        <v>296.443781564</v>
       </c>
       <c r="Q22">
-        <v>621.10707768</v>
+        <v>616.943781564</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08805731398747317</v>
+        <v>0.08852786086966483</v>
       </c>
       <c r="T22">
-        <v>0.975919491627556</v>
+        <v>0.9867866251654697</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.610205343366452</v>
+        <v>4.390671755587098</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07967517208703521</v>
+        <v>0.07981793298409191</v>
       </c>
       <c r="C23">
-        <v>7097.168263103368</v>
+        <v>6970.777023951969</v>
       </c>
       <c r="D23">
-        <v>8723.948263103368</v>
+        <v>8687.337023951968</v>
       </c>
       <c r="E23">
-        <v>278.4799999999996</v>
+        <v>368.2599999999998</v>
       </c>
       <c r="F23">
-        <v>1885.38</v>
+        <v>1975.16</v>
       </c>
       <c r="G23">
         <v>258.6</v>
@@ -3179,45 +3179,45 @@
         <v>449.5</v>
       </c>
       <c r="M23">
-        <v>102.376134</v>
+        <v>109.226348</v>
       </c>
       <c r="N23">
-        <v>347.123866</v>
+        <v>340.273652</v>
       </c>
       <c r="O23">
-        <v>50.680084436</v>
+        <v>49.67995319199999</v>
       </c>
       <c r="P23">
-        <v>296.443781564</v>
+        <v>290.593698808</v>
       </c>
       <c r="Q23">
-        <v>616.943781564</v>
+        <v>611.093698808</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08852786086966483</v>
+        <v>0.08901047305652809</v>
       </c>
       <c r="T23">
-        <v>0.9867866251654697</v>
+        <v>0.9979324031530737</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.146</v>
       </c>
       <c r="W23">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.390671755587098</v>
+        <v>4.11530741648526</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07981793298409191</v>
+        <v>0.0797813538811486</v>
       </c>
       <c r="C24">
-        <v>6970.777023951969</v>
+        <v>6890.348475822128</v>
       </c>
       <c r="D24">
-        <v>8687.337023951968</v>
+        <v>8696.688475822128</v>
       </c>
       <c r="E24">
-        <v>368.2599999999998</v>
+        <v>458.0399999999997</v>
       </c>
       <c r="F24">
-        <v>1975.16</v>
+        <v>2064.94</v>
       </c>
       <c r="G24">
         <v>258.6</v>
@@ -3261,28 +3261,28 @@
         <v>449.5</v>
       </c>
       <c r="M24">
-        <v>109.226348</v>
+        <v>114.191182</v>
       </c>
       <c r="N24">
-        <v>340.273652</v>
+        <v>335.308818</v>
       </c>
       <c r="O24">
-        <v>49.67995319199999</v>
+        <v>48.95508742799999</v>
       </c>
       <c r="P24">
-        <v>290.593698808</v>
+        <v>286.353730572</v>
       </c>
       <c r="Q24">
-        <v>611.093698808</v>
+        <v>606.8537305719999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08901047305652809</v>
+        <v>0.0895056206248683</v>
       </c>
       <c r="T24">
-        <v>0.9979324031530737</v>
+        <v>1.009367681867628</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.11530741648526</v>
+        <v>3.936381007072857</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0797813538811486</v>
+        <v>0.07974477477820528</v>
       </c>
       <c r="C25">
-        <v>6890.348475822128</v>
+        <v>6809.94008205907</v>
       </c>
       <c r="D25">
-        <v>8696.688475822128</v>
+        <v>8706.06008205907</v>
       </c>
       <c r="E25">
-        <v>458.0399999999997</v>
+        <v>547.8199999999999</v>
       </c>
       <c r="F25">
-        <v>2064.94</v>
+        <v>2154.72</v>
       </c>
       <c r="G25">
         <v>258.6</v>
@@ -3343,28 +3343,28 @@
         <v>449.5</v>
       </c>
       <c r="M25">
-        <v>114.191182</v>
+        <v>119.156016</v>
       </c>
       <c r="N25">
-        <v>335.308818</v>
+        <v>330.343984</v>
       </c>
       <c r="O25">
-        <v>48.95508742799999</v>
+        <v>48.23022166399999</v>
       </c>
       <c r="P25">
-        <v>286.353730572</v>
+        <v>282.113762336</v>
       </c>
       <c r="Q25">
-        <v>606.8537305719999</v>
+        <v>602.613762336</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0895056206248683</v>
+        <v>0.09001379839237537</v>
       </c>
       <c r="T25">
-        <v>1.009367681867628</v>
+        <v>1.021103888969408</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.936381007072857</v>
+        <v>3.772365131778155</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07974477477820528</v>
+        <v>0.07970819567526197</v>
       </c>
       <c r="C26">
-        <v>6809.940082059071</v>
+        <v>6729.551907888501</v>
       </c>
       <c r="D26">
-        <v>8706.06008205907</v>
+        <v>8715.451907888501</v>
       </c>
       <c r="E26">
-        <v>547.8199999999995</v>
+        <v>637.5999999999997</v>
       </c>
       <c r="F26">
-        <v>2154.72</v>
+        <v>2244.5</v>
       </c>
       <c r="G26">
         <v>258.6</v>
@@ -3425,28 +3425,28 @@
         <v>449.5</v>
       </c>
       <c r="M26">
-        <v>119.156016</v>
+        <v>124.12085</v>
       </c>
       <c r="N26">
-        <v>330.343984</v>
+        <v>325.37915</v>
       </c>
       <c r="O26">
-        <v>48.23022166399999</v>
+        <v>47.5053559</v>
       </c>
       <c r="P26">
-        <v>282.113762336</v>
+        <v>277.8737941</v>
       </c>
       <c r="Q26">
-        <v>602.613762336</v>
+        <v>598.3737940999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09001379839237537</v>
+        <v>0.09053552756701595</v>
       </c>
       <c r="T26">
-        <v>1.021103888969408</v>
+        <v>1.033153061593902</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.772365131778155</v>
+        <v>3.621470526507029</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07970819567526197</v>
+        <v>0.07967161657231867</v>
       </c>
       <c r="C27">
-        <v>6729.551907888501</v>
+        <v>6649.184018817879</v>
       </c>
       <c r="D27">
-        <v>8715.451907888501</v>
+        <v>8724.86401881788</v>
       </c>
       <c r="E27">
-        <v>637.5999999999997</v>
+        <v>727.3799999999999</v>
       </c>
       <c r="F27">
-        <v>2244.5</v>
+        <v>2334.28</v>
       </c>
       <c r="G27">
         <v>258.6</v>
@@ -3507,28 +3507,28 @@
         <v>449.5</v>
       </c>
       <c r="M27">
-        <v>124.12085</v>
+        <v>129.085684</v>
       </c>
       <c r="N27">
-        <v>325.37915</v>
+        <v>320.414316</v>
       </c>
       <c r="O27">
-        <v>47.5053559</v>
+        <v>46.780490136</v>
       </c>
       <c r="P27">
-        <v>277.8737941</v>
+        <v>273.633825864</v>
       </c>
       <c r="Q27">
-        <v>598.3737940999999</v>
+        <v>594.133825864</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09053552756701595</v>
+        <v>0.09107135753016035</v>
       </c>
       <c r="T27">
-        <v>1.033153061593902</v>
+        <v>1.045527887532572</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.621470526507029</v>
+        <v>3.482183198564451</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07967161657231867</v>
+        <v>0.07963503746937535</v>
       </c>
       <c r="C28">
-        <v>6649.184018817879</v>
+        <v>6568.83648063796</v>
       </c>
       <c r="D28">
-        <v>8724.86401881788</v>
+        <v>8734.296480637959</v>
       </c>
       <c r="E28">
-        <v>727.3799999999999</v>
+        <v>817.1599999999996</v>
       </c>
       <c r="F28">
-        <v>2334.28</v>
+        <v>2424.06</v>
       </c>
       <c r="G28">
         <v>258.6</v>
@@ -3589,28 +3589,28 @@
         <v>449.5</v>
       </c>
       <c r="M28">
-        <v>129.085684</v>
+        <v>134.050518</v>
       </c>
       <c r="N28">
-        <v>320.414316</v>
+        <v>315.449482</v>
       </c>
       <c r="O28">
-        <v>46.780490136</v>
+        <v>46.055624372</v>
       </c>
       <c r="P28">
-        <v>273.633825864</v>
+        <v>269.393857628</v>
       </c>
       <c r="Q28">
-        <v>594.133825864</v>
+        <v>589.893857628</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09107135753016035</v>
+        <v>0.0916218677662676</v>
       </c>
       <c r="T28">
-        <v>1.045527887532572</v>
+        <v>1.058241749798328</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.482183198564451</v>
+        <v>3.353213450469471</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07963503746937535</v>
+        <v>0.07959845836643203</v>
       </c>
       <c r="C29">
-        <v>6568.83648063796</v>
+        <v>6488.509359424288</v>
       </c>
       <c r="D29">
-        <v>8734.296480637959</v>
+        <v>8743.749359424288</v>
       </c>
       <c r="E29">
-        <v>817.1599999999996</v>
+        <v>906.9399999999998</v>
       </c>
       <c r="F29">
-        <v>2424.06</v>
+        <v>2513.84</v>
       </c>
       <c r="G29">
         <v>258.6</v>
@@ -3671,28 +3671,28 @@
         <v>449.5</v>
       </c>
       <c r="M29">
-        <v>134.050518</v>
+        <v>139.015352</v>
       </c>
       <c r="N29">
-        <v>315.449482</v>
+        <v>310.484648</v>
       </c>
       <c r="O29">
-        <v>46.055624372</v>
+        <v>45.330758608</v>
       </c>
       <c r="P29">
-        <v>269.393857628</v>
+        <v>265.153889392</v>
       </c>
       <c r="Q29">
-        <v>589.893857628</v>
+        <v>585.653889392</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0916218677662676</v>
+        <v>0.09218766995337782</v>
       </c>
       <c r="T29">
-        <v>1.058241749798328</v>
+        <v>1.0713087749048</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.353213450469471</v>
+        <v>3.233455827238419</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07959845836643203</v>
+        <v>0.07956187926348872</v>
       </c>
       <c r="C30">
-        <v>6488.509359424288</v>
+        <v>6408.202721538782</v>
       </c>
       <c r="D30">
-        <v>8743.749359424288</v>
+        <v>8753.222721538783</v>
       </c>
       <c r="E30">
-        <v>906.9399999999998</v>
+        <v>996.72</v>
       </c>
       <c r="F30">
-        <v>2513.84</v>
+        <v>2603.62</v>
       </c>
       <c r="G30">
         <v>258.6</v>
@@ -3753,28 +3753,28 @@
         <v>449.5</v>
       </c>
       <c r="M30">
-        <v>139.015352</v>
+        <v>143.980186</v>
       </c>
       <c r="N30">
-        <v>310.484648</v>
+        <v>305.519814</v>
       </c>
       <c r="O30">
-        <v>45.330758608</v>
+        <v>44.605892844</v>
       </c>
       <c r="P30">
-        <v>265.153889392</v>
+        <v>260.913921156</v>
       </c>
       <c r="Q30">
-        <v>585.653889392</v>
+        <v>581.413921156</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09218766995337782</v>
+        <v>0.0927694102302658</v>
       </c>
       <c r="T30">
-        <v>1.0713087749048</v>
+        <v>1.084743885225538</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.233455827238419</v>
+        <v>3.121957350437094</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07956187926348872</v>
+        <v>0.0795253001605454</v>
       </c>
       <c r="C31">
-        <v>6408.202721538783</v>
+        <v>6327.91663363127</v>
       </c>
       <c r="D31">
-        <v>8753.222721538783</v>
+        <v>8762.716633631269</v>
       </c>
       <c r="E31">
-        <v>996.7199999999996</v>
+        <v>1086.5</v>
       </c>
       <c r="F31">
-        <v>2603.62</v>
+        <v>2693.4</v>
       </c>
       <c r="G31">
         <v>258.6</v>
@@ -3835,28 +3835,28 @@
         <v>449.5</v>
       </c>
       <c r="M31">
-        <v>143.980186</v>
+        <v>148.94502</v>
       </c>
       <c r="N31">
-        <v>305.519814</v>
+        <v>300.55498</v>
       </c>
       <c r="O31">
-        <v>44.605892844</v>
+        <v>43.88102708</v>
       </c>
       <c r="P31">
-        <v>260.913921156</v>
+        <v>256.67395292</v>
       </c>
       <c r="Q31">
-        <v>581.413921156</v>
+        <v>577.17395292</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0927694102302658</v>
+        <v>0.09336777165792201</v>
       </c>
       <c r="T31">
-        <v>1.084743885225538</v>
+        <v>1.098562855841155</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.121957350437094</v>
+        <v>3.017892105422524</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0795253001605454</v>
+        <v>0.08015057105760208</v>
       </c>
       <c r="C32">
-        <v>6327.91663363127</v>
+        <v>6078.63210367815</v>
       </c>
       <c r="D32">
-        <v>8762.716633631269</v>
+        <v>8603.21210367815</v>
       </c>
       <c r="E32">
-        <v>1086.5</v>
+        <v>1176.28</v>
       </c>
       <c r="F32">
-        <v>2693.4</v>
+        <v>2783.18</v>
       </c>
       <c r="G32">
         <v>258.6</v>
@@ -3917,45 +3917,45 @@
         <v>449.5</v>
       </c>
       <c r="M32">
-        <v>148.94502</v>
+        <v>160.867804</v>
       </c>
       <c r="N32">
-        <v>300.55498</v>
+        <v>288.632196</v>
       </c>
       <c r="O32">
-        <v>43.88102708</v>
+        <v>42.140300616</v>
       </c>
       <c r="P32">
-        <v>256.67395292</v>
+        <v>246.491895384</v>
       </c>
       <c r="Q32">
-        <v>577.17395292</v>
+        <v>566.991895384</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09336777165792201</v>
+        <v>0.0939834768950755</v>
       </c>
       <c r="T32">
-        <v>1.098562855841155</v>
+        <v>1.112782376329688</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.146</v>
       </c>
       <c r="W32">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.017892105422524</v>
+        <v>2.794219780609425</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08015057105760208</v>
+        <v>0.08013534195465877</v>
       </c>
       <c r="C33">
-        <v>6078.63210367815</v>
+        <v>5992.667973720833</v>
       </c>
       <c r="D33">
-        <v>8603.21210367815</v>
+        <v>8607.027973720833</v>
       </c>
       <c r="E33">
-        <v>1176.28</v>
+        <v>1266.06</v>
       </c>
       <c r="F33">
-        <v>2783.18</v>
+        <v>2872.96</v>
       </c>
       <c r="G33">
         <v>258.6</v>
@@ -3999,28 +3999,28 @@
         <v>449.5</v>
       </c>
       <c r="M33">
-        <v>160.867804</v>
+        <v>166.057088</v>
       </c>
       <c r="N33">
-        <v>288.632196</v>
+        <v>283.442912</v>
       </c>
       <c r="O33">
-        <v>42.140300616</v>
+        <v>41.38266515199999</v>
       </c>
       <c r="P33">
-        <v>246.491895384</v>
+        <v>242.060246848</v>
       </c>
       <c r="Q33">
-        <v>566.991895384</v>
+        <v>562.560246848</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0939834768950755</v>
+        <v>0.09461729110979232</v>
       </c>
       <c r="T33">
-        <v>1.112782376329688</v>
+        <v>1.127420118009061</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.794219780609425</v>
+        <v>2.70690041246538</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08013534195465877</v>
+        <v>0.08012011285171547</v>
       </c>
       <c r="C34">
-        <v>5992.667973720833</v>
+        <v>5906.707230248747</v>
       </c>
       <c r="D34">
-        <v>8607.027973720833</v>
+        <v>8610.847230248746</v>
       </c>
       <c r="E34">
-        <v>1266.06</v>
+        <v>1355.84</v>
       </c>
       <c r="F34">
-        <v>2872.96</v>
+        <v>2962.74</v>
       </c>
       <c r="G34">
         <v>258.6</v>
@@ -4081,28 +4081,28 @@
         <v>449.5</v>
       </c>
       <c r="M34">
-        <v>166.057088</v>
+        <v>171.246372</v>
       </c>
       <c r="N34">
-        <v>283.442912</v>
+        <v>278.2536279999999</v>
       </c>
       <c r="O34">
-        <v>41.38266515199999</v>
+        <v>40.62502968799999</v>
       </c>
       <c r="P34">
-        <v>242.060246848</v>
+        <v>237.628598312</v>
       </c>
       <c r="Q34">
-        <v>562.560246848</v>
+        <v>558.1285983119999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09461729110979232</v>
+        <v>0.09527002515181413</v>
       </c>
       <c r="T34">
-        <v>1.127420118009061</v>
+        <v>1.14249480720125</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.70690041246538</v>
+        <v>2.624873127239156</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08012011285171547</v>
+        <v>0.08010488374877214</v>
       </c>
       <c r="C35">
-        <v>5906.707230248747</v>
+        <v>5820.749877772027</v>
       </c>
       <c r="D35">
-        <v>8610.847230248746</v>
+        <v>8614.669877772027</v>
       </c>
       <c r="E35">
-        <v>1355.84</v>
+        <v>1445.62</v>
       </c>
       <c r="F35">
-        <v>2962.74</v>
+        <v>3052.52</v>
       </c>
       <c r="G35">
         <v>258.6</v>
@@ -4163,28 +4163,28 @@
         <v>449.5</v>
       </c>
       <c r="M35">
-        <v>171.246372</v>
+        <v>176.4356560000001</v>
       </c>
       <c r="N35">
-        <v>278.2536279999999</v>
+        <v>273.0643439999999</v>
       </c>
       <c r="O35">
-        <v>40.62502968799999</v>
+        <v>39.86739422399999</v>
       </c>
       <c r="P35">
-        <v>237.628598312</v>
+        <v>233.196949776</v>
       </c>
       <c r="Q35">
-        <v>558.1285983119999</v>
+        <v>553.696949776</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09527002515181413</v>
+        <v>0.09594253901329114</v>
       </c>
       <c r="T35">
-        <v>1.14249480720125</v>
+        <v>1.158026305156839</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.624873127239156</v>
+        <v>2.547670976438004</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08010488374877214</v>
+        <v>0.08113580464582884</v>
       </c>
       <c r="C36">
-        <v>5820.749877772027</v>
+        <v>5479.637177490972</v>
       </c>
       <c r="D36">
-        <v>8614.669877772027</v>
+        <v>8363.337177490972</v>
       </c>
       <c r="E36">
-        <v>1445.62</v>
+        <v>1535.4</v>
       </c>
       <c r="F36">
-        <v>3052.52</v>
+        <v>3142.3</v>
       </c>
       <c r="G36">
         <v>258.6</v>
@@ -4245,45 +4245,45 @@
         <v>449.5</v>
       </c>
       <c r="M36">
-        <v>176.4356560000001</v>
+        <v>192.62299</v>
       </c>
       <c r="N36">
-        <v>273.0643439999999</v>
+        <v>256.87701</v>
       </c>
       <c r="O36">
-        <v>39.86739422399999</v>
+        <v>37.50404346</v>
       </c>
       <c r="P36">
-        <v>233.196949776</v>
+        <v>219.37296654</v>
       </c>
       <c r="Q36">
-        <v>553.696949776</v>
+        <v>539.87296654</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09594253901329114</v>
+        <v>0.09663574560896744</v>
       </c>
       <c r="T36">
-        <v>1.158026305156839</v>
+        <v>1.174035695357216</v>
       </c>
       <c r="U36">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V36">
         <v>0.146</v>
       </c>
       <c r="W36">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.547670976438004</v>
+        <v>2.333573993426226</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08113580464582884</v>
+        <v>0.08115046554288552</v>
       </c>
       <c r="C37">
-        <v>5479.637177490972</v>
+        <v>5386.388651022467</v>
       </c>
       <c r="D37">
-        <v>8363.337177490972</v>
+        <v>8359.868651022467</v>
       </c>
       <c r="E37">
-        <v>1535.4</v>
+        <v>1625.18</v>
       </c>
       <c r="F37">
-        <v>3142.3</v>
+        <v>3232.08</v>
       </c>
       <c r="G37">
         <v>258.6</v>
@@ -4327,28 +4327,28 @@
         <v>449.5</v>
       </c>
       <c r="M37">
-        <v>192.62299</v>
+        <v>198.126504</v>
       </c>
       <c r="N37">
-        <v>256.87701</v>
+        <v>251.373496</v>
       </c>
       <c r="O37">
-        <v>37.50404346</v>
+        <v>36.700530416</v>
       </c>
       <c r="P37">
-        <v>219.37296654</v>
+        <v>214.672965584</v>
       </c>
       <c r="Q37">
-        <v>539.87296654</v>
+        <v>535.1729655839999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09663574560896744</v>
+        <v>0.09735061491075864</v>
       </c>
       <c r="T37">
-        <v>1.174035695357216</v>
+        <v>1.190545379001354</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.333573993426226</v>
+        <v>2.268752493608831</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08115046554288552</v>
+        <v>0.08204987043994222</v>
       </c>
       <c r="C38">
-        <v>5386.388651022467</v>
+        <v>5089.189790976125</v>
       </c>
       <c r="D38">
-        <v>8359.868651022467</v>
+        <v>8152.449790976125</v>
       </c>
       <c r="E38">
-        <v>1625.18</v>
+        <v>1714.96</v>
       </c>
       <c r="F38">
-        <v>3232.08</v>
+        <v>3321.86</v>
       </c>
       <c r="G38">
         <v>258.6</v>
@@ -4409,45 +4409,45 @@
         <v>449.5</v>
       </c>
       <c r="M38">
-        <v>198.126504</v>
+        <v>212.931226</v>
       </c>
       <c r="N38">
-        <v>251.373496</v>
+        <v>236.568774</v>
       </c>
       <c r="O38">
-        <v>36.700530416</v>
+        <v>34.539041004</v>
       </c>
       <c r="P38">
-        <v>214.672965584</v>
+        <v>202.029732996</v>
       </c>
       <c r="Q38">
-        <v>535.1729655840001</v>
+        <v>522.529732996</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09735061491075864</v>
+        <v>0.09808817847609874</v>
       </c>
       <c r="T38">
-        <v>1.190545379001354</v>
+        <v>1.207579179586576</v>
       </c>
       <c r="U38">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.146</v>
       </c>
       <c r="W38">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.268752493608831</v>
+        <v>2.111010247036289</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08204987043994222</v>
+        <v>0.0820884433369989</v>
       </c>
       <c r="C39">
-        <v>5089.189790976125</v>
+        <v>4990.744122856202</v>
       </c>
       <c r="D39">
-        <v>8152.449790976125</v>
+        <v>8143.784122856202</v>
       </c>
       <c r="E39">
-        <v>1714.96</v>
+        <v>1804.74</v>
       </c>
       <c r="F39">
-        <v>3321.86</v>
+        <v>3411.64</v>
       </c>
       <c r="G39">
         <v>258.6</v>
@@ -4491,28 +4491,28 @@
         <v>449.5</v>
       </c>
       <c r="M39">
-        <v>212.931226</v>
+        <v>218.686124</v>
       </c>
       <c r="N39">
-        <v>236.568774</v>
+        <v>230.813876</v>
       </c>
       <c r="O39">
-        <v>34.539041004</v>
+        <v>33.698825896</v>
       </c>
       <c r="P39">
-        <v>202.029732996</v>
+        <v>197.115050104</v>
       </c>
       <c r="Q39">
-        <v>522.529732996</v>
+        <v>517.615050104</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09808817847609874</v>
+        <v>0.09884953441451434</v>
       </c>
       <c r="T39">
-        <v>1.207579179586576</v>
+        <v>1.225162457610031</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.111010247036289</v>
+        <v>2.055457345798493</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0820884433369989</v>
+        <v>0.08212701623405558</v>
       </c>
       <c r="C40">
-        <v>4990.744122856202</v>
+        <v>4892.316857564751</v>
       </c>
       <c r="D40">
-        <v>8143.784122856202</v>
+        <v>8135.13685756475</v>
       </c>
       <c r="E40">
-        <v>1804.74</v>
+        <v>1894.52</v>
       </c>
       <c r="F40">
-        <v>3411.64</v>
+        <v>3501.42</v>
       </c>
       <c r="G40">
         <v>258.6</v>
@@ -4573,28 +4573,28 @@
         <v>449.5</v>
       </c>
       <c r="M40">
-        <v>218.686124</v>
+        <v>224.441022</v>
       </c>
       <c r="N40">
-        <v>230.813876</v>
+        <v>225.058978</v>
       </c>
       <c r="O40">
-        <v>33.698825896</v>
+        <v>32.85861078799999</v>
       </c>
       <c r="P40">
-        <v>197.115050104</v>
+        <v>192.200367212</v>
       </c>
       <c r="Q40">
-        <v>517.615050104</v>
+        <v>512.7003672119999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09884953441451434</v>
+        <v>0.09963585284271406</v>
       </c>
       <c r="T40">
-        <v>1.225162457610031</v>
+        <v>1.243322236552288</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.055457345798493</v>
+        <v>2.002753311290839</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08212701623405558</v>
+        <v>0.08616230913111227</v>
       </c>
       <c r="C41">
-        <v>4892.316857564751</v>
+        <v>3989.212231580684</v>
       </c>
       <c r="D41">
-        <v>8135.13685756475</v>
+        <v>7321.812231580684</v>
       </c>
       <c r="E41">
-        <v>1894.52</v>
+        <v>1984.3</v>
       </c>
       <c r="F41">
-        <v>3501.42</v>
+        <v>3591.2</v>
       </c>
       <c r="G41">
         <v>258.6</v>
@@ -4655,45 +4655,45 @@
         <v>449.5</v>
       </c>
       <c r="M41">
-        <v>224.441022</v>
+        <v>272.2129600000001</v>
       </c>
       <c r="N41">
-        <v>225.058978</v>
+        <v>177.2870399999999</v>
       </c>
       <c r="O41">
-        <v>32.85861078799999</v>
+        <v>25.88390783999999</v>
       </c>
       <c r="P41">
-        <v>192.200367212</v>
+        <v>151.40313216</v>
       </c>
       <c r="Q41">
-        <v>512.7003672119999</v>
+        <v>471.9031321599999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09963585284271406</v>
+        <v>0.1004483818851871</v>
       </c>
       <c r="T41">
-        <v>1.243322236552288</v>
+        <v>1.262087341459287</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V41">
         <v>0.146</v>
       </c>
       <c r="W41">
-        <v>0.0547414</v>
+        <v>0.0647332</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.002753311290839</v>
+        <v>1.651280673778353</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08616230913111227</v>
+        <v>0.08630080002816896</v>
       </c>
       <c r="C42">
-        <v>3989.212231580684</v>
+        <v>3874.39558185211</v>
       </c>
       <c r="D42">
-        <v>7321.812231580684</v>
+        <v>7296.77558185211</v>
       </c>
       <c r="E42">
-        <v>1984.3</v>
+        <v>2074.08</v>
       </c>
       <c r="F42">
-        <v>3591.2</v>
+        <v>3680.98</v>
       </c>
       <c r="G42">
         <v>258.6</v>
@@ -4737,28 +4737,28 @@
         <v>449.5</v>
       </c>
       <c r="M42">
-        <v>272.2129600000001</v>
+        <v>279.0182840000001</v>
       </c>
       <c r="N42">
-        <v>177.2870399999999</v>
+        <v>170.4817159999999</v>
       </c>
       <c r="O42">
-        <v>25.88390783999999</v>
+        <v>24.89033053599999</v>
       </c>
       <c r="P42">
-        <v>151.40313216</v>
+        <v>145.591385464</v>
       </c>
       <c r="Q42">
-        <v>471.9031321599999</v>
+        <v>466.0913854639999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1004483818851871</v>
+        <v>0.1012884542850321</v>
       </c>
       <c r="T42">
-        <v>1.262087341459287</v>
+        <v>1.28148855161737</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.651280673778353</v>
+        <v>1.611005535393515</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08630080002816896</v>
+        <v>0.08643929092522565</v>
       </c>
       <c r="C43">
-        <v>3874.39558185211</v>
+        <v>3759.749572309489</v>
       </c>
       <c r="D43">
-        <v>7296.77558185211</v>
+        <v>7271.909572309489</v>
       </c>
       <c r="E43">
-        <v>2074.08</v>
+        <v>2163.86</v>
       </c>
       <c r="F43">
-        <v>3680.98</v>
+        <v>3770.76</v>
       </c>
       <c r="G43">
         <v>258.6</v>
@@ -4819,28 +4819,28 @@
         <v>449.5</v>
       </c>
       <c r="M43">
-        <v>279.0182840000001</v>
+        <v>285.823608</v>
       </c>
       <c r="N43">
-        <v>170.4817159999999</v>
+        <v>163.676392</v>
       </c>
       <c r="O43">
-        <v>24.89033053599999</v>
+        <v>23.89675323199999</v>
       </c>
       <c r="P43">
-        <v>145.591385464</v>
+        <v>139.779638768</v>
       </c>
       <c r="Q43">
-        <v>466.0913854639999</v>
+        <v>460.279638768</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1012884542850321</v>
+        <v>0.1021574946986649</v>
       </c>
       <c r="T43">
-        <v>1.28148855161737</v>
+        <v>1.301558769022284</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.611005535393515</v>
+        <v>1.572648260741289</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08643929092522565</v>
+        <v>0.08657778182228233</v>
       </c>
       <c r="C44">
-        <v>3759.749572309489</v>
+        <v>3645.272464350715</v>
       </c>
       <c r="D44">
-        <v>7271.909572309489</v>
+        <v>7247.212464350715</v>
       </c>
       <c r="E44">
-        <v>2163.86</v>
+        <v>2253.639999999999</v>
       </c>
       <c r="F44">
-        <v>3770.76</v>
+        <v>3860.54</v>
       </c>
       <c r="G44">
         <v>258.6</v>
@@ -4901,28 +4901,28 @@
         <v>449.5</v>
       </c>
       <c r="M44">
-        <v>285.823608</v>
+        <v>292.628932</v>
       </c>
       <c r="N44">
-        <v>163.676392</v>
+        <v>156.871068</v>
       </c>
       <c r="O44">
-        <v>23.896753232</v>
+        <v>22.903175928</v>
       </c>
       <c r="P44">
-        <v>139.779638768</v>
+        <v>133.967892072</v>
       </c>
       <c r="Q44">
-        <v>460.279638768</v>
+        <v>454.467892072</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1021574946986649</v>
+        <v>0.10305702775839</v>
       </c>
       <c r="T44">
-        <v>1.301558769022284</v>
+        <v>1.322333204581756</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.572648260741289</v>
+        <v>1.536075045375212</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08657778182228233</v>
+        <v>0.08671627271933902</v>
       </c>
       <c r="C45">
-        <v>3645.272464350715</v>
+        <v>3530.962542912541</v>
       </c>
       <c r="D45">
-        <v>7247.212464350715</v>
+        <v>7222.682542912541</v>
       </c>
       <c r="E45">
-        <v>2253.639999999999</v>
+        <v>2343.42</v>
       </c>
       <c r="F45">
-        <v>3860.54</v>
+        <v>3950.32</v>
       </c>
       <c r="G45">
         <v>258.6</v>
@@ -4983,28 +4983,28 @@
         <v>449.5</v>
       </c>
       <c r="M45">
-        <v>292.628932</v>
+        <v>299.4342560000001</v>
       </c>
       <c r="N45">
-        <v>156.871068</v>
+        <v>150.0657439999999</v>
       </c>
       <c r="O45">
-        <v>22.903175928</v>
+        <v>21.90959862399999</v>
       </c>
       <c r="P45">
-        <v>133.967892072</v>
+        <v>128.156145376</v>
       </c>
       <c r="Q45">
-        <v>454.467892072</v>
+        <v>448.6561453759999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.10305702775839</v>
+        <v>0.1039886869988197</v>
       </c>
       <c r="T45">
-        <v>1.322333204581756</v>
+        <v>1.343849584268352</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.536075045375212</v>
+        <v>1.501164248889412</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08671627271933902</v>
+        <v>0.1039266657614567</v>
       </c>
       <c r="C46">
-        <v>3530.962542912541</v>
+        <v>1302.659650646583</v>
       </c>
       <c r="D46">
-        <v>7222.682542912541</v>
+        <v>5084.159650646583</v>
       </c>
       <c r="E46">
-        <v>2343.42</v>
+        <v>2433.2</v>
       </c>
       <c r="F46">
-        <v>3950.32</v>
+        <v>4040.1</v>
       </c>
       <c r="G46">
         <v>258.6</v>
@@ -5065,45 +5065,45 @@
         <v>449.5</v>
       </c>
       <c r="M46">
-        <v>299.4342560000001</v>
+        <v>479.15586</v>
       </c>
       <c r="N46">
-        <v>150.0657439999999</v>
+        <v>-29.65586000000002</v>
       </c>
       <c r="O46">
-        <v>21.90959862399999</v>
+        <v>-4.329755560000002</v>
       </c>
       <c r="P46">
-        <v>128.156145376</v>
+        <v>-25.32610444000002</v>
       </c>
       <c r="Q46">
-        <v>448.6561453759999</v>
+        <v>295.17389556</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1039886869988197</v>
+        <v>0.1052116780830633</v>
       </c>
       <c r="T46">
-        <v>1.343849584268352</v>
+        <v>1.37209418205689</v>
       </c>
       <c r="U46">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V46">
-        <v>0.146</v>
+        <v>0.136963784602363</v>
       </c>
       <c r="W46">
-        <v>0.0647332</v>
+        <v>0.1023560951461598</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.501164248889412</v>
+        <v>0.9381081137148151</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1039266657614567</v>
+        <v>0.1046546657614567</v>
       </c>
       <c r="C47">
-        <v>1302.659650646583</v>
+        <v>1149.991378701036</v>
       </c>
       <c r="D47">
-        <v>5084.159650646583</v>
+        <v>5021.271378701035</v>
       </c>
       <c r="E47">
-        <v>2433.2</v>
+        <v>2522.98</v>
       </c>
       <c r="F47">
-        <v>4040.1</v>
+        <v>4129.88</v>
       </c>
       <c r="G47">
         <v>258.6</v>
@@ -5147,37 +5147,37 @@
         <v>449.5</v>
       </c>
       <c r="M47">
-        <v>479.15586</v>
+        <v>489.803768</v>
       </c>
       <c r="N47">
-        <v>-29.65586000000002</v>
+        <v>-40.30376800000005</v>
       </c>
       <c r="O47">
-        <v>-4.329755560000002</v>
+        <v>-5.884350128000007</v>
       </c>
       <c r="P47">
-        <v>-25.32610444000002</v>
+        <v>-34.41941787200004</v>
       </c>
       <c r="Q47">
-        <v>295.17389556</v>
+        <v>286.0805821279999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1052116780830633</v>
+        <v>0.1063118943438608</v>
       </c>
       <c r="T47">
-        <v>1.37209418205689</v>
+        <v>1.397503333576463</v>
       </c>
       <c r="U47">
         <v>0.1186</v>
       </c>
       <c r="V47">
-        <v>0.136963784602363</v>
+        <v>0.1339863110240507</v>
       </c>
       <c r="W47">
-        <v>0.1023560951461598</v>
+        <v>0.1027092235125476</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.9381081137148151</v>
+        <v>0.9177144590688407</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1046546657614567</v>
+        <v>0.1053826657614567</v>
       </c>
       <c r="C48">
-        <v>1149.991378701036</v>
+        <v>998.8598846552795</v>
       </c>
       <c r="D48">
-        <v>5021.271378701035</v>
+        <v>4959.919884655279</v>
       </c>
       <c r="E48">
-        <v>2522.98</v>
+        <v>2612.759999999999</v>
       </c>
       <c r="F48">
-        <v>4129.88</v>
+        <v>4219.66</v>
       </c>
       <c r="G48">
         <v>258.6</v>
@@ -5229,37 +5229,37 @@
         <v>449.5</v>
       </c>
       <c r="M48">
-        <v>489.803768</v>
+        <v>500.451676</v>
       </c>
       <c r="N48">
-        <v>-40.30376800000005</v>
+        <v>-50.95167600000002</v>
       </c>
       <c r="O48">
-        <v>-5.884350128000007</v>
+        <v>-7.438944696000003</v>
       </c>
       <c r="P48">
-        <v>-34.41941787200004</v>
+        <v>-43.51273130400002</v>
       </c>
       <c r="Q48">
-        <v>286.0805821279999</v>
+        <v>276.987268696</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1063118943438608</v>
+        <v>0.1074536281994054</v>
       </c>
       <c r="T48">
-        <v>1.397503333576463</v>
+        <v>1.423871321002433</v>
       </c>
       <c r="U48">
         <v>0.1186</v>
       </c>
       <c r="V48">
-        <v>0.1339863110240507</v>
+        <v>0.1311355384490709</v>
       </c>
       <c r="W48">
-        <v>0.1027092235125476</v>
+        <v>0.1030473251399402</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.9177144590688407</v>
+        <v>0.8981886195141846</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1053826657614567</v>
+        <v>0.1061106657614568</v>
       </c>
       <c r="C49">
-        <v>998.8598846552795</v>
+        <v>849.2095179392027</v>
       </c>
       <c r="D49">
-        <v>4959.919884655279</v>
+        <v>4900.049517939203</v>
       </c>
       <c r="E49">
-        <v>2612.759999999999</v>
+        <v>2702.54</v>
       </c>
       <c r="F49">
-        <v>4219.66</v>
+        <v>4309.440000000001</v>
       </c>
       <c r="G49">
         <v>258.6</v>
@@ -5311,37 +5311,37 @@
         <v>449.5</v>
       </c>
       <c r="M49">
-        <v>500.451676</v>
+        <v>511.0995840000001</v>
       </c>
       <c r="N49">
-        <v>-50.95167600000002</v>
+        <v>-61.59958400000011</v>
       </c>
       <c r="O49">
-        <v>-7.438944696000003</v>
+        <v>-8.993539264000015</v>
       </c>
       <c r="P49">
-        <v>-43.51273130400002</v>
+        <v>-52.60604473600009</v>
       </c>
       <c r="Q49">
-        <v>276.987268696</v>
+        <v>267.8939552639999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1074536281994054</v>
+        <v>0.1086392748955478</v>
       </c>
       <c r="T49">
-        <v>1.423871321002433</v>
+        <v>1.451253461790942</v>
       </c>
       <c r="U49">
         <v>0.1186</v>
       </c>
       <c r="V49">
-        <v>0.1311355384490709</v>
+        <v>0.1284035480647153</v>
       </c>
       <c r="W49">
-        <v>0.1030473251399402</v>
+        <v>0.1033713391995248</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8981886195141846</v>
+        <v>0.8794763566076389</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1061106657614568</v>
+        <v>0.1068386657614567</v>
       </c>
       <c r="C50">
-        <v>849.2095179392036</v>
+        <v>700.9872829303213</v>
       </c>
       <c r="D50">
-        <v>4900.049517939203</v>
+        <v>4841.607282930321</v>
       </c>
       <c r="E50">
-        <v>2702.539999999999</v>
+        <v>2792.32</v>
       </c>
       <c r="F50">
-        <v>4309.44</v>
+        <v>4399.22</v>
       </c>
       <c r="G50">
         <v>258.6</v>
@@ -5393,37 +5393,37 @@
         <v>449.5</v>
       </c>
       <c r="M50">
-        <v>511.099584</v>
+        <v>521.7474920000001</v>
       </c>
       <c r="N50">
-        <v>-61.59958399999999</v>
+        <v>-72.24749200000008</v>
       </c>
       <c r="O50">
-        <v>-8.993539263999999</v>
+        <v>-10.54813383200001</v>
       </c>
       <c r="P50">
-        <v>-52.60604473599999</v>
+        <v>-61.69935816800007</v>
       </c>
       <c r="Q50">
-        <v>267.893955264</v>
+        <v>258.8006418319999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1086392748955478</v>
+        <v>0.1098714175405585</v>
       </c>
       <c r="T50">
-        <v>1.451253461790942</v>
+        <v>1.479709412022137</v>
       </c>
       <c r="U50">
         <v>0.1186</v>
       </c>
       <c r="V50">
-        <v>0.1284035480647153</v>
+        <v>0.125783067491966</v>
       </c>
       <c r="W50">
-        <v>0.1033713391995248</v>
+        <v>0.1036821281954528</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8794763566076391</v>
+        <v>0.8615278595340137</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1068386657614567</v>
+        <v>0.1075666657614567</v>
       </c>
       <c r="C51">
-        <v>700.9872829303213</v>
+        <v>554.1426824938062</v>
       </c>
       <c r="D51">
-        <v>4841.607282930321</v>
+        <v>4784.542682493806</v>
       </c>
       <c r="E51">
-        <v>2792.32</v>
+        <v>2882.099999999999</v>
       </c>
       <c r="F51">
-        <v>4399.22</v>
+        <v>4489</v>
       </c>
       <c r="G51">
         <v>258.6</v>
@@ -5475,37 +5475,37 @@
         <v>449.5</v>
       </c>
       <c r="M51">
-        <v>521.7474920000001</v>
+        <v>532.3954</v>
       </c>
       <c r="N51">
-        <v>-72.24749200000008</v>
+        <v>-82.8954</v>
       </c>
       <c r="O51">
-        <v>-10.54813383200001</v>
+        <v>-12.1027284</v>
       </c>
       <c r="P51">
-        <v>-61.69935816800007</v>
+        <v>-70.79267159999999</v>
       </c>
       <c r="Q51">
-        <v>258.8006418319999</v>
+        <v>249.7073284</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1098714175405585</v>
+        <v>0.1111528458913697</v>
       </c>
       <c r="T51">
-        <v>1.479709412022137</v>
+        <v>1.509303600262579</v>
       </c>
       <c r="U51">
         <v>0.1186</v>
       </c>
       <c r="V51">
-        <v>0.125783067491966</v>
+        <v>0.1232674061421267</v>
       </c>
       <c r="W51">
-        <v>0.1036821281954528</v>
+        <v>0.1039804856315438</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8615278595340137</v>
+        <v>0.8442973023433336</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1075666657614567</v>
+        <v>0.1082946657614567</v>
       </c>
       <c r="C52">
-        <v>554.1426824938062</v>
+        <v>408.6275724581637</v>
       </c>
       <c r="D52">
-        <v>4784.542682493806</v>
+        <v>4728.807572458163</v>
       </c>
       <c r="E52">
-        <v>2882.099999999999</v>
+        <v>2971.879999999999</v>
       </c>
       <c r="F52">
-        <v>4489</v>
+        <v>4578.78</v>
       </c>
       <c r="G52">
         <v>258.6</v>
@@ -5557,37 +5557,37 @@
         <v>449.5</v>
       </c>
       <c r="M52">
-        <v>532.3954</v>
+        <v>543.043308</v>
       </c>
       <c r="N52">
-        <v>-82.8954</v>
+        <v>-93.54330800000002</v>
       </c>
       <c r="O52">
-        <v>-12.1027284</v>
+        <v>-13.657322968</v>
       </c>
       <c r="P52">
-        <v>-70.79267159999999</v>
+        <v>-79.88598503200002</v>
       </c>
       <c r="Q52">
-        <v>249.7073284</v>
+        <v>240.614014968</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1111528458913697</v>
+        <v>0.1124865774401732</v>
       </c>
       <c r="T52">
-        <v>1.509303600262579</v>
+        <v>1.540105714553653</v>
       </c>
       <c r="U52">
         <v>0.1186</v>
       </c>
       <c r="V52">
-        <v>0.1232674061421267</v>
+        <v>0.1208503981785556</v>
       </c>
       <c r="W52">
-        <v>0.1039804856315438</v>
+        <v>0.1042671427760233</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8442973023433336</v>
+        <v>0.827742453277778</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1082946657614567</v>
+        <v>0.1090226657614567</v>
       </c>
       <c r="C53">
-        <v>408.6275724581637</v>
+        <v>264.396026145032</v>
       </c>
       <c r="D53">
-        <v>4728.807572458163</v>
+        <v>4674.356026145032</v>
       </c>
       <c r="E53">
-        <v>2971.879999999999</v>
+        <v>3061.66</v>
       </c>
       <c r="F53">
-        <v>4578.78</v>
+        <v>4668.56</v>
       </c>
       <c r="G53">
         <v>258.6</v>
@@ -5639,37 +5639,37 @@
         <v>449.5</v>
       </c>
       <c r="M53">
-        <v>543.043308</v>
+        <v>553.6912160000001</v>
       </c>
       <c r="N53">
-        <v>-93.54330800000002</v>
+        <v>-104.1912160000001</v>
       </c>
       <c r="O53">
-        <v>-13.657322968</v>
+        <v>-15.21191753600001</v>
       </c>
       <c r="P53">
-        <v>-79.88598503200002</v>
+        <v>-88.97929846400005</v>
       </c>
       <c r="Q53">
-        <v>240.614014968</v>
+        <v>231.5207015359999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1124865774401732</v>
+        <v>0.1138758811368434</v>
       </c>
       <c r="T53">
-        <v>1.540105714553653</v>
+        <v>1.57219125027352</v>
       </c>
       <c r="U53">
         <v>0.1186</v>
       </c>
       <c r="V53">
-        <v>0.1208503981785556</v>
+        <v>0.1185263520597372</v>
       </c>
       <c r="W53">
-        <v>0.1042671427760233</v>
+        <v>0.1045427746457152</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.827742453277778</v>
+        <v>0.8118243291762821</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1090226657614567</v>
+        <v>0.154195260258069</v>
       </c>
       <c r="C54">
-        <v>264.396026145032</v>
+        <v>-1773.37310916522</v>
       </c>
       <c r="D54">
-        <v>4674.356026145032</v>
+        <v>2726.36689083478</v>
       </c>
       <c r="E54">
-        <v>3061.66</v>
+        <v>3151.44</v>
       </c>
       <c r="F54">
-        <v>4668.56</v>
+        <v>4758.34</v>
       </c>
       <c r="G54">
         <v>258.6</v>
@@ -5721,45 +5721,45 @@
         <v>449.5</v>
       </c>
       <c r="M54">
-        <v>553.6912160000001</v>
+        <v>955.4746720000001</v>
       </c>
       <c r="N54">
-        <v>-104.1912160000001</v>
+        <v>-505.9746720000001</v>
       </c>
       <c r="O54">
-        <v>-15.21191753600001</v>
+        <v>-73.872302112</v>
       </c>
       <c r="P54">
-        <v>-88.97929846400005</v>
+        <v>-432.1023698880001</v>
       </c>
       <c r="Q54">
-        <v>231.5207015359999</v>
+        <v>-111.6023698880001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1138758811368434</v>
+        <v>0.1171936541325471</v>
       </c>
       <c r="T54">
-        <v>1.57219125027352</v>
+        <v>1.648814183199702</v>
       </c>
       <c r="U54">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1185263520597372</v>
+        <v>0.0686852325060899</v>
       </c>
       <c r="W54">
-        <v>0.1045427746457152</v>
+        <v>0.1870080053127771</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.8118243291762821</v>
+        <v>0.4704467979869172</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.154195260258069</v>
+        <v>0.155745260258069</v>
       </c>
       <c r="C55">
-        <v>-1773.37310916522</v>
+        <v>-1901.589224290827</v>
       </c>
       <c r="D55">
-        <v>2726.36689083478</v>
+        <v>2687.930775709173</v>
       </c>
       <c r="E55">
-        <v>3151.44</v>
+        <v>3241.219999999999</v>
       </c>
       <c r="F55">
-        <v>4758.34</v>
+        <v>4848.12</v>
       </c>
       <c r="G55">
         <v>258.6</v>
@@ -5803,37 +5803,37 @@
         <v>449.5</v>
       </c>
       <c r="M55">
-        <v>955.4746720000001</v>
+        <v>973.5024960000001</v>
       </c>
       <c r="N55">
-        <v>-505.9746720000001</v>
+        <v>-524.0024960000001</v>
       </c>
       <c r="O55">
-        <v>-73.872302112</v>
+        <v>-76.504364416</v>
       </c>
       <c r="P55">
-        <v>-432.1023698880001</v>
+        <v>-447.4981315840001</v>
       </c>
       <c r="Q55">
-        <v>-111.6023698880001</v>
+        <v>-126.9981315840001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1171936541325471</v>
+        <v>0.1187456900919503</v>
       </c>
       <c r="T55">
-        <v>1.648814183199702</v>
+        <v>1.684657969791</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.0686852325060899</v>
+        <v>0.06741328375597713</v>
       </c>
       <c r="W55">
-        <v>0.1870080053127771</v>
+        <v>0.1872634126217998</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4704467979869172</v>
+        <v>0.4617348202464188</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.155745260258069</v>
+        <v>0.157295260258069</v>
       </c>
       <c r="C56">
-        <v>-1901.589224290827</v>
+        <v>-2028.736666572282</v>
       </c>
       <c r="D56">
-        <v>2687.930775709173</v>
+        <v>2650.563333427719</v>
       </c>
       <c r="E56">
-        <v>3241.219999999999</v>
+        <v>3331</v>
       </c>
       <c r="F56">
-        <v>4848.12</v>
+        <v>4937.900000000001</v>
       </c>
       <c r="G56">
         <v>258.6</v>
@@ -5885,37 +5885,37 @@
         <v>449.5</v>
       </c>
       <c r="M56">
-        <v>973.5024960000001</v>
+        <v>991.5303200000002</v>
       </c>
       <c r="N56">
-        <v>-524.0024960000001</v>
+        <v>-542.0303200000002</v>
       </c>
       <c r="O56">
-        <v>-76.504364416</v>
+        <v>-79.13642672000002</v>
       </c>
       <c r="P56">
-        <v>-447.4981315840001</v>
+        <v>-462.8938932800002</v>
       </c>
       <c r="Q56">
-        <v>-126.9981315840001</v>
+        <v>-142.3938932800002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1187456900919503</v>
+        <v>0.120366705427327</v>
       </c>
       <c r="T56">
-        <v>1.684657969791</v>
+        <v>1.722094813564134</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.06741328375597713</v>
+        <v>0.06618758768768662</v>
       </c>
       <c r="W56">
-        <v>0.1872634126217998</v>
+        <v>0.1875095323923125</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4617348202464188</v>
+        <v>0.4533396416964838</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.157295260258069</v>
+        <v>0.158845260258069</v>
       </c>
       <c r="C57">
-        <v>-2028.736666572282</v>
+        <v>-2154.859394763044</v>
       </c>
       <c r="D57">
-        <v>2650.563333427719</v>
+        <v>2614.220605236957</v>
       </c>
       <c r="E57">
-        <v>3331</v>
+        <v>3420.78</v>
       </c>
       <c r="F57">
-        <v>4937.900000000001</v>
+        <v>5027.68</v>
       </c>
       <c r="G57">
         <v>258.6</v>
@@ -5967,37 +5967,37 @@
         <v>449.5</v>
       </c>
       <c r="M57">
-        <v>991.5303200000002</v>
+        <v>1009.558144</v>
       </c>
       <c r="N57">
-        <v>-542.0303200000002</v>
+        <v>-560.0581440000001</v>
       </c>
       <c r="O57">
-        <v>-79.13642672000002</v>
+        <v>-81.768489024</v>
       </c>
       <c r="P57">
-        <v>-462.8938932800002</v>
+        <v>-478.2896549760001</v>
       </c>
       <c r="Q57">
-        <v>-142.3938932800002</v>
+        <v>-157.7896549760001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.120366705427327</v>
+        <v>0.122061403277948</v>
       </c>
       <c r="T57">
-        <v>1.722094813564134</v>
+        <v>1.761233332054227</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.06618758768768662</v>
+        <v>0.06500566647897794</v>
       </c>
       <c r="W57">
-        <v>0.1875095323923125</v>
+        <v>0.1877468621710212</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4533396416964838</v>
+        <v>0.4452442909519038</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.158845260258069</v>
+        <v>0.1603952602580691</v>
       </c>
       <c r="C58">
-        <v>-2154.859394763044</v>
+        <v>-2279.998989295943</v>
       </c>
       <c r="D58">
-        <v>2614.220605236957</v>
+        <v>2578.861010704058</v>
       </c>
       <c r="E58">
-        <v>3420.78</v>
+        <v>3510.56</v>
       </c>
       <c r="F58">
-        <v>5027.68</v>
+        <v>5117.460000000001</v>
       </c>
       <c r="G58">
         <v>258.6</v>
@@ -6049,37 +6049,37 @@
         <v>449.5</v>
       </c>
       <c r="M58">
-        <v>1009.558144</v>
+        <v>1027.585968</v>
       </c>
       <c r="N58">
-        <v>-560.0581440000001</v>
+        <v>-578.0859680000003</v>
       </c>
       <c r="O58">
-        <v>-81.768489024</v>
+        <v>-84.40055132800005</v>
       </c>
       <c r="P58">
-        <v>-478.2896549760001</v>
+        <v>-493.6854166720003</v>
       </c>
       <c r="Q58">
-        <v>-157.7896549760001</v>
+        <v>-173.1854166720003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.122061403277948</v>
+        <v>0.123834924284412</v>
       </c>
       <c r="T58">
-        <v>1.761233332054227</v>
+        <v>1.802192246753163</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.06500566647897794</v>
+        <v>0.06386521618987305</v>
       </c>
       <c r="W58">
-        <v>0.1877468621710212</v>
+        <v>0.1879758645890735</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4452442909519038</v>
+        <v>0.4374329876018702</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1603952602580691</v>
+        <v>0.161945260258069</v>
       </c>
       <c r="C59">
-        <v>-2279.998989295943</v>
+        <v>-2404.194810980871</v>
       </c>
       <c r="D59">
-        <v>2578.861010704058</v>
+        <v>2544.44518901913</v>
       </c>
       <c r="E59">
-        <v>3510.56</v>
+        <v>3600.34</v>
       </c>
       <c r="F59">
-        <v>5117.460000000001</v>
+        <v>5207.240000000001</v>
       </c>
       <c r="G59">
         <v>258.6</v>
@@ -6131,37 +6131,37 @@
         <v>449.5</v>
       </c>
       <c r="M59">
-        <v>1027.585968</v>
+        <v>1045.613792</v>
       </c>
       <c r="N59">
-        <v>-578.0859680000003</v>
+        <v>-596.1137920000001</v>
       </c>
       <c r="O59">
-        <v>-84.40055132800005</v>
+        <v>-87.03261363200001</v>
       </c>
       <c r="P59">
-        <v>-493.6854166720003</v>
+        <v>-509.0811783680001</v>
       </c>
       <c r="Q59">
-        <v>-173.1854166720003</v>
+        <v>-188.5811783680001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.123834924284412</v>
+        <v>0.125692898672136</v>
       </c>
       <c r="T59">
-        <v>1.802192246753163</v>
+        <v>1.845101585961572</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.06386521618987305</v>
+        <v>0.06276409177280629</v>
       </c>
       <c r="W59">
-        <v>0.1879758645890735</v>
+        <v>0.1881969703720205</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4374329876018702</v>
+        <v>0.4298910395397691</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.161945260258069</v>
+        <v>0.163495260258069</v>
       </c>
       <c r="C60">
-        <v>-2404.19481098087</v>
+        <v>-2527.484147162564</v>
       </c>
       <c r="D60">
-        <v>2544.44518901913</v>
+        <v>2510.935852837436</v>
       </c>
       <c r="E60">
-        <v>3600.339999999999</v>
+        <v>3690.119999999999</v>
       </c>
       <c r="F60">
-        <v>5207.24</v>
+        <v>5297.02</v>
       </c>
       <c r="G60">
         <v>258.6</v>
@@ -6213,37 +6213,37 @@
         <v>449.5</v>
       </c>
       <c r="M60">
-        <v>1045.613792</v>
+        <v>1063.641616</v>
       </c>
       <c r="N60">
-        <v>-596.1137919999999</v>
+        <v>-614.1416159999999</v>
       </c>
       <c r="O60">
-        <v>-87.03261363199998</v>
+        <v>-89.66467593599998</v>
       </c>
       <c r="P60">
-        <v>-509.0811783679999</v>
+        <v>-524.4769400639999</v>
       </c>
       <c r="Q60">
-        <v>-188.5811783679999</v>
+        <v>-203.9769400639999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.125692898672136</v>
+        <v>0.1276415059568223</v>
       </c>
       <c r="T60">
-        <v>1.845101585961572</v>
+        <v>1.890104063667951</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.06276409177280631</v>
+        <v>0.06170029360716552</v>
       </c>
       <c r="W60">
-        <v>0.1881969703720205</v>
+        <v>0.1884105810436812</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4298910395397693</v>
+        <v>0.4226047507340105</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.163495260258069</v>
+        <v>0.165045260258069</v>
       </c>
       <c r="C61">
-        <v>-2527.484147162564</v>
+        <v>-2649.902346479461</v>
       </c>
       <c r="D61">
-        <v>2510.935852837436</v>
+        <v>2478.297653520539</v>
       </c>
       <c r="E61">
-        <v>3690.119999999999</v>
+        <v>3779.9</v>
       </c>
       <c r="F61">
-        <v>5297.02</v>
+        <v>5386.8</v>
       </c>
       <c r="G61">
         <v>258.6</v>
@@ -6295,37 +6295,37 @@
         <v>449.5</v>
       </c>
       <c r="M61">
-        <v>1063.641616</v>
+        <v>1081.66944</v>
       </c>
       <c r="N61">
-        <v>-614.1416159999999</v>
+        <v>-632.1694400000001</v>
       </c>
       <c r="O61">
-        <v>-89.66467593599998</v>
+        <v>-92.29673824000001</v>
       </c>
       <c r="P61">
-        <v>-524.4769400639999</v>
+        <v>-539.8727017600002</v>
       </c>
       <c r="Q61">
-        <v>-203.9769400639999</v>
+        <v>-219.3727017600002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1276415059568223</v>
+        <v>0.1296875436057428</v>
       </c>
       <c r="T61">
-        <v>1.890104063667951</v>
+        <v>1.93735666525965</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.06170029360716552</v>
+        <v>0.06067195538037942</v>
       </c>
       <c r="W61">
-        <v>0.1884105810436812</v>
+        <v>0.1886170713596198</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4226047507340105</v>
+        <v>0.4155613382217769</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.165045260258069</v>
+        <v>0.166595260258069</v>
       </c>
       <c r="C62">
-        <v>-2649.902346479461</v>
+        <v>-2771.482943247497</v>
       </c>
       <c r="D62">
-        <v>2478.297653520539</v>
+        <v>2446.497056752503</v>
       </c>
       <c r="E62">
-        <v>3779.9</v>
+        <v>3869.679999999999</v>
       </c>
       <c r="F62">
-        <v>5386.8</v>
+        <v>5476.58</v>
       </c>
       <c r="G62">
         <v>258.6</v>
@@ -6377,37 +6377,37 @@
         <v>449.5</v>
       </c>
       <c r="M62">
-        <v>1081.66944</v>
+        <v>1099.697264</v>
       </c>
       <c r="N62">
-        <v>-632.1694400000001</v>
+        <v>-650.1972640000001</v>
       </c>
       <c r="O62">
-        <v>-92.29673824000001</v>
+        <v>-94.92880054400001</v>
       </c>
       <c r="P62">
-        <v>-539.8727017600002</v>
+        <v>-555.2684634560001</v>
       </c>
       <c r="Q62">
-        <v>-219.3727017600002</v>
+        <v>-234.7684634560001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1296875436057428</v>
+        <v>0.1318385062623004</v>
       </c>
       <c r="T62">
-        <v>1.93735666525965</v>
+        <v>1.987032477189385</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.06067195538037942</v>
+        <v>0.05967733316102893</v>
       </c>
       <c r="W62">
-        <v>0.1886170713596198</v>
+        <v>0.1888167915012654</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4155613382217769</v>
+        <v>0.4087488572673215</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.166595260258069</v>
+        <v>0.168145260258069</v>
       </c>
       <c r="C63">
-        <v>-2771.482943247497</v>
+        <v>-2892.257772388957</v>
       </c>
       <c r="D63">
-        <v>2446.497056752503</v>
+        <v>2415.502227611043</v>
       </c>
       <c r="E63">
-        <v>3869.679999999999</v>
+        <v>3959.459999999999</v>
       </c>
       <c r="F63">
-        <v>5476.58</v>
+        <v>5566.36</v>
       </c>
       <c r="G63">
         <v>258.6</v>
@@ -6459,37 +6459,37 @@
         <v>449.5</v>
       </c>
       <c r="M63">
-        <v>1099.697264</v>
+        <v>1117.725088</v>
       </c>
       <c r="N63">
-        <v>-650.1972640000001</v>
+        <v>-668.2250879999999</v>
       </c>
       <c r="O63">
-        <v>-94.92880054400001</v>
+        <v>-97.56086284799999</v>
       </c>
       <c r="P63">
-        <v>-555.2684634560001</v>
+        <v>-570.664225152</v>
       </c>
       <c r="Q63">
-        <v>-234.7684634560001</v>
+        <v>-250.164225152</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1318385062623004</v>
+        <v>0.1341026774797293</v>
       </c>
       <c r="T63">
-        <v>1.987032477189385</v>
+        <v>2.039322805536474</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.05967733316102893</v>
+        <v>0.05871479552939944</v>
       </c>
       <c r="W63">
-        <v>0.1888167915012654</v>
+        <v>0.1890100690576966</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4087488572673215</v>
+        <v>0.40215613376301</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.168145260258069</v>
+        <v>0.169695260258069</v>
       </c>
       <c r="C64">
-        <v>-2892.257772388957</v>
+        <v>-3012.257075734368</v>
       </c>
       <c r="D64">
-        <v>2415.502227611043</v>
+        <v>2385.282924265633</v>
       </c>
       <c r="E64">
-        <v>3959.459999999999</v>
+        <v>4049.24</v>
       </c>
       <c r="F64">
-        <v>5566.36</v>
+        <v>5656.14</v>
       </c>
       <c r="G64">
         <v>258.6</v>
@@ -6541,37 +6541,37 @@
         <v>449.5</v>
       </c>
       <c r="M64">
-        <v>1117.725088</v>
+        <v>1135.752912</v>
       </c>
       <c r="N64">
-        <v>-668.2250879999999</v>
+        <v>-686.2529120000002</v>
       </c>
       <c r="O64">
-        <v>-97.56086284799999</v>
+        <v>-100.192925152</v>
       </c>
       <c r="P64">
-        <v>-570.664225152</v>
+        <v>-586.0599868480001</v>
       </c>
       <c r="Q64">
-        <v>-250.164225152</v>
+        <v>-265.5599868480001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1341026774797293</v>
+        <v>0.1364892363305328</v>
       </c>
       <c r="T64">
-        <v>2.039322805536474</v>
+        <v>2.094439638118541</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.05871479552939944</v>
+        <v>0.05778281464798039</v>
       </c>
       <c r="W64">
-        <v>0.1890100690576966</v>
+        <v>0.1891972108186855</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.40215613376301</v>
+        <v>0.3957727030683589</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.169695260258069</v>
+        <v>0.171245260258069</v>
       </c>
       <c r="C65">
-        <v>-3012.257075734368</v>
+        <v>-3131.509600443597</v>
       </c>
       <c r="D65">
-        <v>2385.282924265633</v>
+        <v>2355.810399556403</v>
       </c>
       <c r="E65">
-        <v>4049.24</v>
+        <v>4139.02</v>
       </c>
       <c r="F65">
-        <v>5656.14</v>
+        <v>5745.92</v>
       </c>
       <c r="G65">
         <v>258.6</v>
@@ -6623,37 +6623,37 @@
         <v>449.5</v>
       </c>
       <c r="M65">
-        <v>1135.752912</v>
+        <v>1153.780736</v>
       </c>
       <c r="N65">
-        <v>-686.2529120000002</v>
+        <v>-704.2807360000002</v>
       </c>
       <c r="O65">
-        <v>-100.192925152</v>
+        <v>-102.824987456</v>
       </c>
       <c r="P65">
-        <v>-586.0599868480001</v>
+        <v>-601.4557485440001</v>
       </c>
       <c r="Q65">
-        <v>-265.5599868480001</v>
+        <v>-280.9557485440001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1364892363305328</v>
+        <v>0.1390083817841587</v>
       </c>
       <c r="T65">
-        <v>2.094439638118541</v>
+        <v>2.152618516955167</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.05778281464798039</v>
+        <v>0.0568799581691057</v>
       </c>
       <c r="W65">
-        <v>0.1891972108186855</v>
+        <v>0.1893785043996436</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3957727030683589</v>
+        <v>0.3895887545829158</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.171245260258069</v>
+        <v>0.172795260258069</v>
       </c>
       <c r="C66">
-        <v>-3131.509600443597</v>
+        <v>-3250.042690219484</v>
       </c>
       <c r="D66">
-        <v>2355.810399556403</v>
+        <v>2327.057309780515</v>
       </c>
       <c r="E66">
-        <v>4139.02</v>
+        <v>4228.799999999999</v>
       </c>
       <c r="F66">
-        <v>5745.92</v>
+        <v>5835.7</v>
       </c>
       <c r="G66">
         <v>258.6</v>
@@ -6705,37 +6705,37 @@
         <v>449.5</v>
       </c>
       <c r="M66">
-        <v>1153.780736</v>
+        <v>1171.80856</v>
       </c>
       <c r="N66">
-        <v>-704.2807360000002</v>
+        <v>-722.3085599999999</v>
       </c>
       <c r="O66">
-        <v>-102.824987456</v>
+        <v>-105.45704976</v>
       </c>
       <c r="P66">
-        <v>-601.4557485440001</v>
+        <v>-616.8515102399999</v>
       </c>
       <c r="Q66">
-        <v>-280.9557485440001</v>
+        <v>-296.3515102399999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1390083817841587</v>
+        <v>0.1416714784065632</v>
       </c>
       <c r="T66">
-        <v>2.152618516955167</v>
+        <v>2.214121903153886</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.0568799581691057</v>
+        <v>0.05600488188958101</v>
       </c>
       <c r="W66">
-        <v>0.1893785043996436</v>
+        <v>0.1895542197165722</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3895887545829158</v>
+        <v>0.3835950814354864</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.172795260258069</v>
+        <v>0.174345260258069</v>
       </c>
       <c r="C67">
-        <v>-3250.042690219484</v>
+        <v>-3367.882369922327</v>
       </c>
       <c r="D67">
-        <v>2327.057309780515</v>
+        <v>2298.997630077673</v>
       </c>
       <c r="E67">
-        <v>4228.799999999999</v>
+        <v>4318.58</v>
       </c>
       <c r="F67">
-        <v>5835.7</v>
+        <v>5925.48</v>
       </c>
       <c r="G67">
         <v>258.6</v>
@@ -6787,37 +6787,37 @@
         <v>449.5</v>
       </c>
       <c r="M67">
-        <v>1171.80856</v>
+        <v>1189.836384</v>
       </c>
       <c r="N67">
-        <v>-722.3085599999999</v>
+        <v>-740.3363840000002</v>
       </c>
       <c r="O67">
-        <v>-105.45704976</v>
+        <v>-108.089112064</v>
       </c>
       <c r="P67">
-        <v>-616.8515102399999</v>
+        <v>-632.2472719360002</v>
       </c>
       <c r="Q67">
-        <v>-296.3515102399999</v>
+        <v>-311.7472719360002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1416714784065632</v>
+        <v>0.1444912277714622</v>
       </c>
       <c r="T67">
-        <v>2.214121903153886</v>
+        <v>2.279243135599589</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.05600488188958101</v>
+        <v>0.05515632307307219</v>
       </c>
       <c r="W67">
-        <v>0.1895542197165722</v>
+        <v>0.1897246103269271</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3835950814354864</v>
+        <v>0.3777830347470699</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.174345260258069</v>
+        <v>0.175895260258069</v>
       </c>
       <c r="C68">
-        <v>-3367.882369922327</v>
+        <v>-3485.053424135613</v>
       </c>
       <c r="D68">
-        <v>2298.997630077673</v>
+        <v>2271.606575864387</v>
       </c>
       <c r="E68">
-        <v>4318.58</v>
+        <v>4408.36</v>
       </c>
       <c r="F68">
-        <v>5925.48</v>
+        <v>6015.26</v>
       </c>
       <c r="G68">
         <v>258.6</v>
@@ -6869,37 +6869,37 @@
         <v>449.5</v>
       </c>
       <c r="M68">
-        <v>1189.836384</v>
+        <v>1207.864208</v>
       </c>
       <c r="N68">
-        <v>-740.3363840000002</v>
+        <v>-758.3642080000002</v>
       </c>
       <c r="O68">
-        <v>-108.089112064</v>
+        <v>-110.721174368</v>
       </c>
       <c r="P68">
-        <v>-632.2472719360002</v>
+        <v>-647.6430336320002</v>
       </c>
       <c r="Q68">
-        <v>-311.7472719360002</v>
+        <v>-327.1430336320002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1444912277714622</v>
+        <v>0.1474818710372641</v>
       </c>
       <c r="T68">
-        <v>2.279243135599589</v>
+        <v>2.348311109405637</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.05515632307307219</v>
+        <v>0.05433309437048903</v>
       </c>
       <c r="W68">
-        <v>0.1897246103269271</v>
+        <v>0.1898899146504058</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3777830347470699</v>
+        <v>0.3721444819896509</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.175895260258069</v>
+        <v>0.1774452602580691</v>
       </c>
       <c r="C69">
-        <v>-3485.053424135613</v>
+        <v>-3601.579470181537</v>
       </c>
       <c r="D69">
-        <v>2271.606575864387</v>
+        <v>2244.860529818464</v>
       </c>
       <c r="E69">
-        <v>4408.36</v>
+        <v>4498.14</v>
       </c>
       <c r="F69">
-        <v>6015.26</v>
+        <v>6105.040000000001</v>
       </c>
       <c r="G69">
         <v>258.6</v>
@@ -6951,37 +6951,37 @@
         <v>449.5</v>
       </c>
       <c r="M69">
-        <v>1207.864208</v>
+        <v>1225.892032</v>
       </c>
       <c r="N69">
-        <v>-758.3642080000002</v>
+        <v>-776.3920320000002</v>
       </c>
       <c r="O69">
-        <v>-110.721174368</v>
+        <v>-113.353236672</v>
       </c>
       <c r="P69">
-        <v>-647.6430336320002</v>
+        <v>-663.0387953280002</v>
       </c>
       <c r="Q69">
-        <v>-327.1430336320002</v>
+        <v>-342.5387953280002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1474818710372641</v>
+        <v>0.1506594295071786</v>
       </c>
       <c r="T69">
-        <v>2.348311109405637</v>
+        <v>2.421695831574563</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.05433309437048903</v>
+        <v>0.05353407827680536</v>
       </c>
       <c r="W69">
-        <v>0.1898899146504058</v>
+        <v>0.1900503570820175</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3721444819896509</v>
+        <v>0.3666717690192148</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1774452602580691</v>
+        <v>0.1789952602580691</v>
       </c>
       <c r="C70">
-        <v>-3601.579470181537</v>
+        <v>-3717.483026038381</v>
       </c>
       <c r="D70">
-        <v>2244.860529818464</v>
+        <v>2218.73697396162</v>
       </c>
       <c r="E70">
-        <v>4498.14</v>
+        <v>4587.92</v>
       </c>
       <c r="F70">
-        <v>6105.040000000001</v>
+        <v>6194.820000000001</v>
       </c>
       <c r="G70">
         <v>258.6</v>
@@ -7033,37 +7033,37 @@
         <v>449.5</v>
       </c>
       <c r="M70">
-        <v>1225.892032</v>
+        <v>1243.919856</v>
       </c>
       <c r="N70">
-        <v>-776.3920320000002</v>
+        <v>-794.4198560000002</v>
       </c>
       <c r="O70">
-        <v>-113.353236672</v>
+        <v>-115.985298976</v>
       </c>
       <c r="P70">
-        <v>-663.0387953280002</v>
+        <v>-678.4345570240002</v>
       </c>
       <c r="Q70">
-        <v>-342.5387953280002</v>
+        <v>-357.9345570240002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1506594295071786</v>
+        <v>0.1540419917493456</v>
       </c>
       <c r="T70">
-        <v>2.421695831574563</v>
+        <v>2.499815051947936</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.05353407827680536</v>
+        <v>0.05275822206989514</v>
       </c>
       <c r="W70">
-        <v>0.1900503570820175</v>
+        <v>0.1902061490083651</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3666717690192148</v>
+        <v>0.3613576854102407</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1789952602580691</v>
+        <v>0.1805452602580691</v>
       </c>
       <c r="C71">
-        <v>-3717.483026038381</v>
+        <v>-3832.785573570323</v>
       </c>
       <c r="D71">
-        <v>2218.73697396162</v>
+        <v>2193.214426429678</v>
       </c>
       <c r="E71">
-        <v>4587.92</v>
+        <v>4677.7</v>
       </c>
       <c r="F71">
-        <v>6194.820000000001</v>
+        <v>6284.6</v>
       </c>
       <c r="G71">
         <v>258.6</v>
@@ -7115,37 +7115,37 @@
         <v>449.5</v>
       </c>
       <c r="M71">
-        <v>1243.919856</v>
+        <v>1261.94768</v>
       </c>
       <c r="N71">
-        <v>-794.4198560000002</v>
+        <v>-812.4476800000002</v>
       </c>
       <c r="O71">
-        <v>-115.985298976</v>
+        <v>-118.61736128</v>
       </c>
       <c r="P71">
-        <v>-678.4345570240002</v>
+        <v>-693.8303187200002</v>
       </c>
       <c r="Q71">
-        <v>-357.9345570240002</v>
+        <v>-373.3303187200002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1540419917493456</v>
+        <v>0.1576500581409905</v>
       </c>
       <c r="T71">
-        <v>2.499815051947936</v>
+        <v>2.5831422203462</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.05275822206989514</v>
+        <v>0.05200453318318235</v>
       </c>
       <c r="W71">
-        <v>0.1902061490083651</v>
+        <v>0.190357489736817</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3613576854102407</v>
+        <v>0.356195432761523</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1805452602580691</v>
+        <v>0.182095260258069</v>
       </c>
       <c r="C72">
-        <v>-3832.785573570323</v>
+        <v>-3947.50761744279</v>
       </c>
       <c r="D72">
-        <v>2193.214426429678</v>
+        <v>2168.272382557211</v>
       </c>
       <c r="E72">
-        <v>4677.7</v>
+        <v>4767.48</v>
       </c>
       <c r="F72">
-        <v>6284.6</v>
+        <v>6374.380000000001</v>
       </c>
       <c r="G72">
         <v>258.6</v>
@@ -7197,37 +7197,37 @@
         <v>449.5</v>
       </c>
       <c r="M72">
-        <v>1261.94768</v>
+        <v>1279.975504</v>
       </c>
       <c r="N72">
-        <v>-812.4476800000002</v>
+        <v>-830.4755040000002</v>
       </c>
       <c r="O72">
-        <v>-118.61736128</v>
+        <v>-121.249423584</v>
       </c>
       <c r="P72">
-        <v>-693.8303187200002</v>
+        <v>-709.2260804160002</v>
       </c>
       <c r="Q72">
-        <v>-373.3303187200002</v>
+        <v>-388.7260804160002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1576500581409905</v>
+        <v>0.1615069566975764</v>
       </c>
       <c r="T72">
-        <v>2.5831422203462</v>
+        <v>2.672216090013311</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.05200453318318235</v>
+        <v>0.05127207496933472</v>
       </c>
       <c r="W72">
-        <v>0.190357489736817</v>
+        <v>0.1905045673461576</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.356195432761523</v>
+        <v>0.3511785956803748</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.182095260258069</v>
+        <v>0.183645260258069</v>
       </c>
       <c r="C73">
-        <v>-3947.507617442789</v>
+        <v>-4061.668740062977</v>
       </c>
       <c r="D73">
-        <v>2168.272382557211</v>
+        <v>2143.891259937023</v>
       </c>
       <c r="E73">
-        <v>4767.48</v>
+        <v>4857.259999999999</v>
       </c>
       <c r="F73">
-        <v>6374.38</v>
+        <v>6464.16</v>
       </c>
       <c r="G73">
         <v>258.6</v>
@@ -7279,37 +7279,37 @@
         <v>449.5</v>
       </c>
       <c r="M73">
-        <v>1279.975504</v>
+        <v>1298.003328</v>
       </c>
       <c r="N73">
-        <v>-830.475504</v>
+        <v>-848.503328</v>
       </c>
       <c r="O73">
-        <v>-121.249423584</v>
+        <v>-123.881485888</v>
       </c>
       <c r="P73">
-        <v>-709.2260804160001</v>
+        <v>-724.621842112</v>
       </c>
       <c r="Q73">
-        <v>-388.7260804160001</v>
+        <v>-404.121842112</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1615069566975763</v>
+        <v>0.1656393480082041</v>
       </c>
       <c r="T73">
-        <v>2.67221609001331</v>
+        <v>2.767652378942357</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.05127207496933472</v>
+        <v>0.05055996281698285</v>
       </c>
       <c r="W73">
-        <v>0.1905045673461576</v>
+        <v>0.1906475594663498</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3511785956803748</v>
+        <v>0.3463011151848141</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.183645260258069</v>
+        <v>0.185195260258069</v>
       </c>
       <c r="C74">
-        <v>-4061.668740062977</v>
+        <v>-4175.28765285492</v>
       </c>
       <c r="D74">
-        <v>2143.891259937023</v>
+        <v>2120.05234714508</v>
       </c>
       <c r="E74">
-        <v>4857.259999999999</v>
+        <v>4947.039999999999</v>
       </c>
       <c r="F74">
-        <v>6464.16</v>
+        <v>6553.94</v>
       </c>
       <c r="G74">
         <v>258.6</v>
@@ -7361,37 +7361,37 @@
         <v>449.5</v>
       </c>
       <c r="M74">
-        <v>1298.003328</v>
+        <v>1316.031152</v>
       </c>
       <c r="N74">
-        <v>-848.503328</v>
+        <v>-866.531152</v>
       </c>
       <c r="O74">
-        <v>-123.881485888</v>
+        <v>-126.513548192</v>
       </c>
       <c r="P74">
-        <v>-724.621842112</v>
+        <v>-740.017603808</v>
       </c>
       <c r="Q74">
-        <v>-404.121842112</v>
+        <v>-419.517603808</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1656393480082041</v>
+        <v>0.1700778423788783</v>
       </c>
       <c r="T74">
-        <v>2.767652378942357</v>
+        <v>2.870158022606889</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.05055996281698285</v>
+        <v>0.04986736058661322</v>
       </c>
       <c r="W74">
-        <v>0.1906475594663498</v>
+        <v>0.1907866339942081</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3463011151848141</v>
+        <v>0.3415572642918714</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.185195260258069</v>
+        <v>0.186745260258069</v>
       </c>
       <c r="C75">
-        <v>-4175.28765285492</v>
+        <v>-4288.382244151273</v>
       </c>
       <c r="D75">
-        <v>2120.05234714508</v>
+        <v>2096.737755848727</v>
       </c>
       <c r="E75">
-        <v>4947.039999999999</v>
+        <v>5036.82</v>
       </c>
       <c r="F75">
-        <v>6553.94</v>
+        <v>6643.72</v>
       </c>
       <c r="G75">
         <v>258.6</v>
@@ -7443,37 +7443,37 @@
         <v>449.5</v>
       </c>
       <c r="M75">
-        <v>1316.031152</v>
+        <v>1334.058976</v>
       </c>
       <c r="N75">
-        <v>-866.531152</v>
+        <v>-884.558976</v>
       </c>
       <c r="O75">
-        <v>-126.513548192</v>
+        <v>-129.145610496</v>
       </c>
       <c r="P75">
-        <v>-740.017603808</v>
+        <v>-755.413365504</v>
       </c>
       <c r="Q75">
-        <v>-419.517603808</v>
+        <v>-434.913365504</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1700778423788783</v>
+        <v>0.1748577593934505</v>
       </c>
       <c r="T75">
-        <v>2.870158022606889</v>
+        <v>2.980548715784077</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.04986736058661322</v>
+        <v>0.04919347733544278</v>
       </c>
       <c r="W75">
-        <v>0.1907866339942081</v>
+        <v>0.1909219497510431</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3415572642918714</v>
+        <v>0.3369416255852244</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.186745260258069</v>
+        <v>0.188295260258069</v>
       </c>
       <c r="C76">
-        <v>-4288.382244151273</v>
+        <v>-4400.969623959413</v>
       </c>
       <c r="D76">
-        <v>2096.737755848727</v>
+        <v>2073.930376040587</v>
       </c>
       <c r="E76">
-        <v>5036.82</v>
+        <v>5126.599999999999</v>
       </c>
       <c r="F76">
-        <v>6643.72</v>
+        <v>6733.5</v>
       </c>
       <c r="G76">
         <v>258.6</v>
@@ -7525,37 +7525,37 @@
         <v>449.5</v>
       </c>
       <c r="M76">
-        <v>1334.058976</v>
+        <v>1352.0868</v>
       </c>
       <c r="N76">
-        <v>-884.558976</v>
+        <v>-902.5868</v>
       </c>
       <c r="O76">
-        <v>-129.145610496</v>
+        <v>-131.7776728</v>
       </c>
       <c r="P76">
-        <v>-755.413365504</v>
+        <v>-770.8091272</v>
       </c>
       <c r="Q76">
-        <v>-434.913365504</v>
+        <v>-450.3091272</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1748577593934505</v>
+        <v>0.1800200697691886</v>
       </c>
       <c r="T76">
-        <v>2.980548715784077</v>
+        <v>3.09977066441544</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.04919347733544278</v>
+        <v>0.04853756430430354</v>
       </c>
       <c r="W76">
-        <v>0.1909219497510431</v>
+        <v>0.1910536570876958</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3369416255852244</v>
+        <v>0.3324490705774215</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.188295260258069</v>
+        <v>0.189845260258069</v>
       </c>
       <c r="C77">
-        <v>-4400.969623959413</v>
+        <v>-4513.066165837317</v>
       </c>
       <c r="D77">
-        <v>2073.930376040587</v>
+        <v>2051.613834162683</v>
       </c>
       <c r="E77">
-        <v>5126.599999999999</v>
+        <v>5216.379999999999</v>
       </c>
       <c r="F77">
-        <v>6733.5</v>
+        <v>6823.28</v>
       </c>
       <c r="G77">
         <v>258.6</v>
@@ -7607,37 +7607,37 @@
         <v>449.5</v>
       </c>
       <c r="M77">
-        <v>1352.0868</v>
+        <v>1370.114624</v>
       </c>
       <c r="N77">
-        <v>-902.5868</v>
+        <v>-920.614624</v>
       </c>
       <c r="O77">
-        <v>-131.7776728</v>
+        <v>-134.409735104</v>
       </c>
       <c r="P77">
-        <v>-770.8091272</v>
+        <v>-786.2048888960001</v>
       </c>
       <c r="Q77">
-        <v>-450.3091272</v>
+        <v>-465.7048888960001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1800200697691886</v>
+        <v>0.1856125726762381</v>
       </c>
       <c r="T77">
-        <v>3.09977066441544</v>
+        <v>3.22892777543275</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.04853756430430354</v>
+        <v>0.04789891214240481</v>
       </c>
       <c r="W77">
-        <v>0.1910536570876958</v>
+        <v>0.1911818984418051</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3324490705774215</v>
+        <v>0.3280747407014027</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.189845260258069</v>
+        <v>0.191395260258069</v>
       </c>
       <c r="C78">
-        <v>-4513.066165837317</v>
+        <v>-4624.687546094584</v>
       </c>
       <c r="D78">
-        <v>2051.613834162683</v>
+        <v>2029.772453905416</v>
       </c>
       <c r="E78">
-        <v>5216.379999999999</v>
+        <v>5306.16</v>
       </c>
       <c r="F78">
-        <v>6823.28</v>
+        <v>6913.06</v>
       </c>
       <c r="G78">
         <v>258.6</v>
@@ -7689,37 +7689,37 @@
         <v>449.5</v>
       </c>
       <c r="M78">
-        <v>1370.114624</v>
+        <v>1388.142448</v>
       </c>
       <c r="N78">
-        <v>-920.614624</v>
+        <v>-938.6424480000001</v>
       </c>
       <c r="O78">
-        <v>-134.409735104</v>
+        <v>-137.041797408</v>
       </c>
       <c r="P78">
-        <v>-786.2048888960001</v>
+        <v>-801.6006505920001</v>
       </c>
       <c r="Q78">
-        <v>-465.7048888960001</v>
+        <v>-481.1006505920001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1856125726762381</v>
+        <v>0.1916913801839006</v>
       </c>
       <c r="T78">
-        <v>3.22892777543275</v>
+        <v>3.369315939582</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.04789891214240481</v>
+        <v>0.0472768483483476</v>
       </c>
       <c r="W78">
-        <v>0.1911818984418051</v>
+        <v>0.1913068088516518</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3280747407014027</v>
+        <v>0.3238140297832027</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.191395260258069</v>
+        <v>0.192945260258069</v>
       </c>
       <c r="C79">
-        <v>-4624.687546094584</v>
+        <v>-4735.848780515833</v>
       </c>
       <c r="D79">
-        <v>2029.772453905416</v>
+        <v>2008.391219484167</v>
       </c>
       <c r="E79">
-        <v>5306.16</v>
+        <v>5395.94</v>
       </c>
       <c r="F79">
-        <v>6913.06</v>
+        <v>7002.84</v>
       </c>
       <c r="G79">
         <v>258.6</v>
@@ -7771,37 +7771,37 @@
         <v>449.5</v>
       </c>
       <c r="M79">
-        <v>1388.142448</v>
+        <v>1406.170272</v>
       </c>
       <c r="N79">
-        <v>-938.6424480000001</v>
+        <v>-956.6702720000001</v>
       </c>
       <c r="O79">
-        <v>-137.041797408</v>
+        <v>-139.673859712</v>
       </c>
       <c r="P79">
-        <v>-801.6006505920001</v>
+        <v>-816.9964122880001</v>
       </c>
       <c r="Q79">
-        <v>-481.1006505920001</v>
+        <v>-496.4964122880001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1916913801839006</v>
+        <v>0.1983228065558961</v>
       </c>
       <c r="T79">
-        <v>3.369315939582</v>
+        <v>3.522466664108455</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.0472768483483476</v>
+        <v>0.04667073490798417</v>
       </c>
       <c r="W79">
-        <v>0.1913068088516518</v>
+        <v>0.1914285164304768</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3238140297832027</v>
+        <v>0.3196625678629053</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.192945260258069</v>
+        <v>0.1944952602580691</v>
       </c>
       <c r="C80">
-        <v>-4735.848780515833</v>
+        <v>-4846.564258787283</v>
       </c>
       <c r="D80">
-        <v>2008.391219484167</v>
+        <v>1987.455741212717</v>
       </c>
       <c r="E80">
-        <v>5395.94</v>
+        <v>5485.719999999999</v>
       </c>
       <c r="F80">
-        <v>7002.84</v>
+        <v>7092.62</v>
       </c>
       <c r="G80">
         <v>258.6</v>
@@ -7853,37 +7853,37 @@
         <v>449.5</v>
       </c>
       <c r="M80">
-        <v>1406.170272</v>
+        <v>1424.198096</v>
       </c>
       <c r="N80">
-        <v>-956.6702720000001</v>
+        <v>-974.6980960000001</v>
       </c>
       <c r="O80">
-        <v>-139.673859712</v>
+        <v>-142.305922016</v>
       </c>
       <c r="P80">
-        <v>-816.9964122880001</v>
+        <v>-832.392173984</v>
       </c>
       <c r="Q80">
-        <v>-496.4964122880001</v>
+        <v>-511.892173984</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1983228065558961</v>
+        <v>0.2055857973442721</v>
       </c>
       <c r="T80">
-        <v>3.522466664108455</v>
+        <v>3.690203171923144</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.04667073490798417</v>
+        <v>0.04607996611168057</v>
       </c>
       <c r="W80">
-        <v>0.1914285164304768</v>
+        <v>0.1915471428047746</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3196625678629053</v>
+        <v>0.3156162062443875</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1944952602580691</v>
+        <v>0.196045260258069</v>
       </c>
       <c r="C81">
-        <v>-4846.564258787283</v>
+        <v>-4956.847776792367</v>
       </c>
       <c r="D81">
-        <v>1987.455741212717</v>
+        <v>1966.952223207634</v>
       </c>
       <c r="E81">
-        <v>5485.719999999999</v>
+        <v>5575.5</v>
       </c>
       <c r="F81">
-        <v>7092.62</v>
+        <v>7182.400000000001</v>
       </c>
       <c r="G81">
         <v>258.6</v>
@@ -7935,37 +7935,37 @@
         <v>449.5</v>
       </c>
       <c r="M81">
-        <v>1424.198096</v>
+        <v>1442.22592</v>
       </c>
       <c r="N81">
-        <v>-974.6980960000001</v>
+        <v>-992.7259200000001</v>
       </c>
       <c r="O81">
-        <v>-142.305922016</v>
+        <v>-144.93798432</v>
       </c>
       <c r="P81">
-        <v>-832.392173984</v>
+        <v>-847.7879356800001</v>
       </c>
       <c r="Q81">
-        <v>-511.892173984</v>
+        <v>-527.2879356800001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2055857973442721</v>
+        <v>0.2135750872114857</v>
       </c>
       <c r="T81">
-        <v>3.690203171923144</v>
+        <v>3.874713330519301</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.04607996611168057</v>
+        <v>0.04550396653528457</v>
       </c>
       <c r="W81">
-        <v>0.1915471428047746</v>
+        <v>0.1916628035197149</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3156162062443875</v>
+        <v>0.3116710036663326</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.196045260258069</v>
+        <v>0.1975952602580691</v>
       </c>
       <c r="C82">
-        <v>-4956.847776792367</v>
+        <v>-5066.712566928689</v>
       </c>
       <c r="D82">
-        <v>1966.952223207634</v>
+        <v>1946.867433071311</v>
       </c>
       <c r="E82">
-        <v>5575.5</v>
+        <v>5665.28</v>
       </c>
       <c r="F82">
-        <v>7182.400000000001</v>
+        <v>7272.18</v>
       </c>
       <c r="G82">
         <v>258.6</v>
@@ -8017,37 +8017,37 @@
         <v>449.5</v>
       </c>
       <c r="M82">
-        <v>1442.22592</v>
+        <v>1460.253744</v>
       </c>
       <c r="N82">
-        <v>-992.7259200000001</v>
+        <v>-1010.753744</v>
       </c>
       <c r="O82">
-        <v>-144.93798432</v>
+        <v>-147.570046624</v>
       </c>
       <c r="P82">
-        <v>-847.7879356800001</v>
+        <v>-863.1836973760001</v>
       </c>
       <c r="Q82">
-        <v>-527.2879356800001</v>
+        <v>-542.6836973760001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2135750872114857</v>
+        <v>0.2224053549594587</v>
       </c>
       <c r="T82">
-        <v>3.874713330519301</v>
+        <v>4.078645611072949</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.04550396653528457</v>
+        <v>0.04494218917065142</v>
       </c>
       <c r="W82">
-        <v>0.1916628035197149</v>
+        <v>0.1917756084145332</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3116710036663326</v>
+        <v>0.3078232134976124</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1975952602580691</v>
+        <v>0.1991452602580691</v>
       </c>
       <c r="C83">
-        <v>-5066.712566928689</v>
+        <v>-5176.171326586355</v>
       </c>
       <c r="D83">
-        <v>1946.867433071311</v>
+        <v>1927.188673413647</v>
       </c>
       <c r="E83">
-        <v>5665.28</v>
+        <v>5755.06</v>
       </c>
       <c r="F83">
-        <v>7272.18</v>
+        <v>7361.960000000001</v>
       </c>
       <c r="G83">
         <v>258.6</v>
@@ -8099,37 +8099,37 @@
         <v>449.5</v>
       </c>
       <c r="M83">
-        <v>1460.253744</v>
+        <v>1478.281568</v>
       </c>
       <c r="N83">
-        <v>-1010.753744</v>
+        <v>-1028.781568</v>
       </c>
       <c r="O83">
-        <v>-147.570046624</v>
+        <v>-150.202108928</v>
       </c>
       <c r="P83">
-        <v>-863.1836973760001</v>
+        <v>-878.5794590720003</v>
       </c>
       <c r="Q83">
-        <v>-542.6836973760001</v>
+        <v>-558.0794590720003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2224053549594587</v>
+        <v>0.2322167635683175</v>
       </c>
       <c r="T83">
-        <v>4.078645611072949</v>
+        <v>4.305237033910335</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.04494218917065142</v>
+        <v>0.04439411369296054</v>
       </c>
       <c r="W83">
-        <v>0.1917756084145332</v>
+        <v>0.1918856619704535</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3078232134976124</v>
+        <v>0.3040692718695928</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1991452602580691</v>
+        <v>0.2006952602580691</v>
       </c>
       <c r="C84">
-        <v>-5176.171326586355</v>
+        <v>-5285.236244916419</v>
       </c>
       <c r="D84">
-        <v>1927.188673413647</v>
+        <v>1907.903755083581</v>
       </c>
       <c r="E84">
-        <v>5755.06</v>
+        <v>5844.84</v>
       </c>
       <c r="F84">
-        <v>7361.960000000001</v>
+        <v>7451.740000000001</v>
       </c>
       <c r="G84">
         <v>258.6</v>
@@ -8181,37 +8181,37 @@
         <v>449.5</v>
       </c>
       <c r="M84">
-        <v>1478.281568</v>
+        <v>1496.309392</v>
       </c>
       <c r="N84">
-        <v>-1028.781568</v>
+        <v>-1046.809392</v>
       </c>
       <c r="O84">
-        <v>-150.202108928</v>
+        <v>-152.834171232</v>
       </c>
       <c r="P84">
-        <v>-878.5794590720003</v>
+        <v>-893.9752207680001</v>
       </c>
       <c r="Q84">
-        <v>-558.0794590720003</v>
+        <v>-573.4752207680001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2322167635683175</v>
+        <v>0.2431824555429244</v>
       </c>
       <c r="T84">
-        <v>4.305237033910335</v>
+        <v>4.558486271199178</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.04439411369296054</v>
+        <v>0.04385924485328632</v>
       </c>
       <c r="W84">
-        <v>0.1918856619704535</v>
+        <v>0.1919930636334601</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3040692718695928</v>
+        <v>0.3004057866663448</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2006952602580691</v>
+        <v>0.202245260258069</v>
       </c>
       <c r="C85">
-        <v>-5285.236244916419</v>
+        <v>-5393.919028008098</v>
       </c>
       <c r="D85">
-        <v>1907.903755083581</v>
+        <v>1889.000971991902</v>
       </c>
       <c r="E85">
-        <v>5844.84</v>
+        <v>5934.62</v>
       </c>
       <c r="F85">
-        <v>7451.740000000001</v>
+        <v>7541.52</v>
       </c>
       <c r="G85">
         <v>258.6</v>
@@ -8263,37 +8263,37 @@
         <v>449.5</v>
       </c>
       <c r="M85">
-        <v>1496.309392</v>
+        <v>1514.337216</v>
       </c>
       <c r="N85">
-        <v>-1046.809392</v>
+        <v>-1064.837216</v>
       </c>
       <c r="O85">
-        <v>-152.834171232</v>
+        <v>-155.466233536</v>
       </c>
       <c r="P85">
-        <v>-893.9752207680001</v>
+        <v>-909.3709824640001</v>
       </c>
       <c r="Q85">
-        <v>-573.4752207680001</v>
+        <v>-588.8709824640001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2431824555429244</v>
+        <v>0.2555188590143572</v>
       </c>
       <c r="T85">
-        <v>4.558486271199178</v>
+        <v>4.843391663149128</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.04385924485328632</v>
+        <v>0.04333711098598529</v>
       </c>
       <c r="W85">
-        <v>0.1919930636334601</v>
+        <v>0.1920979081140142</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3004057866663448</v>
+        <v>0.2968295273012692</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.202245260258069</v>
+        <v>0.203795260258069</v>
       </c>
       <c r="C86">
-        <v>-5393.919028008097</v>
+        <v>-5502.230922583953</v>
       </c>
       <c r="D86">
-        <v>1889.000971991902</v>
+        <v>1870.469077416047</v>
       </c>
       <c r="E86">
-        <v>5934.619999999999</v>
+        <v>6024.4</v>
       </c>
       <c r="F86">
-        <v>7541.52</v>
+        <v>7631.3</v>
       </c>
       <c r="G86">
         <v>258.6</v>
@@ -8345,37 +8345,37 @@
         <v>449.5</v>
       </c>
       <c r="M86">
-        <v>1514.337216</v>
+        <v>1532.36504</v>
       </c>
       <c r="N86">
-        <v>-1064.837216</v>
+        <v>-1082.86504</v>
       </c>
       <c r="O86">
-        <v>-155.466233536</v>
+        <v>-158.09829584</v>
       </c>
       <c r="P86">
-        <v>-909.3709824639999</v>
+        <v>-924.7667441600001</v>
       </c>
       <c r="Q86">
-        <v>-588.8709824639999</v>
+        <v>-604.2667441600001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2555188590143571</v>
+        <v>0.2695001162819809</v>
       </c>
       <c r="T86">
-        <v>4.843391663149125</v>
+        <v>5.1662844406924</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.04333711098598531</v>
+        <v>0.04282726262144429</v>
       </c>
       <c r="W86">
-        <v>0.1920979081140142</v>
+        <v>0.192200285665614</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2968295273012692</v>
+        <v>0.2933374152153719</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.203795260258069</v>
+        <v>0.205345260258069</v>
       </c>
       <c r="C87">
-        <v>-5502.230922583953</v>
+        <v>-5610.182738313893</v>
       </c>
       <c r="D87">
-        <v>1870.469077416047</v>
+        <v>1852.297261686107</v>
       </c>
       <c r="E87">
-        <v>6024.4</v>
+        <v>6114.179999999999</v>
       </c>
       <c r="F87">
-        <v>7631.3</v>
+        <v>7721.08</v>
       </c>
       <c r="G87">
         <v>258.6</v>
@@ -8427,37 +8427,37 @@
         <v>449.5</v>
       </c>
       <c r="M87">
-        <v>1532.36504</v>
+        <v>1550.392864</v>
       </c>
       <c r="N87">
-        <v>-1082.86504</v>
+        <v>-1100.892864</v>
       </c>
       <c r="O87">
-        <v>-158.09829584</v>
+        <v>-160.730358144</v>
       </c>
       <c r="P87">
-        <v>-924.7667441600001</v>
+        <v>-940.1625058560002</v>
       </c>
       <c r="Q87">
-        <v>-604.2667441600001</v>
+        <v>-619.6625058560002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2695001162819809</v>
+        <v>0.2854786960164081</v>
       </c>
       <c r="T87">
-        <v>5.1662844406924</v>
+        <v>5.535304757884714</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.04282726262144429</v>
+        <v>0.04232927119561355</v>
       </c>
       <c r="W87">
-        <v>0.192200285665614</v>
+        <v>0.1923002823439208</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2933374152153719</v>
+        <v>0.289926515038449</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.205345260258069</v>
+        <v>0.206895260258069</v>
       </c>
       <c r="C88">
-        <v>-5610.182738313893</v>
+        <v>-5717.784868840974</v>
       </c>
       <c r="D88">
-        <v>1852.297261686107</v>
+        <v>1834.475131159025</v>
       </c>
       <c r="E88">
-        <v>6114.179999999999</v>
+        <v>6203.959999999999</v>
       </c>
       <c r="F88">
-        <v>7721.08</v>
+        <v>7810.86</v>
       </c>
       <c r="G88">
         <v>258.6</v>
@@ -8509,37 +8509,37 @@
         <v>449.5</v>
       </c>
       <c r="M88">
-        <v>1550.392864</v>
+        <v>1568.420688</v>
       </c>
       <c r="N88">
-        <v>-1100.892864</v>
+        <v>-1118.920688</v>
       </c>
       <c r="O88">
-        <v>-160.730358144</v>
+        <v>-163.362420448</v>
       </c>
       <c r="P88">
-        <v>-940.1625058560002</v>
+        <v>-955.558267552</v>
       </c>
       <c r="Q88">
-        <v>-619.6625058560002</v>
+        <v>-635.058267552</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2854786960164081</v>
+        <v>0.303915518786901</v>
       </c>
       <c r="T88">
-        <v>5.535304757884714</v>
+        <v>5.961097431568153</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.04232927119561355</v>
+        <v>0.04184272784853754</v>
       </c>
       <c r="W88">
-        <v>0.1923002823439208</v>
+        <v>0.1923979802480137</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.289926515038449</v>
+        <v>0.2865940263598461</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.206895260258069</v>
+        <v>0.208445260258069</v>
       </c>
       <c r="C89">
-        <v>-5717.784868840974</v>
+        <v>-5825.047311604969</v>
       </c>
       <c r="D89">
-        <v>1834.475131159025</v>
+        <v>1816.992688395032</v>
       </c>
       <c r="E89">
-        <v>6203.959999999999</v>
+        <v>6293.74</v>
       </c>
       <c r="F89">
-        <v>7810.86</v>
+        <v>7900.64</v>
       </c>
       <c r="G89">
         <v>258.6</v>
@@ -8591,37 +8591,37 @@
         <v>449.5</v>
       </c>
       <c r="M89">
-        <v>1568.420688</v>
+        <v>1586.448512</v>
       </c>
       <c r="N89">
-        <v>-1118.920688</v>
+        <v>-1136.948512</v>
       </c>
       <c r="O89">
-        <v>-163.362420448</v>
+        <v>-165.994482752</v>
       </c>
       <c r="P89">
-        <v>-955.558267552</v>
+        <v>-970.9540292480001</v>
       </c>
       <c r="Q89">
-        <v>-635.058267552</v>
+        <v>-650.4540292480001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.303915518786901</v>
+        <v>0.3254251453524761</v>
       </c>
       <c r="T89">
-        <v>5.961097431568153</v>
+        <v>6.4578555508655</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.04184272784853754</v>
+        <v>0.04136724230480415</v>
       </c>
       <c r="W89">
-        <v>0.1923979802480137</v>
+        <v>0.1924934577451953</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2865940263598461</v>
+        <v>0.2833372760603023</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.208445260258069</v>
+        <v>0.209995260258069</v>
       </c>
       <c r="C90">
-        <v>-5825.047311604969</v>
+        <v>-5931.979686543111</v>
       </c>
       <c r="D90">
-        <v>1816.992688395032</v>
+        <v>1799.84031345689</v>
       </c>
       <c r="E90">
-        <v>6293.74</v>
+        <v>6383.52</v>
       </c>
       <c r="F90">
-        <v>7900.64</v>
+        <v>7990.42</v>
       </c>
       <c r="G90">
         <v>258.6</v>
@@ -8673,37 +8673,37 @@
         <v>449.5</v>
       </c>
       <c r="M90">
-        <v>1586.448512</v>
+        <v>1604.476336</v>
       </c>
       <c r="N90">
-        <v>-1136.948512</v>
+        <v>-1154.976336</v>
       </c>
       <c r="O90">
-        <v>-165.994482752</v>
+        <v>-168.626545056</v>
       </c>
       <c r="P90">
-        <v>-970.9540292480001</v>
+        <v>-986.3497909440001</v>
       </c>
       <c r="Q90">
-        <v>-650.4540292480001</v>
+        <v>-665.8497909440001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3254251453524761</v>
+        <v>0.3508456131117922</v>
       </c>
       <c r="T90">
-        <v>6.4578555508655</v>
+        <v>7.04493332821691</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.04136724230480415</v>
+        <v>0.04090244182946927</v>
       </c>
       <c r="W90">
-        <v>0.1924934577451953</v>
+        <v>0.1925867896806426</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2833372760603023</v>
+        <v>0.2801537111607484</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.209995260258069</v>
+        <v>0.211545260258069</v>
       </c>
       <c r="C91">
-        <v>-5931.979686543111</v>
+        <v>-6038.59125374156</v>
       </c>
       <c r="D91">
-        <v>1799.84031345689</v>
+        <v>1783.00874625844</v>
       </c>
       <c r="E91">
-        <v>6383.52</v>
+        <v>6473.299999999999</v>
       </c>
       <c r="F91">
-        <v>7990.42</v>
+        <v>8080.2</v>
       </c>
       <c r="G91">
         <v>258.6</v>
@@ -8755,37 +8755,37 @@
         <v>449.5</v>
       </c>
       <c r="M91">
-        <v>1604.476336</v>
+        <v>1622.50416</v>
       </c>
       <c r="N91">
-        <v>-1154.976336</v>
+        <v>-1173.00416</v>
       </c>
       <c r="O91">
-        <v>-168.626545056</v>
+        <v>-171.25860736</v>
       </c>
       <c r="P91">
-        <v>-986.3497909440001</v>
+        <v>-1001.74555264</v>
       </c>
       <c r="Q91">
-        <v>-665.8497909440001</v>
+        <v>-681.2455526399999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3508456131117922</v>
+        <v>0.3813501744229715</v>
       </c>
       <c r="T91">
-        <v>7.04493332821691</v>
+        <v>7.749426661038602</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.04090244182946927</v>
+        <v>0.04044797025358628</v>
       </c>
       <c r="W91">
-        <v>0.1925867896806426</v>
+        <v>0.1926780475730799</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2801537111607484</v>
+        <v>0.2770408921478512</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.211545260258069</v>
+        <v>0.213095260258069</v>
       </c>
       <c r="C92">
-        <v>-6038.59125374156</v>
+        <v>-6144.890930105597</v>
       </c>
       <c r="D92">
-        <v>1783.00874625844</v>
+        <v>1766.489069894403</v>
       </c>
       <c r="E92">
-        <v>6473.299999999999</v>
+        <v>6563.08</v>
       </c>
       <c r="F92">
-        <v>8080.2</v>
+        <v>8169.98</v>
       </c>
       <c r="G92">
         <v>258.6</v>
@@ -8837,37 +8837,37 @@
         <v>449.5</v>
       </c>
       <c r="M92">
-        <v>1622.50416</v>
+        <v>1640.531984</v>
       </c>
       <c r="N92">
-        <v>-1173.00416</v>
+        <v>-1191.031984</v>
       </c>
       <c r="O92">
-        <v>-171.25860736</v>
+        <v>-173.890669664</v>
       </c>
       <c r="P92">
-        <v>-1001.74555264</v>
+        <v>-1017.141314336</v>
       </c>
       <c r="Q92">
-        <v>-681.2455526399999</v>
+        <v>-696.6413143360002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3813501744229715</v>
+        <v>0.418633527136635</v>
       </c>
       <c r="T92">
-        <v>7.749426661038602</v>
+        <v>8.61047406782067</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.04044797025358628</v>
+        <v>0.04000348706398642</v>
       </c>
       <c r="W92">
-        <v>0.1926780475730799</v>
+        <v>0.1927672997975515</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2770408921478512</v>
+        <v>0.2739964867396331</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.213095260258069</v>
+        <v>0.214645260258069</v>
       </c>
       <c r="C93">
-        <v>-6144.890930105597</v>
+        <v>-6250.887305111632</v>
       </c>
       <c r="D93">
-        <v>1766.489069894403</v>
+        <v>1750.272694888369</v>
       </c>
       <c r="E93">
-        <v>6563.08</v>
+        <v>6652.86</v>
       </c>
       <c r="F93">
-        <v>8169.98</v>
+        <v>8259.76</v>
       </c>
       <c r="G93">
         <v>258.6</v>
@@ -8919,37 +8919,37 @@
         <v>449.5</v>
       </c>
       <c r="M93">
-        <v>1640.531984</v>
+        <v>1658.559808</v>
       </c>
       <c r="N93">
-        <v>-1191.031984</v>
+        <v>-1209.059808</v>
       </c>
       <c r="O93">
-        <v>-173.890669664</v>
+        <v>-176.522731968</v>
       </c>
       <c r="P93">
-        <v>-1017.141314336</v>
+        <v>-1032.537076032</v>
       </c>
       <c r="Q93">
-        <v>-696.6413143360002</v>
+        <v>-712.0370760320002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.418633527136635</v>
+        <v>0.4652377180287145</v>
       </c>
       <c r="T93">
-        <v>8.61047406782067</v>
+        <v>9.686783326298256</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.04000348706398642</v>
+        <v>0.03956866655242135</v>
       </c>
       <c r="W93">
-        <v>0.1927672997975515</v>
+        <v>0.1928546117562738</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2739964867396331</v>
+        <v>0.2710182640576806</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.214645260258069</v>
+        <v>0.2161952602580691</v>
       </c>
       <c r="C94">
-        <v>-6250.887305111632</v>
+        <v>-6356.588655699485</v>
       </c>
       <c r="D94">
-        <v>1750.272694888369</v>
+        <v>1734.351344300517</v>
       </c>
       <c r="E94">
-        <v>6652.86</v>
+        <v>6742.64</v>
       </c>
       <c r="F94">
-        <v>8259.76</v>
+        <v>8349.540000000001</v>
       </c>
       <c r="G94">
         <v>258.6</v>
@@ -9001,37 +9001,37 @@
         <v>449.5</v>
       </c>
       <c r="M94">
-        <v>1658.559808</v>
+        <v>1676.587632</v>
       </c>
       <c r="N94">
-        <v>-1209.059808</v>
+        <v>-1227.087632</v>
       </c>
       <c r="O94">
-        <v>-176.522731968</v>
+        <v>-179.154794272</v>
       </c>
       <c r="P94">
-        <v>-1032.537076032</v>
+        <v>-1047.932837728</v>
       </c>
       <c r="Q94">
-        <v>-712.0370760320002</v>
+        <v>-727.4328377280001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4652377180287145</v>
+        <v>0.5251573920328166</v>
       </c>
       <c r="T94">
-        <v>9.686783326298256</v>
+        <v>11.07060951576944</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.03956866655242135</v>
+        <v>0.03914319701959963</v>
       </c>
       <c r="W94">
-        <v>0.1928546117562738</v>
+        <v>0.1929400460384644</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2710182640576806</v>
+        <v>0.2681040891753399</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2161952602580691</v>
+        <v>0.2177452602580691</v>
       </c>
       <c r="C95">
-        <v>-6356.588655699485</v>
+        <v>-6462.002960359182</v>
       </c>
       <c r="D95">
-        <v>1734.351344300517</v>
+        <v>1718.717039640818</v>
       </c>
       <c r="E95">
-        <v>6742.64</v>
+        <v>6832.419999999999</v>
       </c>
       <c r="F95">
-        <v>8349.540000000001</v>
+        <v>8439.32</v>
       </c>
       <c r="G95">
         <v>258.6</v>
@@ -9083,37 +9083,37 @@
         <v>449.5</v>
       </c>
       <c r="M95">
-        <v>1676.587632</v>
+        <v>1694.615456</v>
       </c>
       <c r="N95">
-        <v>-1227.087632</v>
+        <v>-1245.115456</v>
       </c>
       <c r="O95">
-        <v>-179.154794272</v>
+        <v>-181.786856576</v>
       </c>
       <c r="P95">
-        <v>-1047.932837728</v>
+        <v>-1063.328599424</v>
       </c>
       <c r="Q95">
-        <v>-727.4328377280001</v>
+        <v>-742.828599424</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5251573920328166</v>
+        <v>0.6050502907049528</v>
       </c>
       <c r="T95">
-        <v>11.07060951576944</v>
+        <v>12.91571110173101</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.03914319701959963</v>
+        <v>0.03872678003002942</v>
       </c>
       <c r="W95">
-        <v>0.1929400460384644</v>
+        <v>0.1930236625699701</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2681040891753399</v>
+        <v>0.2652519180139001</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2177452602580691</v>
+        <v>0.2192952602580691</v>
       </c>
       <c r="C96">
-        <v>-6462.002960359182</v>
+        <v>-6567.137912462661</v>
       </c>
       <c r="D96">
-        <v>1718.717039640818</v>
+        <v>1703.362087537339</v>
       </c>
       <c r="E96">
-        <v>6832.419999999999</v>
+        <v>6922.2</v>
       </c>
       <c r="F96">
-        <v>8439.32</v>
+        <v>8529.1</v>
       </c>
       <c r="G96">
         <v>258.6</v>
@@ -9165,37 +9165,37 @@
         <v>449.5</v>
       </c>
       <c r="M96">
-        <v>1694.615456</v>
+        <v>1712.64328</v>
       </c>
       <c r="N96">
-        <v>-1245.115456</v>
+        <v>-1263.14328</v>
       </c>
       <c r="O96">
-        <v>-181.786856576</v>
+        <v>-184.41891888</v>
       </c>
       <c r="P96">
-        <v>-1063.328599424</v>
+        <v>-1078.72436112</v>
       </c>
       <c r="Q96">
-        <v>-742.828599424</v>
+        <v>-758.2243611200001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6050502907049528</v>
+        <v>0.7169003488459437</v>
       </c>
       <c r="T96">
-        <v>12.91571110173101</v>
+        <v>15.49885332207722</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.03872678003002942</v>
+        <v>0.03831912971392384</v>
       </c>
       <c r="W96">
-        <v>0.1930236625699701</v>
+        <v>0.1931055187534441</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2652519180139001</v>
+        <v>0.2624597925611222</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2192952602580691</v>
+        <v>0.220845260258069</v>
       </c>
       <c r="C97">
-        <v>-6567.137912462661</v>
+        <v>-6672.000932887153</v>
       </c>
       <c r="D97">
-        <v>1703.362087537339</v>
+        <v>1688.279067112848</v>
       </c>
       <c r="E97">
-        <v>6922.2</v>
+        <v>7011.98</v>
       </c>
       <c r="F97">
-        <v>8529.1</v>
+        <v>8618.880000000001</v>
       </c>
       <c r="G97">
         <v>258.6</v>
@@ -9247,37 +9247,37 @@
         <v>449.5</v>
       </c>
       <c r="M97">
-        <v>1712.64328</v>
+        <v>1730.671104</v>
       </c>
       <c r="N97">
-        <v>-1263.14328</v>
+        <v>-1281.171104</v>
       </c>
       <c r="O97">
-        <v>-184.41891888</v>
+        <v>-187.050981184</v>
       </c>
       <c r="P97">
-        <v>-1078.72436112</v>
+        <v>-1094.120122816</v>
       </c>
       <c r="Q97">
-        <v>-758.2243611200001</v>
+        <v>-773.6201228160003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7169003488459437</v>
+        <v>0.8846754360574299</v>
       </c>
       <c r="T97">
-        <v>15.49885332207722</v>
+        <v>19.37356665259654</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.03831912971392384</v>
+        <v>0.03791997211273714</v>
       </c>
       <c r="W97">
-        <v>0.1931055187534441</v>
+        <v>0.1931856695997624</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2624597925611222</v>
+        <v>0.2597258363886105</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.220845260258069</v>
+        <v>0.222395260258069</v>
       </c>
       <c r="C98">
-        <v>-6672.000932887151</v>
+        <v>-6776.599181973797</v>
       </c>
       <c r="D98">
-        <v>1688.279067112848</v>
+        <v>1673.460818026203</v>
       </c>
       <c r="E98">
-        <v>7011.979999999999</v>
+        <v>7101.759999999999</v>
       </c>
       <c r="F98">
-        <v>8618.879999999999</v>
+        <v>8708.66</v>
       </c>
       <c r="G98">
         <v>258.6</v>
@@ -9329,37 +9329,37 @@
         <v>449.5</v>
       </c>
       <c r="M98">
-        <v>1730.671104</v>
+        <v>1748.698928</v>
       </c>
       <c r="N98">
-        <v>-1281.171104</v>
+        <v>-1299.198928</v>
       </c>
       <c r="O98">
-        <v>-187.050981184</v>
+        <v>-189.683043488</v>
       </c>
       <c r="P98">
-        <v>-1094.120122816</v>
+        <v>-1109.515884512</v>
       </c>
       <c r="Q98">
-        <v>-773.6201228159998</v>
+        <v>-789.015884512</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8846754360574277</v>
+        <v>1.164300581409904</v>
       </c>
       <c r="T98">
-        <v>19.37356665259648</v>
+        <v>25.83142220346198</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.03791997211273714</v>
+        <v>0.03752904456518314</v>
       </c>
       <c r="W98">
-        <v>0.1931856695997624</v>
+        <v>0.1932641678513112</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2597258363886106</v>
+        <v>0.25704825044646</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.222395260258069</v>
+        <v>0.223945260258069</v>
       </c>
       <c r="C99">
-        <v>-6776.599181973797</v>
+        <v>-6880.93957086196</v>
       </c>
       <c r="D99">
-        <v>1673.460818026203</v>
+        <v>1658.90042913804</v>
       </c>
       <c r="E99">
-        <v>7101.759999999999</v>
+        <v>7191.54</v>
       </c>
       <c r="F99">
-        <v>8708.66</v>
+        <v>8798.440000000001</v>
       </c>
       <c r="G99">
         <v>258.6</v>
@@ -9411,37 +9411,37 @@
         <v>449.5</v>
       </c>
       <c r="M99">
-        <v>1748.698928</v>
+        <v>1766.726752</v>
       </c>
       <c r="N99">
-        <v>-1299.198928</v>
+        <v>-1317.226752</v>
       </c>
       <c r="O99">
-        <v>-189.683043488</v>
+        <v>-192.315105792</v>
       </c>
       <c r="P99">
-        <v>-1109.515884512</v>
+        <v>-1124.911646208</v>
       </c>
       <c r="Q99">
-        <v>-789.015884512</v>
+        <v>-804.4116462080003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.164300581409904</v>
+        <v>1.723550872114856</v>
       </c>
       <c r="T99">
-        <v>25.83142220346198</v>
+        <v>38.74713330519297</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.03752904456518314</v>
+        <v>0.03714609513084454</v>
       </c>
       <c r="W99">
-        <v>0.1932641678513112</v>
+        <v>0.1933410640977264</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.25704825044646</v>
+        <v>0.2544253091153735</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.223945260258069</v>
+        <v>0.225495260258069</v>
       </c>
       <c r="C100">
-        <v>-6880.93957086196</v>
+        <v>-6985.028772236948</v>
       </c>
       <c r="D100">
-        <v>1658.90042913804</v>
+        <v>1644.59122776305</v>
       </c>
       <c r="E100">
-        <v>7191.54</v>
+        <v>7281.319999999999</v>
       </c>
       <c r="F100">
-        <v>8798.440000000001</v>
+        <v>8888.219999999999</v>
       </c>
       <c r="G100">
         <v>258.6</v>
@@ -9493,37 +9493,37 @@
         <v>449.5</v>
       </c>
       <c r="M100">
-        <v>1766.726752</v>
+        <v>1784.754576</v>
       </c>
       <c r="N100">
-        <v>-1317.226752</v>
+        <v>-1335.254576</v>
       </c>
       <c r="O100">
-        <v>-192.315105792</v>
+        <v>-194.947168096</v>
       </c>
       <c r="P100">
-        <v>-1124.911646208</v>
+        <v>-1140.307407904</v>
       </c>
       <c r="Q100">
-        <v>-804.4116462080003</v>
+        <v>-819.8074079039998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.723550872114856</v>
+        <v>3.401301744229711</v>
       </c>
       <c r="T100">
-        <v>38.74713330519297</v>
+        <v>77.49426661038594</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.03714609513084454</v>
+        <v>0.03677088204871481</v>
       </c>
       <c r="W100">
-        <v>0.1933410640977264</v>
+        <v>0.1934164068846181</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2544253091153735</v>
+        <v>0.2518553564980466</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.225495260258069</v>
-      </c>
-      <c r="C101">
-        <v>-6985.028772236948</v>
-      </c>
-      <c r="D101">
-        <v>1644.59122776305</v>
-      </c>
-      <c r="E101">
-        <v>7281.319999999999</v>
-      </c>
-      <c r="F101">
-        <v>8888.219999999999</v>
-      </c>
-      <c r="G101">
-        <v>258.6</v>
-      </c>
-      <c r="H101">
-        <v>7371.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>770</v>
-      </c>
-      <c r="K101">
-        <v>320.5</v>
-      </c>
-      <c r="L101">
-        <v>449.5</v>
-      </c>
-      <c r="M101">
-        <v>1784.754576</v>
-      </c>
-      <c r="N101">
-        <v>-1335.254576</v>
-      </c>
-      <c r="O101">
-        <v>-194.947168096</v>
-      </c>
-      <c r="P101">
-        <v>-1140.307407904</v>
-      </c>
-      <c r="Q101">
-        <v>-819.8074079039998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.401301744229711</v>
-      </c>
-      <c r="T101">
-        <v>77.49426661038594</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.03677088204871481</v>
-      </c>
-      <c r="W101">
-        <v>0.1934164068846181</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2518553564980466</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
